--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="資料" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'資料'!$A$1:$S$501</definedName>
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.25</v>
+        <v>24.7</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>33.45</v>
+        <v>34.8</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -791,7 +791,7 @@
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -860,7 +860,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>51.9</v>
+        <v>52.6</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -911,7 +911,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -980,7 +980,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1029,7 +1029,7 @@
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>29.3</v>
+        <v>29.05</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1098,7 +1098,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>40.8</v>
+        <v>41.9</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1147,7 +1147,7 @@
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3">
@@ -1194,7 +1194,7 @@
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="n">
-        <v>151.5</v>
+        <v>157</v>
       </c>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3">
@@ -1261,7 +1261,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1330,7 +1330,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>207.5</v>
+        <v>180</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1379,7 +1379,7 @@
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>13.2</v>
+        <v>11.85</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1473,7 +1473,7 @@
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.99</v>
+        <v>7.98</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1540,7 +1540,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1609,7 +1609,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>60.5</v>
+        <v>57.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>27.1</v>
+        <v>29.45</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1725,7 +1725,7 @@
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="n">
-        <v>31</v>
+        <v>24.3</v>
       </c>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3">
@@ -1772,7 +1772,7 @@
       <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="n"/>
       <c r="Q21" s="3" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3">
@@ -1819,7 +1819,7 @@
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n">
-        <v>17.4</v>
+        <v>17.75</v>
       </c>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3">
@@ -1886,7 +1886,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -1955,7 +1955,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2024,7 +2024,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2087,7 +2087,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>198.5</v>
+        <v>199.5</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2223,7 +2223,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2292,7 +2292,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2361,7 +2361,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2410,7 +2410,7 @@
       <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.25</v>
+        <v>49.1</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>725</v>
+        <v>680</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2524,7 +2524,7 @@
       <c r="O33" s="3" t="n"/>
       <c r="P33" s="3" t="n"/>
       <c r="Q33" s="3" t="n">
-        <v>63.5</v>
+        <v>63</v>
       </c>
       <c r="R33" s="3" t="n"/>
       <c r="S33" s="3">
@@ -2580,7 +2580,9 @@
       <c r="P34" s="3" t="n">
         <v>31.09</v>
       </c>
-      <c r="Q34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n">
+        <v>1435</v>
+      </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
       </c>
@@ -2648,7 +2650,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>37.3</v>
+        <v>38.1</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2717,7 +2719,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>35.85</v>
+        <v>36.7</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -2786,7 +2788,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.05</v>
+        <v>37.35</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -2835,7 +2837,7 @@
       <c r="O38" s="3" t="n"/>
       <c r="P38" s="3" t="n"/>
       <c r="Q38" s="3" t="n">
-        <v>51.4</v>
+        <v>49.8</v>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3">
@@ -2902,7 +2904,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>40.1</v>
+        <v>41.4</v>
       </c>
       <c r="R39" s="3" t="n"/>
       <c r="S39" s="3">
@@ -2969,7 +2971,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>39.55</v>
+        <v>39.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3038,7 +3040,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>17</v>
+        <v>16.65</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3107,7 +3109,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>70.2</v>
+        <v>71.3</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3156,7 +3158,7 @@
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n"/>
       <c r="Q43" s="3" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3223,7 +3225,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>46.25</v>
+        <v>46.2</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3272,7 +3274,7 @@
       <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="R45" s="3" t="n"/>
       <c r="S45" s="3">
@@ -3319,7 +3321,7 @@
       <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="R46" s="3" t="n"/>
       <c r="S46" s="3">
@@ -3366,7 +3368,7 @@
       <c r="O47" s="3" t="n"/>
       <c r="P47" s="3" t="n"/>
       <c r="Q47" s="3" t="n">
-        <v>159.5</v>
+        <v>160</v>
       </c>
       <c r="R47" s="3" t="n"/>
       <c r="S47" s="3">
@@ -3433,7 +3435,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3482,7 +3484,7 @@
       <c r="O49" s="3" t="n"/>
       <c r="P49" s="3" t="n"/>
       <c r="Q49" s="3" t="n">
-        <v>20.55</v>
+        <v>19.2</v>
       </c>
       <c r="R49" s="3" t="n"/>
       <c r="S49" s="3">
@@ -3547,7 +3549,7 @@
       </c>
       <c r="P50" s="3" t="n"/>
       <c r="Q50" s="3" t="n">
-        <v>180.5</v>
+        <v>196</v>
       </c>
       <c r="R50" s="3" t="n"/>
       <c r="S50" s="3">
@@ -3612,7 +3614,7 @@
       </c>
       <c r="P51" s="3" t="n"/>
       <c r="Q51" s="3" t="n">
-        <v>57.9</v>
+        <v>56.9</v>
       </c>
       <c r="R51" s="3" t="n"/>
       <c r="S51" s="3">
@@ -3679,7 +3681,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -3748,7 +3750,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>107</v>
+        <v>107.5</v>
       </c>
       <c r="R53" s="3" t="n"/>
       <c r="S53" s="3">
@@ -3795,7 +3797,7 @@
       <c r="O54" s="3" t="n"/>
       <c r="P54" s="3" t="n"/>
       <c r="Q54" s="3" t="n">
-        <v>25.7</v>
+        <v>25.75</v>
       </c>
       <c r="R54" s="3" t="n"/>
       <c r="S54" s="3">
@@ -3842,7 +3844,7 @@
       <c r="O55" s="3" t="n"/>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.65</v>
+        <v>13.4</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -3909,7 +3911,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>28.95</v>
+        <v>31</v>
       </c>
       <c r="R56" s="3" t="n"/>
       <c r="S56" s="3">
@@ -3970,7 +3972,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4039,7 +4041,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="R58" s="3" t="n"/>
       <c r="S58" s="3">
@@ -4086,7 +4088,7 @@
       <c r="O59" s="3" t="n"/>
       <c r="P59" s="3" t="n"/>
       <c r="Q59" s="3" t="n">
-        <v>22.95</v>
+        <v>22.8</v>
       </c>
       <c r="R59" s="3" t="n"/>
       <c r="S59" s="3">
@@ -4133,7 +4135,7 @@
       <c r="O60" s="3" t="n"/>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4180,7 +4182,7 @@
       <c r="O61" s="3" t="n"/>
       <c r="P61" s="3" t="n"/>
       <c r="Q61" s="3" t="n">
-        <v>60.6</v>
+        <v>64.7</v>
       </c>
       <c r="R61" s="3" t="n"/>
       <c r="S61" s="3">
@@ -4294,7 +4296,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4363,7 +4365,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>349</v>
+        <v>343.5</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4432,7 +4434,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>12500</v>
+        <v>14410</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -4501,7 +4503,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>155</v>
+        <v>150.5</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -4550,7 +4552,7 @@
       <c r="O67" s="3" t="n"/>
       <c r="P67" s="3" t="n"/>
       <c r="Q67" s="3" t="n">
-        <v>33.25</v>
+        <v>33.5</v>
       </c>
       <c r="R67" s="3" t="n"/>
       <c r="S67" s="3">
@@ -4597,7 +4599,7 @@
       <c r="O68" s="3" t="n"/>
       <c r="P68" s="3" t="n"/>
       <c r="Q68" s="3" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="R68" s="3" t="n"/>
       <c r="S68" s="3">
@@ -4664,7 +4666,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.4</v>
+        <v>31.45</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -4733,7 +4735,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.65</v>
+        <v>17.45</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -4782,7 +4784,7 @@
       <c r="O71" s="3" t="n"/>
       <c r="P71" s="3" t="n"/>
       <c r="Q71" s="3" t="n">
-        <v>28</v>
+        <v>29.1</v>
       </c>
       <c r="R71" s="3" t="n"/>
       <c r="S71" s="3">
@@ -4829,7 +4831,7 @@
       <c r="O72" s="3" t="n"/>
       <c r="P72" s="3" t="n"/>
       <c r="Q72" s="3" t="n">
-        <v>55.1</v>
+        <v>54.3</v>
       </c>
       <c r="R72" s="3" t="n"/>
       <c r="S72" s="3">
@@ -4896,7 +4898,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>60.9</v>
+        <v>64</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -4955,7 +4957,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5004,7 +5006,7 @@
       <c r="O75" s="3" t="n"/>
       <c r="P75" s="3" t="n"/>
       <c r="Q75" s="3" t="n">
-        <v>15.91</v>
+        <v>19.2</v>
       </c>
       <c r="R75" s="3" t="n"/>
       <c r="S75" s="3">
@@ -5071,7 +5073,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5120,7 +5122,7 @@
       <c r="O77" s="3" t="n"/>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>49.05</v>
+        <v>49</v>
       </c>
       <c r="R77" s="3" t="n"/>
       <c r="S77" s="3">
@@ -5167,7 +5169,7 @@
       <c r="O78" s="3" t="n"/>
       <c r="P78" s="3" t="n"/>
       <c r="Q78" s="3" t="n">
-        <v>226.5</v>
+        <v>226</v>
       </c>
       <c r="R78" s="3" t="n"/>
       <c r="S78" s="3">
@@ -5232,7 +5234,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.5</v>
+        <v>31.45</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -5299,7 +5301,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -5368,7 +5370,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>121</v>
+        <v>123.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -5437,7 +5439,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1620</v>
+        <v>1735</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -5486,7 +5488,7 @@
       <c r="O83" s="3" t="n"/>
       <c r="P83" s="3" t="n"/>
       <c r="Q83" s="3" t="n">
-        <v>31.05</v>
+        <v>31.75</v>
       </c>
       <c r="R83" s="3" t="n"/>
       <c r="S83" s="3">
@@ -5553,7 +5555,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>215.5</v>
+        <v>212.5</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -5622,7 +5624,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>158.5</v>
+        <v>155.5</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -5691,7 +5693,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>264.5</v>
+        <v>243.5</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -5760,7 +5762,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>43.2</v>
+        <v>41.6</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -5829,7 +5831,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>622</v>
+        <v>551</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -5925,7 +5927,7 @@
       <c r="O90" s="3" t="n"/>
       <c r="P90" s="3" t="n"/>
       <c r="Q90" s="3" t="n">
-        <v>52.3</v>
+        <v>43.7</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -5994,7 +5996,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2395</v>
+        <v>2375</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6043,7 +6045,7 @@
       <c r="O92" s="3" t="n"/>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>20.2</v>
+        <v>20.35</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6110,7 +6112,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6175,7 +6177,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>38.25</v>
+        <v>38.35</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -6244,7 +6246,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>183.5</v>
+        <v>177</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -6313,7 +6315,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2300</v>
+        <v>2070</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -6382,7 +6384,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -6431,7 +6433,7 @@
       <c r="O98" s="3" t="n"/>
       <c r="P98" s="3" t="n"/>
       <c r="Q98" s="3" t="n">
-        <v>197.5</v>
+        <v>200.5</v>
       </c>
       <c r="R98" s="3" t="n"/>
       <c r="S98" s="3">
@@ -6498,7 +6500,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>29.5</v>
+        <v>28.65</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -6565,7 +6567,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>32.3</v>
+        <v>31.1</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -6634,7 +6636,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>62.5</v>
+        <v>60.5</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -6683,7 +6685,7 @@
       <c r="O102" s="3" t="n"/>
       <c r="P102" s="3" t="n"/>
       <c r="Q102" s="3" t="n">
-        <v>41.7</v>
+        <v>41.65</v>
       </c>
       <c r="R102" s="3" t="n"/>
       <c r="S102" s="3">
@@ -6750,7 +6752,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -6815,7 +6817,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>996</v>
+        <v>923</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -6864,7 +6866,7 @@
       <c r="O105" s="3" t="n"/>
       <c r="P105" s="3" t="n"/>
       <c r="Q105" s="3" t="n">
-        <v>150</v>
+        <v>145.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -6927,7 +6929,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2300</v>
+        <v>2070</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -6976,7 +6978,7 @@
       <c r="O107" s="3" t="n"/>
       <c r="P107" s="3" t="n"/>
       <c r="Q107" s="3" t="n">
-        <v>47.35</v>
+        <v>48.85</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7025,7 +7027,7 @@
       <c r="O108" s="3" t="n"/>
       <c r="P108" s="3" t="n"/>
       <c r="Q108" s="3" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="R108" s="3" t="n"/>
       <c r="S108" s="3">
@@ -7080,7 +7082,7 @@
       <c r="O109" s="3" t="n"/>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>51.5</v>
+        <v>42.5</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -7147,7 +7149,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1015</v>
+        <v>948</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -7214,7 +7216,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>26.35</v>
+        <v>27.45</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -7261,7 +7263,7 @@
       <c r="O112" s="3" t="n"/>
       <c r="P112" s="3" t="n"/>
       <c r="Q112" s="3" t="n">
-        <v>68.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="R112" s="3" t="n"/>
       <c r="S112" s="3">
@@ -7308,7 +7310,7 @@
       <c r="O113" s="3" t="n"/>
       <c r="P113" s="3" t="n"/>
       <c r="Q113" s="3" t="n">
-        <v>122.5</v>
+        <v>120.5</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -7370,7 +7372,9 @@
       <c r="P114" s="3" t="n">
         <v>12.87</v>
       </c>
-      <c r="Q114" s="3" t="n"/>
+      <c r="Q114" s="3" t="n">
+        <v>341</v>
+      </c>
       <c r="R114" s="3" t="n"/>
       <c r="S114" s="3">
         <f>IF(OR(Q114="",R114="",Q114=0),"",R114/Q114*100)</f>
@@ -7436,7 +7440,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -7503,7 +7507,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -7570,7 +7574,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -7639,7 +7643,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>6165</v>
+        <v>5430</v>
       </c>
       <c r="R118" s="3" t="n"/>
       <c r="S118" s="3">
@@ -7700,7 +7704,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>107.5</v>
+        <v>105.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -7749,7 +7753,7 @@
       <c r="O120" s="3" t="n"/>
       <c r="P120" s="3" t="n"/>
       <c r="Q120" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="R120" s="3" t="n"/>
       <c r="S120" s="3">
@@ -7796,7 +7800,7 @@
       <c r="O121" s="3" t="n"/>
       <c r="P121" s="3" t="n"/>
       <c r="Q121" s="3" t="n">
-        <v>41.6</v>
+        <v>44.25</v>
       </c>
       <c r="R121" s="3" t="n"/>
       <c r="S121" s="3">
@@ -7863,7 +7867,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>64.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -7932,7 +7936,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>683</v>
+        <v>658</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -7981,7 +7985,7 @@
       <c r="O124" s="3" t="n"/>
       <c r="P124" s="3" t="n"/>
       <c r="Q124" s="3" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="R124" s="3" t="n"/>
       <c r="S124" s="3">
@@ -8028,7 +8032,7 @@
       <c r="O125" s="3" t="n"/>
       <c r="P125" s="3" t="n"/>
       <c r="Q125" s="3" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
       <c r="R125" s="3" t="n"/>
       <c r="S125" s="3">
@@ -8095,7 +8099,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1125</v>
+        <v>1065</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -8164,7 +8168,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -8233,7 +8237,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>25.6</v>
+        <v>25.25</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -8351,7 +8355,7 @@
       <c r="O130" s="3" t="n"/>
       <c r="P130" s="3" t="n"/>
       <c r="Q130" s="3" t="n">
-        <v>125.5</v>
+        <v>143.5</v>
       </c>
       <c r="R130" s="3" t="n"/>
       <c r="S130" s="3">
@@ -8398,7 +8402,7 @@
       <c r="O131" s="3" t="n"/>
       <c r="P131" s="3" t="n"/>
       <c r="Q131" s="3" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R131" s="3" t="n"/>
       <c r="S131" s="3">
@@ -8445,7 +8449,7 @@
       <c r="O132" s="3" t="n"/>
       <c r="P132" s="3" t="n"/>
       <c r="Q132" s="3" t="n">
-        <v>276.5</v>
+        <v>250.5</v>
       </c>
       <c r="R132" s="3" t="n"/>
       <c r="S132" s="3">
@@ -8492,7 +8496,7 @@
       <c r="O133" s="3" t="n"/>
       <c r="P133" s="3" t="n"/>
       <c r="Q133" s="3" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R133" s="3" t="n"/>
       <c r="S133" s="3">
@@ -8539,7 +8543,7 @@
       <c r="O134" s="3" t="n"/>
       <c r="P134" s="3" t="n"/>
       <c r="Q134" s="3" t="n">
-        <v>112.5</v>
+        <v>113.5</v>
       </c>
       <c r="R134" s="3" t="n"/>
       <c r="S134" s="3">
@@ -8606,7 +8610,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -8675,7 +8679,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>284.5</v>
+        <v>316</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -8744,7 +8748,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4210</v>
+        <v>3765</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -8793,7 +8797,7 @@
       <c r="O138" s="3" t="n"/>
       <c r="P138" s="3" t="n"/>
       <c r="Q138" s="3" t="n">
-        <v>364</v>
+        <v>381.5</v>
       </c>
       <c r="R138" s="3" t="n"/>
       <c r="S138" s="3">
@@ -8840,7 +8844,7 @@
       <c r="O139" s="3" t="n"/>
       <c r="P139" s="3" t="n"/>
       <c r="Q139" s="3" t="n">
-        <v>140.5</v>
+        <v>139</v>
       </c>
       <c r="R139" s="3" t="n"/>
       <c r="S139" s="3">
@@ -8889,7 +8893,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>174.5</v>
+        <v>187.5</v>
       </c>
       <c r="R140" s="3" t="n"/>
       <c r="S140" s="3">
@@ -8936,7 +8940,7 @@
       <c r="O141" s="3" t="n"/>
       <c r="P141" s="3" t="n"/>
       <c r="Q141" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -9003,7 +9007,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -9052,7 +9056,7 @@
       <c r="O143" s="3" t="n"/>
       <c r="P143" s="3" t="n"/>
       <c r="Q143" s="3" t="n">
-        <v>376</v>
+        <v>220</v>
       </c>
       <c r="R143" s="3" t="n"/>
       <c r="S143" s="3">
@@ -9168,7 +9172,7 @@
       <c r="O145" s="3" t="n"/>
       <c r="P145" s="3" t="n"/>
       <c r="Q145" s="3" t="n">
-        <v>121.82</v>
+        <v>115.5</v>
       </c>
       <c r="R145" s="3" t="n"/>
       <c r="S145" s="3">
@@ -9215,7 +9219,7 @@
       <c r="O146" s="3" t="n"/>
       <c r="P146" s="3" t="n"/>
       <c r="Q146" s="3" t="n">
-        <v>225.5</v>
+        <v>120.5</v>
       </c>
       <c r="R146" s="3" t="n"/>
       <c r="S146" s="3">
@@ -9282,7 +9286,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>160</v>
+        <v>160.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -9331,7 +9335,7 @@
       <c r="O148" s="3" t="n"/>
       <c r="P148" s="3" t="n"/>
       <c r="Q148" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R148" s="3" t="n"/>
       <c r="S148" s="3">
@@ -9378,7 +9382,7 @@
       <c r="O149" s="3" t="n"/>
       <c r="P149" s="3" t="n"/>
       <c r="Q149" s="3" t="n">
-        <v>276.5</v>
+        <v>249</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -9447,7 +9451,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>35.65</v>
+        <v>36.9</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -9516,7 +9520,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>302.5</v>
+        <v>265</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -9565,7 +9569,7 @@
       <c r="O152" s="3" t="n"/>
       <c r="P152" s="3" t="n"/>
       <c r="Q152" s="3" t="n">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="R152" s="3" t="n"/>
       <c r="S152" s="3">
@@ -9612,7 +9616,7 @@
       <c r="O153" s="3" t="n"/>
       <c r="P153" s="3" t="n"/>
       <c r="Q153" s="3" t="n">
-        <v>40.95</v>
+        <v>40.5</v>
       </c>
       <c r="R153" s="3" t="n"/>
       <c r="S153" s="3">
@@ -9679,7 +9683,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>23.15</v>
+        <v>23.1</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -9748,7 +9752,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.3</v>
+        <v>31.9</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -9844,7 +9848,7 @@
       <c r="O157" s="3" t="n"/>
       <c r="P157" s="3" t="n"/>
       <c r="Q157" s="3" t="n">
-        <v>36.8</v>
+        <v>36.45</v>
       </c>
       <c r="R157" s="3" t="n"/>
       <c r="S157" s="3">
@@ -9891,7 +9895,7 @@
       <c r="O158" s="3" t="n"/>
       <c r="P158" s="3" t="n"/>
       <c r="Q158" s="3" t="n">
-        <v>19.9</v>
+        <v>19.45</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -9938,7 +9942,7 @@
       <c r="O159" s="3" t="n"/>
       <c r="P159" s="3" t="n"/>
       <c r="Q159" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="R159" s="3" t="n"/>
       <c r="S159" s="3">
@@ -10005,7 +10009,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>41.3</v>
+        <v>35.05</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -10072,7 +10076,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -10141,7 +10145,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>46.2</v>
+        <v>48.3</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -10190,7 +10194,7 @@
       <c r="O163" s="3" t="n"/>
       <c r="P163" s="3" t="n"/>
       <c r="Q163" s="3" t="n">
-        <v>38.95</v>
+        <v>38.65</v>
       </c>
       <c r="R163" s="3" t="n"/>
       <c r="S163" s="3">
@@ -10284,7 +10288,7 @@
       <c r="O165" s="3" t="n"/>
       <c r="P165" s="3" t="n"/>
       <c r="Q165" s="3" t="n">
-        <v>105.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R165" s="3" t="n"/>
       <c r="S165" s="3">
@@ -10331,7 +10335,7 @@
       <c r="O166" s="3" t="n"/>
       <c r="P166" s="3" t="n"/>
       <c r="Q166" s="3" t="n">
-        <v>169.5</v>
+        <v>168.5</v>
       </c>
       <c r="R166" s="3" t="n"/>
       <c r="S166" s="3">
@@ -10398,7 +10402,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>219</v>
+        <v>250.5</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -10447,7 +10451,7 @@
       <c r="O168" s="3" t="n"/>
       <c r="P168" s="3" t="n"/>
       <c r="Q168" s="3" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="R168" s="3" t="n"/>
       <c r="S168" s="3">
@@ -10494,7 +10498,7 @@
       <c r="O169" s="3" t="n"/>
       <c r="P169" s="3" t="n"/>
       <c r="Q169" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="R169" s="3" t="n"/>
       <c r="S169" s="3">
@@ -10541,7 +10545,7 @@
       <c r="O170" s="3" t="n"/>
       <c r="P170" s="3" t="n"/>
       <c r="Q170" s="3" t="n">
-        <v>49.6</v>
+        <v>52.3</v>
       </c>
       <c r="R170" s="3" t="n"/>
       <c r="S170" s="3">
@@ -10608,7 +10612,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>51.6</v>
+        <v>64.5</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -10671,7 +10675,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>19.9</v>
+        <v>20.5</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -10740,7 +10744,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>124.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -10809,7 +10813,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>39.9</v>
+        <v>42.65</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -10878,7 +10882,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -10927,7 +10931,7 @@
       <c r="O176" s="3" t="n"/>
       <c r="P176" s="3" t="n"/>
       <c r="Q176" s="3" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -10994,7 +10998,7 @@
       </c>
       <c r="P177" s="3" t="n"/>
       <c r="Q177" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R177" s="3" t="n"/>
       <c r="S177" s="3">
@@ -11061,7 +11065,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -11128,7 +11132,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -11195,7 +11199,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>46.5</v>
+        <v>45.8</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -11264,7 +11268,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>183</v>
+        <v>180.5</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -11315,7 +11319,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>237.5</v>
+        <v>235.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -11382,7 +11386,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.35</v>
+        <v>22.8</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -11443,7 +11447,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.65</v>
+        <v>17.3</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -11512,7 +11516,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>214.5</v>
+        <v>223.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -11575,7 +11579,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -11642,7 +11646,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>25.25</v>
+        <v>24.55</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -11711,7 +11715,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>116.5</v>
+        <v>116</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -11780,7 +11784,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -11849,7 +11853,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>4610</v>
+        <v>5385</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -11916,7 +11920,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>126</v>
+        <v>126.5</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -11985,7 +11989,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -12054,7 +12058,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>130</v>
+        <v>129.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -12123,7 +12127,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -12192,7 +12196,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3235</v>
+        <v>2855</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -12243,7 +12247,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>135.5</v>
+        <v>133</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -12312,7 +12316,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>90.2</v>
+        <v>93.8</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -12381,7 +12385,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -12450,7 +12454,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -12501,7 +12505,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -12552,7 +12556,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>111</v>
+        <v>113.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -12620,7 +12624,9 @@
       <c r="P202" s="3" t="n">
         <v>22.35</v>
       </c>
-      <c r="Q202" s="3" t="n"/>
+      <c r="Q202" s="3" t="n">
+        <v>281.5</v>
+      </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
       </c>
@@ -12688,7 +12694,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>45.45</v>
+        <v>46.8</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -12757,7 +12763,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="R204" s="3" t="n"/>
       <c r="S204" s="3">
@@ -12824,7 +12830,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R205" s="3" t="n"/>
       <c r="S205" s="3">
@@ -12891,7 +12897,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>206</v>
+        <v>200.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -12960,7 +12966,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>1020</v>
+        <v>1075</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -13009,7 +13015,7 @@
       <c r="O208" s="3" t="n"/>
       <c r="P208" s="3" t="n"/>
       <c r="Q208" s="3" t="n">
-        <v>200.26</v>
+        <v>177.5</v>
       </c>
       <c r="R208" s="3" t="n"/>
       <c r="S208" s="3">
@@ -13076,7 +13082,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -13214,7 +13220,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>2540</v>
+        <v>2765</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -13263,7 +13269,7 @@
       <c r="O212" s="3" t="n"/>
       <c r="P212" s="3" t="n"/>
       <c r="Q212" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R212" s="3" t="n"/>
       <c r="S212" s="3">
@@ -13310,7 +13316,7 @@
       <c r="O213" s="3" t="n"/>
       <c r="P213" s="3" t="n"/>
       <c r="Q213" s="3" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R213" s="3" t="n"/>
       <c r="S213" s="3">
@@ -13377,7 +13383,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -13446,7 +13452,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2535</v>
+        <v>2335</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -13495,7 +13501,7 @@
       <c r="O216" s="3" t="n"/>
       <c r="P216" s="3" t="n"/>
       <c r="Q216" s="3" t="n">
-        <v>170.5</v>
+        <v>177</v>
       </c>
       <c r="R216" s="3" t="n"/>
       <c r="S216" s="3">
@@ -13542,7 +13548,7 @@
       <c r="O217" s="3" t="n"/>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -13609,7 +13615,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -13678,7 +13684,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -13747,7 +13753,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>862</v>
+        <v>794</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -13816,7 +13822,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>391</v>
+        <v>326</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -13885,7 +13891,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>138.5</v>
+        <v>137</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -13934,7 +13940,7 @@
       <c r="O223" s="3" t="n"/>
       <c r="P223" s="3" t="n"/>
       <c r="Q223" s="3" t="n">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="R223" s="3" t="n"/>
       <c r="S223" s="3">
@@ -14001,7 +14007,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>193.5</v>
+        <v>175.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -14068,7 +14074,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>136.5</v>
+        <v>166</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -14137,7 +14143,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>402</v>
+        <v>438.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -14206,7 +14212,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>225.5</v>
+        <v>205.5</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -14275,7 +14281,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -14344,7 +14350,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>137</v>
+        <v>133.5</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -14413,7 +14419,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>750</v>
+        <v>721</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -14462,7 +14468,7 @@
       <c r="O231" s="3" t="n"/>
       <c r="P231" s="3" t="n"/>
       <c r="Q231" s="3" t="n">
-        <v>108</v>
+        <v>107.5</v>
       </c>
       <c r="R231" s="3" t="n"/>
       <c r="S231" s="3">
@@ -14529,7 +14535,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -14598,7 +14604,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>228.5</v>
+        <v>210</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -14665,7 +14671,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>172</v>
+        <v>188.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -14732,7 +14738,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -14801,7 +14807,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>325</v>
+        <v>302.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -14870,7 +14876,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>183</v>
+        <v>186.5</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -14919,7 +14925,7 @@
       <c r="O238" s="3" t="n"/>
       <c r="P238" s="3" t="n"/>
       <c r="Q238" s="3" t="n">
-        <v>27.55</v>
+        <v>27.15</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -14983,7 +14989,9 @@
         <v>6.15</v>
       </c>
       <c r="P239" s="3" t="n"/>
-      <c r="Q239" s="3" t="n"/>
+      <c r="Q239" s="3" t="n">
+        <v>657</v>
+      </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
       </c>
@@ -15100,7 +15108,7 @@
       <c r="O241" s="3" t="n"/>
       <c r="P241" s="3" t="n"/>
       <c r="Q241" s="3" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R241" s="3" t="n"/>
       <c r="S241" s="3">
@@ -15165,7 +15173,7 @@
       </c>
       <c r="P242" s="3" t="n"/>
       <c r="Q242" s="3" t="n">
-        <v>5465</v>
+        <v>5365</v>
       </c>
       <c r="R242" s="3" t="n"/>
       <c r="S242" s="3">
@@ -15232,7 +15240,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>551</v>
+        <v>507</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -15301,7 +15309,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>46</v>
+        <v>45.45</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -15370,7 +15378,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1375</v>
+        <v>1290</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -15419,7 +15427,7 @@
       <c r="O246" s="3" t="n"/>
       <c r="P246" s="3" t="n"/>
       <c r="Q246" s="3" t="n">
-        <v>218.5</v>
+        <v>221</v>
       </c>
       <c r="R246" s="3" t="n"/>
       <c r="S246" s="3">
@@ -15484,7 +15492,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>289.5</v>
+        <v>279</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -15553,7 +15561,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2655</v>
+        <v>2200</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -15620,7 +15628,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>340</v>
+        <v>376.5</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -15687,7 +15695,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1720</v>
+        <v>1610</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -15736,7 +15744,7 @@
       <c r="O251" s="3" t="n"/>
       <c r="P251" s="3" t="n"/>
       <c r="Q251" s="3" t="n">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="R251" s="3" t="n"/>
       <c r="S251" s="3">
@@ -15803,7 +15811,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -15850,7 +15858,7 @@
       <c r="O253" s="3" t="n"/>
       <c r="P253" s="3" t="n"/>
       <c r="Q253" s="3" t="n">
-        <v>845</v>
+        <v>688</v>
       </c>
       <c r="R253" s="3" t="n"/>
       <c r="S253" s="3">
@@ -15915,7 +15923,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -15984,7 +15992,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>223.5</v>
+        <v>224.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -16053,7 +16061,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -16102,7 +16110,7 @@
       <c r="O257" s="3" t="n"/>
       <c r="P257" s="3" t="n"/>
       <c r="Q257" s="3" t="n">
-        <v>259.5</v>
+        <v>257.5</v>
       </c>
       <c r="R257" s="3" t="n"/>
       <c r="S257" s="3">
@@ -16169,7 +16177,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5600</v>
+        <v>5155</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -16228,7 +16236,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4210</v>
+        <v>3735</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -16287,7 +16295,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2200</v>
+        <v>2050</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -16336,7 +16344,7 @@
       <c r="O261" s="3" t="n"/>
       <c r="P261" s="3" t="n"/>
       <c r="Q261" s="3" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="R261" s="3" t="n"/>
       <c r="S261" s="3">
@@ -16403,7 +16411,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="R262" s="3" t="n"/>
       <c r="S262" s="3">
@@ -16470,7 +16478,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>463.5</v>
+        <v>464</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -16539,7 +16547,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -16608,7 +16616,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -16677,7 +16685,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.85</v>
+        <v>19.8</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -16726,7 +16734,7 @@
       <c r="O267" s="3" t="n"/>
       <c r="P267" s="3" t="n"/>
       <c r="Q267" s="3" t="n">
-        <v>45.35</v>
+        <v>41.9</v>
       </c>
       <c r="R267" s="3" t="n"/>
       <c r="S267" s="3">
@@ -16773,7 +16781,7 @@
       <c r="O268" s="3" t="n"/>
       <c r="P268" s="3" t="n"/>
       <c r="Q268" s="3" t="n">
-        <v>54.6</v>
+        <v>55.8</v>
       </c>
       <c r="R268" s="3" t="n"/>
       <c r="S268" s="3">
@@ -16840,7 +16848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>92.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -16905,7 +16913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>62</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -16972,7 +16980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>621</v>
+        <v>592</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -17021,7 +17029,7 @@
       <c r="O272" s="3" t="n"/>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>49.42</v>
+        <v>57.2</v>
       </c>
       <c r="R272" s="3" t="n"/>
       <c r="S272" s="3">
@@ -17068,7 +17076,7 @@
       <c r="O273" s="3" t="n"/>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="R273" s="3" t="n"/>
       <c r="S273" s="3">
@@ -17135,7 +17143,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>79</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -17199,7 +17207,9 @@
       <c r="P275" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q275" s="3" t="n"/>
+      <c r="Q275" s="3" t="n">
+        <v>30.25</v>
+      </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
       </c>
@@ -17264,7 +17274,9 @@
         <v>-13.93</v>
       </c>
       <c r="P276" s="3" t="n"/>
-      <c r="Q276" s="3" t="n"/>
+      <c r="Q276" s="3" t="n">
+        <v>32.35</v>
+      </c>
       <c r="R276" s="3" t="n"/>
       <c r="S276" s="3">
         <f>IF(OR(Q276="",R276="",Q276=0),"",R276/Q276*100)</f>
@@ -17328,7 +17340,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>64.2</v>
+        <v>63.7</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -17395,7 +17407,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -17444,7 +17456,7 @@
       <c r="O279" s="3" t="n"/>
       <c r="P279" s="3" t="n"/>
       <c r="Q279" s="3" t="n">
-        <v>163.5</v>
+        <v>171.5</v>
       </c>
       <c r="R279" s="3" t="n"/>
       <c r="S279" s="3">
@@ -17491,7 +17503,7 @@
       <c r="O280" s="3" t="n"/>
       <c r="P280" s="3" t="n"/>
       <c r="Q280" s="3" t="n">
-        <v>155.5</v>
+        <v>154</v>
       </c>
       <c r="R280" s="3" t="n"/>
       <c r="S280" s="3">
@@ -17538,7 +17550,7 @@
       <c r="O281" s="3" t="n"/>
       <c r="P281" s="3" t="n"/>
       <c r="Q281" s="3" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="R281" s="3" t="n"/>
       <c r="S281" s="3">
@@ -17593,7 +17605,7 @@
       <c r="O282" s="3" t="n"/>
       <c r="P282" s="3" t="n"/>
       <c r="Q282" s="3" t="n">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -17642,7 +17654,7 @@
       <c r="O283" s="3" t="n"/>
       <c r="P283" s="3" t="n"/>
       <c r="Q283" s="3" t="n">
-        <v>301.5</v>
+        <v>292.5</v>
       </c>
       <c r="R283" s="3" t="n"/>
       <c r="S283" s="3">
@@ -17709,7 +17721,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>32.55</v>
+        <v>35.8</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -17758,7 +17770,7 @@
       <c r="O285" s="3" t="n"/>
       <c r="P285" s="3" t="n"/>
       <c r="Q285" s="3" t="n">
-        <v>299.27</v>
+        <v>202.5</v>
       </c>
       <c r="R285" s="3" t="n"/>
       <c r="S285" s="3">
@@ -17825,7 +17837,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>395.5</v>
+        <v>401</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -17894,7 +17906,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -17961,7 +17973,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>787</v>
+        <v>746</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -18020,7 +18032,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>50.2</v>
+        <v>46.8</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -18067,7 +18079,7 @@
       <c r="O290" s="3" t="n"/>
       <c r="P290" s="3" t="n"/>
       <c r="Q290" s="3" t="n">
-        <v>279.31</v>
+        <v>206.5</v>
       </c>
       <c r="R290" s="3" t="n"/>
       <c r="S290" s="3">
@@ -18134,7 +18146,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>352.5</v>
+        <v>353.5</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -18201,7 +18213,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -18270,7 +18282,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -18339,7 +18351,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>254</v>
+        <v>264.5</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -18408,7 +18420,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>99</v>
+        <v>101.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -18457,7 +18469,7 @@
       <c r="O296" s="3" t="n"/>
       <c r="P296" s="3" t="n"/>
       <c r="Q296" s="3" t="n">
-        <v>44.85</v>
+        <v>34</v>
       </c>
       <c r="R296" s="3" t="n"/>
       <c r="S296" s="3">
@@ -18504,7 +18516,7 @@
       <c r="O297" s="3" t="n"/>
       <c r="P297" s="3" t="n"/>
       <c r="Q297" s="3" t="n">
-        <v>74.3</v>
+        <v>60.5</v>
       </c>
       <c r="R297" s="3" t="n"/>
       <c r="S297" s="3">
@@ -18569,7 +18581,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>118.5</v>
+        <v>116</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -18630,7 +18642,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -18699,7 +18711,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>94.8</v>
+        <v>89.3</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -18768,7 +18780,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>463</v>
+        <v>435.5</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -18837,7 +18849,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -18906,7 +18918,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -18955,7 +18967,7 @@
       <c r="O304" s="3" t="n"/>
       <c r="P304" s="3" t="n"/>
       <c r="Q304" s="3" t="n">
-        <v>250.5</v>
+        <v>278</v>
       </c>
       <c r="R304" s="3" t="n"/>
       <c r="S304" s="3">
@@ -19012,7 +19024,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -19081,7 +19093,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -19140,7 +19152,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -19276,7 +19288,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>32.65</v>
+        <v>34.15</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -19345,7 +19357,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>20.95</v>
+        <v>21.65</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -19414,7 +19426,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>302.5</v>
+        <v>300</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -19473,7 +19485,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>97.8</v>
+        <v>89.3</v>
       </c>
       <c r="R312" s="3" t="n"/>
       <c r="S312" s="3">
@@ -19540,7 +19552,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1380</v>
+        <v>1400</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -19609,7 +19621,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>17690</v>
+        <v>15115</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -19658,7 +19670,7 @@
       <c r="O315" s="3" t="n"/>
       <c r="P315" s="3" t="n"/>
       <c r="Q315" s="3" t="n">
-        <v>373.5</v>
+        <v>318.5</v>
       </c>
       <c r="R315" s="3" t="n"/>
       <c r="S315" s="3">
@@ -19725,7 +19737,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1475</v>
+        <v>1570</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -19794,7 +19806,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>16.2</v>
+        <v>28.6</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -19863,7 +19875,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -19932,7 +19944,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>160.5</v>
+        <v>151</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -20001,7 +20013,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -20068,7 +20080,7 @@
         <v>337.2</v>
       </c>
       <c r="Q321" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="R321" s="3" t="n">
         <v>0.3</v>
@@ -20203,7 +20215,9 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="P323" s="3" t="n"/>
-      <c r="Q323" s="3" t="n"/>
+      <c r="Q323" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
       </c>
@@ -20340,7 +20354,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -20409,7 +20423,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>106</v>
+        <v>101.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -20466,7 +20480,7 @@
       <c r="O327" s="3" t="n"/>
       <c r="P327" s="3" t="n"/>
       <c r="Q327" s="3" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R327" s="3" t="n"/>
       <c r="S327" s="3">
@@ -20532,7 +20546,9 @@
       <c r="P328" s="3" t="n">
         <v>132.17</v>
       </c>
-      <c r="Q328" s="3" t="n"/>
+      <c r="Q328" s="3" t="n">
+        <v>159.5</v>
+      </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
         <f>IF(OR(Q328="",R328="",Q328=0),"",R328/Q328*100)</f>
@@ -20578,7 +20594,7 @@
       <c r="O329" s="3" t="n"/>
       <c r="P329" s="3" t="n"/>
       <c r="Q329" s="3" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="R329" s="3" t="n"/>
       <c r="S329" s="3">
@@ -20645,7 +20661,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>188</v>
+        <v>181.5</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -20713,7 +20729,9 @@
       <c r="P331" s="3" t="n">
         <v>6.19</v>
       </c>
-      <c r="Q331" s="3" t="n"/>
+      <c r="Q331" s="3" t="n">
+        <v>63.5</v>
+      </c>
       <c r="R331" s="3" t="n"/>
       <c r="S331" s="3">
         <f>IF(OR(Q331="",R331="",Q331=0),"",R331/Q331*100)</f>
@@ -20779,7 +20797,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -20826,7 +20844,7 @@
       <c r="O333" s="3" t="n"/>
       <c r="P333" s="3" t="n"/>
       <c r="Q333" s="3" t="n">
-        <v>78.8</v>
+        <v>80.2</v>
       </c>
       <c r="R333" s="3" t="n"/>
       <c r="S333" s="3">
@@ -20893,7 +20911,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -20942,7 +20960,7 @@
       <c r="O335" s="3" t="n"/>
       <c r="P335" s="3" t="n"/>
       <c r="Q335" s="3" t="n">
-        <v>50.9</v>
+        <v>55.5</v>
       </c>
       <c r="R335" s="3" t="n"/>
       <c r="S335" s="3">
@@ -20997,7 +21015,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>111.5</v>
+        <v>115.5</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -21066,7 +21084,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>186</v>
+        <v>185.5</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -21135,7 +21153,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>79</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -21184,7 +21202,7 @@
       <c r="O339" s="3" t="n"/>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>15.55</v>
+        <v>14.2</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -21251,7 +21269,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -21320,7 +21338,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51.6</v>
+        <v>52.4</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -21389,7 +21407,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>290</v>
+        <v>275.5</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -21458,7 +21476,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>798</v>
+        <v>758</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -21596,7 +21614,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -21645,7 +21663,7 @@
       <c r="O346" s="3" t="n"/>
       <c r="P346" s="3" t="n"/>
       <c r="Q346" s="3" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="R346" s="3" t="n"/>
       <c r="S346" s="3">
@@ -21692,7 +21710,7 @@
       <c r="O347" s="3" t="n"/>
       <c r="P347" s="3" t="n"/>
       <c r="Q347" s="3" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="R347" s="3" t="n"/>
       <c r="S347" s="3">
@@ -21759,7 +21777,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>81.3</v>
+        <v>101.5</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -21828,7 +21846,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -21893,7 +21911,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>111.5</v>
+        <v>110</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -21962,7 +21980,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1275</v>
+        <v>1205</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -22031,7 +22049,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -22080,7 +22098,7 @@
       <c r="O353" s="3" t="n"/>
       <c r="P353" s="3" t="n"/>
       <c r="Q353" s="3" t="n">
-        <v>84.41</v>
+        <v>65</v>
       </c>
       <c r="R353" s="3" t="n"/>
       <c r="S353" s="3">
@@ -22147,7 +22165,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -22214,7 +22232,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -22263,7 +22281,7 @@
       <c r="O356" s="3" t="n"/>
       <c r="P356" s="3" t="n"/>
       <c r="Q356" s="3" t="n">
-        <v>369</v>
+        <v>290</v>
       </c>
       <c r="R356" s="3" t="n"/>
       <c r="S356" s="3">
@@ -22330,7 +22348,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -22379,7 +22397,7 @@
       <c r="O358" s="3" t="n"/>
       <c r="P358" s="3" t="n"/>
       <c r="Q358" s="3" t="n">
-        <v>138.5</v>
+        <v>139</v>
       </c>
       <c r="R358" s="3" t="n"/>
       <c r="S358" s="3">
@@ -22446,7 +22464,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>510</v>
+        <v>482.5</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -22495,7 +22513,7 @@
       <c r="O360" s="3" t="n"/>
       <c r="P360" s="3" t="n"/>
       <c r="Q360" s="3" t="n">
-        <v>137</v>
+        <v>179.5</v>
       </c>
       <c r="R360" s="3" t="n"/>
       <c r="S360" s="3">
@@ -22559,7 +22577,9 @@
         <v>-0.3</v>
       </c>
       <c r="P361" s="3" t="n"/>
-      <c r="Q361" s="3" t="n"/>
+      <c r="Q361" s="3" t="n">
+        <v>148</v>
+      </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
         <f>IF(OR(Q361="",R361="",Q361=0),"",R361/Q361*100)</f>
@@ -22625,7 +22645,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>6495</v>
+        <v>5565</v>
       </c>
       <c r="R362" s="3" t="n"/>
       <c r="S362" s="3">
@@ -22689,7 +22709,9 @@
         <v>2.99</v>
       </c>
       <c r="P363" s="3" t="n"/>
-      <c r="Q363" s="3" t="n"/>
+      <c r="Q363" s="3" t="n">
+        <v>269.5</v>
+      </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
         <f>IF(OR(Q363="",R363="",Q363=0),"",R363/Q363*100)</f>
@@ -22755,7 +22777,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>199.5</v>
+        <v>197.5</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -22804,7 +22826,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>56.2</v>
+        <v>61.9</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -22851,7 +22873,7 @@
       <c r="O366" s="3" t="n"/>
       <c r="P366" s="3" t="n"/>
       <c r="Q366" s="3" t="n">
-        <v>249.5</v>
+        <v>193</v>
       </c>
       <c r="R366" s="3" t="n"/>
       <c r="S366" s="3">
@@ -22914,7 +22936,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1575</v>
+        <v>1455</v>
       </c>
       <c r="R367" s="3" t="n"/>
       <c r="S367" s="3">
@@ -22961,7 +22983,7 @@
       <c r="O368" s="3" t="n"/>
       <c r="P368" s="3" t="n"/>
       <c r="Q368" s="3" t="n">
-        <v>201.5</v>
+        <v>179</v>
       </c>
       <c r="R368" s="3" t="n"/>
       <c r="S368" s="3">
@@ -23008,7 +23030,7 @@
       <c r="O369" s="3" t="n"/>
       <c r="P369" s="3" t="n"/>
       <c r="Q369" s="3" t="n">
-        <v>58.3</v>
+        <v>44.35</v>
       </c>
       <c r="R369" s="3" t="n"/>
       <c r="S369" s="3">
@@ -23074,7 +23096,9 @@
       <c r="P370" s="3" t="n">
         <v>20.21</v>
       </c>
-      <c r="Q370" s="3" t="n"/>
+      <c r="Q370" s="3" t="n">
+        <v>74.8</v>
+      </c>
       <c r="R370" s="3" t="n"/>
       <c r="S370" s="3">
         <f>IF(OR(Q370="",R370="",Q370=0),"",R370/Q370*100)</f>
@@ -23140,7 +23164,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>245</v>
+        <v>230.5</v>
       </c>
       <c r="R371" s="3" t="n"/>
       <c r="S371" s="3">
@@ -23207,7 +23231,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>214.5</v>
+        <v>229</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -23275,7 +23299,9 @@
       <c r="P373" s="3" t="n">
         <v>33.25</v>
       </c>
-      <c r="Q373" s="3" t="n"/>
+      <c r="Q373" s="3" t="n">
+        <v>366</v>
+      </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
       </c>
@@ -23343,7 +23369,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1040</v>
+        <v>1010</v>
       </c>
       <c r="R374" s="3" t="n"/>
       <c r="S374" s="3">
@@ -23410,7 +23436,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>78</v>
+        <v>77.7</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -23479,7 +23505,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>395</v>
+        <v>395.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -23538,7 +23564,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -23606,7 +23632,9 @@
       <c r="P378" s="3" t="n">
         <v>46.15</v>
       </c>
-      <c r="Q378" s="3" t="n"/>
+      <c r="Q378" s="3" t="n">
+        <v>1460</v>
+      </c>
       <c r="R378" s="3" t="n"/>
       <c r="S378" s="3">
         <f>IF(OR(Q378="",R378="",Q378=0),"",R378/Q378*100)</f>
@@ -23652,7 +23680,7 @@
       <c r="O379" s="3" t="n"/>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>36.4</v>
+        <v>25.85</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -23719,7 +23747,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -23788,7 +23816,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>214</v>
+        <v>210.5</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -23837,7 +23865,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>400.1</v>
+        <v>400</v>
       </c>
       <c r="R382" s="3" t="n"/>
       <c r="S382" s="3">
@@ -23902,7 +23930,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>68</v>
+        <v>65.5</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -23949,7 +23977,7 @@
       <c r="O384" s="3" t="n"/>
       <c r="P384" s="3" t="n"/>
       <c r="Q384" s="3" t="n">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="R384" s="3" t="n"/>
       <c r="S384" s="3">
@@ -24016,7 +24044,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>854</v>
+        <v>1010</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -24065,7 +24093,7 @@
       <c r="O386" s="3" t="n"/>
       <c r="P386" s="3" t="n"/>
       <c r="Q386" s="3" t="n">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -24134,7 +24162,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -24203,7 +24231,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2990</v>
+        <v>2650</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -24272,7 +24300,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6750</v>
+        <v>6145</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -24321,7 +24349,7 @@
       <c r="O390" s="3" t="n"/>
       <c r="P390" s="3" t="n"/>
       <c r="Q390" s="3" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="R390" s="3" t="n"/>
       <c r="S390" s="3">
@@ -24388,7 +24416,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>610</v>
+        <v>578</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -24457,7 +24485,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>932</v>
+        <v>845</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -24524,7 +24552,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -24589,7 +24617,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>51.5</v>
+        <v>55.5</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -24655,7 +24683,9 @@
       <c r="P395" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="Q395" s="3" t="n"/>
+      <c r="Q395" s="3" t="n">
+        <v>70.8</v>
+      </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
       </c>
@@ -24719,7 +24749,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R396" s="3" t="n"/>
       <c r="S396" s="3">
@@ -24766,7 +24796,7 @@
       <c r="O397" s="3" t="n"/>
       <c r="P397" s="3" t="n"/>
       <c r="Q397" s="3" t="n">
-        <v>180.5</v>
+        <v>147</v>
       </c>
       <c r="R397" s="3" t="n"/>
       <c r="S397" s="3">
@@ -24830,7 +24860,9 @@
         <v>3.14</v>
       </c>
       <c r="P398" s="3" t="n"/>
-      <c r="Q398" s="3" t="n"/>
+      <c r="Q398" s="3" t="n">
+        <v>586</v>
+      </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
         <f>IF(OR(Q398="",R398="",Q398=0),"",R398/Q398*100)</f>
@@ -24896,7 +24928,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.3</v>
+        <v>61.2</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -24945,7 +24977,7 @@
       <c r="O400" s="3" t="n"/>
       <c r="P400" s="3" t="n"/>
       <c r="Q400" s="3" t="n">
-        <v>126</v>
+        <v>139.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -25011,7 +25043,9 @@
       <c r="P401" s="3" t="n">
         <v>16.06</v>
       </c>
-      <c r="Q401" s="3" t="n"/>
+      <c r="Q401" s="3" t="n">
+        <v>251</v>
+      </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
       </c>
@@ -25079,7 +25113,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1085</v>
+        <v>968</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -25148,7 +25182,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -25216,7 +25250,9 @@
       <c r="P404" s="3" t="n">
         <v>20.96</v>
       </c>
-      <c r="Q404" s="3" t="n"/>
+      <c r="Q404" s="3" t="n">
+        <v>353</v>
+      </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
       </c>
@@ -25278,7 +25314,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>6325</v>
+        <v>6300</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -25327,7 +25363,7 @@
       <c r="O406" s="3" t="n"/>
       <c r="P406" s="3" t="n"/>
       <c r="Q406" s="3" t="n">
-        <v>263.5</v>
+        <v>265.5</v>
       </c>
       <c r="R406" s="3" t="n"/>
       <c r="S406" s="3">
@@ -25374,7 +25410,7 @@
       <c r="O407" s="3" t="n"/>
       <c r="P407" s="3" t="n"/>
       <c r="Q407" s="3" t="n">
-        <v>260.81</v>
+        <v>259</v>
       </c>
       <c r="R407" s="3" t="n"/>
       <c r="S407" s="3">
@@ -25441,7 +25477,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1370</v>
+        <v>1090</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -25509,7 +25545,9 @@
       <c r="P409" s="3" t="n">
         <v>21.78</v>
       </c>
-      <c r="Q409" s="3" t="n"/>
+      <c r="Q409" s="3" t="n">
+        <v>611</v>
+      </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
       </c>
@@ -25577,7 +25615,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="R410" s="3" t="n"/>
       <c r="S410" s="3">
@@ -25624,7 +25662,7 @@
       <c r="O411" s="3" t="n"/>
       <c r="P411" s="3" t="n"/>
       <c r="Q411" s="3" t="n">
-        <v>386.99</v>
+        <v>403.5</v>
       </c>
       <c r="R411" s="3" t="n"/>
       <c r="S411" s="3">
@@ -25691,7 +25729,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>193.5</v>
+        <v>191.5</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -25760,7 +25798,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -25829,10 +25867,10 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="R414" s="3" t="n">
-        <v>1.24935115</v>
+        <v>1.25</v>
       </c>
       <c r="S414" s="3">
         <f>IF(OR(Q414="",R414="",Q414=0),"",R414/Q414*100)</f>
@@ -25878,7 +25916,7 @@
       <c r="O415" s="3" t="n"/>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -25945,10 +25983,10 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>65.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="R416" s="3" t="n">
-        <v>5.15512584</v>
+        <v>5.16</v>
       </c>
       <c r="S416" s="3">
         <f>IF(OR(Q416="",R416="",Q416=0),"",R416/Q416*100)</f>
@@ -26014,7 +26052,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -26073,7 +26111,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1120</v>
+        <v>1045</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -26142,7 +26180,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>442.5</v>
+        <v>415</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -26211,7 +26249,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>269.5</v>
+        <v>270</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -26280,7 +26318,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>1805</v>
+        <v>1710</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -26329,7 +26367,7 @@
       <c r="O422" s="3" t="n"/>
       <c r="P422" s="3" t="n"/>
       <c r="Q422" s="3" t="n">
-        <v>498.95</v>
+        <v>446.5</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -26378,7 +26416,7 @@
       <c r="O423" s="3" t="n"/>
       <c r="P423" s="3" t="n"/>
       <c r="Q423" s="3" t="n">
-        <v>782</v>
+        <v>549</v>
       </c>
       <c r="R423" s="3" t="n"/>
       <c r="S423" s="3">
@@ -26435,7 +26473,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>168.5</v>
+        <v>163.5</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -26484,7 +26522,7 @@
       <c r="O425" s="3" t="n"/>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>16.95</v>
+        <v>16.6</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -26551,7 +26589,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>313.5</v>
+        <v>304.5</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -26618,7 +26656,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>104</v>
+        <v>110.5</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -26665,7 +26703,7 @@
       <c r="O428" s="3" t="n"/>
       <c r="P428" s="3" t="n"/>
       <c r="Q428" s="3" t="n">
-        <v>273.5</v>
+        <v>260.5</v>
       </c>
       <c r="R428" s="3" t="n"/>
       <c r="S428" s="3">
@@ -26732,7 +26770,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -26781,7 +26819,7 @@
       <c r="O430" s="3" t="n"/>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>46.75</v>
+        <v>1235</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -26828,7 +26866,7 @@
       <c r="O431" s="3" t="n"/>
       <c r="P431" s="3" t="n"/>
       <c r="Q431" s="3" t="n">
-        <v>31.2</v>
+        <v>31.35</v>
       </c>
       <c r="R431" s="3" t="n"/>
       <c r="S431" s="3">
@@ -26895,7 +26933,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1685</v>
+        <v>1710</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -26944,7 +26982,7 @@
       <c r="O433" s="3" t="n"/>
       <c r="P433" s="3" t="n"/>
       <c r="Q433" s="3" t="n">
-        <v>461.5</v>
+        <v>497.5</v>
       </c>
       <c r="R433" s="3" t="n"/>
       <c r="S433" s="3">
@@ -26991,7 +27029,7 @@
       <c r="O434" s="3" t="n"/>
       <c r="P434" s="3" t="n"/>
       <c r="Q434" s="3" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="R434" s="3" t="n"/>
       <c r="S434" s="3">
@@ -27058,7 +27096,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2815</v>
+        <v>2780</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -27127,7 +27165,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -27176,7 +27214,7 @@
       <c r="O437" s="3" t="n"/>
       <c r="P437" s="3" t="n"/>
       <c r="Q437" s="3" t="n">
-        <v>347.49</v>
+        <v>382</v>
       </c>
       <c r="R437" s="3" t="n"/>
       <c r="S437" s="3">
@@ -27242,7 +27280,9 @@
       <c r="P438" s="3" t="n">
         <v>40.48</v>
       </c>
-      <c r="Q438" s="3" t="n"/>
+      <c r="Q438" s="3" t="n">
+        <v>2140</v>
+      </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
       </c>
@@ -27310,7 +27350,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1575</v>
+        <v>1665</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -27379,7 +27419,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -27447,7 +27487,9 @@
       <c r="P441" s="3" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="Q441" s="3" t="n"/>
+      <c r="Q441" s="3" t="n">
+        <v>6255</v>
+      </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
       </c>
@@ -27495,7 +27537,7 @@
       <c r="O442" s="3" t="n"/>
       <c r="P442" s="3" t="n"/>
       <c r="Q442" s="3" t="n">
-        <v>17.9</v>
+        <v>16.9</v>
       </c>
       <c r="R442" s="3" t="n"/>
       <c r="S442" s="3">
@@ -27562,7 +27604,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -27611,7 +27653,7 @@
       <c r="O444" s="3" t="n"/>
       <c r="P444" s="3" t="n"/>
       <c r="Q444" s="3" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R444" s="3" t="n"/>
       <c r="S444" s="3">
@@ -27658,7 +27700,7 @@
       <c r="O445" s="3" t="n"/>
       <c r="P445" s="3" t="n"/>
       <c r="Q445" s="3" t="n">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="R445" s="3" t="n"/>
       <c r="S445" s="3">
@@ -27705,7 +27747,7 @@
       <c r="O446" s="3" t="n"/>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>344.45</v>
+        <v>355</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -27772,7 +27814,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>690</v>
+        <v>514</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -27821,7 +27863,7 @@
       <c r="O448" s="3" t="n"/>
       <c r="P448" s="3" t="n"/>
       <c r="Q448" s="3" t="n">
-        <v>997.98</v>
+        <v>915</v>
       </c>
       <c r="R448" s="3" t="n"/>
       <c r="S448" s="3">
@@ -27868,7 +27910,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>164.07</v>
+        <v>159</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -27935,7 +27977,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1650</v>
+        <v>1550</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -27984,7 +28026,7 @@
       <c r="O451" s="3" t="n"/>
       <c r="P451" s="3" t="n"/>
       <c r="Q451" s="3" t="n">
-        <v>264.5</v>
+        <v>295.5</v>
       </c>
       <c r="R451" s="3" t="n"/>
       <c r="S451" s="3">
@@ -28031,7 +28073,7 @@
       <c r="O452" s="3" t="n"/>
       <c r="P452" s="3" t="n"/>
       <c r="Q452" s="3" t="n">
-        <v>397</v>
+        <v>388.5</v>
       </c>
       <c r="R452" s="3" t="n"/>
       <c r="S452" s="3">
@@ -28095,7 +28137,9 @@
         <v>-0.24</v>
       </c>
       <c r="P453" s="3" t="n"/>
-      <c r="Q453" s="3" t="n"/>
+      <c r="Q453" s="3" t="n">
+        <v>167.5</v>
+      </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
         <f>IF(OR(Q453="",R453="",Q453=0),"",R453/Q453*100)</f>
@@ -28188,7 +28232,7 @@
       <c r="O455" s="3" t="n"/>
       <c r="P455" s="3" t="n"/>
       <c r="Q455" s="3" t="n">
-        <v>183.5</v>
+        <v>185</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -28255,7 +28299,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -28324,7 +28368,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1195</v>
+        <v>1135</v>
       </c>
       <c r="R457" s="3" t="n"/>
       <c r="S457" s="3">
@@ -28391,7 +28435,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>98.7</v>
+        <v>97</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -28459,7 +28503,9 @@
       <c r="P459" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q459" s="3" t="n"/>
+      <c r="Q459" s="3" t="n">
+        <v>158.5</v>
+      </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
       </c>
@@ -28507,7 +28553,7 @@
       <c r="O460" s="3" t="n"/>
       <c r="P460" s="3" t="n"/>
       <c r="Q460" s="3" t="n">
-        <v>52.7</v>
+        <v>49</v>
       </c>
       <c r="R460" s="3" t="n"/>
       <c r="S460" s="3">
@@ -28574,7 +28620,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -28643,7 +28689,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>114.5</v>
+        <v>112</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -28712,7 +28758,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -28781,7 +28827,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>116.5</v>
+        <v>106</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -28848,7 +28894,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>45.2</v>
+        <v>45.55</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -28897,7 +28943,7 @@
       <c r="O466" s="3" t="n"/>
       <c r="P466" s="3" t="n"/>
       <c r="Q466" s="3" t="n">
-        <v>88.14</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="R466" s="3" t="n"/>
       <c r="S466" s="3">
@@ -28944,7 +28990,7 @@
       <c r="O467" s="3" t="n"/>
       <c r="P467" s="3" t="n"/>
       <c r="Q467" s="3" t="n">
-        <v>198.5</v>
+        <v>195.5</v>
       </c>
       <c r="R467" s="3" t="n"/>
       <c r="S467" s="3">
@@ -29080,7 +29126,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>86.7</v>
+        <v>87.7</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -29149,7 +29195,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>320.5</v>
+        <v>318</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -29218,7 +29264,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>1000</v>
+        <v>967</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -29277,7 +29323,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -29326,7 +29372,7 @@
       <c r="O473" s="3" t="n"/>
       <c r="P473" s="3" t="n"/>
       <c r="Q473" s="3" t="n">
-        <v>215</v>
+        <v>177.5</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -29373,7 +29419,7 @@
       <c r="O474" s="3" t="n"/>
       <c r="P474" s="3" t="n"/>
       <c r="Q474" s="3" t="n">
-        <v>171.61</v>
+        <v>235.5</v>
       </c>
       <c r="R474" s="3" t="n"/>
       <c r="S474" s="3">
@@ -29438,7 +29484,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2080</v>
+        <v>2135</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -29507,7 +29553,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>428.5</v>
+        <v>417</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -29576,7 +29622,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.5</v>
+        <v>38.45</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -29643,7 +29689,7 @@
       </c>
       <c r="P478" s="3" t="n"/>
       <c r="Q478" s="3" t="n">
-        <v>28.25</v>
+        <v>27.2</v>
       </c>
       <c r="R478" s="3" t="n"/>
       <c r="S478" s="3">
@@ -29710,7 +29756,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>262.5</v>
+        <v>251</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -29779,7 +29825,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>374.5</v>
+        <v>360.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -29828,7 +29874,7 @@
       <c r="O481" s="3" t="n"/>
       <c r="P481" s="3" t="n"/>
       <c r="Q481" s="3" t="n">
-        <v>154</v>
+        <v>141.5</v>
       </c>
       <c r="R481" s="3" t="n"/>
       <c r="S481" s="3">
@@ -29875,7 +29921,7 @@
       <c r="O482" s="3" t="n"/>
       <c r="P482" s="3" t="n"/>
       <c r="Q482" s="3" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="R482" s="3" t="n"/>
       <c r="S482" s="3">
@@ -29942,7 +29988,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>112</v>
+        <v>105.5</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -30011,7 +30057,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -30060,7 +30106,7 @@
       <c r="O485" s="3" t="n"/>
       <c r="P485" s="3" t="n"/>
       <c r="Q485" s="3" t="n">
-        <v>74.5</v>
+        <v>72.2</v>
       </c>
       <c r="R485" s="3" t="n"/>
       <c r="S485" s="3">
@@ -30176,7 +30222,7 @@
       <c r="O487" s="3" t="n"/>
       <c r="P487" s="3" t="n"/>
       <c r="Q487" s="3" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="R487" s="3" t="n"/>
       <c r="S487" s="3">
@@ -30223,7 +30269,7 @@
       <c r="O488" s="3" t="n"/>
       <c r="P488" s="3" t="n"/>
       <c r="Q488" s="3" t="n">
-        <v>29.1</v>
+        <v>29.15</v>
       </c>
       <c r="R488" s="3" t="n"/>
       <c r="S488" s="3">
@@ -30289,7 +30335,9 @@
       <c r="P489" s="3" t="n">
         <v>14.11</v>
       </c>
-      <c r="Q489" s="3" t="n"/>
+      <c r="Q489" s="3" t="n">
+        <v>71</v>
+      </c>
       <c r="R489" s="3" t="n"/>
       <c r="S489" s="3">
         <f>IF(OR(Q489="",R489="",Q489=0),"",R489/Q489*100)</f>
@@ -30335,7 +30383,7 @@
       <c r="O490" s="3" t="n"/>
       <c r="P490" s="3" t="n"/>
       <c r="Q490" s="3" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R490" s="3" t="n"/>
       <c r="S490" s="3">
@@ -30382,7 +30430,7 @@
       <c r="O491" s="3" t="n"/>
       <c r="P491" s="3" t="n"/>
       <c r="Q491" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="R491" s="3" t="n"/>
       <c r="S491" s="3">
@@ -30517,7 +30565,9 @@
       <c r="P493" s="3" t="n">
         <v>68.39</v>
       </c>
-      <c r="Q493" s="3" t="n"/>
+      <c r="Q493" s="3" t="n">
+        <v>104</v>
+      </c>
       <c r="R493" s="3" t="n"/>
       <c r="S493" s="3">
         <f>IF(OR(Q493="",R493="",Q493=0),"",R493/Q493*100)</f>
@@ -30581,7 +30631,7 @@
       </c>
       <c r="P494" s="3" t="n"/>
       <c r="Q494" s="3" t="n">
-        <v>41.25</v>
+        <v>40.15</v>
       </c>
       <c r="R494" s="3" t="n"/>
       <c r="S494" s="3">
@@ -30648,7 +30698,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -30717,7 +30767,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>42.15</v>
+        <v>41.55</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -30784,7 +30834,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -30833,7 +30883,7 @@
       <c r="O498" s="3" t="n"/>
       <c r="P498" s="3" t="n"/>
       <c r="Q498" s="3" t="n">
-        <v>124</v>
+        <v>134.5</v>
       </c>
       <c r="R498" s="3" t="n"/>
       <c r="S498" s="3">
@@ -30900,7 +30950,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -30968,7 +31018,9 @@
       <c r="P500" s="3" t="n">
         <v>5.21</v>
       </c>
-      <c r="Q500" s="3" t="n"/>
+      <c r="Q500" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="R500" s="3" t="n"/>
       <c r="S500" s="3">
         <f>IF(OR(Q500="",R500="",Q500=0),"",R500/Q500*100)</f>
@@ -31034,7 +31086,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>102</v>
+        <v>97.3</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -791,7 +791,7 @@
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n">
-        <v>26.8</v>
+        <v>26.65</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -980,7 +980,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1029,7 +1029,7 @@
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>29.05</v>
+        <v>28.85</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1098,7 +1098,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1147,7 +1147,7 @@
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3">
@@ -1194,7 +1194,7 @@
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3">
@@ -1261,7 +1261,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1330,7 +1330,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>180</v>
+        <v>188.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1426,7 +1426,7 @@
       <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.6</v>
+        <v>11.65</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1473,7 +1473,7 @@
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1609,7 +1609,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>29.45</v>
+        <v>29</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1725,7 +1725,7 @@
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="n">
-        <v>24.3</v>
+        <v>24.45</v>
       </c>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3">
@@ -1772,7 +1772,7 @@
       <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="n"/>
       <c r="Q21" s="3" t="n">
-        <v>66</v>
+        <v>65.3</v>
       </c>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3">
@@ -1819,7 +1819,7 @@
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n">
-        <v>17.75</v>
+        <v>17.7</v>
       </c>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3">
@@ -1886,7 +1886,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -1955,7 +1955,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>71.5</v>
+        <v>70.8</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2223,7 +2223,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>164</v>
+        <v>165.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2292,7 +2292,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2361,7 +2361,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2410,7 +2410,7 @@
       <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2524,7 +2524,7 @@
       <c r="O33" s="3" t="n"/>
       <c r="P33" s="3" t="n"/>
       <c r="Q33" s="3" t="n">
-        <v>63</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="R33" s="3" t="n"/>
       <c r="S33" s="3">
@@ -2581,7 +2581,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1435</v>
+        <v>1460</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2650,7 +2650,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.1</v>
+        <v>38.45</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2719,7 +2719,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -2837,7 +2837,7 @@
       <c r="O38" s="3" t="n"/>
       <c r="P38" s="3" t="n"/>
       <c r="Q38" s="3" t="n">
-        <v>49.8</v>
+        <v>50.6</v>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3">
@@ -2904,7 +2904,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>41.4</v>
+        <v>41.25</v>
       </c>
       <c r="R39" s="3" t="n"/>
       <c r="S39" s="3">
@@ -2971,7 +2971,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3040,7 +3040,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.65</v>
+        <v>16.5</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3109,7 +3109,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3158,7 +3158,7 @@
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n"/>
       <c r="Q43" s="3" t="n">
-        <v>10.75</v>
+        <v>10.65</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3225,7 +3225,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>46.2</v>
+        <v>44.6</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3274,7 +3274,7 @@
       <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="R45" s="3" t="n"/>
       <c r="S45" s="3">
@@ -3321,7 +3321,7 @@
       <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="n">
-        <v>127</v>
+        <v>126.5</v>
       </c>
       <c r="R46" s="3" t="n"/>
       <c r="S46" s="3">
@@ -3368,7 +3368,7 @@
       <c r="O47" s="3" t="n"/>
       <c r="P47" s="3" t="n"/>
       <c r="Q47" s="3" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R47" s="3" t="n"/>
       <c r="S47" s="3">
@@ -3435,7 +3435,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3484,7 +3484,7 @@
       <c r="O49" s="3" t="n"/>
       <c r="P49" s="3" t="n"/>
       <c r="Q49" s="3" t="n">
-        <v>19.2</v>
+        <v>18.95</v>
       </c>
       <c r="R49" s="3" t="n"/>
       <c r="S49" s="3">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="P50" s="3" t="n"/>
       <c r="Q50" s="3" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R50" s="3" t="n"/>
       <c r="S50" s="3">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="P51" s="3" t="n"/>
       <c r="Q51" s="3" t="n">
-        <v>56.9</v>
+        <v>58</v>
       </c>
       <c r="R51" s="3" t="n"/>
       <c r="S51" s="3">
@@ -3681,7 +3681,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>35.7</v>
+        <v>36.35</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -3750,7 +3750,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>107.5</v>
+        <v>109</v>
       </c>
       <c r="R53" s="3" t="n"/>
       <c r="S53" s="3">
@@ -3797,7 +3797,7 @@
       <c r="O54" s="3" t="n"/>
       <c r="P54" s="3" t="n"/>
       <c r="Q54" s="3" t="n">
-        <v>25.75</v>
+        <v>25.35</v>
       </c>
       <c r="R54" s="3" t="n"/>
       <c r="S54" s="3">
@@ -3844,7 +3844,7 @@
       <c r="O55" s="3" t="n"/>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.4</v>
+        <v>13.55</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -3911,7 +3911,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>31</v>
+        <v>30.45</v>
       </c>
       <c r="R56" s="3" t="n"/>
       <c r="S56" s="3">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.2</v>
+        <v>19.05</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4041,7 +4041,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="R58" s="3" t="n"/>
       <c r="S58" s="3">
@@ -4088,7 +4088,7 @@
       <c r="O59" s="3" t="n"/>
       <c r="P59" s="3" t="n"/>
       <c r="Q59" s="3" t="n">
-        <v>22.8</v>
+        <v>22.65</v>
       </c>
       <c r="R59" s="3" t="n"/>
       <c r="S59" s="3">
@@ -4135,7 +4135,7 @@
       <c r="O60" s="3" t="n"/>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4229,7 +4229,7 @@
       <c r="O62" s="3" t="n"/>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.95</v>
+        <v>13.85</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4296,7 +4296,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4365,7 +4365,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>343.5</v>
+        <v>345.5</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4434,7 +4434,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14410</v>
+        <v>14285</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -4503,7 +4503,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>150.5</v>
+        <v>149</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -4552,7 +4552,7 @@
       <c r="O67" s="3" t="n"/>
       <c r="P67" s="3" t="n"/>
       <c r="Q67" s="3" t="n">
-        <v>33.5</v>
+        <v>33.15</v>
       </c>
       <c r="R67" s="3" t="n"/>
       <c r="S67" s="3">
@@ -4599,7 +4599,7 @@
       <c r="O68" s="3" t="n"/>
       <c r="P68" s="3" t="n"/>
       <c r="Q68" s="3" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="R68" s="3" t="n"/>
       <c r="S68" s="3">
@@ -4666,7 +4666,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>31.45</v>
+        <v>31.35</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -4735,7 +4735,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.45</v>
+        <v>17.25</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -4784,7 +4784,7 @@
       <c r="O71" s="3" t="n"/>
       <c r="P71" s="3" t="n"/>
       <c r="Q71" s="3" t="n">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
       <c r="R71" s="3" t="n"/>
       <c r="S71" s="3">
@@ -4831,7 +4831,7 @@
       <c r="O72" s="3" t="n"/>
       <c r="P72" s="3" t="n"/>
       <c r="Q72" s="3" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="R72" s="3" t="n"/>
       <c r="S72" s="3">
@@ -4898,7 +4898,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -4957,7 +4957,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5006,7 +5006,7 @@
       <c r="O75" s="3" t="n"/>
       <c r="P75" s="3" t="n"/>
       <c r="Q75" s="3" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="R75" s="3" t="n"/>
       <c r="S75" s="3">
@@ -5073,7 +5073,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>84.8</v>
+        <v>83.7</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5122,7 +5122,7 @@
       <c r="O77" s="3" t="n"/>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R77" s="3" t="n"/>
       <c r="S77" s="3">
@@ -5169,7 +5169,7 @@
       <c r="O78" s="3" t="n"/>
       <c r="P78" s="3" t="n"/>
       <c r="Q78" s="3" t="n">
-        <v>226</v>
+        <v>225.5</v>
       </c>
       <c r="R78" s="3" t="n"/>
       <c r="S78" s="3">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.45</v>
+        <v>31</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -5301,7 +5301,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -5370,7 +5370,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>123.5</v>
+        <v>125</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -5439,7 +5439,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1735</v>
+        <v>1710</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -5488,7 +5488,7 @@
       <c r="O83" s="3" t="n"/>
       <c r="P83" s="3" t="n"/>
       <c r="Q83" s="3" t="n">
-        <v>31.75</v>
+        <v>31.4</v>
       </c>
       <c r="R83" s="3" t="n"/>
       <c r="S83" s="3">
@@ -5555,7 +5555,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>212.5</v>
+        <v>217.5</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -5624,7 +5624,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>155.5</v>
+        <v>156</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -5693,7 +5693,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -5762,7 +5762,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -5831,7 +5831,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -5880,7 +5880,7 @@
       <c r="O89" s="3" t="n"/>
       <c r="P89" s="3" t="n"/>
       <c r="Q89" s="3" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="R89" s="3" t="n"/>
       <c r="S89" s="3">
@@ -5927,7 +5927,7 @@
       <c r="O90" s="3" t="n"/>
       <c r="P90" s="3" t="n"/>
       <c r="Q90" s="3" t="n">
-        <v>43.7</v>
+        <v>43.35</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -5996,7 +5996,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6045,7 +6045,7 @@
       <c r="O92" s="3" t="n"/>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>20.35</v>
+        <v>20.1</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6112,7 +6112,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>38.35</v>
+        <v>38.55</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -6246,7 +6246,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -6315,7 +6315,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2070</v>
+        <v>2030</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -6384,7 +6384,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>88.3</v>
+        <v>86.7</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -6433,7 +6433,7 @@
       <c r="O98" s="3" t="n"/>
       <c r="P98" s="3" t="n"/>
       <c r="Q98" s="3" t="n">
-        <v>200.5</v>
+        <v>199.5</v>
       </c>
       <c r="R98" s="3" t="n"/>
       <c r="S98" s="3">
@@ -6500,7 +6500,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.65</v>
+        <v>28.15</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.1</v>
+        <v>31.05</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -6752,7 +6752,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -6817,7 +6817,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -6866,7 +6866,7 @@
       <c r="O105" s="3" t="n"/>
       <c r="P105" s="3" t="n"/>
       <c r="Q105" s="3" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -6929,7 +6929,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2070</v>
+        <v>1965</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -6978,7 +6978,7 @@
       <c r="O107" s="3" t="n"/>
       <c r="P107" s="3" t="n"/>
       <c r="Q107" s="3" t="n">
-        <v>48.85</v>
+        <v>48.55</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7027,7 +7027,7 @@
       <c r="O108" s="3" t="n"/>
       <c r="P108" s="3" t="n"/>
       <c r="Q108" s="3" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="R108" s="3" t="n"/>
       <c r="S108" s="3">
@@ -7082,7 +7082,7 @@
       <c r="O109" s="3" t="n"/>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>42.5</v>
+        <v>43.05</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -7149,7 +7149,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>948</v>
+        <v>971</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>27.45</v>
+        <v>27.7</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -7263,7 +7263,7 @@
       <c r="O112" s="3" t="n"/>
       <c r="P112" s="3" t="n"/>
       <c r="Q112" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="R112" s="3" t="n"/>
       <c r="S112" s="3">
@@ -7310,7 +7310,7 @@
       <c r="O113" s="3" t="n"/>
       <c r="P113" s="3" t="n"/>
       <c r="Q113" s="3" t="n">
-        <v>120.5</v>
+        <v>122.5</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -7373,7 +7373,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>341</v>
+        <v>347.5</v>
       </c>
       <c r="R114" s="3" t="n"/>
       <c r="S114" s="3">
@@ -7507,7 +7507,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -7574,7 +7574,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>325</v>
+        <v>328.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -7643,7 +7643,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5430</v>
+        <v>5595</v>
       </c>
       <c r="R118" s="3" t="n"/>
       <c r="S118" s="3">
@@ -7704,7 +7704,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -7753,7 +7753,7 @@
       <c r="O120" s="3" t="n"/>
       <c r="P120" s="3" t="n"/>
       <c r="Q120" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="R120" s="3" t="n"/>
       <c r="S120" s="3">
@@ -7800,7 +7800,7 @@
       <c r="O121" s="3" t="n"/>
       <c r="P121" s="3" t="n"/>
       <c r="Q121" s="3" t="n">
-        <v>44.25</v>
+        <v>45.1</v>
       </c>
       <c r="R121" s="3" t="n"/>
       <c r="S121" s="3">
@@ -7867,7 +7867,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -7936,7 +7936,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -7985,7 +7985,7 @@
       <c r="O124" s="3" t="n"/>
       <c r="P124" s="3" t="n"/>
       <c r="Q124" s="3" t="n">
-        <v>25.2</v>
+        <v>25.15</v>
       </c>
       <c r="R124" s="3" t="n"/>
       <c r="S124" s="3">
@@ -8032,7 +8032,7 @@
       <c r="O125" s="3" t="n"/>
       <c r="P125" s="3" t="n"/>
       <c r="Q125" s="3" t="n">
-        <v>54.4</v>
+        <v>55.8</v>
       </c>
       <c r="R125" s="3" t="n"/>
       <c r="S125" s="3">
@@ -8099,7 +8099,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -8168,7 +8168,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -8237,7 +8237,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>25.25</v>
+        <v>25.65</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -8355,7 +8355,7 @@
       <c r="O130" s="3" t="n"/>
       <c r="P130" s="3" t="n"/>
       <c r="Q130" s="3" t="n">
-        <v>143.5</v>
+        <v>144</v>
       </c>
       <c r="R130" s="3" t="n"/>
       <c r="S130" s="3">
@@ -8402,7 +8402,7 @@
       <c r="O131" s="3" t="n"/>
       <c r="P131" s="3" t="n"/>
       <c r="Q131" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="R131" s="3" t="n"/>
       <c r="S131" s="3">
@@ -8449,7 +8449,7 @@
       <c r="O132" s="3" t="n"/>
       <c r="P132" s="3" t="n"/>
       <c r="Q132" s="3" t="n">
-        <v>250.5</v>
+        <v>249.5</v>
       </c>
       <c r="R132" s="3" t="n"/>
       <c r="S132" s="3">
@@ -8496,7 +8496,7 @@
       <c r="O133" s="3" t="n"/>
       <c r="P133" s="3" t="n"/>
       <c r="Q133" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="R133" s="3" t="n"/>
       <c r="S133" s="3">
@@ -8543,7 +8543,7 @@
       <c r="O134" s="3" t="n"/>
       <c r="P134" s="3" t="n"/>
       <c r="Q134" s="3" t="n">
-        <v>113.5</v>
+        <v>115</v>
       </c>
       <c r="R134" s="3" t="n"/>
       <c r="S134" s="3">
@@ -8610,7 +8610,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>239</v>
+        <v>239.5</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -8679,7 +8679,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -8748,7 +8748,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>3765</v>
+        <v>3735</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -8797,7 +8797,7 @@
       <c r="O138" s="3" t="n"/>
       <c r="P138" s="3" t="n"/>
       <c r="Q138" s="3" t="n">
-        <v>381.5</v>
+        <v>419.5</v>
       </c>
       <c r="R138" s="3" t="n"/>
       <c r="S138" s="3">
@@ -8844,7 +8844,7 @@
       <c r="O139" s="3" t="n"/>
       <c r="P139" s="3" t="n"/>
       <c r="Q139" s="3" t="n">
-        <v>139</v>
+        <v>137.5</v>
       </c>
       <c r="R139" s="3" t="n"/>
       <c r="S139" s="3">
@@ -8893,7 +8893,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>187.5</v>
+        <v>193</v>
       </c>
       <c r="R140" s="3" t="n"/>
       <c r="S140" s="3">
@@ -8940,7 +8940,7 @@
       <c r="O141" s="3" t="n"/>
       <c r="P141" s="3" t="n"/>
       <c r="Q141" s="3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -9007,7 +9007,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -9056,7 +9056,7 @@
       <c r="O143" s="3" t="n"/>
       <c r="P143" s="3" t="n"/>
       <c r="Q143" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R143" s="3" t="n"/>
       <c r="S143" s="3">
@@ -9172,7 +9172,7 @@
       <c r="O145" s="3" t="n"/>
       <c r="P145" s="3" t="n"/>
       <c r="Q145" s="3" t="n">
-        <v>115.5</v>
+        <v>120.5</v>
       </c>
       <c r="R145" s="3" t="n"/>
       <c r="S145" s="3">
@@ -9286,7 +9286,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>160.5</v>
+        <v>159</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -9335,7 +9335,7 @@
       <c r="O148" s="3" t="n"/>
       <c r="P148" s="3" t="n"/>
       <c r="Q148" s="3" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="R148" s="3" t="n"/>
       <c r="S148" s="3">
@@ -9382,7 +9382,7 @@
       <c r="O149" s="3" t="n"/>
       <c r="P149" s="3" t="n"/>
       <c r="Q149" s="3" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -9451,7 +9451,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>36.9</v>
+        <v>40.55</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -9520,7 +9520,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -9569,7 +9569,7 @@
       <c r="O152" s="3" t="n"/>
       <c r="P152" s="3" t="n"/>
       <c r="Q152" s="3" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="R152" s="3" t="n"/>
       <c r="S152" s="3">
@@ -9683,7 +9683,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -9752,7 +9752,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.9</v>
+        <v>31.85</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -9848,7 +9848,7 @@
       <c r="O157" s="3" t="n"/>
       <c r="P157" s="3" t="n"/>
       <c r="Q157" s="3" t="n">
-        <v>36.45</v>
+        <v>35.4</v>
       </c>
       <c r="R157" s="3" t="n"/>
       <c r="S157" s="3">
@@ -9895,7 +9895,7 @@
       <c r="O158" s="3" t="n"/>
       <c r="P158" s="3" t="n"/>
       <c r="Q158" s="3" t="n">
-        <v>19.45</v>
+        <v>19.35</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -9942,7 +9942,7 @@
       <c r="O159" s="3" t="n"/>
       <c r="P159" s="3" t="n"/>
       <c r="Q159" s="3" t="n">
-        <v>91</v>
+        <v>90.2</v>
       </c>
       <c r="R159" s="3" t="n"/>
       <c r="S159" s="3">
@@ -10009,7 +10009,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.05</v>
+        <v>34.9</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -10145,7 +10145,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -10194,7 +10194,7 @@
       <c r="O163" s="3" t="n"/>
       <c r="P163" s="3" t="n"/>
       <c r="Q163" s="3" t="n">
-        <v>38.65</v>
+        <v>38.5</v>
       </c>
       <c r="R163" s="3" t="n"/>
       <c r="S163" s="3">
@@ -10241,7 +10241,7 @@
       <c r="O164" s="3" t="n"/>
       <c r="P164" s="3" t="n"/>
       <c r="Q164" s="3" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="R164" s="3" t="n"/>
       <c r="S164" s="3">
@@ -10288,7 +10288,7 @@
       <c r="O165" s="3" t="n"/>
       <c r="P165" s="3" t="n"/>
       <c r="Q165" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R165" s="3" t="n"/>
       <c r="S165" s="3">
@@ -10335,7 +10335,7 @@
       <c r="O166" s="3" t="n"/>
       <c r="P166" s="3" t="n"/>
       <c r="Q166" s="3" t="n">
-        <v>168.5</v>
+        <v>168</v>
       </c>
       <c r="R166" s="3" t="n"/>
       <c r="S166" s="3">
@@ -10402,7 +10402,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>250.5</v>
+        <v>246</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -10451,7 +10451,7 @@
       <c r="O168" s="3" t="n"/>
       <c r="P168" s="3" t="n"/>
       <c r="Q168" s="3" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="R168" s="3" t="n"/>
       <c r="S168" s="3">
@@ -10498,7 +10498,7 @@
       <c r="O169" s="3" t="n"/>
       <c r="P169" s="3" t="n"/>
       <c r="Q169" s="3" t="n">
-        <v>72.3</v>
+        <v>78</v>
       </c>
       <c r="R169" s="3" t="n"/>
       <c r="S169" s="3">
@@ -10545,7 +10545,7 @@
       <c r="O170" s="3" t="n"/>
       <c r="P170" s="3" t="n"/>
       <c r="Q170" s="3" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="R170" s="3" t="n"/>
       <c r="S170" s="3">
@@ -10612,7 +10612,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>64.5</v>
+        <v>63.6</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -10675,7 +10675,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -10744,7 +10744,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>124.5</v>
+        <v>126.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -10813,7 +10813,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.65</v>
+        <v>42.2</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -10882,7 +10882,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -10931,7 +10931,7 @@
       <c r="O176" s="3" t="n"/>
       <c r="P176" s="3" t="n"/>
       <c r="Q176" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="P177" s="3" t="n"/>
       <c r="Q177" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="R177" s="3" t="n"/>
       <c r="S177" s="3">
@@ -11065,7 +11065,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>174</v>
+        <v>170.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -11199,7 +11199,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.8</v>
+        <v>45.55</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -11319,7 +11319,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>235.5</v>
+        <v>237</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.8</v>
+        <v>22.65</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -11447,7 +11447,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.3</v>
+        <v>17.45</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>223.5</v>
+        <v>224</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -11579,7 +11579,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>59.7</v>
+        <v>59</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>24.55</v>
+        <v>24.65</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -11715,7 +11715,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -11784,7 +11784,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -11853,7 +11853,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>5385</v>
+        <v>5720</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>126.5</v>
+        <v>130</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -11989,7 +11989,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -12058,7 +12058,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>129.5</v>
+        <v>130.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -12127,7 +12127,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -12196,7 +12196,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>2855</v>
+        <v>2950</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -12316,7 +12316,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>93.8</v>
+        <v>93</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -12385,7 +12385,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>318</v>
+        <v>320.5</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -12454,7 +12454,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -12505,7 +12505,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -12556,7 +12556,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>113.5</v>
+        <v>110.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -12625,7 +12625,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>281.5</v>
+        <v>282.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -12694,7 +12694,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>46.8</v>
+        <v>45.95</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -12763,7 +12763,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="R204" s="3" t="n"/>
       <c r="S204" s="3">
@@ -12830,7 +12830,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R205" s="3" t="n"/>
       <c r="S205" s="3">
@@ -12897,7 +12897,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>200.5</v>
+        <v>198.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -12966,7 +12966,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>1075</v>
+        <v>1095</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -13015,7 +13015,7 @@
       <c r="O208" s="3" t="n"/>
       <c r="P208" s="3" t="n"/>
       <c r="Q208" s="3" t="n">
-        <v>177.5</v>
+        <v>185</v>
       </c>
       <c r="R208" s="3" t="n"/>
       <c r="S208" s="3">
@@ -13082,7 +13082,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -13151,7 +13151,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -13220,7 +13220,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>2765</v>
+        <v>2960</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -13269,7 +13269,7 @@
       <c r="O212" s="3" t="n"/>
       <c r="P212" s="3" t="n"/>
       <c r="Q212" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R212" s="3" t="n"/>
       <c r="S212" s="3">
@@ -13316,7 +13316,7 @@
       <c r="O213" s="3" t="n"/>
       <c r="P213" s="3" t="n"/>
       <c r="Q213" s="3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="R213" s="3" t="n"/>
       <c r="S213" s="3">
@@ -13383,7 +13383,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -13452,7 +13452,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2335</v>
+        <v>2260</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -13501,7 +13501,7 @@
       <c r="O216" s="3" t="n"/>
       <c r="P216" s="3" t="n"/>
       <c r="Q216" s="3" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="R216" s="3" t="n"/>
       <c r="S216" s="3">
@@ -13548,7 +13548,7 @@
       <c r="O217" s="3" t="n"/>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -13615,7 +13615,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>727</v>
+        <v>770</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -13684,7 +13684,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -13753,7 +13753,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -13822,7 +13822,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -13891,7 +13891,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>137</v>
+        <v>135.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -13940,7 +13940,7 @@
       <c r="O223" s="3" t="n"/>
       <c r="P223" s="3" t="n"/>
       <c r="Q223" s="3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R223" s="3" t="n"/>
       <c r="S223" s="3">
@@ -14007,7 +14007,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>175.5</v>
+        <v>178.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>166</v>
+        <v>182.5</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -14143,7 +14143,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>438.5</v>
+        <v>418.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -14212,7 +14212,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>205.5</v>
+        <v>213</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -14281,7 +14281,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -14350,7 +14350,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>133.5</v>
+        <v>135</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -14419,7 +14419,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -14468,7 +14468,7 @@
       <c r="O231" s="3" t="n"/>
       <c r="P231" s="3" t="n"/>
       <c r="Q231" s="3" t="n">
-        <v>107.5</v>
+        <v>107</v>
       </c>
       <c r="R231" s="3" t="n"/>
       <c r="S231" s="3">
@@ -14535,7 +14535,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1015</v>
+        <v>1065</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -14604,7 +14604,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>210</v>
+        <v>209.5</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>188.5</v>
+        <v>195</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -14807,7 +14807,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>302.5</v>
+        <v>311</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -14876,7 +14876,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>186.5</v>
+        <v>189</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -14925,7 +14925,7 @@
       <c r="O238" s="3" t="n"/>
       <c r="P238" s="3" t="n"/>
       <c r="Q238" s="3" t="n">
-        <v>27.15</v>
+        <v>27.25</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>657</v>
+        <v>690</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -15059,7 +15059,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>284.5</v>
+        <v>285.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P242" s="3" t="n"/>
       <c r="Q242" s="3" t="n">
-        <v>5365</v>
+        <v>5570</v>
       </c>
       <c r="R242" s="3" t="n"/>
       <c r="S242" s="3">
@@ -15240,7 +15240,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -15309,7 +15309,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>45.45</v>
+        <v>46.8</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -15378,7 +15378,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1290</v>
+        <v>1270</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -15561,7 +15561,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>376.5</v>
+        <v>378</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -15744,7 +15744,7 @@
       <c r="O251" s="3" t="n"/>
       <c r="P251" s="3" t="n"/>
       <c r="Q251" s="3" t="n">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="R251" s="3" t="n"/>
       <c r="S251" s="3">
@@ -15811,7 +15811,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -15858,7 +15858,7 @@
       <c r="O253" s="3" t="n"/>
       <c r="P253" s="3" t="n"/>
       <c r="Q253" s="3" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="R253" s="3" t="n"/>
       <c r="S253" s="3">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>247</v>
+        <v>251.5</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -15992,7 +15992,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>224.5</v>
+        <v>225.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -16061,7 +16061,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -16110,7 +16110,7 @@
       <c r="O257" s="3" t="n"/>
       <c r="P257" s="3" t="n"/>
       <c r="Q257" s="3" t="n">
-        <v>257.5</v>
+        <v>247.5</v>
       </c>
       <c r="R257" s="3" t="n"/>
       <c r="S257" s="3">
@@ -16177,7 +16177,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5155</v>
+        <v>5205</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -16236,7 +16236,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>3735</v>
+        <v>3865</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -16295,7 +16295,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2050</v>
+        <v>2075</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -16344,7 +16344,7 @@
       <c r="O261" s="3" t="n"/>
       <c r="P261" s="3" t="n"/>
       <c r="Q261" s="3" t="n">
-        <v>63.1</v>
+        <v>66</v>
       </c>
       <c r="R261" s="3" t="n"/>
       <c r="S261" s="3">
@@ -16411,7 +16411,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R262" s="3" t="n"/>
       <c r="S262" s="3">
@@ -16478,7 +16478,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>464</v>
+        <v>461.5</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -16547,7 +16547,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -16616,7 +16616,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -16685,7 +16685,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.8</v>
+        <v>19.65</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -16734,7 +16734,7 @@
       <c r="O267" s="3" t="n"/>
       <c r="P267" s="3" t="n"/>
       <c r="Q267" s="3" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="R267" s="3" t="n"/>
       <c r="S267" s="3">
@@ -16781,7 +16781,7 @@
       <c r="O268" s="3" t="n"/>
       <c r="P268" s="3" t="n"/>
       <c r="Q268" s="3" t="n">
-        <v>55.8</v>
+        <v>55.6</v>
       </c>
       <c r="R268" s="3" t="n"/>
       <c r="S268" s="3">
@@ -16848,7 +16848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -16980,7 +16980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -17029,7 +17029,7 @@
       <c r="O272" s="3" t="n"/>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>57.2</v>
+        <v>59.6</v>
       </c>
       <c r="R272" s="3" t="n"/>
       <c r="S272" s="3">
@@ -17076,7 +17076,7 @@
       <c r="O273" s="3" t="n"/>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="R273" s="3" t="n"/>
       <c r="S273" s="3">
@@ -17143,7 +17143,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -17208,7 +17208,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>30.25</v>
+        <v>29.9</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="P276" s="3" t="n"/>
       <c r="Q276" s="3" t="n">
-        <v>32.35</v>
+        <v>32.45</v>
       </c>
       <c r="R276" s="3" t="n"/>
       <c r="S276" s="3">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>63.7</v>
+        <v>63.8</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -17407,7 +17407,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>122</v>
+        <v>123.5</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -17456,7 +17456,7 @@
       <c r="O279" s="3" t="n"/>
       <c r="P279" s="3" t="n"/>
       <c r="Q279" s="3" t="n">
-        <v>171.5</v>
+        <v>169.5</v>
       </c>
       <c r="R279" s="3" t="n"/>
       <c r="S279" s="3">
@@ -17503,7 +17503,7 @@
       <c r="O280" s="3" t="n"/>
       <c r="P280" s="3" t="n"/>
       <c r="Q280" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R280" s="3" t="n"/>
       <c r="S280" s="3">
@@ -17550,7 +17550,7 @@
       <c r="O281" s="3" t="n"/>
       <c r="P281" s="3" t="n"/>
       <c r="Q281" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R281" s="3" t="n"/>
       <c r="S281" s="3">
@@ -17605,7 +17605,7 @@
       <c r="O282" s="3" t="n"/>
       <c r="P282" s="3" t="n"/>
       <c r="Q282" s="3" t="n">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -17654,7 +17654,7 @@
       <c r="O283" s="3" t="n"/>
       <c r="P283" s="3" t="n"/>
       <c r="Q283" s="3" t="n">
-        <v>292.5</v>
+        <v>300</v>
       </c>
       <c r="R283" s="3" t="n"/>
       <c r="S283" s="3">
@@ -17721,7 +17721,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>35.8</v>
+        <v>35.15</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -17770,7 +17770,7 @@
       <c r="O285" s="3" t="n"/>
       <c r="P285" s="3" t="n"/>
       <c r="Q285" s="3" t="n">
-        <v>202.5</v>
+        <v>205</v>
       </c>
       <c r="R285" s="3" t="n"/>
       <c r="S285" s="3">
@@ -17837,7 +17837,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -17906,7 +17906,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>47.6</v>
+        <v>46.95</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -17973,7 +17973,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -18032,7 +18032,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>46.8</v>
+        <v>44.95</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -18079,7 +18079,7 @@
       <c r="O290" s="3" t="n"/>
       <c r="P290" s="3" t="n"/>
       <c r="Q290" s="3" t="n">
-        <v>206.5</v>
+        <v>212</v>
       </c>
       <c r="R290" s="3" t="n"/>
       <c r="S290" s="3">
@@ -18146,7 +18146,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>353.5</v>
+        <v>343.5</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -18282,7 +18282,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>206</v>
+        <v>206.5</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -18351,7 +18351,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>264.5</v>
+        <v>260.5</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -18420,7 +18420,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -18469,7 +18469,7 @@
       <c r="O296" s="3" t="n"/>
       <c r="P296" s="3" t="n"/>
       <c r="Q296" s="3" t="n">
-        <v>34</v>
+        <v>34.55</v>
       </c>
       <c r="R296" s="3" t="n"/>
       <c r="S296" s="3">
@@ -18516,7 +18516,7 @@
       <c r="O297" s="3" t="n"/>
       <c r="P297" s="3" t="n"/>
       <c r="Q297" s="3" t="n">
-        <v>60.5</v>
+        <v>59.8</v>
       </c>
       <c r="R297" s="3" t="n"/>
       <c r="S297" s="3">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -18711,7 +18711,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>89.3</v>
+        <v>88.8</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -18780,7 +18780,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>435.5</v>
+        <v>444</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -18849,7 +18849,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -18918,7 +18918,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -18967,7 +18967,7 @@
       <c r="O304" s="3" t="n"/>
       <c r="P304" s="3" t="n"/>
       <c r="Q304" s="3" t="n">
-        <v>278</v>
+        <v>272.5</v>
       </c>
       <c r="R304" s="3" t="n"/>
       <c r="S304" s="3">
@@ -19024,7 +19024,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -19093,7 +19093,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>547</v>
+        <v>601</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -19152,7 +19152,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -19219,7 +19219,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -19288,7 +19288,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>34.15</v>
+        <v>33.75</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -19357,7 +19357,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.65</v>
+        <v>21.4</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -19426,7 +19426,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -19485,7 +19485,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>89.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R312" s="3" t="n"/>
       <c r="S312" s="3">
@@ -19552,7 +19552,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1400</v>
+        <v>1415</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -19621,7 +19621,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>15115</v>
+        <v>15400</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -19670,7 +19670,7 @@
       <c r="O315" s="3" t="n"/>
       <c r="P315" s="3" t="n"/>
       <c r="Q315" s="3" t="n">
-        <v>318.5</v>
+        <v>322</v>
       </c>
       <c r="R315" s="3" t="n"/>
       <c r="S315" s="3">
@@ -19737,7 +19737,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1570</v>
+        <v>1510</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -19806,7 +19806,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>28.6</v>
+        <v>31.45</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -19944,7 +19944,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>151</v>
+        <v>150.5</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -20013,7 +20013,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>118</v>
+        <v>115.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -20149,7 +20149,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -20354,7 +20354,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>239.5</v>
+        <v>241.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -20423,7 +20423,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -20480,7 +20480,7 @@
       <c r="O327" s="3" t="n"/>
       <c r="P327" s="3" t="n"/>
       <c r="Q327" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R327" s="3" t="n"/>
       <c r="S327" s="3">
@@ -20547,7 +20547,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>159.5</v>
+        <v>173</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -20594,7 +20594,7 @@
       <c r="O329" s="3" t="n"/>
       <c r="P329" s="3" t="n"/>
       <c r="Q329" s="3" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="R329" s="3" t="n"/>
       <c r="S329" s="3">
@@ -20661,7 +20661,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>181.5</v>
+        <v>183</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -20730,7 +20730,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="R331" s="3" t="n"/>
       <c r="S331" s="3">
@@ -20797,7 +20797,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -20844,7 +20844,7 @@
       <c r="O333" s="3" t="n"/>
       <c r="P333" s="3" t="n"/>
       <c r="Q333" s="3" t="n">
-        <v>80.2</v>
+        <v>75.3</v>
       </c>
       <c r="R333" s="3" t="n"/>
       <c r="S333" s="3">
@@ -20911,7 +20911,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -20960,7 +20960,7 @@
       <c r="O335" s="3" t="n"/>
       <c r="P335" s="3" t="n"/>
       <c r="Q335" s="3" t="n">
-        <v>55.5</v>
+        <v>53.9</v>
       </c>
       <c r="R335" s="3" t="n"/>
       <c r="S335" s="3">
@@ -21015,7 +21015,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>115.5</v>
+        <v>115</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -21153,7 +21153,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -21202,7 +21202,7 @@
       <c r="O339" s="3" t="n"/>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -21269,7 +21269,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -21338,7 +21338,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -21407,7 +21407,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>275.5</v>
+        <v>283</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -21476,7 +21476,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -21545,7 +21545,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -21614,7 +21614,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -21663,7 +21663,7 @@
       <c r="O346" s="3" t="n"/>
       <c r="P346" s="3" t="n"/>
       <c r="Q346" s="3" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R346" s="3" t="n"/>
       <c r="S346" s="3">
@@ -21710,7 +21710,7 @@
       <c r="O347" s="3" t="n"/>
       <c r="P347" s="3" t="n"/>
       <c r="Q347" s="3" t="n">
-        <v>203</v>
+        <v>203.5</v>
       </c>
       <c r="R347" s="3" t="n"/>
       <c r="S347" s="3">
@@ -21777,7 +21777,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>101.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -21846,7 +21846,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.2</v>
+        <v>48.05</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -21911,7 +21911,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -21980,7 +21980,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1205</v>
+        <v>1270</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -22098,7 +22098,7 @@
       <c r="O353" s="3" t="n"/>
       <c r="P353" s="3" t="n"/>
       <c r="Q353" s="3" t="n">
-        <v>65</v>
+        <v>66.8</v>
       </c>
       <c r="R353" s="3" t="n"/>
       <c r="S353" s="3">
@@ -22165,7 +22165,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -22232,7 +22232,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -22281,7 +22281,7 @@
       <c r="O356" s="3" t="n"/>
       <c r="P356" s="3" t="n"/>
       <c r="Q356" s="3" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="R356" s="3" t="n"/>
       <c r="S356" s="3">
@@ -22348,7 +22348,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>56.2</v>
+        <v>56.7</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -22397,7 +22397,7 @@
       <c r="O358" s="3" t="n"/>
       <c r="P358" s="3" t="n"/>
       <c r="Q358" s="3" t="n">
-        <v>139</v>
+        <v>139.5</v>
       </c>
       <c r="R358" s="3" t="n"/>
       <c r="S358" s="3">
@@ -22464,7 +22464,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>482.5</v>
+        <v>530</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -22513,7 +22513,7 @@
       <c r="O360" s="3" t="n"/>
       <c r="P360" s="3" t="n"/>
       <c r="Q360" s="3" t="n">
-        <v>179.5</v>
+        <v>181.5</v>
       </c>
       <c r="R360" s="3" t="n"/>
       <c r="S360" s="3">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -22645,7 +22645,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5565</v>
+        <v>5600</v>
       </c>
       <c r="R362" s="3" t="n"/>
       <c r="S362" s="3">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="P363" s="3" t="n"/>
       <c r="Q363" s="3" t="n">
-        <v>269.5</v>
+        <v>273.5</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -22777,7 +22777,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>197.5</v>
+        <v>198.5</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -22873,7 +22873,7 @@
       <c r="O366" s="3" t="n"/>
       <c r="P366" s="3" t="n"/>
       <c r="Q366" s="3" t="n">
-        <v>193</v>
+        <v>199.5</v>
       </c>
       <c r="R366" s="3" t="n"/>
       <c r="S366" s="3">
@@ -22936,7 +22936,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1455</v>
+        <v>1485</v>
       </c>
       <c r="R367" s="3" t="n"/>
       <c r="S367" s="3">
@@ -22983,7 +22983,7 @@
       <c r="O368" s="3" t="n"/>
       <c r="P368" s="3" t="n"/>
       <c r="Q368" s="3" t="n">
-        <v>179</v>
+        <v>181.5</v>
       </c>
       <c r="R368" s="3" t="n"/>
       <c r="S368" s="3">
@@ -23030,7 +23030,7 @@
       <c r="O369" s="3" t="n"/>
       <c r="P369" s="3" t="n"/>
       <c r="Q369" s="3" t="n">
-        <v>44.35</v>
+        <v>44</v>
       </c>
       <c r="R369" s="3" t="n"/>
       <c r="S369" s="3">
@@ -23097,7 +23097,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>74.8</v>
+        <v>77</v>
       </c>
       <c r="R370" s="3" t="n"/>
       <c r="S370" s="3">
@@ -23164,7 +23164,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>230.5</v>
+        <v>233.5</v>
       </c>
       <c r="R371" s="3" t="n"/>
       <c r="S371" s="3">
@@ -23231,7 +23231,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -23300,7 +23300,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>366</v>
+        <v>383.5</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -23369,7 +23369,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="R374" s="3" t="n"/>
       <c r="S374" s="3">
@@ -23436,7 +23436,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -23505,7 +23505,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>395.5</v>
+        <v>394</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -23564,7 +23564,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>450</v>
+        <v>451.5</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -23633,7 +23633,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1460</v>
+        <v>1605</v>
       </c>
       <c r="R378" s="3" t="n"/>
       <c r="S378" s="3">
@@ -23680,7 +23680,7 @@
       <c r="O379" s="3" t="n"/>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>25.85</v>
+        <v>26.45</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -23747,7 +23747,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1475</v>
+        <v>1490</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -23816,7 +23816,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>210.5</v>
+        <v>224</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -23865,7 +23865,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="R382" s="3" t="n"/>
       <c r="S382" s="3">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>65.5</v>
+        <v>67.7</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -23977,7 +23977,7 @@
       <c r="O384" s="3" t="n"/>
       <c r="P384" s="3" t="n"/>
       <c r="Q384" s="3" t="n">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="R384" s="3" t="n"/>
       <c r="S384" s="3">
@@ -24044,7 +24044,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -24093,7 +24093,7 @@
       <c r="O386" s="3" t="n"/>
       <c r="P386" s="3" t="n"/>
       <c r="Q386" s="3" t="n">
-        <v>366</v>
+        <v>372.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -24162,7 +24162,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -24231,7 +24231,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2650</v>
+        <v>2680</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -24300,7 +24300,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6145</v>
+        <v>6255</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -24349,7 +24349,7 @@
       <c r="O390" s="3" t="n"/>
       <c r="P390" s="3" t="n"/>
       <c r="Q390" s="3" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R390" s="3" t="n"/>
       <c r="S390" s="3">
@@ -24485,7 +24485,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -24552,7 +24552,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>55.5</v>
+        <v>56.3</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -24684,7 +24684,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -24749,7 +24749,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R396" s="3" t="n"/>
       <c r="S396" s="3">
@@ -24796,7 +24796,7 @@
       <c r="O397" s="3" t="n"/>
       <c r="P397" s="3" t="n"/>
       <c r="Q397" s="3" t="n">
-        <v>147</v>
+        <v>145.5</v>
       </c>
       <c r="R397" s="3" t="n"/>
       <c r="S397" s="3">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="P398" s="3" t="n"/>
       <c r="Q398" s="3" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -24928,7 +24928,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>61.2</v>
+        <v>61.6</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -24977,7 +24977,7 @@
       <c r="O400" s="3" t="n"/>
       <c r="P400" s="3" t="n"/>
       <c r="Q400" s="3" t="n">
-        <v>139.5</v>
+        <v>138.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -25044,7 +25044,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -25113,7 +25113,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -25182,7 +25182,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>406</v>
+        <v>414.5</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -25251,7 +25251,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -25314,7 +25314,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>6300</v>
+        <v>6440</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -25363,7 +25363,7 @@
       <c r="O406" s="3" t="n"/>
       <c r="P406" s="3" t="n"/>
       <c r="Q406" s="3" t="n">
-        <v>265.5</v>
+        <v>264</v>
       </c>
       <c r="R406" s="3" t="n"/>
       <c r="S406" s="3">
@@ -25410,7 +25410,7 @@
       <c r="O407" s="3" t="n"/>
       <c r="P407" s="3" t="n"/>
       <c r="Q407" s="3" t="n">
-        <v>259</v>
+        <v>270.5</v>
       </c>
       <c r="R407" s="3" t="n"/>
       <c r="S407" s="3">
@@ -25477,7 +25477,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1090</v>
+        <v>1130</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -25546,7 +25546,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -25615,7 +25615,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="R410" s="3" t="n"/>
       <c r="S410" s="3">
@@ -25662,7 +25662,7 @@
       <c r="O411" s="3" t="n"/>
       <c r="P411" s="3" t="n"/>
       <c r="Q411" s="3" t="n">
-        <v>403.5</v>
+        <v>363.5</v>
       </c>
       <c r="R411" s="3" t="n"/>
       <c r="S411" s="3">
@@ -25729,7 +25729,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>191.5</v>
+        <v>192</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -25798,7 +25798,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -25867,7 +25867,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>141</v>
+        <v>139.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -25916,7 +25916,7 @@
       <c r="O415" s="3" t="n"/>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>56</v>
+        <v>55.8</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -25983,7 +25983,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -26052,7 +26052,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>70.8</v>
+        <v>69</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -26111,7 +26111,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1045</v>
+        <v>1065</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -26180,7 +26180,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>415</v>
+        <v>420.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -26249,7 +26249,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -26318,7 +26318,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>1710</v>
+        <v>1845</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -26367,7 +26367,7 @@
       <c r="O422" s="3" t="n"/>
       <c r="P422" s="3" t="n"/>
       <c r="Q422" s="3" t="n">
-        <v>446.5</v>
+        <v>491</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -26416,7 +26416,7 @@
       <c r="O423" s="3" t="n"/>
       <c r="P423" s="3" t="n"/>
       <c r="Q423" s="3" t="n">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="R423" s="3" t="n"/>
       <c r="S423" s="3">
@@ -26473,7 +26473,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>163.5</v>
+        <v>159.5</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -26522,7 +26522,7 @@
       <c r="O425" s="3" t="n"/>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>16.6</v>
+        <v>16.35</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -26589,7 +26589,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>304.5</v>
+        <v>306</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>110.5</v>
+        <v>105.5</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -26703,7 +26703,7 @@
       <c r="O428" s="3" t="n"/>
       <c r="P428" s="3" t="n"/>
       <c r="Q428" s="3" t="n">
-        <v>260.5</v>
+        <v>262</v>
       </c>
       <c r="R428" s="3" t="n"/>
       <c r="S428" s="3">
@@ -26770,7 +26770,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -26819,7 +26819,7 @@
       <c r="O430" s="3" t="n"/>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>1235</v>
+        <v>1355</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -26866,7 +26866,7 @@
       <c r="O431" s="3" t="n"/>
       <c r="P431" s="3" t="n"/>
       <c r="Q431" s="3" t="n">
-        <v>31.35</v>
+        <v>31.25</v>
       </c>
       <c r="R431" s="3" t="n"/>
       <c r="S431" s="3">
@@ -26933,7 +26933,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1710</v>
+        <v>1635</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -26982,7 +26982,7 @@
       <c r="O433" s="3" t="n"/>
       <c r="P433" s="3" t="n"/>
       <c r="Q433" s="3" t="n">
-        <v>497.5</v>
+        <v>515</v>
       </c>
       <c r="R433" s="3" t="n"/>
       <c r="S433" s="3">
@@ -27029,7 +27029,7 @@
       <c r="O434" s="3" t="n"/>
       <c r="P434" s="3" t="n"/>
       <c r="Q434" s="3" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="R434" s="3" t="n"/>
       <c r="S434" s="3">
@@ -27096,7 +27096,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2780</v>
+        <v>2890</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -27165,7 +27165,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -27281,7 +27281,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2140</v>
+        <v>2350</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -27350,7 +27350,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1665</v>
+        <v>1810</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -27419,7 +27419,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -27488,7 +27488,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6255</v>
+        <v>6210</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -27537,7 +27537,7 @@
       <c r="O442" s="3" t="n"/>
       <c r="P442" s="3" t="n"/>
       <c r="Q442" s="3" t="n">
-        <v>16.9</v>
+        <v>16.85</v>
       </c>
       <c r="R442" s="3" t="n"/>
       <c r="S442" s="3">
@@ -27604,7 +27604,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>121.5</v>
+        <v>121</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -27653,7 +27653,7 @@
       <c r="O444" s="3" t="n"/>
       <c r="P444" s="3" t="n"/>
       <c r="Q444" s="3" t="n">
-        <v>253</v>
+        <v>258.5</v>
       </c>
       <c r="R444" s="3" t="n"/>
       <c r="S444" s="3">
@@ -27700,7 +27700,7 @@
       <c r="O445" s="3" t="n"/>
       <c r="P445" s="3" t="n"/>
       <c r="Q445" s="3" t="n">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="R445" s="3" t="n"/>
       <c r="S445" s="3">
@@ -27747,7 +27747,7 @@
       <c r="O446" s="3" t="n"/>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>355</v>
+        <v>356.5</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -27814,7 +27814,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -27863,7 +27863,7 @@
       <c r="O448" s="3" t="n"/>
       <c r="P448" s="3" t="n"/>
       <c r="Q448" s="3" t="n">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="R448" s="3" t="n"/>
       <c r="S448" s="3">
@@ -27977,7 +27977,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1550</v>
+        <v>1520</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -28026,7 +28026,7 @@
       <c r="O451" s="3" t="n"/>
       <c r="P451" s="3" t="n"/>
       <c r="Q451" s="3" t="n">
-        <v>295.5</v>
+        <v>292.5</v>
       </c>
       <c r="R451" s="3" t="n"/>
       <c r="S451" s="3">
@@ -28073,7 +28073,7 @@
       <c r="O452" s="3" t="n"/>
       <c r="P452" s="3" t="n"/>
       <c r="Q452" s="3" t="n">
-        <v>388.5</v>
+        <v>404</v>
       </c>
       <c r="R452" s="3" t="n"/>
       <c r="S452" s="3">
@@ -28138,7 +28138,7 @@
       </c>
       <c r="P453" s="3" t="n"/>
       <c r="Q453" s="3" t="n">
-        <v>167.5</v>
+        <v>169.5</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -28185,7 +28185,7 @@
       <c r="O454" s="3" t="n"/>
       <c r="P454" s="3" t="n"/>
       <c r="Q454" s="3" t="n">
-        <v>242.5</v>
+        <v>242</v>
       </c>
       <c r="R454" s="3" t="n"/>
       <c r="S454" s="3">
@@ -28232,7 +28232,7 @@
       <c r="O455" s="3" t="n"/>
       <c r="P455" s="3" t="n"/>
       <c r="Q455" s="3" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -28299,7 +28299,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>265</v>
+        <v>291.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -28368,7 +28368,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1135</v>
+        <v>1160</v>
       </c>
       <c r="R457" s="3" t="n"/>
       <c r="S457" s="3">
@@ -28435,7 +28435,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -28553,7 +28553,7 @@
       <c r="O460" s="3" t="n"/>
       <c r="P460" s="3" t="n"/>
       <c r="Q460" s="3" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="R460" s="3" t="n"/>
       <c r="S460" s="3">
@@ -28689,7 +28689,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>112</v>
+        <v>115.5</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -28758,7 +28758,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -28827,7 +28827,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>106</v>
+        <v>107.5</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -28894,7 +28894,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>45.55</v>
+        <v>45.65</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -28943,7 +28943,7 @@
       <c r="O466" s="3" t="n"/>
       <c r="P466" s="3" t="n"/>
       <c r="Q466" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="R466" s="3" t="n"/>
       <c r="S466" s="3">
@@ -28990,7 +28990,7 @@
       <c r="O467" s="3" t="n"/>
       <c r="P467" s="3" t="n"/>
       <c r="Q467" s="3" t="n">
-        <v>195.5</v>
+        <v>195</v>
       </c>
       <c r="R467" s="3" t="n"/>
       <c r="S467" s="3">
@@ -29057,7 +29057,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>62.4</v>
+        <v>61.5</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -29126,7 +29126,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -29264,7 +29264,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -29323,7 +29323,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -29419,7 +29419,7 @@
       <c r="O474" s="3" t="n"/>
       <c r="P474" s="3" t="n"/>
       <c r="Q474" s="3" t="n">
-        <v>235.5</v>
+        <v>230</v>
       </c>
       <c r="R474" s="3" t="n"/>
       <c r="S474" s="3">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2135</v>
+        <v>2085</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -29553,7 +29553,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -29622,7 +29622,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>38.45</v>
+        <v>38.15</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -29756,7 +29756,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>251</v>
+        <v>251.5</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -29825,7 +29825,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>360.5</v>
+        <v>367.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -29874,7 +29874,7 @@
       <c r="O481" s="3" t="n"/>
       <c r="P481" s="3" t="n"/>
       <c r="Q481" s="3" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="R481" s="3" t="n"/>
       <c r="S481" s="3">
@@ -29921,7 +29921,7 @@
       <c r="O482" s="3" t="n"/>
       <c r="P482" s="3" t="n"/>
       <c r="Q482" s="3" t="n">
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="R482" s="3" t="n"/>
       <c r="S482" s="3">
@@ -29988,7 +29988,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>105.5</v>
+        <v>112</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -30057,7 +30057,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1145</v>
+        <v>1215</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -30106,7 +30106,7 @@
       <c r="O485" s="3" t="n"/>
       <c r="P485" s="3" t="n"/>
       <c r="Q485" s="3" t="n">
-        <v>72.2</v>
+        <v>73</v>
       </c>
       <c r="R485" s="3" t="n"/>
       <c r="S485" s="3">
@@ -30173,7 +30173,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>25.05</v>
+        <v>25.1</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -30222,7 +30222,7 @@
       <c r="O487" s="3" t="n"/>
       <c r="P487" s="3" t="n"/>
       <c r="Q487" s="3" t="n">
-        <v>15.3</v>
+        <v>15.35</v>
       </c>
       <c r="R487" s="3" t="n"/>
       <c r="S487" s="3">
@@ -30269,7 +30269,7 @@
       <c r="O488" s="3" t="n"/>
       <c r="P488" s="3" t="n"/>
       <c r="Q488" s="3" t="n">
-        <v>29.15</v>
+        <v>29</v>
       </c>
       <c r="R488" s="3" t="n"/>
       <c r="S488" s="3">
@@ -30336,7 +30336,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R489" s="3" t="n"/>
       <c r="S489" s="3">
@@ -30383,7 +30383,7 @@
       <c r="O490" s="3" t="n"/>
       <c r="P490" s="3" t="n"/>
       <c r="Q490" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="R490" s="3" t="n"/>
       <c r="S490" s="3">
@@ -30430,7 +30430,7 @@
       <c r="O491" s="3" t="n"/>
       <c r="P491" s="3" t="n"/>
       <c r="Q491" s="3" t="n">
-        <v>84.5</v>
+        <v>86.2</v>
       </c>
       <c r="R491" s="3" t="n"/>
       <c r="S491" s="3">
@@ -30497,7 +30497,7 @@
         <v>15.67</v>
       </c>
       <c r="Q492" s="3" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="R492" s="3" t="n">
         <v>5.7</v>
@@ -30566,7 +30566,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="R493" s="3" t="n"/>
       <c r="S493" s="3">
@@ -30631,7 +30631,7 @@
       </c>
       <c r="P494" s="3" t="n"/>
       <c r="Q494" s="3" t="n">
-        <v>40.15</v>
+        <v>39.9</v>
       </c>
       <c r="R494" s="3" t="n"/>
       <c r="S494" s="3">
@@ -30698,7 +30698,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -30767,7 +30767,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>41.55</v>
+        <v>42.2</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -30883,7 +30883,7 @@
       <c r="O498" s="3" t="n"/>
       <c r="P498" s="3" t="n"/>
       <c r="Q498" s="3" t="n">
-        <v>134.5</v>
+        <v>132.5</v>
       </c>
       <c r="R498" s="3" t="n"/>
       <c r="S498" s="3">
@@ -30950,7 +30950,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -31019,7 +31019,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>29</v>
+        <v>28.75</v>
       </c>
       <c r="R500" s="3" t="n"/>
       <c r="S500" s="3">
@@ -31086,7 +31086,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>97.3</v>
+        <v>94.8</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -768,12 +768,24 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>27.46</v>
+      </c>
       <c r="J4" s="4">
         <f>IF(OR(D4="",G4=""),"",G4-D4)</f>
         <v/>
@@ -786,10 +798,18 @@
         <f>IF(OR(F4="",I4=""),"",I4-F4)</f>
         <v/>
       </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
+      <c r="M4" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>9.94</v>
+      </c>
       <c r="Q4" s="3" t="n">
         <v>26.65</v>
       </c>
@@ -886,12 +906,24 @@
           <t>食品工業</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8.19</v>
+      </c>
       <c r="J6" s="4">
         <f>IF(OR(D6="",G6=""),"",G6-D6)</f>
         <v/>
@@ -904,9 +936,15 @@
         <f>IF(OR(F6="",I6=""),"",I6-F6)</f>
         <v/>
       </c>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="M6" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>1.97</v>
+      </c>
       <c r="P6" s="3" t="n">
         <v>12.9</v>
       </c>
@@ -1006,12 +1044,24 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>4.18</v>
+      </c>
       <c r="J8" s="4">
         <f>IF(OR(D8="",G8=""),"",G8-D8)</f>
         <v/>
@@ -1024,10 +1074,18 @@
         <f>IF(OR(F8="",I8=""),"",I8-F8)</f>
         <v/>
       </c>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
+      <c r="M8" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>18.26</v>
+      </c>
       <c r="Q8" s="3" t="n">
         <v>28.85</v>
       </c>
@@ -1124,12 +1182,24 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>13.12</v>
+      </c>
       <c r="J10" s="4">
         <f>IF(OR(D10="",G10=""),"",G10-D10)</f>
         <v/>
@@ -1142,14 +1212,24 @@
         <f>IF(OR(F10="",I10=""),"",I10-F10)</f>
         <v/>
       </c>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+      <c r="M10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>18.27</v>
+      </c>
       <c r="Q10" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="R10" s="3" t="n"/>
+      <c r="R10" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="S10" s="3">
         <f>IF(OR(Q10="",R10="",Q10=0),"",R10/Q10*100)</f>
         <v/>
@@ -1171,12 +1251,24 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>7.17</v>
+      </c>
       <c r="J11" s="4">
         <f>IF(OR(D11="",G11=""),"",G11-D11)</f>
         <v/>
@@ -1189,14 +1281,24 @@
         <f>IF(OR(F11="",I11=""),"",I11-F11)</f>
         <v/>
       </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
+      <c r="M11" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Q11" s="3" t="n">
         <v>156.5</v>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="S11" s="3">
         <f>IF(OR(Q11="",R11="",Q11=0),"",R11/Q11*100)</f>
         <v/>
@@ -1356,12 +1458,24 @@
           <t>塑膠</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>-5.08</v>
+      </c>
       <c r="J14" s="4">
         <f>IF(OR(D14="",G14=""),"",G14-D14)</f>
         <v/>
@@ -1374,9 +1488,15 @@
         <f>IF(OR(F14="",I14=""),"",I14-F14)</f>
         <v/>
       </c>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
+      <c r="M14" s="3" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>-0.17</v>
+      </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
         <v>11.85</v>
@@ -1403,12 +1523,24 @@
           <t>塑膠</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.88</v>
+      </c>
       <c r="J15" s="4">
         <f>IF(OR(D15="",G15=""),"",G15-D15)</f>
         <v/>
@@ -1421,9 +1553,15 @@
         <f>IF(OR(F15="",I15=""),"",I15-F15)</f>
         <v/>
       </c>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
+      <c r="M15" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0.23</v>
+      </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
         <v>11.65</v>
@@ -1450,12 +1588,24 @@
           <t>塑膠工業</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-8.42</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-4.79</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>-44.42</v>
+      </c>
       <c r="J16" s="4">
         <f>IF(OR(D16="",G16=""),"",G16-D16)</f>
         <v/>
@@ -1468,9 +1618,15 @@
         <f>IF(OR(F16="",I16=""),"",I16-F16)</f>
         <v/>
       </c>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
+      <c r="M16" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
         <v>7.9</v>
@@ -1702,12 +1858,24 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>13.37</v>
+      </c>
       <c r="J20" s="4">
         <f>IF(OR(D20="",G20=""),"",G20-D20)</f>
         <v/>
@@ -1720,14 +1888,24 @@
         <f>IF(OR(F20="",I20=""),"",I20-F20)</f>
         <v/>
       </c>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
+      <c r="M20" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>11.48</v>
+      </c>
       <c r="Q20" s="3" t="n">
         <v>24.45</v>
       </c>
-      <c r="R20" s="3" t="n"/>
+      <c r="R20" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="S20" s="3">
         <f>IF(OR(Q20="",R20="",Q20=0),"",R20/Q20*100)</f>
         <v/>
@@ -1749,12 +1927,24 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>192.99</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>49.29</v>
+      </c>
       <c r="J21" s="4">
         <f>IF(OR(D21="",G21=""),"",G21-D21)</f>
         <v/>
@@ -1767,14 +1957,24 @@
         <f>IF(OR(F21="",I21=""),"",I21-F21)</f>
         <v/>
       </c>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
+      <c r="M21" s="3" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>4.81</v>
+      </c>
       <c r="Q21" s="3" t="n">
         <v>65.3</v>
       </c>
-      <c r="R21" s="3" t="n"/>
+      <c r="R21" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="S21" s="3">
         <f>IF(OR(Q21="",R21="",Q21=0),"",R21/Q21*100)</f>
         <v/>
@@ -1796,12 +1996,24 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>6.97</v>
+      </c>
       <c r="J22" s="4">
         <f>IF(OR(D22="",G22=""),"",G22-D22)</f>
         <v/>
@@ -1814,14 +2026,24 @@
         <f>IF(OR(F22="",I22=""),"",I22-F22)</f>
         <v/>
       </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
-      <c r="P22" s="3" t="n"/>
+      <c r="M22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>19.02</v>
+      </c>
       <c r="Q22" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="R22" s="3" t="n"/>
+      <c r="R22" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S22" s="3">
         <f>IF(OR(Q22="",R22="",Q22=0),"",R22/Q22*100)</f>
         <v/>
@@ -2080,9 +2302,15 @@
         <f>IF(OR(F26="",I26=""),"",I26-F26)</f>
         <v/>
       </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
+      <c r="M26" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>2.25</v>
+      </c>
       <c r="P26" s="3" t="n">
         <v>27.34</v>
       </c>
@@ -2387,12 +2615,24 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-13.52</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-12.43</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>-14.19</v>
+      </c>
       <c r="J31" s="4">
         <f>IF(OR(D31="",G31=""),"",G31-D31)</f>
         <v/>
@@ -2405,9 +2645,15 @@
         <f>IF(OR(F31="",I31=""),"",I31-F31)</f>
         <v/>
       </c>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
+      <c r="M31" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-0.59</v>
+      </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
         <v>49.6</v>
@@ -2501,12 +2747,24 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="J33" s="4">
         <f>IF(OR(D33="",G33=""),"",G33-D33)</f>
         <v/>
@@ -2519,14 +2777,24 @@
         <f>IF(OR(F33="",I33=""),"",I33-F33)</f>
         <v/>
       </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+      <c r="M33" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>59.91</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R33" s="3" t="n"/>
+      <c r="R33" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S33" s="3">
         <f>IF(OR(Q33="",R33="",Q33=0),"",R33/Q33*100)</f>
         <v/>
@@ -2557,9 +2825,15 @@
       <c r="F34" s="3" t="n">
         <v>26.67</v>
       </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>27.22</v>
+      </c>
       <c r="J34" s="4">
         <f>IF(OR(D34="",G34=""),"",G34-D34)</f>
         <v/>
@@ -2575,8 +2849,12 @@
       <c r="M34" s="3" t="n">
         <v>13.35</v>
       </c>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
+      <c r="N34" s="3" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>16.55</v>
+      </c>
       <c r="P34" s="3" t="n">
         <v>31.09</v>
       </c>
@@ -2814,12 +3092,24 @@
           <t>化學工業</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>12.27</v>
+      </c>
       <c r="J38" s="4">
         <f>IF(OR(D38="",G38=""),"",G38-D38)</f>
         <v/>
@@ -2832,14 +3122,24 @@
         <f>IF(OR(F38="",I38=""),"",I38-F38)</f>
         <v/>
       </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
-      <c r="P38" s="3" t="n"/>
+      <c r="M38" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>12.45</v>
+      </c>
       <c r="Q38" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="R38" s="3" t="n"/>
+      <c r="R38" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="S38" s="3">
         <f>IF(OR(Q38="",R38="",Q38=0),"",R38/Q38*100)</f>
         <v/>
@@ -2906,7 +3206,9 @@
       <c r="Q39" s="3" t="n">
         <v>41.25</v>
       </c>
-      <c r="R39" s="3" t="n"/>
+      <c r="R39" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S39" s="3">
         <f>IF(OR(Q39="",R39="",Q39=0),"",R39/Q39*100)</f>
         <v/>
@@ -3135,12 +3437,24 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>22.88</v>
+      </c>
       <c r="J43" s="4">
         <f>IF(OR(D43="",G43=""),"",G43-D43)</f>
         <v/>
@@ -3153,10 +3467,18 @@
         <f>IF(OR(F43="",I43=""),"",I43-F43)</f>
         <v/>
       </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
+      <c r="M43" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>18.14</v>
+      </c>
       <c r="Q43" s="3" t="n">
         <v>10.65</v>
       </c>
@@ -3251,12 +3573,24 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
+      <c r="D45" s="3" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>14.77</v>
+      </c>
       <c r="J45" s="4">
         <f>IF(OR(D45="",G45=""),"",G45-D45)</f>
         <v/>
@@ -3269,14 +3603,24 @@
         <f>IF(OR(F45="",I45=""),"",I45-F45)</f>
         <v/>
       </c>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
-      <c r="P45" s="3" t="n"/>
+      <c r="M45" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>28.39</v>
+      </c>
       <c r="Q45" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
-      <c r="R45" s="3" t="n"/>
+      <c r="R45" s="3" t="n">
+        <v>1.85</v>
+      </c>
       <c r="S45" s="3">
         <f>IF(OR(Q45="",R45="",Q45=0),"",R45/Q45*100)</f>
         <v/>
@@ -3298,12 +3642,24 @@
           <t>化學生技醫療</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>7.31</v>
+      </c>
       <c r="J46" s="4">
         <f>IF(OR(D46="",G46=""),"",G46-D46)</f>
         <v/>
@@ -3316,14 +3672,24 @@
         <f>IF(OR(F46="",I46=""),"",I46-F46)</f>
         <v/>
       </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n"/>
+      <c r="M46" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>11.48</v>
+      </c>
       <c r="Q46" s="3" t="n">
         <v>126.5</v>
       </c>
-      <c r="R46" s="3" t="n"/>
+      <c r="R46" s="3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="S46" s="3">
         <f>IF(OR(Q46="",R46="",Q46=0),"",R46/Q46*100)</f>
         <v/>
@@ -3345,12 +3711,24 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>19.65</v>
+      </c>
       <c r="J47" s="4">
         <f>IF(OR(D47="",G47=""),"",G47-D47)</f>
         <v/>
@@ -3363,14 +3741,24 @@
         <f>IF(OR(F47="",I47=""),"",I47-F47)</f>
         <v/>
       </c>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="3" t="n"/>
-      <c r="O47" s="3" t="n"/>
-      <c r="P47" s="3" t="n"/>
+      <c r="M47" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>19.89</v>
+      </c>
       <c r="Q47" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="R47" s="3" t="n"/>
+      <c r="R47" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="S47" s="3">
         <f>IF(OR(Q47="",R47="",Q47=0),"",R47/Q47*100)</f>
         <v/>
@@ -3461,12 +3849,24 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>-5.24</v>
+      </c>
       <c r="J49" s="4">
         <f>IF(OR(D49="",G49=""),"",G49-D49)</f>
         <v/>
@@ -3479,14 +3879,24 @@
         <f>IF(OR(F49="",I49=""),"",I49-F49)</f>
         <v/>
       </c>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
-      <c r="P49" s="3" t="n"/>
+      <c r="M49" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>389</v>
+      </c>
       <c r="Q49" s="3" t="n">
         <v>18.95</v>
       </c>
-      <c r="R49" s="3" t="n"/>
+      <c r="R49" s="3" t="n">
+        <v>0.29</v>
+      </c>
       <c r="S49" s="3">
         <f>IF(OR(Q49="",R49="",Q49=0),"",R49/Q49*100)</f>
         <v/>
@@ -3547,11 +3957,15 @@
       <c r="O50" s="3" t="n">
         <v>2.47</v>
       </c>
-      <c r="P50" s="3" t="n"/>
+      <c r="P50" s="3" t="n">
+        <v>13.89</v>
+      </c>
       <c r="Q50" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="R50" s="3" t="n"/>
+      <c r="R50" s="3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="S50" s="3">
         <f>IF(OR(Q50="",R50="",Q50=0),"",R50/Q50*100)</f>
         <v/>
@@ -3612,11 +4026,15 @@
       <c r="O51" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="P51" s="3" t="n"/>
+      <c r="P51" s="3" t="n">
+        <v>66.98</v>
+      </c>
       <c r="Q51" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="R51" s="3" t="n"/>
+      <c r="R51" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S51" s="3">
         <f>IF(OR(Q51="",R51="",Q51=0),"",R51/Q51*100)</f>
         <v/>
@@ -3752,7 +4170,9 @@
       <c r="Q53" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="R53" s="3" t="n"/>
+      <c r="R53" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S53" s="3">
         <f>IF(OR(Q53="",R53="",Q53=0),"",R53/Q53*100)</f>
         <v/>
@@ -3774,12 +4194,24 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>9.27</v>
+      </c>
       <c r="J54" s="4">
         <f>IF(OR(D54="",G54=""),"",G54-D54)</f>
         <v/>
@@ -3792,14 +4224,24 @@
         <f>IF(OR(F54="",I54=""),"",I54-F54)</f>
         <v/>
       </c>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="3" t="n"/>
-      <c r="O54" s="3" t="n"/>
-      <c r="P54" s="3" t="n"/>
+      <c r="M54" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>11.84</v>
+      </c>
       <c r="Q54" s="3" t="n">
         <v>25.35</v>
       </c>
-      <c r="R54" s="3" t="n"/>
+      <c r="R54" s="3" t="n">
+        <v>0.45</v>
+      </c>
       <c r="S54" s="3">
         <f>IF(OR(Q54="",R54="",Q54=0),"",R54/Q54*100)</f>
         <v/>
@@ -3821,12 +4263,24 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-4.89</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>-9.19</v>
+      </c>
       <c r="J55" s="4">
         <f>IF(OR(D55="",G55=""),"",G55-D55)</f>
         <v/>
@@ -3839,9 +4293,15 @@
         <f>IF(OR(F55="",I55=""),"",I55-F55)</f>
         <v/>
       </c>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="3" t="n"/>
-      <c r="O55" s="3" t="n"/>
+      <c r="M55" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>-0.36</v>
+      </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
         <v>13.55</v>
@@ -3913,7 +4373,9 @@
       <c r="Q56" s="3" t="n">
         <v>30.45</v>
       </c>
-      <c r="R56" s="3" t="n"/>
+      <c r="R56" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S56" s="3">
         <f>IF(OR(Q56="",R56="",Q56=0),"",R56/Q56*100)</f>
         <v/>
@@ -4043,7 +4505,9 @@
       <c r="Q58" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="R58" s="3" t="n"/>
+      <c r="R58" s="3" t="n">
+        <v>4.3</v>
+      </c>
       <c r="S58" s="3">
         <f>IF(OR(Q58="",R58="",Q58=0),"",R58/Q58*100)</f>
         <v/>
@@ -4065,12 +4529,24 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>7.95</v>
+      </c>
       <c r="J59" s="4">
         <f>IF(OR(D59="",G59=""),"",G59-D59)</f>
         <v/>
@@ -4083,14 +4559,24 @@
         <f>IF(OR(F59="",I59=""),"",I59-F59)</f>
         <v/>
       </c>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="3" t="n"/>
-      <c r="O59" s="3" t="n"/>
-      <c r="P59" s="3" t="n"/>
+      <c r="M59" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>9.08</v>
+      </c>
       <c r="Q59" s="3" t="n">
         <v>22.65</v>
       </c>
-      <c r="R59" s="3" t="n"/>
+      <c r="R59" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S59" s="3">
         <f>IF(OR(Q59="",R59="",Q59=0),"",R59/Q59*100)</f>
         <v/>
@@ -4112,12 +4598,24 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>4.28</v>
+      </c>
       <c r="J60" s="4">
         <f>IF(OR(D60="",G60=""),"",G60-D60)</f>
         <v/>
@@ -4130,9 +4628,15 @@
         <f>IF(OR(F60="",I60=""),"",I60-F60)</f>
         <v/>
       </c>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
-      <c r="O60" s="3" t="n"/>
+      <c r="M60" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>0.17</v>
+      </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
         <v>17.2</v>
@@ -4159,12 +4663,24 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>11.16</v>
+      </c>
       <c r="J61" s="4">
         <f>IF(OR(D61="",G61=""),"",G61-D61)</f>
         <v/>
@@ -4177,14 +4693,24 @@
         <f>IF(OR(F61="",I61=""),"",I61-F61)</f>
         <v/>
       </c>
-      <c r="M61" s="3" t="n"/>
-      <c r="N61" s="3" t="n"/>
-      <c r="O61" s="3" t="n"/>
-      <c r="P61" s="3" t="n"/>
+      <c r="M61" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>14.86</v>
+      </c>
       <c r="Q61" s="3" t="n">
         <v>64.7</v>
       </c>
-      <c r="R61" s="3" t="n"/>
+      <c r="R61" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="S61" s="3">
         <f>IF(OR(Q61="",R61="",Q61=0),"",R61/Q61*100)</f>
         <v/>
@@ -4206,12 +4732,24 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>-1.55</v>
+      </c>
       <c r="J62" s="4">
         <f>IF(OR(D62="",G62=""),"",G62-D62)</f>
         <v/>
@@ -4224,9 +4762,15 @@
         <f>IF(OR(F62="",I62=""),"",I62-F62)</f>
         <v/>
       </c>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
+      <c r="M62" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>-0.11</v>
+      </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
         <v>13.85</v>
@@ -4529,12 +5073,24 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>20.95</v>
+      </c>
       <c r="J67" s="4">
         <f>IF(OR(D67="",G67=""),"",G67-D67)</f>
         <v/>
@@ -4547,14 +5103,24 @@
         <f>IF(OR(F67="",I67=""),"",I67-F67)</f>
         <v/>
       </c>
-      <c r="M67" s="3" t="n"/>
-      <c r="N67" s="3" t="n"/>
-      <c r="O67" s="3" t="n"/>
-      <c r="P67" s="3" t="n"/>
+      <c r="M67" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>5.72</v>
+      </c>
       <c r="Q67" s="3" t="n">
         <v>33.15</v>
       </c>
-      <c r="R67" s="3" t="n"/>
+      <c r="R67" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="S67" s="3">
         <f>IF(OR(Q67="",R67="",Q67=0),"",R67/Q67*100)</f>
         <v/>
@@ -4576,11 +5142,21 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>15.25</v>
+      </c>
       <c r="I68" s="3" t="n"/>
       <c r="J68" s="4">
         <f>IF(OR(D68="",G68=""),"",G68-D68)</f>
@@ -4594,14 +5170,24 @@
         <f>IF(OR(F68="",I68=""),"",I68-F68)</f>
         <v/>
       </c>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
-      <c r="P68" s="3" t="n"/>
+      <c r="M68" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>10.78</v>
+      </c>
       <c r="Q68" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="R68" s="3" t="n"/>
+      <c r="R68" s="3" t="n">
+        <v>0.27</v>
+      </c>
       <c r="S68" s="3">
         <f>IF(OR(Q68="",R68="",Q68=0),"",R68/Q68*100)</f>
         <v/>
@@ -4761,12 +5347,24 @@
           <t>汽車工業</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>5.5</v>
+      </c>
       <c r="J71" s="4">
         <f>IF(OR(D71="",G71=""),"",G71-D71)</f>
         <v/>
@@ -4779,14 +5377,24 @@
         <f>IF(OR(F71="",I71=""),"",I71-F71)</f>
         <v/>
       </c>
-      <c r="M71" s="3" t="n"/>
-      <c r="N71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
-      <c r="P71" s="3" t="n"/>
+      <c r="M71" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>32.92</v>
+      </c>
       <c r="Q71" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="R71" s="3" t="n"/>
+      <c r="R71" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="S71" s="3">
         <f>IF(OR(Q71="",R71="",Q71=0),"",R71/Q71*100)</f>
         <v/>
@@ -4808,12 +5416,24 @@
           <t>汽車工業</t>
         </is>
       </c>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>13.16</v>
+      </c>
       <c r="J72" s="4">
         <f>IF(OR(D72="",G72=""),"",G72-D72)</f>
         <v/>
@@ -4826,14 +5446,24 @@
         <f>IF(OR(F72="",I72=""),"",I72-F72)</f>
         <v/>
       </c>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
-      <c r="P72" s="3" t="n"/>
+      <c r="M72" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>8.550000000000001</v>
+      </c>
       <c r="Q72" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="R72" s="3" t="n"/>
+      <c r="R72" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="S72" s="3">
         <f>IF(OR(Q72="",R72="",Q72=0),"",R72/Q72*100)</f>
         <v/>
@@ -4924,14 +5554,24 @@
           <t>汽車工業</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>9.16</v>
+      </c>
       <c r="F74" s="3" t="n">
         <v>7.37</v>
       </c>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>9.49</v>
+      </c>
       <c r="J74" s="4">
         <f>IF(OR(D74="",G74=""),"",G74-D74)</f>
         <v/>
@@ -4983,12 +5623,24 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>-15.12</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>5.4</v>
+      </c>
       <c r="J75" s="4">
         <f>IF(OR(D75="",G75=""),"",G75-D75)</f>
         <v/>
@@ -5001,14 +5653,24 @@
         <f>IF(OR(F75="",I75=""),"",I75-F75)</f>
         <v/>
       </c>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
-      <c r="P75" s="3" t="n"/>
+      <c r="M75" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>39.9</v>
+      </c>
       <c r="Q75" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="R75" s="3" t="n"/>
+      <c r="R75" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S75" s="3">
         <f>IF(OR(Q75="",R75="",Q75=0),"",R75/Q75*100)</f>
         <v/>
@@ -5099,12 +5761,24 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>-8.42</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>-14.46</v>
+      </c>
       <c r="J77" s="4">
         <f>IF(OR(D77="",G77=""),"",G77-D77)</f>
         <v/>
@@ -5117,14 +5791,22 @@
         <f>IF(OR(F77="",I77=""),"",I77-F77)</f>
         <v/>
       </c>
-      <c r="M77" s="3" t="n"/>
-      <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
+      <c r="M77" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>-1.71</v>
+      </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="R77" s="3" t="n"/>
+      <c r="R77" s="3" t="n">
+        <v>0.84</v>
+      </c>
       <c r="S77" s="3">
         <f>IF(OR(Q77="",R77="",Q77=0),"",R77/Q77*100)</f>
         <v/>
@@ -5146,12 +5828,24 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="J78" s="4">
         <f>IF(OR(D78="",G78=""),"",G78-D78)</f>
         <v/>
@@ -5164,14 +5858,24 @@
         <f>IF(OR(F78="",I78=""),"",I78-F78)</f>
         <v/>
       </c>
-      <c r="M78" s="3" t="n"/>
-      <c r="N78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
-      <c r="P78" s="3" t="n"/>
+      <c r="M78" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="Q78" s="3" t="n">
         <v>225.5</v>
       </c>
-      <c r="R78" s="3" t="n"/>
+      <c r="R78" s="3" t="n">
+        <v>14.5</v>
+      </c>
       <c r="S78" s="3">
         <f>IF(OR(Q78="",R78="",Q78=0),"",R78/Q78*100)</f>
         <v/>
@@ -5465,12 +6169,24 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
+      <c r="D83" s="3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>1.98</v>
+      </c>
       <c r="J83" s="4">
         <f>IF(OR(D83="",G83=""),"",G83-D83)</f>
         <v/>
@@ -5483,14 +6199,24 @@
         <f>IF(OR(F83="",I83=""),"",I83-F83)</f>
         <v/>
       </c>
-      <c r="M83" s="3" t="n"/>
-      <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
-      <c r="P83" s="3" t="n"/>
+      <c r="M83" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>28.36</v>
+      </c>
       <c r="Q83" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="R83" s="3" t="n"/>
+      <c r="R83" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S83" s="3">
         <f>IF(OR(Q83="",R83="",Q83=0),"",R83/Q83*100)</f>
         <v/>
@@ -5857,12 +6583,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
+      <c r="D89" s="3" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>-0.96</v>
+      </c>
       <c r="J89" s="4">
         <f>IF(OR(D89="",G89=""),"",G89-D89)</f>
         <v/>
@@ -5875,14 +6613,24 @@
         <f>IF(OR(F89="",I89=""),"",I89-F89)</f>
         <v/>
       </c>
-      <c r="M89" s="3" t="n"/>
-      <c r="N89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
-      <c r="P89" s="3" t="n"/>
+      <c r="M89" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>104.42</v>
+      </c>
       <c r="Q89" s="3" t="n">
         <v>44.7</v>
       </c>
-      <c r="R89" s="3" t="n"/>
+      <c r="R89" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="S89" s="3">
         <f>IF(OR(Q89="",R89="",Q89=0),"",R89/Q89*100)</f>
         <v/>
@@ -5901,15 +6649,27 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>半導體</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>7.45</v>
+      </c>
       <c r="J90" s="4">
         <f>IF(OR(D90="",G90=""),"",G90-D90)</f>
         <v/>
@@ -5922,10 +6682,18 @@
         <f>IF(OR(F90="",I90=""),"",I90-F90)</f>
         <v/>
       </c>
-      <c r="M90" s="3" t="n"/>
-      <c r="N90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
-      <c r="P90" s="3" t="n"/>
+      <c r="M90" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>19.26</v>
+      </c>
       <c r="Q90" s="3" t="n">
         <v>43.35</v>
       </c>
@@ -6022,12 +6790,24 @@
           <t>通訊網路</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
+      <c r="D92" s="3" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.36</v>
+      </c>
       <c r="J92" s="4">
         <f>IF(OR(D92="",G92=""),"",G92-D92)</f>
         <v/>
@@ -6040,9 +6820,15 @@
         <f>IF(OR(F92="",I92=""),"",I92-F92)</f>
         <v/>
       </c>
-      <c r="M92" s="3" t="n"/>
-      <c r="N92" s="3" t="n"/>
-      <c r="O92" s="3" t="n"/>
+      <c r="M92" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
         <v>20.1</v>
@@ -6410,12 +7196,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n"/>
-      <c r="G98" s="3" t="n"/>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
+      <c r="D98" s="3" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>9.050000000000001</v>
+      </c>
       <c r="J98" s="4">
         <f>IF(OR(D98="",G98=""),"",G98-D98)</f>
         <v/>
@@ -6428,14 +7226,24 @@
         <f>IF(OR(F98="",I98=""),"",I98-F98)</f>
         <v/>
       </c>
-      <c r="M98" s="3" t="n"/>
-      <c r="N98" s="3" t="n"/>
-      <c r="O98" s="3" t="n"/>
-      <c r="P98" s="3" t="n"/>
+      <c r="M98" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>46.8</v>
+      </c>
       <c r="Q98" s="3" t="n">
         <v>199.5</v>
       </c>
-      <c r="R98" s="3" t="n"/>
+      <c r="R98" s="3" t="n">
+        <v>1.03</v>
+      </c>
       <c r="S98" s="3">
         <f>IF(OR(Q98="",R98="",Q98=0),"",R98/Q98*100)</f>
         <v/>
@@ -6662,12 +7470,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="3" t="n"/>
-      <c r="G102" s="3" t="n"/>
-      <c r="H102" s="3" t="n"/>
-      <c r="I102" s="3" t="n"/>
+      <c r="D102" s="3" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>4.24</v>
+      </c>
       <c r="J102" s="4">
         <f>IF(OR(D102="",G102=""),"",G102-D102)</f>
         <v/>
@@ -6680,14 +7500,24 @@
         <f>IF(OR(F102="",I102=""),"",I102-F102)</f>
         <v/>
       </c>
-      <c r="M102" s="3" t="n"/>
-      <c r="N102" s="3" t="n"/>
-      <c r="O102" s="3" t="n"/>
-      <c r="P102" s="3" t="n"/>
+      <c r="M102" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>21.95</v>
+      </c>
       <c r="Q102" s="3" t="n">
         <v>41.65</v>
       </c>
-      <c r="R102" s="3" t="n"/>
+      <c r="R102" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S102" s="3">
         <f>IF(OR(Q102="",R102="",Q102=0),"",R102/Q102*100)</f>
         <v/>
@@ -6843,12 +7673,24 @@
           <t>其他電子</t>
         </is>
       </c>
-      <c r="D105" s="3" t="n"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="3" t="n"/>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="n"/>
+      <c r="D105" s="3" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>50.64</v>
+      </c>
       <c r="J105" s="4">
         <f>IF(OR(D105="",G105=""),"",G105-D105)</f>
         <v/>
@@ -6861,10 +7703,18 @@
         <f>IF(OR(F105="",I105=""),"",I105-F105)</f>
         <v/>
       </c>
-      <c r="M105" s="3" t="n"/>
-      <c r="N105" s="3" t="n"/>
-      <c r="O105" s="3" t="n"/>
-      <c r="P105" s="3" t="n"/>
+      <c r="M105" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N105" s="3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P105" s="3" t="n">
+        <v>23.99</v>
+      </c>
       <c r="Q105" s="3" t="n">
         <v>145</v>
       </c>
@@ -6955,12 +7805,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="3" t="n"/>
-      <c r="H107" s="3" t="n"/>
-      <c r="I107" s="3" t="n"/>
+      <c r="D107" s="3" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>30.47</v>
+      </c>
       <c r="J107" s="4">
         <f>IF(OR(D107="",G107=""),"",G107-D107)</f>
         <v/>
@@ -6973,10 +7835,18 @@
         <f>IF(OR(F107="",I107=""),"",I107-F107)</f>
         <v/>
       </c>
-      <c r="M107" s="3" t="n"/>
-      <c r="N107" s="3" t="n"/>
-      <c r="O107" s="3" t="n"/>
-      <c r="P107" s="3" t="n"/>
+      <c r="M107" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P107" s="3" t="n">
+        <v>8.029999999999999</v>
+      </c>
       <c r="Q107" s="3" t="n">
         <v>48.55</v>
       </c>
@@ -7004,12 +7874,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
-      <c r="G108" s="3" t="n"/>
-      <c r="H108" s="3" t="n"/>
-      <c r="I108" s="3" t="n"/>
+      <c r="D108" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="J108" s="4">
         <f>IF(OR(D108="",G108=""),"",G108-D108)</f>
         <v/>
@@ -7022,14 +7904,24 @@
         <f>IF(OR(F108="",I108=""),"",I108-F108)</f>
         <v/>
       </c>
-      <c r="M108" s="3" t="n"/>
-      <c r="N108" s="3" t="n"/>
-      <c r="O108" s="3" t="n"/>
-      <c r="P108" s="3" t="n"/>
+      <c r="M108" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>93.89</v>
+      </c>
       <c r="Q108" s="3" t="n">
         <v>50.4</v>
       </c>
-      <c r="R108" s="3" t="n"/>
+      <c r="R108" s="3" t="n">
+        <v>0.61</v>
+      </c>
       <c r="S108" s="3">
         <f>IF(OR(Q108="",R108="",Q108=0),"",R108/Q108*100)</f>
         <v/>
@@ -7060,9 +7952,15 @@
       <c r="F109" s="3" t="n">
         <v>-7.3</v>
       </c>
-      <c r="G109" s="3" t="n"/>
-      <c r="H109" s="3" t="n"/>
-      <c r="I109" s="3" t="n"/>
+      <c r="G109" s="3" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>-5.35</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>-4.06</v>
+      </c>
       <c r="J109" s="4">
         <f>IF(OR(D109="",G109=""),"",G109-D109)</f>
         <v/>
@@ -7078,8 +7976,12 @@
       <c r="M109" s="3" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N109" s="3" t="n"/>
-      <c r="O109" s="3" t="n"/>
+      <c r="N109" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>-0.24</v>
+      </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
         <v>43.05</v>
@@ -7240,12 +8142,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
+      <c r="D112" s="3" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>8.84</v>
+      </c>
       <c r="J112" s="4">
         <f>IF(OR(D112="",G112=""),"",G112-D112)</f>
         <v/>
@@ -7258,14 +8172,24 @@
         <f>IF(OR(F112="",I112=""),"",I112-F112)</f>
         <v/>
       </c>
-      <c r="M112" s="3" t="n"/>
-      <c r="N112" s="3" t="n"/>
-      <c r="O112" s="3" t="n"/>
-      <c r="P112" s="3" t="n"/>
+      <c r="M112" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N112" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O112" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P112" s="3" t="n">
+        <v>20.71</v>
+      </c>
       <c r="Q112" s="3" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="R112" s="3" t="n"/>
+      <c r="R112" s="3" t="n">
+        <v>1.99</v>
+      </c>
       <c r="S112" s="3">
         <f>IF(OR(Q112="",R112="",Q112=0),"",R112/Q112*100)</f>
         <v/>
@@ -7287,12 +8211,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
+      <c r="D113" s="3" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>7.35</v>
+      </c>
       <c r="J113" s="4">
         <f>IF(OR(D113="",G113=""),"",G113-D113)</f>
         <v/>
@@ -7305,10 +8241,18 @@
         <f>IF(OR(F113="",I113=""),"",I113-F113)</f>
         <v/>
       </c>
-      <c r="M113" s="3" t="n"/>
-      <c r="N113" s="3" t="n"/>
-      <c r="O113" s="3" t="n"/>
-      <c r="P113" s="3" t="n"/>
+      <c r="M113" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N113" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O113" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P113" s="3" t="n">
+        <v>29.45</v>
+      </c>
       <c r="Q113" s="3" t="n">
         <v>122.5</v>
       </c>
@@ -7375,7 +8319,9 @@
       <c r="Q114" s="3" t="n">
         <v>347.5</v>
       </c>
-      <c r="R114" s="3" t="n"/>
+      <c r="R114" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="S114" s="3">
         <f>IF(OR(Q114="",R114="",Q114=0),"",R114/Q114*100)</f>
         <v/>
@@ -7645,7 +8591,9 @@
       <c r="Q118" s="3" t="n">
         <v>5595</v>
       </c>
-      <c r="R118" s="3" t="n"/>
+      <c r="R118" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="S118" s="3">
         <f>IF(OR(Q118="",R118="",Q118=0),"",R118/Q118*100)</f>
         <v/>
@@ -7697,9 +8645,15 @@
         <f>IF(OR(F119="",I119=""),"",I119-F119)</f>
         <v/>
       </c>
-      <c r="M119" s="3" t="n"/>
-      <c r="N119" s="3" t="n"/>
-      <c r="O119" s="3" t="n"/>
+      <c r="M119" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>3.06</v>
+      </c>
       <c r="P119" s="3" t="n">
         <v>12.01</v>
       </c>
@@ -7730,12 +8684,24 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="n"/>
+      <c r="D120" s="3" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-24.02</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>3.44</v>
+      </c>
       <c r="J120" s="4">
         <f>IF(OR(D120="",G120=""),"",G120-D120)</f>
         <v/>
@@ -7748,14 +8714,24 @@
         <f>IF(OR(F120="",I120=""),"",I120-F120)</f>
         <v/>
       </c>
-      <c r="M120" s="3" t="n"/>
-      <c r="N120" s="3" t="n"/>
-      <c r="O120" s="3" t="n"/>
-      <c r="P120" s="3" t="n"/>
+      <c r="M120" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N120" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P120" s="3" t="n">
+        <v>46.19</v>
+      </c>
       <c r="Q120" s="3" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="R120" s="3" t="n"/>
+      <c r="R120" s="3" t="n">
+        <v>0.05</v>
+      </c>
       <c r="S120" s="3">
         <f>IF(OR(Q120="",R120="",Q120=0),"",R120/Q120*100)</f>
         <v/>
@@ -7777,12 +8753,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D121" s="3" t="n"/>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
-      <c r="H121" s="3" t="n"/>
-      <c r="I121" s="3" t="n"/>
+      <c r="D121" s="3" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>-7.66</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>25.04</v>
+      </c>
       <c r="J121" s="4">
         <f>IF(OR(D121="",G121=""),"",G121-D121)</f>
         <v/>
@@ -7795,14 +8783,24 @@
         <f>IF(OR(F121="",I121=""),"",I121-F121)</f>
         <v/>
       </c>
-      <c r="M121" s="3" t="n"/>
-      <c r="N121" s="3" t="n"/>
-      <c r="O121" s="3" t="n"/>
-      <c r="P121" s="3" t="n"/>
+      <c r="M121" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="N121" s="3" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="P121" s="3" t="n">
+        <v>5.36</v>
+      </c>
       <c r="Q121" s="3" t="n">
         <v>45.1</v>
       </c>
-      <c r="R121" s="3" t="n"/>
+      <c r="R121" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S121" s="3">
         <f>IF(OR(Q121="",R121="",Q121=0),"",R121/Q121*100)</f>
         <v/>
@@ -7962,12 +8960,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D124" s="3" t="n"/>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
+      <c r="D124" s="3" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>16.85</v>
+      </c>
       <c r="J124" s="4">
         <f>IF(OR(D124="",G124=""),"",G124-D124)</f>
         <v/>
@@ -7980,14 +8990,24 @@
         <f>IF(OR(F124="",I124=""),"",I124-F124)</f>
         <v/>
       </c>
-      <c r="M124" s="3" t="n"/>
-      <c r="N124" s="3" t="n"/>
-      <c r="O124" s="3" t="n"/>
-      <c r="P124" s="3" t="n"/>
+      <c r="M124" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="N124" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P124" s="3" t="n">
+        <v>255</v>
+      </c>
       <c r="Q124" s="3" t="n">
         <v>25.15</v>
       </c>
-      <c r="R124" s="3" t="n"/>
+      <c r="R124" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S124" s="3">
         <f>IF(OR(Q124="",R124="",Q124=0),"",R124/Q124*100)</f>
         <v/>
@@ -8009,12 +9029,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D125" s="3" t="n"/>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="n"/>
+      <c r="D125" s="3" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>3.69</v>
+      </c>
       <c r="J125" s="4">
         <f>IF(OR(D125="",G125=""),"",G125-D125)</f>
         <v/>
@@ -8027,14 +9059,24 @@
         <f>IF(OR(F125="",I125=""),"",I125-F125)</f>
         <v/>
       </c>
-      <c r="M125" s="3" t="n"/>
-      <c r="N125" s="3" t="n"/>
-      <c r="O125" s="3" t="n"/>
-      <c r="P125" s="3" t="n"/>
+      <c r="M125" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P125" s="3" t="n">
+        <v>32.81</v>
+      </c>
       <c r="Q125" s="3" t="n">
         <v>55.8</v>
       </c>
-      <c r="R125" s="3" t="n"/>
+      <c r="R125" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S125" s="3">
         <f>IF(OR(Q125="",R125="",Q125=0),"",R125/Q125*100)</f>
         <v/>
@@ -8332,12 +9374,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D130" s="3" t="n"/>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
+      <c r="D130" s="3" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>12.74</v>
+      </c>
       <c r="J130" s="4">
         <f>IF(OR(D130="",G130=""),"",G130-D130)</f>
         <v/>
@@ -8350,14 +9404,24 @@
         <f>IF(OR(F130="",I130=""),"",I130-F130)</f>
         <v/>
       </c>
-      <c r="M130" s="3" t="n"/>
-      <c r="N130" s="3" t="n"/>
-      <c r="O130" s="3" t="n"/>
-      <c r="P130" s="3" t="n"/>
+      <c r="M130" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>15.32</v>
+      </c>
       <c r="Q130" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="R130" s="3" t="n"/>
+      <c r="R130" s="3" t="n">
+        <v>5.24</v>
+      </c>
       <c r="S130" s="3">
         <f>IF(OR(Q130="",R130="",Q130=0),"",R130/Q130*100)</f>
         <v/>
@@ -8379,12 +9443,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
+      <c r="D131" s="3" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="J131" s="4">
         <f>IF(OR(D131="",G131=""),"",G131-D131)</f>
         <v/>
@@ -8397,14 +9473,24 @@
         <f>IF(OR(F131="",I131=""),"",I131-F131)</f>
         <v/>
       </c>
-      <c r="M131" s="3" t="n"/>
-      <c r="N131" s="3" t="n"/>
-      <c r="O131" s="3" t="n"/>
-      <c r="P131" s="3" t="n"/>
+      <c r="M131" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P131" s="3" t="n">
+        <v>822</v>
+      </c>
       <c r="Q131" s="3" t="n">
         <v>90.8</v>
       </c>
-      <c r="R131" s="3" t="n"/>
+      <c r="R131" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="S131" s="3">
         <f>IF(OR(Q131="",R131="",Q131=0),"",R131/Q131*100)</f>
         <v/>
@@ -8426,12 +9512,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D132" s="3" t="n"/>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
+      <c r="D132" s="3" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>25.38</v>
+      </c>
       <c r="J132" s="4">
         <f>IF(OR(D132="",G132=""),"",G132-D132)</f>
         <v/>
@@ -8444,14 +9542,24 @@
         <f>IF(OR(F132="",I132=""),"",I132-F132)</f>
         <v/>
       </c>
-      <c r="M132" s="3" t="n"/>
-      <c r="N132" s="3" t="n"/>
-      <c r="O132" s="3" t="n"/>
-      <c r="P132" s="3" t="n"/>
+      <c r="M132" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="P132" s="3" t="n">
+        <v>18.02</v>
+      </c>
       <c r="Q132" s="3" t="n">
         <v>249.5</v>
       </c>
-      <c r="R132" s="3" t="n"/>
+      <c r="R132" s="3" t="n">
+        <v>5.9</v>
+      </c>
       <c r="S132" s="3">
         <f>IF(OR(Q132="",R132="",Q132=0),"",R132/Q132*100)</f>
         <v/>
@@ -8473,12 +9581,24 @@
           <t>通訊網路</t>
         </is>
       </c>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
+      <c r="D133" s="3" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>2.42</v>
+      </c>
       <c r="J133" s="4">
         <f>IF(OR(D133="",G133=""),"",G133-D133)</f>
         <v/>
@@ -8491,14 +9611,24 @@
         <f>IF(OR(F133="",I133=""),"",I133-F133)</f>
         <v/>
       </c>
-      <c r="M133" s="3" t="n"/>
-      <c r="N133" s="3" t="n"/>
-      <c r="O133" s="3" t="n"/>
-      <c r="P133" s="3" t="n"/>
+      <c r="M133" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>15.05</v>
+      </c>
       <c r="Q133" s="3" t="n">
         <v>82.3</v>
       </c>
-      <c r="R133" s="3" t="n"/>
+      <c r="R133" s="3" t="n">
+        <v>4.084</v>
+      </c>
       <c r="S133" s="3">
         <f>IF(OR(Q133="",R133="",Q133=0),"",R133/Q133*100)</f>
         <v/>
@@ -8517,15 +9647,27 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>半導體</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>16.93</v>
+      </c>
       <c r="J134" s="4">
         <f>IF(OR(D134="",G134=""),"",G134-D134)</f>
         <v/>
@@ -8538,14 +9680,24 @@
         <f>IF(OR(F134="",I134=""),"",I134-F134)</f>
         <v/>
       </c>
-      <c r="M134" s="3" t="n"/>
-      <c r="N134" s="3" t="n"/>
-      <c r="O134" s="3" t="n"/>
-      <c r="P134" s="3" t="n"/>
+      <c r="M134" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P134" s="3" t="n">
+        <v>20.83</v>
+      </c>
       <c r="Q134" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="R134" s="3" t="n"/>
+      <c r="R134" s="3" t="n">
+        <v>3.01</v>
+      </c>
       <c r="S134" s="3">
         <f>IF(OR(Q134="",R134="",Q134=0),"",R134/Q134*100)</f>
         <v/>
@@ -8774,12 +9926,24 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D138" s="3" t="n"/>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
+      <c r="D138" s="3" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>22.12</v>
+      </c>
       <c r="J138" s="4">
         <f>IF(OR(D138="",G138=""),"",G138-D138)</f>
         <v/>
@@ -8792,14 +9956,24 @@
         <f>IF(OR(F138="",I138=""),"",I138-F138)</f>
         <v/>
       </c>
-      <c r="M138" s="3" t="n"/>
-      <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
-      <c r="P138" s="3" t="n"/>
+      <c r="M138" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P138" s="3" t="n">
+        <v>99.51000000000001</v>
+      </c>
       <c r="Q138" s="3" t="n">
         <v>419.5</v>
       </c>
-      <c r="R138" s="3" t="n"/>
+      <c r="R138" s="3" t="n">
+        <v>2.62</v>
+      </c>
       <c r="S138" s="3">
         <f>IF(OR(Q138="",R138="",Q138=0),"",R138/Q138*100)</f>
         <v/>
@@ -8821,12 +9995,24 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D139" s="3" t="n"/>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
+      <c r="D139" s="3" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>27.4</v>
+      </c>
       <c r="J139" s="4">
         <f>IF(OR(D139="",G139=""),"",G139-D139)</f>
         <v/>
@@ -8839,14 +10025,24 @@
         <f>IF(OR(F139="",I139=""),"",I139-F139)</f>
         <v/>
       </c>
-      <c r="M139" s="3" t="n"/>
-      <c r="N139" s="3" t="n"/>
-      <c r="O139" s="3" t="n"/>
-      <c r="P139" s="3" t="n"/>
+      <c r="M139" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N139" s="3" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="O139" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P139" s="3" t="n">
+        <v>13.06</v>
+      </c>
       <c r="Q139" s="3" t="n">
         <v>137.5</v>
       </c>
-      <c r="R139" s="3" t="n"/>
+      <c r="R139" s="3" t="n">
+        <v>8.851000000000001</v>
+      </c>
       <c r="S139" s="3">
         <f>IF(OR(Q139="",R139="",Q139=0),"",R139/Q139*100)</f>
         <v/>
@@ -8868,9 +10064,15 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
+      <c r="D140" s="3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>2.65</v>
+      </c>
       <c r="G140" s="3" t="n"/>
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
@@ -8886,16 +10088,24 @@
         <f>IF(OR(F140="",I140=""),"",I140-F140)</f>
         <v/>
       </c>
-      <c r="M140" s="3" t="n"/>
-      <c r="N140" s="3" t="n"/>
-      <c r="O140" s="3" t="n"/>
+      <c r="M140" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O140" s="3" t="n">
+        <v>0.42</v>
+      </c>
       <c r="P140" s="3" t="n">
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="R140" s="3" t="n"/>
+      <c r="R140" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S140" s="3">
         <f>IF(OR(Q140="",R140="",Q140=0),"",R140/Q140*100)</f>
         <v/>
@@ -8917,12 +10127,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
+      <c r="D141" s="3" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-32.41</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>1.44</v>
+      </c>
       <c r="J141" s="4">
         <f>IF(OR(D141="",G141=""),"",G141-D141)</f>
         <v/>
@@ -8935,10 +10157,18 @@
         <f>IF(OR(F141="",I141=""),"",I141-F141)</f>
         <v/>
       </c>
-      <c r="M141" s="3" t="n"/>
-      <c r="N141" s="3" t="n"/>
-      <c r="O141" s="3" t="n"/>
-      <c r="P141" s="3" t="n"/>
+      <c r="M141" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O141" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P141" s="3" t="n">
+        <v>66.23999999999999</v>
+      </c>
       <c r="Q141" s="3" t="n">
         <v>103</v>
       </c>
@@ -9033,12 +10263,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D143" s="3" t="n"/>
-      <c r="E143" s="3" t="n"/>
-      <c r="F143" s="3" t="n"/>
-      <c r="G143" s="3" t="n"/>
-      <c r="H143" s="3" t="n"/>
-      <c r="I143" s="3" t="n"/>
+      <c r="D143" s="3" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>15.28</v>
+      </c>
       <c r="J143" s="4">
         <f>IF(OR(D143="",G143=""),"",G143-D143)</f>
         <v/>
@@ -9051,14 +10293,24 @@
         <f>IF(OR(F143="",I143=""),"",I143-F143)</f>
         <v/>
       </c>
-      <c r="M143" s="3" t="n"/>
-      <c r="N143" s="3" t="n"/>
-      <c r="O143" s="3" t="n"/>
-      <c r="P143" s="3" t="n"/>
+      <c r="M143" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="O143" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P143" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Q143" s="3" t="n">
         <v>218</v>
       </c>
-      <c r="R143" s="3" t="n"/>
+      <c r="R143" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="S143" s="3">
         <f>IF(OR(Q143="",R143="",Q143=0),"",R143/Q143*100)</f>
         <v/>
@@ -9149,12 +10401,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
+      <c r="D145" s="3" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>22.76</v>
+      </c>
       <c r="J145" s="4">
         <f>IF(OR(D145="",G145=""),"",G145-D145)</f>
         <v/>
@@ -9167,14 +10431,24 @@
         <f>IF(OR(F145="",I145=""),"",I145-F145)</f>
         <v/>
       </c>
-      <c r="M145" s="3" t="n"/>
-      <c r="N145" s="3" t="n"/>
-      <c r="O145" s="3" t="n"/>
-      <c r="P145" s="3" t="n"/>
+      <c r="M145" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N145" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O145" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P145" s="3" t="n">
+        <v>18.78</v>
+      </c>
       <c r="Q145" s="3" t="n">
         <v>120.5</v>
       </c>
-      <c r="R145" s="3" t="n"/>
+      <c r="R145" s="3" t="n">
+        <v>2.97</v>
+      </c>
       <c r="S145" s="3">
         <f>IF(OR(Q145="",R145="",Q145=0),"",R145/Q145*100)</f>
         <v/>
@@ -9196,9 +10470,15 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D146" s="3" t="n"/>
-      <c r="E146" s="3" t="n"/>
-      <c r="F146" s="3" t="n"/>
+      <c r="D146" s="3" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>11.45</v>
+      </c>
       <c r="G146" s="3" t="n"/>
       <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="n"/>
@@ -9214,14 +10494,24 @@
         <f>IF(OR(F146="",I146=""),"",I146-F146)</f>
         <v/>
       </c>
-      <c r="M146" s="3" t="n"/>
-      <c r="N146" s="3" t="n"/>
-      <c r="O146" s="3" t="n"/>
-      <c r="P146" s="3" t="n"/>
+      <c r="M146" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N146" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O146" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P146" s="3" t="n">
+        <v>24.79</v>
+      </c>
       <c r="Q146" s="3" t="n">
         <v>120.5</v>
       </c>
-      <c r="R146" s="3" t="n"/>
+      <c r="R146" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S146" s="3">
         <f>IF(OR(Q146="",R146="",Q146=0),"",R146/Q146*100)</f>
         <v/>
@@ -9312,9 +10602,15 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
+      <c r="D148" s="3" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>9.039999999999999</v>
+      </c>
       <c r="G148" s="3" t="n"/>
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
@@ -9330,14 +10626,24 @@
         <f>IF(OR(F148="",I148=""),"",I148-F148)</f>
         <v/>
       </c>
-      <c r="M148" s="3" t="n"/>
-      <c r="N148" s="3" t="n"/>
-      <c r="O148" s="3" t="n"/>
-      <c r="P148" s="3" t="n"/>
+      <c r="M148" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N148" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O148" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P148" s="3" t="n">
+        <v>37</v>
+      </c>
       <c r="Q148" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="R148" s="3" t="n"/>
+      <c r="R148" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="S148" s="3">
         <f>IF(OR(Q148="",R148="",Q148=0),"",R148/Q148*100)</f>
         <v/>
@@ -9359,9 +10665,15 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D149" s="3" t="n"/>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n"/>
+      <c r="D149" s="3" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>3.81</v>
+      </c>
       <c r="G149" s="3" t="n"/>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
@@ -9377,10 +10689,18 @@
         <f>IF(OR(F149="",I149=""),"",I149-F149)</f>
         <v/>
       </c>
-      <c r="M149" s="3" t="n"/>
-      <c r="N149" s="3" t="n"/>
-      <c r="O149" s="3" t="n"/>
-      <c r="P149" s="3" t="n"/>
+      <c r="M149" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O149" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P149" s="3" t="n">
+        <v>214.66</v>
+      </c>
       <c r="Q149" s="3" t="n">
         <v>258</v>
       </c>
@@ -9546,9 +10866,15 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D152" s="3" t="n"/>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n"/>
+      <c r="D152" s="3" t="n">
+        <v>29.19</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>17.01</v>
+      </c>
       <c r="G152" s="3" t="n"/>
       <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="n"/>
@@ -9564,14 +10890,24 @@
         <f>IF(OR(F152="",I152=""),"",I152-F152)</f>
         <v/>
       </c>
-      <c r="M152" s="3" t="n"/>
-      <c r="N152" s="3" t="n"/>
-      <c r="O152" s="3" t="n"/>
-      <c r="P152" s="3" t="n"/>
+      <c r="M152" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O152" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P152" s="3" t="n">
+        <v>33.27</v>
+      </c>
       <c r="Q152" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="R152" s="3" t="n"/>
+      <c r="R152" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="S152" s="3">
         <f>IF(OR(Q152="",R152="",Q152=0),"",R152/Q152*100)</f>
         <v/>
@@ -9593,9 +10929,15 @@
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="D153" s="3" t="n"/>
-      <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
+      <c r="D153" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>-86.23</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>-37.03</v>
+      </c>
       <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
@@ -9611,14 +10953,24 @@
         <f>IF(OR(F153="",I153=""),"",I153-F153)</f>
         <v/>
       </c>
-      <c r="M153" s="3" t="n"/>
-      <c r="N153" s="3" t="n"/>
-      <c r="O153" s="3" t="n"/>
-      <c r="P153" s="3" t="n"/>
+      <c r="M153" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="P153" s="3" t="n">
+        <v>15.64</v>
+      </c>
       <c r="Q153" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="R153" s="3" t="n"/>
+      <c r="R153" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S153" s="3">
         <f>IF(OR(Q153="",R153="",Q153=0),"",R153/Q153*100)</f>
         <v/>
@@ -9778,9 +11130,15 @@
           <t>營建</t>
         </is>
       </c>
-      <c r="D156" s="3" t="n"/>
-      <c r="E156" s="3" t="n"/>
-      <c r="F156" s="3" t="n"/>
+      <c r="D156" s="3" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>3.67</v>
+      </c>
       <c r="G156" s="3" t="n"/>
       <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="n"/>
@@ -9796,14 +11154,20 @@
         <f>IF(OR(F156="",I156=""),"",I156-F156)</f>
         <v/>
       </c>
-      <c r="M156" s="3" t="n"/>
+      <c r="M156" s="3" t="n">
+        <v>0.16</v>
+      </c>
       <c r="N156" s="3" t="n"/>
       <c r="O156" s="3" t="n"/>
-      <c r="P156" s="3" t="n"/>
+      <c r="P156" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="Q156" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="R156" s="3" t="n"/>
+      <c r="R156" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S156" s="3">
         <f>IF(OR(Q156="",R156="",Q156=0),"",R156/Q156*100)</f>
         <v/>
@@ -9825,10 +11189,18 @@
           <t>營建</t>
         </is>
       </c>
-      <c r="D157" s="3" t="n"/>
-      <c r="E157" s="3" t="n"/>
-      <c r="F157" s="3" t="n"/>
-      <c r="G157" s="3" t="n"/>
+      <c r="D157" s="3" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>27.81</v>
+      </c>
       <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="4">
@@ -9843,14 +11215,24 @@
         <f>IF(OR(F157="",I157=""),"",I157-F157)</f>
         <v/>
       </c>
-      <c r="M157" s="3" t="n"/>
-      <c r="N157" s="3" t="n"/>
-      <c r="O157" s="3" t="n"/>
-      <c r="P157" s="3" t="n"/>
+      <c r="M157" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O157" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P157" s="3" t="n">
+        <v>10.85</v>
+      </c>
       <c r="Q157" s="3" t="n">
         <v>35.4</v>
       </c>
-      <c r="R157" s="3" t="n"/>
+      <c r="R157" s="3" t="n">
+        <v>1.62</v>
+      </c>
       <c r="S157" s="3">
         <f>IF(OR(Q157="",R157="",Q157=0),"",R157/Q157*100)</f>
         <v/>
@@ -9864,17 +11246,23 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>華建</t>
+          <t>大華建設</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>營建</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="n"/>
-      <c r="E158" s="3" t="n"/>
-      <c r="F158" s="3" t="n"/>
+          <t>營建業</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>-17.55</v>
+      </c>
       <c r="G158" s="3" t="n"/>
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
@@ -9890,10 +11278,14 @@
         <f>IF(OR(F158="",I158=""),"",I158-F158)</f>
         <v/>
       </c>
-      <c r="M158" s="3" t="n"/>
+      <c r="M158" s="3" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="N158" s="3" t="n"/>
       <c r="O158" s="3" t="n"/>
-      <c r="P158" s="3" t="n"/>
+      <c r="P158" s="3" t="n">
+        <v>29.47</v>
+      </c>
       <c r="Q158" s="3" t="n">
         <v>19.35</v>
       </c>
@@ -9919,9 +11311,15 @@
           <t>營建</t>
         </is>
       </c>
-      <c r="D159" s="3" t="n"/>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n"/>
+      <c r="D159" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>10.45</v>
+      </c>
       <c r="G159" s="3" t="n"/>
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
@@ -9937,14 +11335,24 @@
         <f>IF(OR(F159="",I159=""),"",I159-F159)</f>
         <v/>
       </c>
-      <c r="M159" s="3" t="n"/>
-      <c r="N159" s="3" t="n"/>
-      <c r="O159" s="3" t="n"/>
-      <c r="P159" s="3" t="n"/>
+      <c r="M159" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="O159" s="3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P159" s="3" t="n">
+        <v>8.91</v>
+      </c>
       <c r="Q159" s="3" t="n">
         <v>90.2</v>
       </c>
-      <c r="R159" s="3" t="n"/>
+      <c r="R159" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="S159" s="3">
         <f>IF(OR(Q159="",R159="",Q159=0),"",R159/Q159*100)</f>
         <v/>
@@ -10171,9 +11579,15 @@
           <t>營建</t>
         </is>
       </c>
-      <c r="D163" s="3" t="n"/>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
+      <c r="D163" s="3" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>6.76</v>
+      </c>
       <c r="G163" s="3" t="n"/>
       <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="n"/>
@@ -10189,14 +11603,24 @@
         <f>IF(OR(F163="",I163=""),"",I163-F163)</f>
         <v/>
       </c>
-      <c r="M163" s="3" t="n"/>
-      <c r="N163" s="3" t="n"/>
-      <c r="O163" s="3" t="n"/>
-      <c r="P163" s="3" t="n"/>
+      <c r="M163" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N163" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O163" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P163" s="3" t="n">
+        <v>13.37</v>
+      </c>
       <c r="Q163" s="3" t="n">
         <v>38.5</v>
       </c>
-      <c r="R163" s="3" t="n"/>
+      <c r="R163" s="3" t="n">
+        <v>1.03</v>
+      </c>
       <c r="S163" s="3">
         <f>IF(OR(Q163="",R163="",Q163=0),"",R163/Q163*100)</f>
         <v/>
@@ -10218,9 +11642,15 @@
           <t>營建</t>
         </is>
       </c>
-      <c r="D164" s="3" t="n"/>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
+      <c r="D164" s="3" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="G164" s="3" t="n"/>
       <c r="H164" s="3" t="n"/>
       <c r="I164" s="3" t="n"/>
@@ -10236,14 +11666,24 @@
         <f>IF(OR(F164="",I164=""),"",I164-F164)</f>
         <v/>
       </c>
-      <c r="M164" s="3" t="n"/>
-      <c r="N164" s="3" t="n"/>
-      <c r="O164" s="3" t="n"/>
-      <c r="P164" s="3" t="n"/>
+      <c r="M164" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="N164" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O164" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P164" s="3" t="n">
+        <v>36.53</v>
+      </c>
       <c r="Q164" s="3" t="n">
         <v>34.6</v>
       </c>
-      <c r="R164" s="3" t="n"/>
+      <c r="R164" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="S164" s="3">
         <f>IF(OR(Q164="",R164="",Q164=0),"",R164/Q164*100)</f>
         <v/>
@@ -10265,9 +11705,15 @@
           <t>建材營造</t>
         </is>
       </c>
-      <c r="D165" s="3" t="n"/>
-      <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n"/>
+      <c r="D165" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>17.29</v>
+      </c>
       <c r="G165" s="3" t="n"/>
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="n"/>
@@ -10283,14 +11729,20 @@
         <f>IF(OR(F165="",I165=""),"",I165-F165)</f>
         <v/>
       </c>
-      <c r="M165" s="3" t="n"/>
+      <c r="M165" s="3" t="n">
+        <v>2.28</v>
+      </c>
       <c r="N165" s="3" t="n"/>
       <c r="O165" s="3" t="n"/>
-      <c r="P165" s="3" t="n"/>
+      <c r="P165" s="3" t="n">
+        <v>7.81</v>
+      </c>
       <c r="Q165" s="3" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="R165" s="3" t="n"/>
+      <c r="R165" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="S165" s="3">
         <f>IF(OR(Q165="",R165="",Q165=0),"",R165/Q165*100)</f>
         <v/>
@@ -10312,9 +11764,15 @@
           <t>建材營造</t>
         </is>
       </c>
-      <c r="D166" s="3" t="n"/>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="n"/>
+      <c r="D166" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>11.12</v>
+      </c>
       <c r="G166" s="3" t="n"/>
       <c r="H166" s="3" t="n"/>
       <c r="I166" s="3" t="n"/>
@@ -10330,14 +11788,24 @@
         <f>IF(OR(F166="",I166=""),"",I166-F166)</f>
         <v/>
       </c>
-      <c r="M166" s="3" t="n"/>
-      <c r="N166" s="3" t="n"/>
-      <c r="O166" s="3" t="n"/>
-      <c r="P166" s="3" t="n"/>
+      <c r="M166" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="O166" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P166" s="3" t="n">
+        <v>14.45</v>
+      </c>
       <c r="Q166" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="R166" s="3" t="n"/>
+      <c r="R166" s="3" t="n">
+        <v>9.67</v>
+      </c>
       <c r="S166" s="3">
         <f>IF(OR(Q166="",R166="",Q166=0),"",R166/Q166*100)</f>
         <v/>
@@ -10428,9 +11896,15 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="D168" s="3" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
+      <c r="D168" s="3" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>28.34</v>
+      </c>
       <c r="G168" s="3" t="n"/>
       <c r="H168" s="3" t="n"/>
       <c r="I168" s="3" t="n"/>
@@ -10446,14 +11920,24 @@
         <f>IF(OR(F168="",I168=""),"",I168-F168)</f>
         <v/>
       </c>
-      <c r="M168" s="3" t="n"/>
-      <c r="N168" s="3" t="n"/>
-      <c r="O168" s="3" t="n"/>
-      <c r="P168" s="3" t="n"/>
+      <c r="M168" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N168" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O168" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P168" s="3" t="n">
+        <v>7.47</v>
+      </c>
       <c r="Q168" s="3" t="n">
         <v>36.7</v>
       </c>
-      <c r="R168" s="3" t="n"/>
+      <c r="R168" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S168" s="3">
         <f>IF(OR(Q168="",R168="",Q168=0),"",R168/Q168*100)</f>
         <v/>
@@ -10475,12 +11959,24 @@
           <t>航運業</t>
         </is>
       </c>
-      <c r="D169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="3" t="n"/>
-      <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="n"/>
+      <c r="D169" s="3" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>39.42</v>
+      </c>
       <c r="J169" s="4">
         <f>IF(OR(D169="",G169=""),"",G169-D169)</f>
         <v/>
@@ -10493,14 +11989,24 @@
         <f>IF(OR(F169="",I169=""),"",I169-F169)</f>
         <v/>
       </c>
-      <c r="M169" s="3" t="n"/>
-      <c r="N169" s="3" t="n"/>
-      <c r="O169" s="3" t="n"/>
-      <c r="P169" s="3" t="n"/>
+      <c r="M169" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N169" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="O169" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P169" s="3" t="n">
+        <v>10.71</v>
+      </c>
       <c r="Q169" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="R169" s="3" t="n"/>
+      <c r="R169" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="S169" s="3">
         <f>IF(OR(Q169="",R169="",Q169=0),"",R169/Q169*100)</f>
         <v/>
@@ -10522,12 +12028,24 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
-      <c r="H170" s="3" t="n"/>
-      <c r="I170" s="3" t="n"/>
+      <c r="D170" s="3" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>17.64</v>
+      </c>
       <c r="J170" s="4">
         <f>IF(OR(D170="",G170=""),"",G170-D170)</f>
         <v/>
@@ -10540,14 +12058,24 @@
         <f>IF(OR(F170="",I170=""),"",I170-F170)</f>
         <v/>
       </c>
-      <c r="M170" s="3" t="n"/>
-      <c r="N170" s="3" t="n"/>
-      <c r="O170" s="3" t="n"/>
-      <c r="P170" s="3" t="n"/>
+      <c r="M170" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N170" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O170" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P170" s="3" t="n">
+        <v>10.46</v>
+      </c>
       <c r="Q170" s="3" t="n">
         <v>52.1</v>
       </c>
-      <c r="R170" s="3" t="n"/>
+      <c r="R170" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="S170" s="3">
         <f>IF(OR(Q170="",R170="",Q170=0),"",R170/Q170*100)</f>
         <v/>
@@ -10668,9 +12196,15 @@
         <f>IF(OR(F172="",I172=""),"",I172-F172)</f>
         <v/>
       </c>
-      <c r="M172" s="3" t="n"/>
-      <c r="N172" s="3" t="n"/>
-      <c r="O172" s="3" t="n"/>
+      <c r="M172" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N172" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O172" s="3" t="n">
+        <v>0.23</v>
+      </c>
       <c r="P172" s="3" t="n">
         <v>9.210000000000001</v>
       </c>
@@ -10908,12 +12442,24 @@
           <t>航運業</t>
         </is>
       </c>
-      <c r="D176" s="3" t="n"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="3" t="n"/>
-      <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="n"/>
+      <c r="D176" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="J176" s="4">
         <f>IF(OR(D176="",G176=""),"",G176-D176)</f>
         <v/>
@@ -10926,10 +12472,18 @@
         <f>IF(OR(F176="",I176=""),"",I176-F176)</f>
         <v/>
       </c>
-      <c r="M176" s="3" t="n"/>
-      <c r="N176" s="3" t="n"/>
-      <c r="O176" s="3" t="n"/>
-      <c r="P176" s="3" t="n"/>
+      <c r="M176" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N176" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O176" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P176" s="3" t="n">
+        <v>33.48</v>
+      </c>
       <c r="Q176" s="3" t="n">
         <v>66.7</v>
       </c>
@@ -10996,11 +12550,15 @@
       <c r="O177" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="P177" s="3" t="n"/>
+      <c r="P177" s="3" t="n">
+        <v>11.35</v>
+      </c>
       <c r="Q177" s="3" t="n">
         <v>95.5</v>
       </c>
-      <c r="R177" s="3" t="n"/>
+      <c r="R177" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="S177" s="3">
         <f>IF(OR(Q177="",R177="",Q177=0),"",R177/Q177*100)</f>
         <v/>
@@ -11294,12 +12852,24 @@
           <t>觀光餐旅</t>
         </is>
       </c>
-      <c r="D182" s="3" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="3" t="n"/>
-      <c r="H182" s="3" t="n"/>
-      <c r="I182" s="3" t="n"/>
+      <c r="D182" s="3" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v>6.3</v>
+      </c>
       <c r="J182" s="4">
         <f>IF(OR(D182="",G182=""),"",G182-D182)</f>
         <v/>
@@ -11312,9 +12882,15 @@
         <f>IF(OR(F182="",I182=""),"",I182-F182)</f>
         <v/>
       </c>
-      <c r="M182" s="3" t="n"/>
-      <c r="N182" s="3" t="n"/>
-      <c r="O182" s="3" t="n"/>
+      <c r="M182" s="3" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="N182" s="3" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="O182" s="3" t="n">
+        <v>4.82</v>
+      </c>
       <c r="P182" s="3" t="n">
         <v>13.19</v>
       </c>
@@ -11412,13 +12988,21 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="D184" s="3" t="n"/>
-      <c r="E184" s="3" t="n"/>
+      <c r="D184" s="3" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="F184" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G184" s="3" t="n"/>
-      <c r="H184" s="3" t="n"/>
+      <c r="G184" s="3" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>9.74</v>
+      </c>
       <c r="I184" s="3" t="n">
         <v>8.59</v>
       </c>
@@ -11572,9 +13156,15 @@
         <f>IF(OR(F186="",I186=""),"",I186-F186)</f>
         <v/>
       </c>
-      <c r="M186" s="3" t="n"/>
-      <c r="N186" s="3" t="n"/>
-      <c r="O186" s="3" t="n"/>
+      <c r="M186" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N186" s="3" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="O186" s="3" t="n">
+        <v>6.36</v>
+      </c>
       <c r="P186" s="3" t="n">
         <v>4.28</v>
       </c>
@@ -12222,12 +13812,24 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
-      <c r="H196" s="3" t="n"/>
-      <c r="I196" s="3" t="n"/>
+      <c r="D196" s="3" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>7.76</v>
+      </c>
       <c r="J196" s="4">
         <f>IF(OR(D196="",G196=""),"",G196-D196)</f>
         <v/>
@@ -12240,9 +13842,15 @@
         <f>IF(OR(F196="",I196=""),"",I196-F196)</f>
         <v/>
       </c>
-      <c r="M196" s="3" t="n"/>
-      <c r="N196" s="3" t="n"/>
-      <c r="O196" s="3" t="n"/>
+      <c r="M196" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N196" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O196" s="3" t="n">
+        <v>1.93</v>
+      </c>
       <c r="P196" s="3" t="n">
         <v>22.85</v>
       </c>
@@ -12480,12 +14088,24 @@
           <t>電子通路業</t>
         </is>
       </c>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
+      <c r="D200" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>2.67</v>
+      </c>
       <c r="J200" s="4">
         <f>IF(OR(D200="",G200=""),"",G200-D200)</f>
         <v/>
@@ -12498,9 +14118,15 @@
         <f>IF(OR(F200="",I200=""),"",I200-F200)</f>
         <v/>
       </c>
-      <c r="M200" s="3" t="n"/>
-      <c r="N200" s="3" t="n"/>
-      <c r="O200" s="3" t="n"/>
+      <c r="M200" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N200" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="O200" s="3" t="n">
+        <v>2.19</v>
+      </c>
       <c r="P200" s="3" t="n">
         <v>9.35</v>
       </c>
@@ -12531,12 +14157,24 @@
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="D201" s="3" t="n"/>
-      <c r="E201" s="3" t="n"/>
-      <c r="F201" s="3" t="n"/>
-      <c r="G201" s="3" t="n"/>
-      <c r="H201" s="3" t="n"/>
-      <c r="I201" s="3" t="n"/>
+      <c r="D201" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>5.78</v>
+      </c>
       <c r="J201" s="4">
         <f>IF(OR(D201="",G201=""),"",G201-D201)</f>
         <v/>
@@ -12549,9 +14187,15 @@
         <f>IF(OR(F201="",I201=""),"",I201-F201)</f>
         <v/>
       </c>
-      <c r="M201" s="3" t="n"/>
-      <c r="N201" s="3" t="n"/>
-      <c r="O201" s="3" t="n"/>
+      <c r="M201" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="O201" s="3" t="n">
+        <v>1.86</v>
+      </c>
       <c r="P201" s="3" t="n">
         <v>15.83</v>
       </c>
@@ -12765,7 +14409,9 @@
       <c r="Q204" s="3" t="n">
         <v>555</v>
       </c>
-      <c r="R204" s="3" t="n"/>
+      <c r="R204" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="S204" s="3">
         <f>IF(OR(Q204="",R204="",Q204=0),"",R204/Q204*100)</f>
         <v/>
@@ -12832,7 +14478,9 @@
       <c r="Q205" s="3" t="n">
         <v>172</v>
       </c>
-      <c r="R205" s="3" t="n"/>
+      <c r="R205" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="S205" s="3">
         <f>IF(OR(Q205="",R205="",Q205=0),"",R205/Q205*100)</f>
         <v/>
@@ -12992,9 +14640,15 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D208" s="3" t="n"/>
-      <c r="E208" s="3" t="n"/>
-      <c r="F208" s="3" t="n"/>
+      <c r="D208" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="G208" s="3" t="n"/>
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="n"/>
@@ -13010,14 +14664,20 @@
         <f>IF(OR(F208="",I208=""),"",I208-F208)</f>
         <v/>
       </c>
-      <c r="M208" s="3" t="n"/>
+      <c r="M208" s="3" t="n">
+        <v>1.32</v>
+      </c>
       <c r="N208" s="3" t="n"/>
       <c r="O208" s="3" t="n"/>
-      <c r="P208" s="3" t="n"/>
+      <c r="P208" s="3" t="n">
+        <v>32.82</v>
+      </c>
       <c r="Q208" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="R208" s="3" t="n"/>
+      <c r="R208" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="S208" s="3">
         <f>IF(OR(Q208="",R208="",Q208=0),"",R208/Q208*100)</f>
         <v/>
@@ -13243,15 +14903,27 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>櫃電腦週邊</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="n"/>
-      <c r="E212" s="3" t="n"/>
-      <c r="F212" s="3" t="n"/>
-      <c r="G212" s="3" t="n"/>
-      <c r="H212" s="3" t="n"/>
-      <c r="I212" s="3" t="n"/>
+          <t>電子零組件</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>9.119999999999999</v>
+      </c>
       <c r="J212" s="4">
         <f>IF(OR(D212="",G212=""),"",G212-D212)</f>
         <v/>
@@ -13264,14 +14936,24 @@
         <f>IF(OR(F212="",I212=""),"",I212-F212)</f>
         <v/>
       </c>
-      <c r="M212" s="3" t="n"/>
-      <c r="N212" s="3" t="n"/>
-      <c r="O212" s="3" t="n"/>
-      <c r="P212" s="3" t="n"/>
+      <c r="M212" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N212" s="3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="P212" s="3" t="n">
+        <v>15.63</v>
+      </c>
       <c r="Q212" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="R212" s="3" t="n"/>
+      <c r="R212" s="3" t="n">
+        <v>2.9304</v>
+      </c>
       <c r="S212" s="3">
         <f>IF(OR(Q212="",R212="",Q212=0),"",R212/Q212*100)</f>
         <v/>
@@ -13293,12 +14975,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D213" s="3" t="n"/>
-      <c r="E213" s="3" t="n"/>
-      <c r="F213" s="3" t="n"/>
-      <c r="G213" s="3" t="n"/>
-      <c r="H213" s="3" t="n"/>
-      <c r="I213" s="3" t="n"/>
+      <c r="D213" s="3" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>17.85</v>
+      </c>
       <c r="J213" s="4">
         <f>IF(OR(D213="",G213=""),"",G213-D213)</f>
         <v/>
@@ -13311,14 +15005,24 @@
         <f>IF(OR(F213="",I213=""),"",I213-F213)</f>
         <v/>
       </c>
-      <c r="M213" s="3" t="n"/>
-      <c r="N213" s="3" t="n"/>
-      <c r="O213" s="3" t="n"/>
-      <c r="P213" s="3" t="n"/>
+      <c r="M213" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N213" s="3" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="O213" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="P213" s="3" t="n">
+        <v>19.92</v>
+      </c>
       <c r="Q213" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="R213" s="3" t="n"/>
+      <c r="R213" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="S213" s="3">
         <f>IF(OR(Q213="",R213="",Q213=0),"",R213/Q213*100)</f>
         <v/>
@@ -13475,15 +15179,27 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>半導體</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="n"/>
-      <c r="E216" s="3" t="n"/>
-      <c r="F216" s="3" t="n"/>
-      <c r="G216" s="3" t="n"/>
-      <c r="H216" s="3" t="n"/>
-      <c r="I216" s="3" t="n"/>
+          <t>電子零組件</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>13.22</v>
+      </c>
       <c r="J216" s="4">
         <f>IF(OR(D216="",G216=""),"",G216-D216)</f>
         <v/>
@@ -13496,14 +15212,24 @@
         <f>IF(OR(F216="",I216=""),"",I216-F216)</f>
         <v/>
       </c>
-      <c r="M216" s="3" t="n"/>
-      <c r="N216" s="3" t="n"/>
-      <c r="O216" s="3" t="n"/>
-      <c r="P216" s="3" t="n"/>
+      <c r="M216" s="3" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="O216" s="3" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="P216" s="3" t="n">
+        <v>6.7</v>
+      </c>
       <c r="Q216" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="R216" s="3" t="n"/>
+      <c r="R216" s="3" t="n">
+        <v>3.2586</v>
+      </c>
       <c r="S216" s="3">
         <f>IF(OR(Q216="",R216="",Q216=0),"",R216/Q216*100)</f>
         <v/>
@@ -13525,12 +15251,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D217" s="3" t="n"/>
-      <c r="E217" s="3" t="n"/>
-      <c r="F217" s="3" t="n"/>
-      <c r="G217" s="3" t="n"/>
-      <c r="H217" s="3" t="n"/>
-      <c r="I217" s="3" t="n"/>
+      <c r="D217" s="3" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>-15.79</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>-14.33</v>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>-19.28</v>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v>-19.42</v>
+      </c>
       <c r="J217" s="4">
         <f>IF(OR(D217="",G217=""),"",G217-D217)</f>
         <v/>
@@ -13543,9 +15281,15 @@
         <f>IF(OR(F217="",I217=""),"",I217-F217)</f>
         <v/>
       </c>
-      <c r="M217" s="3" t="n"/>
-      <c r="N217" s="3" t="n"/>
-      <c r="O217" s="3" t="n"/>
+      <c r="M217" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="N217" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="O217" s="3" t="n">
+        <v>-0.48</v>
+      </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
         <v>64.40000000000001</v>
@@ -13917,12 +15661,24 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D223" s="3" t="n"/>
-      <c r="E223" s="3" t="n"/>
-      <c r="F223" s="3" t="n"/>
-      <c r="G223" s="3" t="n"/>
-      <c r="H223" s="3" t="n"/>
-      <c r="I223" s="3" t="n"/>
+      <c r="D223" s="3" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>19.94</v>
+      </c>
       <c r="J223" s="4">
         <f>IF(OR(D223="",G223=""),"",G223-D223)</f>
         <v/>
@@ -13935,14 +15691,24 @@
         <f>IF(OR(F223="",I223=""),"",I223-F223)</f>
         <v/>
       </c>
-      <c r="M223" s="3" t="n"/>
-      <c r="N223" s="3" t="n"/>
-      <c r="O223" s="3" t="n"/>
-      <c r="P223" s="3" t="n"/>
+      <c r="M223" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N223" s="3" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="O223" s="3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P223" s="3" t="n">
+        <v>15.77</v>
+      </c>
       <c r="Q223" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="R223" s="3" t="n"/>
+      <c r="R223" s="3" t="n">
+        <v>10.007</v>
+      </c>
       <c r="S223" s="3">
         <f>IF(OR(Q223="",R223="",Q223=0),"",R223/Q223*100)</f>
         <v/>
@@ -14445,12 +16211,24 @@
           <t>其他電子</t>
         </is>
       </c>
-      <c r="D231" s="3" t="n"/>
-      <c r="E231" s="3" t="n"/>
-      <c r="F231" s="3" t="n"/>
-      <c r="G231" s="3" t="n"/>
-      <c r="H231" s="3" t="n"/>
-      <c r="I231" s="3" t="n"/>
+      <c r="D231" s="3" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>7.09</v>
+      </c>
       <c r="J231" s="4">
         <f>IF(OR(D231="",G231=""),"",G231-D231)</f>
         <v/>
@@ -14463,14 +16241,24 @@
         <f>IF(OR(F231="",I231=""),"",I231-F231)</f>
         <v/>
       </c>
-      <c r="M231" s="3" t="n"/>
-      <c r="N231" s="3" t="n"/>
-      <c r="O231" s="3" t="n"/>
-      <c r="P231" s="3" t="n"/>
+      <c r="M231" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N231" s="3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O231" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P231" s="3" t="n">
+        <v>19.18</v>
+      </c>
       <c r="Q231" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="R231" s="3" t="n"/>
+      <c r="R231" s="3" t="n">
+        <v>2.2833</v>
+      </c>
       <c r="S231" s="3">
         <f>IF(OR(Q231="",R231="",Q231=0),"",R231/Q231*100)</f>
         <v/>
@@ -14902,12 +16690,24 @@
           <t>通訊網路</t>
         </is>
       </c>
-      <c r="D238" s="3" t="n"/>
-      <c r="E238" s="3" t="n"/>
-      <c r="F238" s="3" t="n"/>
-      <c r="G238" s="3" t="n"/>
-      <c r="H238" s="3" t="n"/>
-      <c r="I238" s="3" t="n"/>
+      <c r="D238" s="3" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="I238" s="3" t="n">
+        <v>0.05</v>
+      </c>
       <c r="J238" s="4">
         <f>IF(OR(D238="",G238=""),"",G238-D238)</f>
         <v/>
@@ -14920,10 +16720,18 @@
         <f>IF(OR(F238="",I238=""),"",I238-F238)</f>
         <v/>
       </c>
-      <c r="M238" s="3" t="n"/>
-      <c r="N238" s="3" t="n"/>
-      <c r="O238" s="3" t="n"/>
-      <c r="P238" s="3" t="n"/>
+      <c r="M238" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N238" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O238" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P238" s="3" t="n">
+        <v>188.94</v>
+      </c>
       <c r="Q238" s="3" t="n">
         <v>27.25</v>
       </c>
@@ -15085,12 +16893,24 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="D241" s="3" t="n"/>
-      <c r="E241" s="3" t="n"/>
-      <c r="F241" s="3" t="n"/>
-      <c r="G241" s="3" t="n"/>
-      <c r="H241" s="3" t="n"/>
-      <c r="I241" s="3" t="n"/>
+      <c r="D241" s="3" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="I241" s="3" t="n">
+        <v>16.89</v>
+      </c>
       <c r="J241" s="4">
         <f>IF(OR(D241="",G241=""),"",G241-D241)</f>
         <v/>
@@ -15103,14 +16923,24 @@
         <f>IF(OR(F241="",I241=""),"",I241-F241)</f>
         <v/>
       </c>
-      <c r="M241" s="3" t="n"/>
-      <c r="N241" s="3" t="n"/>
-      <c r="O241" s="3" t="n"/>
-      <c r="P241" s="3" t="n"/>
+      <c r="M241" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N241" s="3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="O241" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P241" s="3" t="n">
+        <v>20.39</v>
+      </c>
       <c r="Q241" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="R241" s="3" t="n"/>
+      <c r="R241" s="3" t="n">
+        <v>5.0959</v>
+      </c>
       <c r="S241" s="3">
         <f>IF(OR(Q241="",R241="",Q241=0),"",R241/Q241*100)</f>
         <v/>
@@ -15171,11 +17001,15 @@
       <c r="O242" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="P242" s="3" t="n"/>
+      <c r="P242" s="3" t="n">
+        <v>137.52</v>
+      </c>
       <c r="Q242" s="3" t="n">
         <v>5570</v>
       </c>
-      <c r="R242" s="3" t="n"/>
+      <c r="R242" s="3" t="n">
+        <v>20</v>
+      </c>
       <c r="S242" s="3">
         <f>IF(OR(Q242="",R242="",Q242=0),"",R242/Q242*100)</f>
         <v/>
@@ -15404,12 +17238,24 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="D246" s="3" t="n"/>
-      <c r="E246" s="3" t="n"/>
-      <c r="F246" s="3" t="n"/>
-      <c r="G246" s="3" t="n"/>
-      <c r="H246" s="3" t="n"/>
-      <c r="I246" s="3" t="n"/>
+      <c r="D246" s="3" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="I246" s="3" t="n">
+        <v>7.88</v>
+      </c>
       <c r="J246" s="4">
         <f>IF(OR(D246="",G246=""),"",G246-D246)</f>
         <v/>
@@ -15422,14 +17268,24 @@
         <f>IF(OR(F246="",I246=""),"",I246-F246)</f>
         <v/>
       </c>
-      <c r="M246" s="3" t="n"/>
-      <c r="N246" s="3" t="n"/>
-      <c r="O246" s="3" t="n"/>
-      <c r="P246" s="3" t="n"/>
+      <c r="M246" s="3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="N246" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O246" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P246" s="3" t="n">
+        <v>14.28</v>
+      </c>
       <c r="Q246" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="R246" s="3" t="n"/>
+      <c r="R246" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="S246" s="3">
         <f>IF(OR(Q246="",R246="",Q246=0),"",R246/Q246*100)</f>
         <v/>
@@ -15721,12 +17577,24 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D251" s="3" t="n"/>
-      <c r="E251" s="3" t="n"/>
-      <c r="F251" s="3" t="n"/>
-      <c r="G251" s="3" t="n"/>
-      <c r="H251" s="3" t="n"/>
-      <c r="I251" s="3" t="n"/>
+      <c r="D251" s="3" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>60.41</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>32.11</v>
+      </c>
       <c r="J251" s="4">
         <f>IF(OR(D251="",G251=""),"",G251-D251)</f>
         <v/>
@@ -15739,14 +17607,24 @@
         <f>IF(OR(F251="",I251=""),"",I251-F251)</f>
         <v/>
       </c>
-      <c r="M251" s="3" t="n"/>
-      <c r="N251" s="3" t="n"/>
-      <c r="O251" s="3" t="n"/>
-      <c r="P251" s="3" t="n"/>
+      <c r="M251" s="3" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="N251" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O251" s="3" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="P251" s="3" t="n">
+        <v>39.02</v>
+      </c>
       <c r="Q251" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="R251" s="3" t="n"/>
+      <c r="R251" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="S251" s="3">
         <f>IF(OR(Q251="",R251="",Q251=0),"",R251/Q251*100)</f>
         <v/>
@@ -15835,12 +17713,24 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D253" s="3" t="n"/>
-      <c r="E253" s="3" t="n"/>
-      <c r="F253" s="3" t="n"/>
-      <c r="G253" s="3" t="n"/>
-      <c r="H253" s="3" t="n"/>
-      <c r="I253" s="3" t="n"/>
+      <c r="D253" s="3" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="G253" s="3" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="I253" s="3" t="n">
+        <v>13.89</v>
+      </c>
       <c r="J253" s="4">
         <f>IF(OR(D253="",G253=""),"",G253-D253)</f>
         <v/>
@@ -15853,14 +17743,24 @@
         <f>IF(OR(F253="",I253=""),"",I253-F253)</f>
         <v/>
       </c>
-      <c r="M253" s="3" t="n"/>
-      <c r="N253" s="3" t="n"/>
-      <c r="O253" s="3" t="n"/>
-      <c r="P253" s="3" t="n"/>
+      <c r="M253" s="3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="N253" s="3" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O253" s="3" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="P253" s="3" t="n">
+        <v>40.66</v>
+      </c>
       <c r="Q253" s="3" t="n">
         <v>693</v>
       </c>
-      <c r="R253" s="3" t="n"/>
+      <c r="R253" s="3" t="n">
+        <v>11.7476</v>
+      </c>
       <c r="S253" s="3">
         <f>IF(OR(Q253="",R253="",Q253=0),"",R253/Q253*100)</f>
         <v/>
@@ -16087,12 +17987,24 @@
           <t>其他電子</t>
         </is>
       </c>
-      <c r="D257" s="3" t="n"/>
-      <c r="E257" s="3" t="n"/>
-      <c r="F257" s="3" t="n"/>
-      <c r="G257" s="3" t="n"/>
-      <c r="H257" s="3" t="n"/>
-      <c r="I257" s="3" t="n"/>
+      <c r="D257" s="3" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="I257" s="3" t="n">
+        <v>20.15</v>
+      </c>
       <c r="J257" s="4">
         <f>IF(OR(D257="",G257=""),"",G257-D257)</f>
         <v/>
@@ -16105,14 +18017,24 @@
         <f>IF(OR(F257="",I257=""),"",I257-F257)</f>
         <v/>
       </c>
-      <c r="M257" s="3" t="n"/>
-      <c r="N257" s="3" t="n"/>
-      <c r="O257" s="3" t="n"/>
-      <c r="P257" s="3" t="n"/>
+      <c r="M257" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N257" s="3" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="O257" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P257" s="3" t="n">
+        <v>12.24</v>
+      </c>
       <c r="Q257" s="3" t="n">
         <v>247.5</v>
       </c>
-      <c r="R257" s="3" t="n"/>
+      <c r="R257" s="3" t="n">
+        <v>9.937099999999999</v>
+      </c>
       <c r="S257" s="3">
         <f>IF(OR(Q257="",R257="",Q257=0),"",R257/Q257*100)</f>
         <v/>
@@ -16271,9 +18193,15 @@
       <c r="F260" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="G260" s="3" t="n"/>
-      <c r="H260" s="3" t="n"/>
-      <c r="I260" s="3" t="n"/>
+      <c r="G260" s="3" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="I260" s="3" t="n">
+        <v>12.81</v>
+      </c>
       <c r="J260" s="4">
         <f>IF(OR(D260="",G260=""),"",G260-D260)</f>
         <v/>
@@ -16289,8 +18217,12 @@
       <c r="M260" s="3" t="n">
         <v>11.66</v>
       </c>
-      <c r="N260" s="3" t="n"/>
-      <c r="O260" s="3" t="n"/>
+      <c r="N260" s="3" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="O260" s="3" t="n">
+        <v>15.28</v>
+      </c>
       <c r="P260" s="3" t="n">
         <v>44.4</v>
       </c>
@@ -16321,12 +18253,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D261" s="3" t="n"/>
-      <c r="E261" s="3" t="n"/>
-      <c r="F261" s="3" t="n"/>
-      <c r="G261" s="3" t="n"/>
-      <c r="H261" s="3" t="n"/>
-      <c r="I261" s="3" t="n"/>
+      <c r="D261" s="3" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H261" s="3" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I261" s="3" t="n">
+        <v>4.24</v>
+      </c>
       <c r="J261" s="4">
         <f>IF(OR(D261="",G261=""),"",G261-D261)</f>
         <v/>
@@ -16339,14 +18283,24 @@
         <f>IF(OR(F261="",I261=""),"",I261-F261)</f>
         <v/>
       </c>
-      <c r="M261" s="3" t="n"/>
-      <c r="N261" s="3" t="n"/>
-      <c r="O261" s="3" t="n"/>
-      <c r="P261" s="3" t="n"/>
+      <c r="M261" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N261" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O261" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P261" s="3" t="n">
+        <v>16.35</v>
+      </c>
       <c r="Q261" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="R261" s="3" t="n"/>
+      <c r="R261" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="S261" s="3">
         <f>IF(OR(Q261="",R261="",Q261=0),"",R261/Q261*100)</f>
         <v/>
@@ -16413,7 +18367,9 @@
       <c r="Q262" s="3" t="n">
         <v>268</v>
       </c>
-      <c r="R262" s="3" t="n"/>
+      <c r="R262" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="S262" s="3">
         <f>IF(OR(Q262="",R262="",Q262=0),"",R262/Q262*100)</f>
         <v/>
@@ -16711,12 +18667,24 @@
           <t>通訊網路</t>
         </is>
       </c>
-      <c r="D267" s="3" t="n"/>
-      <c r="E267" s="3" t="n"/>
-      <c r="F267" s="3" t="n"/>
-      <c r="G267" s="3" t="n"/>
-      <c r="H267" s="3" t="n"/>
-      <c r="I267" s="3" t="n"/>
+      <c r="D267" s="3" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G267" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H267" s="3" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>6.05</v>
+      </c>
       <c r="J267" s="4">
         <f>IF(OR(D267="",G267=""),"",G267-D267)</f>
         <v/>
@@ -16729,14 +18697,24 @@
         <f>IF(OR(F267="",I267=""),"",I267-F267)</f>
         <v/>
       </c>
-      <c r="M267" s="3" t="n"/>
-      <c r="N267" s="3" t="n"/>
-      <c r="O267" s="3" t="n"/>
-      <c r="P267" s="3" t="n"/>
+      <c r="M267" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N267" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O267" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P267" s="3" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q267" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="R267" s="3" t="n"/>
+      <c r="R267" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S267" s="3">
         <f>IF(OR(Q267="",R267="",Q267=0),"",R267/Q267*100)</f>
         <v/>
@@ -16758,12 +18736,24 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="D268" s="3" t="n"/>
-      <c r="E268" s="3" t="n"/>
-      <c r="F268" s="3" t="n"/>
-      <c r="G268" s="3" t="n"/>
-      <c r="H268" s="3" t="n"/>
-      <c r="I268" s="3" t="n"/>
+      <c r="D268" s="3" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="G268" s="3" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="I268" s="3" t="n">
+        <v>11.31</v>
+      </c>
       <c r="J268" s="4">
         <f>IF(OR(D268="",G268=""),"",G268-D268)</f>
         <v/>
@@ -16776,14 +18766,24 @@
         <f>IF(OR(F268="",I268=""),"",I268-F268)</f>
         <v/>
       </c>
-      <c r="M268" s="3" t="n"/>
-      <c r="N268" s="3" t="n"/>
-      <c r="O268" s="3" t="n"/>
-      <c r="P268" s="3" t="n"/>
+      <c r="M268" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N268" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O268" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P268" s="3" t="n">
+        <v>15.93</v>
+      </c>
       <c r="Q268" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="R268" s="3" t="n"/>
+      <c r="R268" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="S268" s="3">
         <f>IF(OR(Q268="",R268="",Q268=0),"",R268/Q268*100)</f>
         <v/>
@@ -17006,12 +19006,24 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D272" s="3" t="n"/>
-      <c r="E272" s="3" t="n"/>
-      <c r="F272" s="3" t="n"/>
-      <c r="G272" s="3" t="n"/>
-      <c r="H272" s="3" t="n"/>
-      <c r="I272" s="3" t="n"/>
+      <c r="D272" s="3" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="G272" s="3" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="I272" s="3" t="n">
+        <v>19.85</v>
+      </c>
       <c r="J272" s="4">
         <f>IF(OR(D272="",G272=""),"",G272-D272)</f>
         <v/>
@@ -17024,14 +19036,22 @@
         <f>IF(OR(F272="",I272=""),"",I272-F272)</f>
         <v/>
       </c>
-      <c r="M272" s="3" t="n"/>
-      <c r="N272" s="3" t="n"/>
-      <c r="O272" s="3" t="n"/>
+      <c r="M272" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N272" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O272" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
         <v>59.6</v>
       </c>
-      <c r="R272" s="3" t="n"/>
+      <c r="R272" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="S272" s="3">
         <f>IF(OR(Q272="",R272="",Q272=0),"",R272/Q272*100)</f>
         <v/>
@@ -17053,12 +19073,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D273" s="3" t="n"/>
-      <c r="E273" s="3" t="n"/>
-      <c r="F273" s="3" t="n"/>
-      <c r="G273" s="3" t="n"/>
-      <c r="H273" s="3" t="n"/>
-      <c r="I273" s="3" t="n"/>
+      <c r="D273" s="3" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="G273" s="3" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="H273" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I273" s="3" t="n">
+        <v>-4.21</v>
+      </c>
       <c r="J273" s="4">
         <f>IF(OR(D273="",G273=""),"",G273-D273)</f>
         <v/>
@@ -17071,14 +19103,22 @@
         <f>IF(OR(F273="",I273=""),"",I273-F273)</f>
         <v/>
       </c>
-      <c r="M273" s="3" t="n"/>
-      <c r="N273" s="3" t="n"/>
-      <c r="O273" s="3" t="n"/>
+      <c r="M273" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="N273" s="3" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="O273" s="3" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
         <v>109.5</v>
       </c>
-      <c r="R273" s="3" t="n"/>
+      <c r="R273" s="3" t="n">
+        <v>1.08</v>
+      </c>
       <c r="S273" s="3">
         <f>IF(OR(Q273="",R273="",Q273=0),"",R273/Q273*100)</f>
         <v/>
@@ -17273,11 +19313,15 @@
       <c r="O276" s="3" t="n">
         <v>-13.93</v>
       </c>
-      <c r="P276" s="3" t="n"/>
+      <c r="P276" s="3" t="n">
+        <v>25.79</v>
+      </c>
       <c r="Q276" s="3" t="n">
         <v>32.45</v>
       </c>
-      <c r="R276" s="3" t="n"/>
+      <c r="R276" s="3" t="n">
+        <v>1.747</v>
+      </c>
       <c r="S276" s="3">
         <f>IF(OR(Q276="",R276="",Q276=0),"",R276/Q276*100)</f>
         <v/>
@@ -17433,12 +19477,24 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D279" s="3" t="n"/>
-      <c r="E279" s="3" t="n"/>
-      <c r="F279" s="3" t="n"/>
-      <c r="G279" s="3" t="n"/>
-      <c r="H279" s="3" t="n"/>
-      <c r="I279" s="3" t="n"/>
+      <c r="D279" s="3" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="G279" s="3" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="H279" s="3" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="I279" s="3" t="n">
+        <v>10.79</v>
+      </c>
       <c r="J279" s="4">
         <f>IF(OR(D279="",G279=""),"",G279-D279)</f>
         <v/>
@@ -17451,14 +19507,24 @@
         <f>IF(OR(F279="",I279=""),"",I279-F279)</f>
         <v/>
       </c>
-      <c r="M279" s="3" t="n"/>
-      <c r="N279" s="3" t="n"/>
-      <c r="O279" s="3" t="n"/>
-      <c r="P279" s="3" t="n"/>
+      <c r="M279" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N279" s="3" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O279" s="3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P279" s="3" t="n">
+        <v>12.98</v>
+      </c>
       <c r="Q279" s="3" t="n">
         <v>169.5</v>
       </c>
-      <c r="R279" s="3" t="n"/>
+      <c r="R279" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="S279" s="3">
         <f>IF(OR(Q279="",R279="",Q279=0),"",R279/Q279*100)</f>
         <v/>
@@ -17480,12 +19546,24 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="D280" s="3" t="n"/>
-      <c r="E280" s="3" t="n"/>
-      <c r="F280" s="3" t="n"/>
-      <c r="G280" s="3" t="n"/>
-      <c r="H280" s="3" t="n"/>
-      <c r="I280" s="3" t="n"/>
+      <c r="D280" s="3" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="G280" s="3" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="H280" s="3" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="I280" s="3" t="n">
+        <v>10.48</v>
+      </c>
       <c r="J280" s="4">
         <f>IF(OR(D280="",G280=""),"",G280-D280)</f>
         <v/>
@@ -17498,14 +19576,24 @@
         <f>IF(OR(F280="",I280=""),"",I280-F280)</f>
         <v/>
       </c>
-      <c r="M280" s="3" t="n"/>
-      <c r="N280" s="3" t="n"/>
-      <c r="O280" s="3" t="n"/>
-      <c r="P280" s="3" t="n"/>
+      <c r="M280" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N280" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="O280" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P280" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="Q280" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="R280" s="3" t="n"/>
+      <c r="R280" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="S280" s="3">
         <f>IF(OR(Q280="",R280="",Q280=0),"",R280/Q280*100)</f>
         <v/>
@@ -17527,12 +19615,24 @@
           <t>電機機械</t>
         </is>
       </c>
-      <c r="D281" s="3" t="n"/>
-      <c r="E281" s="3" t="n"/>
-      <c r="F281" s="3" t="n"/>
-      <c r="G281" s="3" t="n"/>
-      <c r="H281" s="3" t="n"/>
-      <c r="I281" s="3" t="n"/>
+      <c r="D281" s="3" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="E281" s="3" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="F281" s="3" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G281" s="3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="H281" s="3" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="I281" s="3" t="n">
+        <v>12.09</v>
+      </c>
       <c r="J281" s="4">
         <f>IF(OR(D281="",G281=""),"",G281-D281)</f>
         <v/>
@@ -17545,14 +19645,24 @@
         <f>IF(OR(F281="",I281=""),"",I281-F281)</f>
         <v/>
       </c>
-      <c r="M281" s="3" t="n"/>
-      <c r="N281" s="3" t="n"/>
-      <c r="O281" s="3" t="n"/>
-      <c r="P281" s="3" t="n"/>
+      <c r="M281" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N281" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O281" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="P281" s="3" t="n">
+        <v>60.42</v>
+      </c>
       <c r="Q281" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="R281" s="3" t="n"/>
+      <c r="R281" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S281" s="3">
         <f>IF(OR(Q281="",R281="",Q281=0),"",R281/Q281*100)</f>
         <v/>
@@ -17600,10 +19710,18 @@
         <f>IF(OR(F282="",I282=""),"",I282-F282)</f>
         <v/>
       </c>
-      <c r="M282" s="3" t="n"/>
-      <c r="N282" s="3" t="n"/>
-      <c r="O282" s="3" t="n"/>
-      <c r="P282" s="3" t="n"/>
+      <c r="M282" s="3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N282" s="3" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="O282" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P282" s="3" t="n">
+        <v>35.71</v>
+      </c>
       <c r="Q282" s="3" t="n">
         <v>458</v>
       </c>
@@ -17623,7 +19741,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>達明機器人</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -17631,12 +19749,24 @@
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="D283" s="3" t="n"/>
-      <c r="E283" s="3" t="n"/>
-      <c r="F283" s="3" t="n"/>
-      <c r="G283" s="3" t="n"/>
-      <c r="H283" s="3" t="n"/>
-      <c r="I283" s="3" t="n"/>
+      <c r="D283" s="3" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F283" s="3" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="G283" s="3" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="H283" s="3" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="I283" s="3" t="n">
+        <v>24.1</v>
+      </c>
       <c r="J283" s="4">
         <f>IF(OR(D283="",G283=""),"",G283-D283)</f>
         <v/>
@@ -17649,14 +19779,24 @@
         <f>IF(OR(F283="",I283=""),"",I283-F283)</f>
         <v/>
       </c>
-      <c r="M283" s="3" t="n"/>
-      <c r="N283" s="3" t="n"/>
-      <c r="O283" s="3" t="n"/>
-      <c r="P283" s="3" t="n"/>
+      <c r="M283" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N283" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O283" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P283" s="3" t="n">
+        <v>105.22</v>
+      </c>
       <c r="Q283" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="R283" s="3" t="n"/>
+      <c r="R283" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S283" s="3">
         <f>IF(OR(Q283="",R283="",Q283=0),"",R283/Q283*100)</f>
         <v/>
@@ -17747,12 +19887,24 @@
           <t>化學工業</t>
         </is>
       </c>
-      <c r="D285" s="3" t="n"/>
-      <c r="E285" s="3" t="n"/>
-      <c r="F285" s="3" t="n"/>
-      <c r="G285" s="3" t="n"/>
-      <c r="H285" s="3" t="n"/>
-      <c r="I285" s="3" t="n"/>
+      <c r="D285" s="3" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="E285" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G285" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H285" s="3" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="I285" s="3" t="n">
+        <v>10.55</v>
+      </c>
       <c r="J285" s="4">
         <f>IF(OR(D285="",G285=""),"",G285-D285)</f>
         <v/>
@@ -17765,14 +19917,24 @@
         <f>IF(OR(F285="",I285=""),"",I285-F285)</f>
         <v/>
       </c>
-      <c r="M285" s="3" t="n"/>
-      <c r="N285" s="3" t="n"/>
-      <c r="O285" s="3" t="n"/>
-      <c r="P285" s="3" t="n"/>
+      <c r="M285" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N285" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O285" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P285" s="3" t="n">
+        <v>110.95</v>
+      </c>
       <c r="Q285" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="R285" s="3" t="n"/>
+      <c r="R285" s="3" t="n">
+        <v>1.18</v>
+      </c>
       <c r="S285" s="3">
         <f>IF(OR(Q285="",R285="",Q285=0),"",R285/Q285*100)</f>
         <v/>
@@ -18053,15 +20215,27 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>化學</t>
-        </is>
-      </c>
-      <c r="D290" s="3" t="n"/>
-      <c r="E290" s="3" t="n"/>
-      <c r="F290" s="3" t="n"/>
-      <c r="G290" s="3" t="n"/>
-      <c r="H290" s="3" t="n"/>
-      <c r="I290" s="3" t="n"/>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G290" s="3" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="H290" s="3" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="I290" s="3" t="n">
+        <v>11.32</v>
+      </c>
       <c r="J290" s="4">
         <f>IF(OR(D290="",G290=""),"",G290-D290)</f>
         <v/>
@@ -18074,14 +20248,24 @@
         <f>IF(OR(F290="",I290=""),"",I290-F290)</f>
         <v/>
       </c>
-      <c r="M290" s="3" t="n"/>
-      <c r="N290" s="3" t="n"/>
-      <c r="O290" s="3" t="n"/>
-      <c r="P290" s="3" t="n"/>
+      <c r="M290" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N290" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O290" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P290" s="3" t="n">
+        <v>66.61</v>
+      </c>
       <c r="Q290" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="R290" s="3" t="n"/>
+      <c r="R290" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S290" s="3">
         <f>IF(OR(Q290="",R290="",Q290=0),"",R290/Q290*100)</f>
         <v/>
@@ -18446,12 +20630,24 @@
           <t>通訊網路</t>
         </is>
       </c>
-      <c r="D296" s="3" t="n"/>
-      <c r="E296" s="3" t="n"/>
-      <c r="F296" s="3" t="n"/>
-      <c r="G296" s="3" t="n"/>
-      <c r="H296" s="3" t="n"/>
-      <c r="I296" s="3" t="n"/>
+      <c r="D296" s="3" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="G296" s="3" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="H296" s="3" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="I296" s="3" t="n">
+        <v>-0.87</v>
+      </c>
       <c r="J296" s="4">
         <f>IF(OR(D296="",G296=""),"",G296-D296)</f>
         <v/>
@@ -18464,14 +20660,24 @@
         <f>IF(OR(F296="",I296=""),"",I296-F296)</f>
         <v/>
       </c>
-      <c r="M296" s="3" t="n"/>
-      <c r="N296" s="3" t="n"/>
-      <c r="O296" s="3" t="n"/>
-      <c r="P296" s="3" t="n"/>
+      <c r="M296" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="N296" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="O296" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P296" s="3" t="n">
+        <v>283.33</v>
+      </c>
       <c r="Q296" s="3" t="n">
         <v>34.55</v>
       </c>
-      <c r="R296" s="3" t="n"/>
+      <c r="R296" s="3" t="n">
+        <v>0.47</v>
+      </c>
       <c r="S296" s="3">
         <f>IF(OR(Q296="",R296="",Q296=0),"",R296/Q296*100)</f>
         <v/>
@@ -18493,12 +20699,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D297" s="3" t="n"/>
-      <c r="E297" s="3" t="n"/>
-      <c r="F297" s="3" t="n"/>
-      <c r="G297" s="3" t="n"/>
-      <c r="H297" s="3" t="n"/>
-      <c r="I297" s="3" t="n"/>
+      <c r="D297" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E297" s="3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G297" s="3" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="H297" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I297" s="3" t="n">
+        <v>3.37</v>
+      </c>
       <c r="J297" s="4">
         <f>IF(OR(D297="",G297=""),"",G297-D297)</f>
         <v/>
@@ -18511,14 +20729,24 @@
         <f>IF(OR(F297="",I297=""),"",I297-F297)</f>
         <v/>
       </c>
-      <c r="M297" s="3" t="n"/>
-      <c r="N297" s="3" t="n"/>
-      <c r="O297" s="3" t="n"/>
-      <c r="P297" s="3" t="n"/>
+      <c r="M297" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N297" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O297" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P297" s="3" t="n">
+        <v>12.22</v>
+      </c>
       <c r="Q297" s="3" t="n">
         <v>59.8</v>
       </c>
-      <c r="R297" s="3" t="n"/>
+      <c r="R297" s="3" t="n">
+        <v>4.57</v>
+      </c>
       <c r="S297" s="3">
         <f>IF(OR(Q297="",R297="",Q297=0),"",R297/Q297*100)</f>
         <v/>
@@ -18944,12 +21172,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D304" s="3" t="n"/>
-      <c r="E304" s="3" t="n"/>
-      <c r="F304" s="3" t="n"/>
-      <c r="G304" s="3" t="n"/>
-      <c r="H304" s="3" t="n"/>
-      <c r="I304" s="3" t="n"/>
+      <c r="D304" s="3" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="G304" s="3" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="H304" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I304" s="3" t="n">
+        <v>31.79</v>
+      </c>
       <c r="J304" s="4">
         <f>IF(OR(D304="",G304=""),"",G304-D304)</f>
         <v/>
@@ -18962,14 +21202,24 @@
         <f>IF(OR(F304="",I304=""),"",I304-F304)</f>
         <v/>
       </c>
-      <c r="M304" s="3" t="n"/>
-      <c r="N304" s="3" t="n"/>
-      <c r="O304" s="3" t="n"/>
-      <c r="P304" s="3" t="n"/>
+      <c r="M304" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="N304" s="3" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="O304" s="3" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="P304" s="3" t="n">
+        <v>4.13</v>
+      </c>
       <c r="Q304" s="3" t="n">
         <v>272.5</v>
       </c>
-      <c r="R304" s="3" t="n"/>
+      <c r="R304" s="3" t="n">
+        <v>3.45</v>
+      </c>
       <c r="S304" s="3">
         <f>IF(OR(Q304="",R304="",Q304=0),"",R304/Q304*100)</f>
         <v/>
@@ -19487,7 +21737,9 @@
       <c r="Q312" s="3" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="R312" s="3" t="n"/>
+      <c r="R312" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="S312" s="3">
         <f>IF(OR(Q312="",R312="",Q312=0),"",R312/Q312*100)</f>
         <v/>
@@ -19647,9 +21899,15 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="D315" s="3" t="n"/>
-      <c r="E315" s="3" t="n"/>
-      <c r="F315" s="3" t="n"/>
+      <c r="D315" s="3" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="F315" s="3" t="n">
+        <v>18.41</v>
+      </c>
       <c r="G315" s="3" t="n"/>
       <c r="H315" s="3" t="n"/>
       <c r="I315" s="3" t="n"/>
@@ -19665,14 +21923,20 @@
         <f>IF(OR(F315="",I315=""),"",I315-F315)</f>
         <v/>
       </c>
-      <c r="M315" s="3" t="n"/>
+      <c r="M315" s="3" t="n">
+        <v>4.13</v>
+      </c>
       <c r="N315" s="3" t="n"/>
       <c r="O315" s="3" t="n"/>
-      <c r="P315" s="3" t="n"/>
+      <c r="P315" s="3" t="n">
+        <v>23.77</v>
+      </c>
       <c r="Q315" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="R315" s="3" t="n"/>
+      <c r="R315" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="S315" s="3">
         <f>IF(OR(Q315="",R315="",Q315=0),"",R315/Q315*100)</f>
         <v/>
@@ -20458,9 +22722,15 @@
       <c r="F327" s="3" t="n">
         <v>6.72</v>
       </c>
-      <c r="G327" s="3" t="n"/>
-      <c r="H327" s="3" t="n"/>
-      <c r="I327" s="3" t="n"/>
+      <c r="G327" s="3" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="H327" s="3" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="I327" s="3" t="n">
+        <v>3.45</v>
+      </c>
       <c r="J327" s="4">
         <f>IF(OR(D327="",G327=""),"",G327-D327)</f>
         <v/>
@@ -20476,13 +22746,21 @@
       <c r="M327" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="N327" s="3" t="n"/>
-      <c r="O327" s="3" t="n"/>
-      <c r="P327" s="3" t="n"/>
+      <c r="N327" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O327" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P327" s="3" t="n">
+        <v>13.07</v>
+      </c>
       <c r="Q327" s="3" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="R327" s="3" t="n"/>
+      <c r="R327" s="3" t="n">
+        <v>2.52</v>
+      </c>
       <c r="S327" s="3">
         <f>IF(OR(Q327="",R327="",Q327=0),"",R327/Q327*100)</f>
         <v/>
@@ -20501,7 +22779,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電子零組件</t>
         </is>
       </c>
       <c r="D328" s="3" t="n">
@@ -20571,12 +22849,24 @@
           <t>櫃文化創意</t>
         </is>
       </c>
-      <c r="D329" s="3" t="n"/>
-      <c r="E329" s="3" t="n"/>
-      <c r="F329" s="3" t="n"/>
-      <c r="G329" s="3" t="n"/>
-      <c r="H329" s="3" t="n"/>
-      <c r="I329" s="3" t="n"/>
+      <c r="D329" s="3" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="F329" s="3" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="G329" s="3" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="H329" s="3" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="I329" s="3" t="n">
+        <v>21.06</v>
+      </c>
       <c r="J329" s="4">
         <f>IF(OR(D329="",G329=""),"",G329-D329)</f>
         <v/>
@@ -20589,14 +22879,24 @@
         <f>IF(OR(F329="",I329=""),"",I329-F329)</f>
         <v/>
       </c>
-      <c r="M329" s="3" t="n"/>
-      <c r="N329" s="3" t="n"/>
-      <c r="O329" s="3" t="n"/>
-      <c r="P329" s="3" t="n"/>
+      <c r="M329" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N329" s="3" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="O329" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P329" s="3" t="n">
+        <v>12.16</v>
+      </c>
       <c r="Q329" s="3" t="n">
         <v>98.8</v>
       </c>
-      <c r="R329" s="3" t="n"/>
+      <c r="R329" s="3" t="n">
+        <v>7.5</v>
+      </c>
       <c r="S329" s="3">
         <f>IF(OR(Q329="",R329="",Q329=0),"",R329/Q329*100)</f>
         <v/>
@@ -20732,7 +23032,9 @@
       <c r="Q331" s="3" t="n">
         <v>63.7</v>
       </c>
-      <c r="R331" s="3" t="n"/>
+      <c r="R331" s="3" t="n">
+        <v>5.5</v>
+      </c>
       <c r="S331" s="3">
         <f>IF(OR(Q331="",R331="",Q331=0),"",R331/Q331*100)</f>
         <v/>
@@ -20821,12 +23123,24 @@
           <t>營建</t>
         </is>
       </c>
-      <c r="D333" s="3" t="n"/>
-      <c r="E333" s="3" t="n"/>
-      <c r="F333" s="3" t="n"/>
-      <c r="G333" s="3" t="n"/>
-      <c r="H333" s="3" t="n"/>
-      <c r="I333" s="3" t="n"/>
+      <c r="D333" s="3" t="n">
+        <v>63.09</v>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="F333" s="3" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G333" s="3" t="n">
+        <v>30.42</v>
+      </c>
+      <c r="H333" s="3" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="I333" s="3" t="n">
+        <v>18.48</v>
+      </c>
       <c r="J333" s="4">
         <f>IF(OR(D333="",G333=""),"",G333-D333)</f>
         <v/>
@@ -20839,14 +23153,24 @@
         <f>IF(OR(F333="",I333=""),"",I333-F333)</f>
         <v/>
       </c>
-      <c r="M333" s="3" t="n"/>
-      <c r="N333" s="3" t="n"/>
-      <c r="O333" s="3" t="n"/>
-      <c r="P333" s="3" t="n"/>
+      <c r="M333" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N333" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O333" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P333" s="3" t="n">
+        <v>13.42</v>
+      </c>
       <c r="Q333" s="3" t="n">
         <v>75.3</v>
       </c>
-      <c r="R333" s="3" t="n"/>
+      <c r="R333" s="3" t="n">
+        <v>5.06</v>
+      </c>
       <c r="S333" s="3">
         <f>IF(OR(Q333="",R333="",Q333=0),"",R333/Q333*100)</f>
         <v/>
@@ -20937,12 +23261,24 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="D335" s="3" t="n"/>
-      <c r="E335" s="3" t="n"/>
-      <c r="F335" s="3" t="n"/>
-      <c r="G335" s="3" t="n"/>
-      <c r="H335" s="3" t="n"/>
-      <c r="I335" s="3" t="n"/>
+      <c r="D335" s="3" t="n">
+        <v>48.39</v>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="F335" s="3" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="G335" s="3" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H335" s="3" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="I335" s="3" t="n">
+        <v>32.46</v>
+      </c>
       <c r="J335" s="4">
         <f>IF(OR(D335="",G335=""),"",G335-D335)</f>
         <v/>
@@ -20955,14 +23291,24 @@
         <f>IF(OR(F335="",I335=""),"",I335-F335)</f>
         <v/>
       </c>
-      <c r="M335" s="3" t="n"/>
-      <c r="N335" s="3" t="n"/>
-      <c r="O335" s="3" t="n"/>
-      <c r="P335" s="3" t="n"/>
+      <c r="M335" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N335" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O335" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P335" s="3" t="n">
+        <v>15.21</v>
+      </c>
       <c r="Q335" s="3" t="n">
         <v>53.9</v>
       </c>
-      <c r="R335" s="3" t="n"/>
+      <c r="R335" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="S335" s="3">
         <f>IF(OR(Q335="",R335="",Q335=0),"",R335/Q335*100)</f>
         <v/>
@@ -21008,9 +23354,15 @@
         <f>IF(OR(F336="",I336=""),"",I336-F336)</f>
         <v/>
       </c>
-      <c r="M336" s="3" t="n"/>
-      <c r="N336" s="3" t="n"/>
-      <c r="O336" s="3" t="n"/>
+      <c r="M336" s="3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N336" s="3" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="O336" s="3" t="n">
+        <v>2.58</v>
+      </c>
       <c r="P336" s="3" t="n">
         <v>10.44</v>
       </c>
@@ -21179,12 +23531,24 @@
           <t>光電業</t>
         </is>
       </c>
-      <c r="D339" s="3" t="n"/>
-      <c r="E339" s="3" t="n"/>
-      <c r="F339" s="3" t="n"/>
-      <c r="G339" s="3" t="n"/>
-      <c r="H339" s="3" t="n"/>
-      <c r="I339" s="3" t="n"/>
+      <c r="D339" s="3" t="n">
+        <v>-10.81</v>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>-23.43</v>
+      </c>
+      <c r="F339" s="3" t="n">
+        <v>-25.17</v>
+      </c>
+      <c r="G339" s="3" t="n">
+        <v>-5.55</v>
+      </c>
+      <c r="H339" s="3" t="n">
+        <v>-19.44</v>
+      </c>
+      <c r="I339" s="3" t="n">
+        <v>4.46</v>
+      </c>
       <c r="J339" s="4">
         <f>IF(OR(D339="",G339=""),"",G339-D339)</f>
         <v/>
@@ -21197,9 +23561,15 @@
         <f>IF(OR(F339="",I339=""),"",I339-F339)</f>
         <v/>
       </c>
-      <c r="M339" s="3" t="n"/>
-      <c r="N339" s="3" t="n"/>
-      <c r="O339" s="3" t="n"/>
+      <c r="M339" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="N339" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O339" s="3" t="n">
+        <v>0.04</v>
+      </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
         <v>14.1</v>
@@ -21640,12 +24010,24 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="D346" s="3" t="n"/>
-      <c r="E346" s="3" t="n"/>
-      <c r="F346" s="3" t="n"/>
-      <c r="G346" s="3" t="n"/>
-      <c r="H346" s="3" t="n"/>
-      <c r="I346" s="3" t="n"/>
+      <c r="D346" s="3" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="F346" s="3" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="G346" s="3" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="H346" s="3" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I346" s="3" t="n">
+        <v>-0.66</v>
+      </c>
       <c r="J346" s="4">
         <f>IF(OR(D346="",G346=""),"",G346-D346)</f>
         <v/>
@@ -21658,14 +24040,24 @@
         <f>IF(OR(F346="",I346=""),"",I346-F346)</f>
         <v/>
       </c>
-      <c r="M346" s="3" t="n"/>
-      <c r="N346" s="3" t="n"/>
-      <c r="O346" s="3" t="n"/>
-      <c r="P346" s="3" t="n"/>
+      <c r="M346" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N346" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O346" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P346" s="3" t="n">
+        <v>22.62</v>
+      </c>
       <c r="Q346" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="R346" s="3" t="n"/>
+      <c r="R346" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="S346" s="3">
         <f>IF(OR(Q346="",R346="",Q346=0),"",R346/Q346*100)</f>
         <v/>
@@ -21687,12 +24079,24 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D347" s="3" t="n"/>
-      <c r="E347" s="3" t="n"/>
-      <c r="F347" s="3" t="n"/>
-      <c r="G347" s="3" t="n"/>
-      <c r="H347" s="3" t="n"/>
-      <c r="I347" s="3" t="n"/>
+      <c r="D347" s="3" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="E347" s="3" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="F347" s="3" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="G347" s="3" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="H347" s="3" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="I347" s="3" t="n">
+        <v>22.28</v>
+      </c>
       <c r="J347" s="4">
         <f>IF(OR(D347="",G347=""),"",G347-D347)</f>
         <v/>
@@ -21705,14 +24109,24 @@
         <f>IF(OR(F347="",I347=""),"",I347-F347)</f>
         <v/>
       </c>
-      <c r="M347" s="3" t="n"/>
-      <c r="N347" s="3" t="n"/>
-      <c r="O347" s="3" t="n"/>
-      <c r="P347" s="3" t="n"/>
+      <c r="M347" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N347" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O347" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P347" s="3" t="n">
+        <v>38.27</v>
+      </c>
       <c r="Q347" s="3" t="n">
         <v>203.5</v>
       </c>
-      <c r="R347" s="3" t="n"/>
+      <c r="R347" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="S347" s="3">
         <f>IF(OR(Q347="",R347="",Q347=0),"",R347/Q347*100)</f>
         <v/>
@@ -21905,8 +24319,12 @@
       <c r="M350" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N350" s="3" t="n"/>
-      <c r="O350" s="3" t="n"/>
+      <c r="N350" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O350" s="3" t="n">
+        <v>0.05</v>
+      </c>
       <c r="P350" s="3" t="n">
         <v>2787.5</v>
       </c>
@@ -22075,12 +24493,24 @@
           <t>櫃通訊網路</t>
         </is>
       </c>
-      <c r="D353" s="3" t="n"/>
-      <c r="E353" s="3" t="n"/>
-      <c r="F353" s="3" t="n"/>
-      <c r="G353" s="3" t="n"/>
-      <c r="H353" s="3" t="n"/>
-      <c r="I353" s="3" t="n"/>
+      <c r="D353" s="3" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="E353" s="3" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="F353" s="3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G353" s="3" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="H353" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I353" s="3" t="n">
+        <v>6.24</v>
+      </c>
       <c r="J353" s="4">
         <f>IF(OR(D353="",G353=""),"",G353-D353)</f>
         <v/>
@@ -22093,14 +24523,24 @@
         <f>IF(OR(F353="",I353=""),"",I353-F353)</f>
         <v/>
       </c>
-      <c r="M353" s="3" t="n"/>
-      <c r="N353" s="3" t="n"/>
-      <c r="O353" s="3" t="n"/>
-      <c r="P353" s="3" t="n"/>
+      <c r="M353" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N353" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O353" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P353" s="3" t="n">
+        <v>26.68</v>
+      </c>
       <c r="Q353" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="R353" s="3" t="n"/>
+      <c r="R353" s="3" t="n">
+        <v>1.93</v>
+      </c>
       <c r="S353" s="3">
         <f>IF(OR(Q353="",R353="",Q353=0),"",R353/Q353*100)</f>
         <v/>
@@ -22258,12 +24698,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D356" s="3" t="n"/>
-      <c r="E356" s="3" t="n"/>
-      <c r="F356" s="3" t="n"/>
-      <c r="G356" s="3" t="n"/>
-      <c r="H356" s="3" t="n"/>
-      <c r="I356" s="3" t="n"/>
+      <c r="D356" s="3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E356" s="3" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="F356" s="3" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="G356" s="3" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="H356" s="3" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="I356" s="3" t="n">
+        <v>19.09</v>
+      </c>
       <c r="J356" s="4">
         <f>IF(OR(D356="",G356=""),"",G356-D356)</f>
         <v/>
@@ -22276,14 +24728,24 @@
         <f>IF(OR(F356="",I356=""),"",I356-F356)</f>
         <v/>
       </c>
-      <c r="M356" s="3" t="n"/>
-      <c r="N356" s="3" t="n"/>
-      <c r="O356" s="3" t="n"/>
-      <c r="P356" s="3" t="n"/>
+      <c r="M356" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N356" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O356" s="3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="P356" s="3" t="n">
+        <v>25.23</v>
+      </c>
       <c r="Q356" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="R356" s="3" t="n"/>
+      <c r="R356" s="3" t="n">
+        <v>6.92</v>
+      </c>
       <c r="S356" s="3">
         <f>IF(OR(Q356="",R356="",Q356=0),"",R356/Q356*100)</f>
         <v/>
@@ -22374,12 +24836,24 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="D358" s="3" t="n"/>
-      <c r="E358" s="3" t="n"/>
-      <c r="F358" s="3" t="n"/>
-      <c r="G358" s="3" t="n"/>
-      <c r="H358" s="3" t="n"/>
-      <c r="I358" s="3" t="n"/>
+      <c r="D358" s="3" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="E358" s="3" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F358" s="3" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="G358" s="3" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="H358" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I358" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="J358" s="4">
         <f>IF(OR(D358="",G358=""),"",G358-D358)</f>
         <v/>
@@ -22392,14 +24866,24 @@
         <f>IF(OR(F358="",I358=""),"",I358-F358)</f>
         <v/>
       </c>
-      <c r="M358" s="3" t="n"/>
-      <c r="N358" s="3" t="n"/>
-      <c r="O358" s="3" t="n"/>
-      <c r="P358" s="3" t="n"/>
+      <c r="M358" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N358" s="3" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="O358" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P358" s="3" t="n">
+        <v>16.24</v>
+      </c>
       <c r="Q358" s="3" t="n">
         <v>139.5</v>
       </c>
-      <c r="R358" s="3" t="n"/>
+      <c r="R358" s="3" t="n">
+        <v>5.5</v>
+      </c>
       <c r="S358" s="3">
         <f>IF(OR(Q358="",R358="",Q358=0),"",R358/Q358*100)</f>
         <v/>
@@ -22490,9 +24974,15 @@
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="D360" s="3" t="n"/>
-      <c r="E360" s="3" t="n"/>
-      <c r="F360" s="3" t="n"/>
+      <c r="D360" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="F360" s="3" t="n">
+        <v>6.47</v>
+      </c>
       <c r="G360" s="3" t="n"/>
       <c r="H360" s="3" t="n"/>
       <c r="I360" s="3" t="n"/>
@@ -22508,14 +24998,24 @@
         <f>IF(OR(F360="",I360=""),"",I360-F360)</f>
         <v/>
       </c>
-      <c r="M360" s="3" t="n"/>
-      <c r="N360" s="3" t="n"/>
-      <c r="O360" s="3" t="n"/>
-      <c r="P360" s="3" t="n"/>
+      <c r="M360" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N360" s="3" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O360" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P360" s="3" t="n">
+        <v>16.75</v>
+      </c>
       <c r="Q360" s="3" t="n">
         <v>181.5</v>
       </c>
-      <c r="R360" s="3" t="n"/>
+      <c r="R360" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="S360" s="3">
         <f>IF(OR(Q360="",R360="",Q360=0),"",R360/Q360*100)</f>
         <v/>
@@ -22647,7 +25147,9 @@
       <c r="Q362" s="3" t="n">
         <v>5600</v>
       </c>
-      <c r="R362" s="3" t="n"/>
+      <c r="R362" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="S362" s="3">
         <f>IF(OR(Q362="",R362="",Q362=0),"",R362/Q362*100)</f>
         <v/>
@@ -22708,7 +25210,9 @@
       <c r="O363" s="3" t="n">
         <v>2.99</v>
       </c>
-      <c r="P363" s="3" t="n"/>
+      <c r="P363" s="3" t="n">
+        <v>26.53</v>
+      </c>
       <c r="Q363" s="3" t="n">
         <v>273.5</v>
       </c>
@@ -22803,9 +25307,15 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D365" s="3" t="n"/>
-      <c r="E365" s="3" t="n"/>
-      <c r="F365" s="3" t="n"/>
+      <c r="D365" s="3" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E365" s="3" t="n">
+        <v>-18.29</v>
+      </c>
+      <c r="F365" s="3" t="n">
+        <v>-14.95</v>
+      </c>
       <c r="G365" s="3" t="n"/>
       <c r="H365" s="3" t="n"/>
       <c r="I365" s="3" t="n"/>
@@ -22821,7 +25331,9 @@
         <f>IF(OR(F365="",I365=""),"",I365-F365)</f>
         <v/>
       </c>
-      <c r="M365" s="3" t="n"/>
+      <c r="M365" s="3" t="n">
+        <v>-2.6</v>
+      </c>
       <c r="N365" s="3" t="n"/>
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
@@ -22850,12 +25362,24 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D366" s="3" t="n"/>
-      <c r="E366" s="3" t="n"/>
-      <c r="F366" s="3" t="n"/>
-      <c r="G366" s="3" t="n"/>
-      <c r="H366" s="3" t="n"/>
-      <c r="I366" s="3" t="n"/>
+      <c r="D366" s="3" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="F366" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G366" s="3" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="H366" s="3" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="I366" s="3" t="n">
+        <v>16.53</v>
+      </c>
       <c r="J366" s="4">
         <f>IF(OR(D366="",G366=""),"",G366-D366)</f>
         <v/>
@@ -22868,14 +25392,24 @@
         <f>IF(OR(F366="",I366=""),"",I366-F366)</f>
         <v/>
       </c>
-      <c r="M366" s="3" t="n"/>
-      <c r="N366" s="3" t="n"/>
-      <c r="O366" s="3" t="n"/>
-      <c r="P366" s="3" t="n"/>
+      <c r="M366" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N366" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O366" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P366" s="3" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Q366" s="3" t="n">
         <v>199.5</v>
       </c>
-      <c r="R366" s="3" t="n"/>
+      <c r="R366" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="S366" s="3">
         <f>IF(OR(Q366="",R366="",Q366=0),"",R366/Q366*100)</f>
         <v/>
@@ -22938,7 +25472,9 @@
       <c r="Q367" s="3" t="n">
         <v>1485</v>
       </c>
-      <c r="R367" s="3" t="n"/>
+      <c r="R367" s="3" t="n">
+        <v>7.5066</v>
+      </c>
       <c r="S367" s="3">
         <f>IF(OR(Q367="",R367="",Q367=0),"",R367/Q367*100)</f>
         <v/>
@@ -22960,12 +25496,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D368" s="3" t="n"/>
-      <c r="E368" s="3" t="n"/>
-      <c r="F368" s="3" t="n"/>
-      <c r="G368" s="3" t="n"/>
-      <c r="H368" s="3" t="n"/>
-      <c r="I368" s="3" t="n"/>
+      <c r="D368" s="3" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E368" s="3" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="F368" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G368" s="3" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="H368" s="3" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I368" s="3" t="n">
+        <v>6.05</v>
+      </c>
       <c r="J368" s="4">
         <f>IF(OR(D368="",G368=""),"",G368-D368)</f>
         <v/>
@@ -22978,14 +25526,24 @@
         <f>IF(OR(F368="",I368=""),"",I368-F368)</f>
         <v/>
       </c>
-      <c r="M368" s="3" t="n"/>
-      <c r="N368" s="3" t="n"/>
-      <c r="O368" s="3" t="n"/>
-      <c r="P368" s="3" t="n"/>
+      <c r="M368" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N368" s="3" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="O368" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P368" s="3" t="n">
+        <v>19.07</v>
+      </c>
       <c r="Q368" s="3" t="n">
         <v>181.5</v>
       </c>
-      <c r="R368" s="3" t="n"/>
+      <c r="R368" s="3" t="n">
+        <v>5.565</v>
+      </c>
       <c r="S368" s="3">
         <f>IF(OR(Q368="",R368="",Q368=0),"",R368/Q368*100)</f>
         <v/>
@@ -23007,9 +25565,15 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D369" s="3" t="n"/>
-      <c r="E369" s="3" t="n"/>
-      <c r="F369" s="3" t="n"/>
+      <c r="D369" s="3" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="E369" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F369" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="G369" s="3" t="n"/>
       <c r="H369" s="3" t="n"/>
       <c r="I369" s="3" t="n"/>
@@ -23025,14 +25589,20 @@
         <f>IF(OR(F369="",I369=""),"",I369-F369)</f>
         <v/>
       </c>
-      <c r="M369" s="3" t="n"/>
+      <c r="M369" s="3" t="n">
+        <v>0.27</v>
+      </c>
       <c r="N369" s="3" t="n"/>
       <c r="O369" s="3" t="n"/>
-      <c r="P369" s="3" t="n"/>
+      <c r="P369" s="3" t="n">
+        <v>36.58</v>
+      </c>
       <c r="Q369" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="R369" s="3" t="n"/>
+      <c r="R369" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="S369" s="3">
         <f>IF(OR(Q369="",R369="",Q369=0),"",R369/Q369*100)</f>
         <v/>
@@ -23099,7 +25669,9 @@
       <c r="Q370" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="R370" s="3" t="n"/>
+      <c r="R370" s="3" t="n">
+        <v>1.8896</v>
+      </c>
       <c r="S370" s="3">
         <f>IF(OR(Q370="",R370="",Q370=0),"",R370/Q370*100)</f>
         <v/>
@@ -23166,7 +25738,9 @@
       <c r="Q371" s="3" t="n">
         <v>233.5</v>
       </c>
-      <c r="R371" s="3" t="n"/>
+      <c r="R371" s="3" t="n">
+        <v>4.3</v>
+      </c>
       <c r="S371" s="3">
         <f>IF(OR(Q371="",R371="",Q371=0),"",R371/Q371*100)</f>
         <v/>
@@ -23371,7 +25945,9 @@
       <c r="Q374" s="3" t="n">
         <v>1020</v>
       </c>
-      <c r="R374" s="3" t="n"/>
+      <c r="R374" s="3" t="n">
+        <v>36.7702</v>
+      </c>
       <c r="S374" s="3">
         <f>IF(OR(Q374="",R374="",Q374=0),"",R374/Q374*100)</f>
         <v/>
@@ -23635,7 +26211,9 @@
       <c r="Q378" s="3" t="n">
         <v>1605</v>
       </c>
-      <c r="R378" s="3" t="n"/>
+      <c r="R378" s="3" t="n">
+        <v>11.2587</v>
+      </c>
       <c r="S378" s="3">
         <f>IF(OR(Q378="",R378="",Q378=0),"",R378/Q378*100)</f>
         <v/>
@@ -23657,12 +26235,24 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="D379" s="3" t="n"/>
-      <c r="E379" s="3" t="n"/>
-      <c r="F379" s="3" t="n"/>
-      <c r="G379" s="3" t="n"/>
-      <c r="H379" s="3" t="n"/>
-      <c r="I379" s="3" t="n"/>
+      <c r="D379" s="3" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="E379" s="3" t="n">
+        <v>-18.79</v>
+      </c>
+      <c r="F379" s="3" t="n">
+        <v>-24.78</v>
+      </c>
+      <c r="G379" s="3" t="n">
+        <v>-53.3</v>
+      </c>
+      <c r="H379" s="3" t="n">
+        <v>-82.93000000000001</v>
+      </c>
+      <c r="I379" s="3" t="n">
+        <v>-77.01000000000001</v>
+      </c>
       <c r="J379" s="4">
         <f>IF(OR(D379="",G379=""),"",G379-D379)</f>
         <v/>
@@ -23675,9 +26265,15 @@
         <f>IF(OR(F379="",I379=""),"",I379-F379)</f>
         <v/>
       </c>
-      <c r="M379" s="3" t="n"/>
-      <c r="N379" s="3" t="n"/>
-      <c r="O379" s="3" t="n"/>
+      <c r="M379" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N379" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O379" s="3" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
         <v>26.45</v>
@@ -23842,9 +26438,15 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D382" s="3" t="n"/>
-      <c r="E382" s="3" t="n"/>
-      <c r="F382" s="3" t="n"/>
+      <c r="D382" s="3" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="E382" s="3" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="F382" s="3" t="n">
+        <v>-9.48</v>
+      </c>
       <c r="G382" s="3" t="n"/>
       <c r="H382" s="3" t="n"/>
       <c r="I382" s="3" t="n"/>
@@ -23860,14 +26462,18 @@
         <f>IF(OR(F382="",I382=""),"",I382-F382)</f>
         <v/>
       </c>
-      <c r="M382" s="3" t="n"/>
+      <c r="M382" s="3" t="n">
+        <v>-1.45</v>
+      </c>
       <c r="N382" s="3" t="n"/>
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
         <v>423</v>
       </c>
-      <c r="R382" s="3" t="n"/>
+      <c r="R382" s="3" t="n">
+        <v>0.2177</v>
+      </c>
       <c r="S382" s="3">
         <f>IF(OR(Q382="",R382="",Q382=0),"",R382/Q382*100)</f>
         <v/>
@@ -23954,12 +26560,24 @@
           <t>生技醫療業</t>
         </is>
       </c>
-      <c r="D384" s="3" t="n"/>
-      <c r="E384" s="3" t="n"/>
-      <c r="F384" s="3" t="n"/>
-      <c r="G384" s="3" t="n"/>
-      <c r="H384" s="3" t="n"/>
-      <c r="I384" s="3" t="n"/>
+      <c r="D384" s="3" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="E384" s="3" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="F384" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G384" s="3" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="H384" s="3" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="I384" s="3" t="n">
+        <v>13.05</v>
+      </c>
       <c r="J384" s="4">
         <f>IF(OR(D384="",G384=""),"",G384-D384)</f>
         <v/>
@@ -23972,14 +26590,24 @@
         <f>IF(OR(F384="",I384=""),"",I384-F384)</f>
         <v/>
       </c>
-      <c r="M384" s="3" t="n"/>
-      <c r="N384" s="3" t="n"/>
-      <c r="O384" s="3" t="n"/>
-      <c r="P384" s="3" t="n"/>
+      <c r="M384" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N384" s="3" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="O384" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="P384" s="3" t="n">
+        <v>37.51</v>
+      </c>
       <c r="Q384" s="3" t="n">
         <v>470</v>
       </c>
-      <c r="R384" s="3" t="n"/>
+      <c r="R384" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="S384" s="3">
         <f>IF(OR(Q384="",R384="",Q384=0),"",R384/Q384*100)</f>
         <v/>
@@ -24070,12 +26698,24 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="D386" s="3" t="n"/>
-      <c r="E386" s="3" t="n"/>
-      <c r="F386" s="3" t="n"/>
-      <c r="G386" s="3" t="n"/>
-      <c r="H386" s="3" t="n"/>
-      <c r="I386" s="3" t="n"/>
+      <c r="D386" s="3" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="E386" s="3" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="F386" s="3" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="G386" s="3" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="H386" s="3" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="I386" s="3" t="n">
+        <v>25.97</v>
+      </c>
       <c r="J386" s="4">
         <f>IF(OR(D386="",G386=""),"",G386-D386)</f>
         <v/>
@@ -24088,10 +26728,14 @@
         <f>IF(OR(F386="",I386=""),"",I386-F386)</f>
         <v/>
       </c>
-      <c r="M386" s="3" t="n"/>
+      <c r="M386" s="3" t="n">
+        <v>6.06</v>
+      </c>
       <c r="N386" s="3" t="n"/>
       <c r="O386" s="3" t="n"/>
-      <c r="P386" s="3" t="n"/>
+      <c r="P386" s="3" t="n">
+        <v>15.51</v>
+      </c>
       <c r="Q386" s="3" t="n">
         <v>372.5</v>
       </c>
@@ -24326,9 +26970,15 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D390" s="3" t="n"/>
-      <c r="E390" s="3" t="n"/>
-      <c r="F390" s="3" t="n"/>
+      <c r="D390" s="3" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="E390" s="3" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="F390" s="3" t="n">
+        <v>15.38</v>
+      </c>
       <c r="G390" s="3" t="n"/>
       <c r="H390" s="3" t="n"/>
       <c r="I390" s="3" t="n"/>
@@ -24344,14 +26994,20 @@
         <f>IF(OR(F390="",I390=""),"",I390-F390)</f>
         <v/>
       </c>
-      <c r="M390" s="3" t="n"/>
+      <c r="M390" s="3" t="n">
+        <v>1.62</v>
+      </c>
       <c r="N390" s="3" t="n"/>
       <c r="O390" s="3" t="n"/>
-      <c r="P390" s="3" t="n"/>
+      <c r="P390" s="3" t="n">
+        <v>19.19</v>
+      </c>
       <c r="Q390" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="R390" s="3" t="n"/>
+      <c r="R390" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="S390" s="3">
         <f>IF(OR(Q390="",R390="",Q390=0),"",R390/Q390*100)</f>
         <v/>
@@ -24751,7 +27407,9 @@
       <c r="Q396" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="R396" s="3" t="n"/>
+      <c r="R396" s="3" t="n">
+        <v>7.6988</v>
+      </c>
       <c r="S396" s="3">
         <f>IF(OR(Q396="",R396="",Q396=0),"",R396/Q396*100)</f>
         <v/>
@@ -24773,9 +27431,15 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D397" s="3" t="n"/>
-      <c r="E397" s="3" t="n"/>
-      <c r="F397" s="3" t="n"/>
+      <c r="D397" s="3" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="E397" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F397" s="3" t="n">
+        <v>21.61</v>
+      </c>
       <c r="G397" s="3" t="n"/>
       <c r="H397" s="3" t="n"/>
       <c r="I397" s="3" t="n"/>
@@ -24791,14 +27455,24 @@
         <f>IF(OR(F397="",I397=""),"",I397-F397)</f>
         <v/>
       </c>
-      <c r="M397" s="3" t="n"/>
-      <c r="N397" s="3" t="n"/>
-      <c r="O397" s="3" t="n"/>
-      <c r="P397" s="3" t="n"/>
+      <c r="M397" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N397" s="3" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O397" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P397" s="3" t="n">
+        <v>20.22</v>
+      </c>
       <c r="Q397" s="3" t="n">
         <v>145.5</v>
       </c>
-      <c r="R397" s="3" t="n"/>
+      <c r="R397" s="3" t="n">
+        <v>3.75</v>
+      </c>
       <c r="S397" s="3">
         <f>IF(OR(Q397="",R397="",Q397=0),"",R397/Q397*100)</f>
         <v/>
@@ -24859,7 +27533,9 @@
       <c r="O398" s="3" t="n">
         <v>3.14</v>
       </c>
-      <c r="P398" s="3" t="n"/>
+      <c r="P398" s="3" t="n">
+        <v>53.79</v>
+      </c>
       <c r="Q398" s="3" t="n">
         <v>594</v>
       </c>
@@ -24954,9 +27630,15 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="D400" s="3" t="n"/>
-      <c r="E400" s="3" t="n"/>
-      <c r="F400" s="3" t="n"/>
+      <c r="D400" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E400" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F400" s="3" t="n">
+        <v>15.5</v>
+      </c>
       <c r="G400" s="3" t="n"/>
       <c r="H400" s="3" t="n"/>
       <c r="I400" s="3" t="n"/>
@@ -24972,10 +27654,14 @@
         <f>IF(OR(F400="",I400=""),"",I400-F400)</f>
         <v/>
       </c>
-      <c r="M400" s="3" t="n"/>
+      <c r="M400" s="3" t="n">
+        <v>4.41</v>
+      </c>
       <c r="N400" s="3" t="n"/>
       <c r="O400" s="3" t="n"/>
-      <c r="P400" s="3" t="n"/>
+      <c r="P400" s="3" t="n">
+        <v>8.73</v>
+      </c>
       <c r="Q400" s="3" t="n">
         <v>138.5</v>
       </c>
@@ -25307,7 +27993,9 @@
         <f>IF(OR(F405="",I405=""),"",I405-F405)</f>
         <v/>
       </c>
-      <c r="M405" s="3" t="n"/>
+      <c r="M405" s="3" t="n">
+        <v>75.95</v>
+      </c>
       <c r="N405" s="3" t="n"/>
       <c r="O405" s="3" t="n"/>
       <c r="P405" s="3" t="n">
@@ -25340,9 +28028,15 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D406" s="3" t="n"/>
-      <c r="E406" s="3" t="n"/>
-      <c r="F406" s="3" t="n"/>
+      <c r="D406" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E406" s="3" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="F406" s="3" t="n">
+        <v>12.21</v>
+      </c>
       <c r="G406" s="3" t="n"/>
       <c r="H406" s="3" t="n"/>
       <c r="I406" s="3" t="n"/>
@@ -25358,14 +28052,20 @@
         <f>IF(OR(F406="",I406=""),"",I406-F406)</f>
         <v/>
       </c>
-      <c r="M406" s="3" t="n"/>
+      <c r="M406" s="3" t="n">
+        <v>6.96</v>
+      </c>
       <c r="N406" s="3" t="n"/>
       <c r="O406" s="3" t="n"/>
-      <c r="P406" s="3" t="n"/>
+      <c r="P406" s="3" t="n">
+        <v>10.85</v>
+      </c>
       <c r="Q406" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="R406" s="3" t="n"/>
+      <c r="R406" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="S406" s="3">
         <f>IF(OR(Q406="",R406="",Q406=0),"",R406/Q406*100)</f>
         <v/>
@@ -25387,12 +28087,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D407" s="3" t="n"/>
-      <c r="E407" s="3" t="n"/>
-      <c r="F407" s="3" t="n"/>
-      <c r="G407" s="3" t="n"/>
-      <c r="H407" s="3" t="n"/>
-      <c r="I407" s="3" t="n"/>
+      <c r="D407" s="3" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="F407" s="3" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G407" s="3" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="H407" s="3" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="I407" s="3" t="n">
+        <v>14.49</v>
+      </c>
       <c r="J407" s="4">
         <f>IF(OR(D407="",G407=""),"",G407-D407)</f>
         <v/>
@@ -25405,14 +28117,24 @@
         <f>IF(OR(F407="",I407=""),"",I407-F407)</f>
         <v/>
       </c>
-      <c r="M407" s="3" t="n"/>
-      <c r="N407" s="3" t="n"/>
-      <c r="O407" s="3" t="n"/>
-      <c r="P407" s="3" t="n"/>
+      <c r="M407" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="N407" s="3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="O407" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P407" s="3" t="n">
+        <v>40.41</v>
+      </c>
       <c r="Q407" s="3" t="n">
         <v>270.5</v>
       </c>
-      <c r="R407" s="3" t="n"/>
+      <c r="R407" s="3" t="n">
+        <v>3.35</v>
+      </c>
       <c r="S407" s="3">
         <f>IF(OR(Q407="",R407="",Q407=0),"",R407/Q407*100)</f>
         <v/>
@@ -25617,7 +28339,9 @@
       <c r="Q410" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="R410" s="3" t="n"/>
+      <c r="R410" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="S410" s="3">
         <f>IF(OR(Q410="",R410="",Q410=0),"",R410/Q410*100)</f>
         <v/>
@@ -25639,12 +28363,24 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D411" s="3" t="n"/>
-      <c r="E411" s="3" t="n"/>
-      <c r="F411" s="3" t="n"/>
-      <c r="G411" s="3" t="n"/>
-      <c r="H411" s="3" t="n"/>
-      <c r="I411" s="3" t="n"/>
+      <c r="D411" s="3" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="E411" s="3" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="F411" s="3" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="G411" s="3" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="H411" s="3" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="I411" s="3" t="n">
+        <v>-3.84</v>
+      </c>
       <c r="J411" s="4">
         <f>IF(OR(D411="",G411=""),"",G411-D411)</f>
         <v/>
@@ -25657,14 +28393,24 @@
         <f>IF(OR(F411="",I411=""),"",I411-F411)</f>
         <v/>
       </c>
-      <c r="M411" s="3" t="n"/>
-      <c r="N411" s="3" t="n"/>
-      <c r="O411" s="3" t="n"/>
-      <c r="P411" s="3" t="n"/>
+      <c r="M411" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N411" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O411" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="P411" s="3" t="n">
+        <v>294.74</v>
+      </c>
       <c r="Q411" s="3" t="n">
         <v>363.5</v>
       </c>
-      <c r="R411" s="3" t="n"/>
+      <c r="R411" s="3" t="n">
+        <v>1.9431</v>
+      </c>
       <c r="S411" s="3">
         <f>IF(OR(Q411="",R411="",Q411=0),"",R411/Q411*100)</f>
         <v/>
@@ -25893,12 +28639,20 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="D415" s="3" t="n"/>
-      <c r="E415" s="3" t="n"/>
-      <c r="F415" s="3" t="n"/>
+      <c r="D415" s="3" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="E415" s="3" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="F415" s="3" t="n">
+        <v>24.11</v>
+      </c>
       <c r="G415" s="3" t="n"/>
       <c r="H415" s="3" t="n"/>
-      <c r="I415" s="3" t="n"/>
+      <c r="I415" s="3" t="n">
+        <v>2.91</v>
+      </c>
       <c r="J415" s="4">
         <f>IF(OR(D415="",G415=""),"",G415-D415)</f>
         <v/>
@@ -25911,9 +28665,15 @@
         <f>IF(OR(F415="",I415=""),"",I415-F415)</f>
         <v/>
       </c>
-      <c r="M415" s="3" t="n"/>
-      <c r="N415" s="3" t="n"/>
-      <c r="O415" s="3" t="n"/>
+      <c r="M415" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O415" s="3" t="n">
+        <v>9.69</v>
+      </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
         <v>55.8</v>
@@ -26075,7 +28835,7 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>電子工業</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D418" s="3" t="n">
@@ -26344,9 +29104,15 @@
           <t>其他電子</t>
         </is>
       </c>
-      <c r="D422" s="3" t="n"/>
-      <c r="E422" s="3" t="n"/>
-      <c r="F422" s="3" t="n"/>
+      <c r="D422" s="3" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="E422" s="3" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F422" s="3" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="G422" s="3" t="n"/>
       <c r="H422" s="3" t="n"/>
       <c r="I422" s="3" t="n"/>
@@ -26362,10 +29128,14 @@
         <f>IF(OR(F422="",I422=""),"",I422-F422)</f>
         <v/>
       </c>
-      <c r="M422" s="3" t="n"/>
+      <c r="M422" s="3" t="n">
+        <v>-0.61</v>
+      </c>
       <c r="N422" s="3" t="n"/>
       <c r="O422" s="3" t="n"/>
-      <c r="P422" s="3" t="n"/>
+      <c r="P422" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q422" s="3" t="n">
         <v>491</v>
       </c>
@@ -26390,15 +29160,27 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>電子工業</t>
-        </is>
-      </c>
-      <c r="D423" s="3" t="n"/>
-      <c r="E423" s="3" t="n"/>
-      <c r="F423" s="3" t="n"/>
-      <c r="G423" s="3" t="n"/>
-      <c r="H423" s="3" t="n"/>
-      <c r="I423" s="3" t="n"/>
+          <t>電腦週邊</t>
+        </is>
+      </c>
+      <c r="D423" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E423" s="3" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="F423" s="3" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="G423" s="3" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="H423" s="3" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="I423" s="3" t="n">
+        <v>6.46</v>
+      </c>
       <c r="J423" s="4">
         <f>IF(OR(D423="",G423=""),"",G423-D423)</f>
         <v/>
@@ -26411,14 +29193,24 @@
         <f>IF(OR(F423="",I423=""),"",I423-F423)</f>
         <v/>
       </c>
-      <c r="M423" s="3" t="n"/>
-      <c r="N423" s="3" t="n"/>
-      <c r="O423" s="3" t="n"/>
-      <c r="P423" s="3" t="n"/>
+      <c r="M423" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N423" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O423" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P423" s="3" t="n">
+        <v>115.9</v>
+      </c>
       <c r="Q423" s="3" t="n">
         <v>562</v>
       </c>
-      <c r="R423" s="3" t="n"/>
+      <c r="R423" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="S423" s="3">
         <f>IF(OR(Q423="",R423="",Q423=0),"",R423/Q423*100)</f>
         <v/>
@@ -26517,9 +29309,15 @@
         <f>IF(OR(F425="",I425=""),"",I425-F425)</f>
         <v/>
       </c>
-      <c r="M425" s="3" t="n"/>
-      <c r="N425" s="3" t="n"/>
-      <c r="O425" s="3" t="n"/>
+      <c r="M425" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="N425" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="O425" s="3" t="n">
+        <v>4.04</v>
+      </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
         <v>16.35</v>
@@ -26607,12 +29405,12 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>康霈</t>
+          <t>康霈生技</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>生技醫療</t>
         </is>
       </c>
       <c r="D427" s="3" t="n">
@@ -26680,9 +29478,15 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D428" s="3" t="n"/>
-      <c r="E428" s="3" t="n"/>
-      <c r="F428" s="3" t="n"/>
+      <c r="D428" s="3" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="E428" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F428" s="3" t="n">
+        <v>10.6</v>
+      </c>
       <c r="G428" s="3" t="n"/>
       <c r="H428" s="3" t="n"/>
       <c r="I428" s="3" t="n"/>
@@ -26698,14 +29502,20 @@
         <f>IF(OR(F428="",I428=""),"",I428-F428)</f>
         <v/>
       </c>
-      <c r="M428" s="3" t="n"/>
+      <c r="M428" s="3" t="n">
+        <v>0.96</v>
+      </c>
       <c r="N428" s="3" t="n"/>
       <c r="O428" s="3" t="n"/>
-      <c r="P428" s="3" t="n"/>
+      <c r="P428" s="3" t="n">
+        <v>57.36</v>
+      </c>
       <c r="Q428" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="R428" s="3" t="n"/>
+      <c r="R428" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="S428" s="3">
         <f>IF(OR(Q428="",R428="",Q428=0),"",R428/Q428*100)</f>
         <v/>
@@ -26814,9 +29624,15 @@
         <f>IF(OR(F430="",I430=""),"",I430-F430)</f>
         <v/>
       </c>
-      <c r="M430" s="3" t="n"/>
-      <c r="N430" s="3" t="n"/>
-      <c r="O430" s="3" t="n"/>
+      <c r="M430" s="3" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="N430" s="3" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="O430" s="3" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
         <v>1355</v>
@@ -26843,12 +29659,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D431" s="3" t="n"/>
-      <c r="E431" s="3" t="n"/>
-      <c r="F431" s="3" t="n"/>
-      <c r="G431" s="3" t="n"/>
-      <c r="H431" s="3" t="n"/>
-      <c r="I431" s="3" t="n"/>
+      <c r="D431" s="3" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="E431" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F431" s="3" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G431" s="3" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H431" s="3" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="I431" s="3" t="n">
+        <v>0.29</v>
+      </c>
       <c r="J431" s="4">
         <f>IF(OR(D431="",G431=""),"",G431-D431)</f>
         <v/>
@@ -26861,14 +29689,24 @@
         <f>IF(OR(F431="",I431=""),"",I431-F431)</f>
         <v/>
       </c>
-      <c r="M431" s="3" t="n"/>
-      <c r="N431" s="3" t="n"/>
-      <c r="O431" s="3" t="n"/>
-      <c r="P431" s="3" t="n"/>
+      <c r="M431" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N431" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O431" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P431" s="3" t="n">
+        <v>20.63</v>
+      </c>
       <c r="Q431" s="3" t="n">
         <v>31.25</v>
       </c>
-      <c r="R431" s="3" t="n"/>
+      <c r="R431" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="S431" s="3">
         <f>IF(OR(Q431="",R431="",Q431=0),"",R431/Q431*100)</f>
         <v/>
@@ -26959,12 +29797,24 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="D433" s="3" t="n"/>
-      <c r="E433" s="3" t="n"/>
-      <c r="F433" s="3" t="n"/>
-      <c r="G433" s="3" t="n"/>
-      <c r="H433" s="3" t="n"/>
-      <c r="I433" s="3" t="n"/>
+      <c r="D433" s="3" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E433" s="3" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="F433" s="3" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="G433" s="3" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="H433" s="3" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="I433" s="3" t="n">
+        <v>10.05</v>
+      </c>
       <c r="J433" s="4">
         <f>IF(OR(D433="",G433=""),"",G433-D433)</f>
         <v/>
@@ -26977,14 +29827,24 @@
         <f>IF(OR(F433="",I433=""),"",I433-F433)</f>
         <v/>
       </c>
-      <c r="M433" s="3" t="n"/>
-      <c r="N433" s="3" t="n"/>
-      <c r="O433" s="3" t="n"/>
-      <c r="P433" s="3" t="n"/>
+      <c r="M433" s="3" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="N433" s="3" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="O433" s="3" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="P433" s="3" t="n">
+        <v>19.38</v>
+      </c>
       <c r="Q433" s="3" t="n">
         <v>515</v>
       </c>
-      <c r="R433" s="3" t="n"/>
+      <c r="R433" s="3" t="n">
+        <v>8.9871</v>
+      </c>
       <c r="S433" s="3">
         <f>IF(OR(Q433="",R433="",Q433=0),"",R433/Q433*100)</f>
         <v/>
@@ -26998,7 +29858,7 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -27006,12 +29866,24 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="D434" s="3" t="n"/>
-      <c r="E434" s="3" t="n"/>
-      <c r="F434" s="3" t="n"/>
-      <c r="G434" s="3" t="n"/>
-      <c r="H434" s="3" t="n"/>
-      <c r="I434" s="3" t="n"/>
+      <c r="D434" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="F434" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G434" s="3" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="H434" s="3" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="I434" s="3" t="n">
+        <v>7.58</v>
+      </c>
       <c r="J434" s="4">
         <f>IF(OR(D434="",G434=""),"",G434-D434)</f>
         <v/>
@@ -27024,14 +29896,24 @@
         <f>IF(OR(F434="",I434=""),"",I434-F434)</f>
         <v/>
       </c>
-      <c r="M434" s="3" t="n"/>
-      <c r="N434" s="3" t="n"/>
-      <c r="O434" s="3" t="n"/>
-      <c r="P434" s="3" t="n"/>
+      <c r="M434" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N434" s="3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="O434" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P434" s="3" t="n">
+        <v>34.98</v>
+      </c>
       <c r="Q434" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="R434" s="3" t="n"/>
+      <c r="R434" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="S434" s="3">
         <f>IF(OR(Q434="",R434="",Q434=0),"",R434/Q434*100)</f>
         <v/>
@@ -27191,9 +30073,15 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D437" s="3" t="n"/>
-      <c r="E437" s="3" t="n"/>
-      <c r="F437" s="3" t="n"/>
+      <c r="D437" s="3" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="E437" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F437" s="3" t="n">
+        <v>31</v>
+      </c>
       <c r="G437" s="3" t="n"/>
       <c r="H437" s="3" t="n"/>
       <c r="I437" s="3" t="n"/>
@@ -27209,14 +30097,20 @@
         <f>IF(OR(F437="",I437=""),"",I437-F437)</f>
         <v/>
       </c>
-      <c r="M437" s="3" t="n"/>
+      <c r="M437" s="3" t="n">
+        <v>3.56</v>
+      </c>
       <c r="N437" s="3" t="n"/>
       <c r="O437" s="3" t="n"/>
-      <c r="P437" s="3" t="n"/>
+      <c r="P437" s="3" t="n">
+        <v>30.21</v>
+      </c>
       <c r="Q437" s="3" t="n">
         <v>382</v>
       </c>
-      <c r="R437" s="3" t="n"/>
+      <c r="R437" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="S437" s="3">
         <f>IF(OR(Q437="",R437="",Q437=0),"",R437/Q437*100)</f>
         <v/>
@@ -27514,9 +30408,15 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="D442" s="3" t="n"/>
-      <c r="E442" s="3" t="n"/>
-      <c r="F442" s="3" t="n"/>
+      <c r="D442" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="E442" s="3" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="F442" s="3" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G442" s="3" t="n"/>
       <c r="H442" s="3" t="n"/>
       <c r="I442" s="3" t="n"/>
@@ -27532,14 +30432,24 @@
         <f>IF(OR(F442="",I442=""),"",I442-F442)</f>
         <v/>
       </c>
-      <c r="M442" s="3" t="n"/>
-      <c r="N442" s="3" t="n"/>
-      <c r="O442" s="3" t="n"/>
-      <c r="P442" s="3" t="n"/>
+      <c r="M442" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N442" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O442" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P442" s="3" t="n">
+        <v>31.03</v>
+      </c>
       <c r="Q442" s="3" t="n">
         <v>16.85</v>
       </c>
-      <c r="R442" s="3" t="n"/>
+      <c r="R442" s="3" t="n">
+        <v>0.8934</v>
+      </c>
       <c r="S442" s="3">
         <f>IF(OR(Q442="",R442="",Q442=0),"",R442/Q442*100)</f>
         <v/>
@@ -27630,9 +30540,15 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="D444" s="3" t="n"/>
-      <c r="E444" s="3" t="n"/>
-      <c r="F444" s="3" t="n"/>
+      <c r="D444" s="3" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="E444" s="3" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F444" s="3" t="n">
+        <v>9.5</v>
+      </c>
       <c r="G444" s="3" t="n"/>
       <c r="H444" s="3" t="n"/>
       <c r="I444" s="3" t="n"/>
@@ -27648,14 +30564,24 @@
         <f>IF(OR(F444="",I444=""),"",I444-F444)</f>
         <v/>
       </c>
-      <c r="M444" s="3" t="n"/>
-      <c r="N444" s="3" t="n"/>
-      <c r="O444" s="3" t="n"/>
-      <c r="P444" s="3" t="n"/>
+      <c r="M444" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N444" s="3" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="O444" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P444" s="3" t="n">
+        <v>29.91</v>
+      </c>
       <c r="Q444" s="3" t="n">
         <v>258.5</v>
       </c>
-      <c r="R444" s="3" t="n"/>
+      <c r="R444" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S444" s="3">
         <f>IF(OR(Q444="",R444="",Q444=0),"",R444/Q444*100)</f>
         <v/>
@@ -27677,12 +30603,24 @@
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="D445" s="3" t="n"/>
-      <c r="E445" s="3" t="n"/>
-      <c r="F445" s="3" t="n"/>
-      <c r="G445" s="3" t="n"/>
-      <c r="H445" s="3" t="n"/>
-      <c r="I445" s="3" t="n"/>
+      <c r="D445" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E445" s="3" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F445" s="3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G445" s="3" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="H445" s="3" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="I445" s="3" t="n">
+        <v>11.21</v>
+      </c>
       <c r="J445" s="4">
         <f>IF(OR(D445="",G445=""),"",G445-D445)</f>
         <v/>
@@ -27695,14 +30633,24 @@
         <f>IF(OR(F445="",I445=""),"",I445-F445)</f>
         <v/>
       </c>
-      <c r="M445" s="3" t="n"/>
-      <c r="N445" s="3" t="n"/>
-      <c r="O445" s="3" t="n"/>
-      <c r="P445" s="3" t="n"/>
+      <c r="M445" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N445" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O445" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P445" s="3" t="n">
+        <v>251.33</v>
+      </c>
       <c r="Q445" s="3" t="n">
         <v>551</v>
       </c>
-      <c r="R445" s="3" t="n"/>
+      <c r="R445" s="3" t="n">
+        <v>2.15</v>
+      </c>
       <c r="S445" s="3">
         <f>IF(OR(Q445="",R445="",Q445=0),"",R445/Q445*100)</f>
         <v/>
@@ -27724,12 +30672,24 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="D446" s="3" t="n"/>
-      <c r="E446" s="3" t="n"/>
-      <c r="F446" s="3" t="n"/>
-      <c r="G446" s="3" t="n"/>
-      <c r="H446" s="3" t="n"/>
-      <c r="I446" s="3" t="n"/>
+      <c r="D446" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E446" s="3" t="n">
+        <v>-3067.28</v>
+      </c>
+      <c r="F446" s="3" t="n">
+        <v>-1995.78</v>
+      </c>
+      <c r="G446" s="3" t="n">
+        <v>-1506.35</v>
+      </c>
+      <c r="H446" s="3" t="n">
+        <v>-28244.25</v>
+      </c>
+      <c r="I446" s="3" t="n">
+        <v>-21313.29</v>
+      </c>
       <c r="J446" s="4">
         <f>IF(OR(D446="",G446=""),"",G446-D446)</f>
         <v/>
@@ -27742,9 +30702,15 @@
         <f>IF(OR(F446="",I446=""),"",I446-F446)</f>
         <v/>
       </c>
-      <c r="M446" s="3" t="n"/>
-      <c r="N446" s="3" t="n"/>
-      <c r="O446" s="3" t="n"/>
+      <c r="M446" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="N446" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="O446" s="3" t="n">
+        <v>-0.68</v>
+      </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
         <v>356.5</v>
@@ -27840,12 +30806,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D448" s="3" t="n"/>
-      <c r="E448" s="3" t="n"/>
-      <c r="F448" s="3" t="n"/>
-      <c r="G448" s="3" t="n"/>
-      <c r="H448" s="3" t="n"/>
-      <c r="I448" s="3" t="n"/>
+      <c r="D448" s="3" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E448" s="3" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="F448" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G448" s="3" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="H448" s="3" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="I448" s="3" t="n">
+        <v>32.1</v>
+      </c>
       <c r="J448" s="4">
         <f>IF(OR(D448="",G448=""),"",G448-D448)</f>
         <v/>
@@ -27858,14 +30836,24 @@
         <f>IF(OR(F448="",I448=""),"",I448-F448)</f>
         <v/>
       </c>
-      <c r="M448" s="3" t="n"/>
-      <c r="N448" s="3" t="n"/>
-      <c r="O448" s="3" t="n"/>
-      <c r="P448" s="3" t="n"/>
+      <c r="M448" s="3" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="N448" s="3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="O448" s="3" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="P448" s="3" t="n">
+        <v>51.64</v>
+      </c>
       <c r="Q448" s="3" t="n">
         <v>925</v>
       </c>
-      <c r="R448" s="3" t="n"/>
+      <c r="R448" s="3" t="n">
+        <v>6.39</v>
+      </c>
       <c r="S448" s="3">
         <f>IF(OR(Q448="",R448="",Q448=0),"",R448/Q448*100)</f>
         <v/>
@@ -28003,12 +30991,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D451" s="3" t="n"/>
-      <c r="E451" s="3" t="n"/>
-      <c r="F451" s="3" t="n"/>
-      <c r="G451" s="3" t="n"/>
-      <c r="H451" s="3" t="n"/>
-      <c r="I451" s="3" t="n"/>
+      <c r="D451" s="3" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="E451" s="3" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="F451" s="3" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="G451" s="3" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="H451" s="3" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="I451" s="3" t="n">
+        <v>16.86</v>
+      </c>
       <c r="J451" s="4">
         <f>IF(OR(D451="",G451=""),"",G451-D451)</f>
         <v/>
@@ -28021,14 +31021,24 @@
         <f>IF(OR(F451="",I451=""),"",I451-F451)</f>
         <v/>
       </c>
-      <c r="M451" s="3" t="n"/>
-      <c r="N451" s="3" t="n"/>
-      <c r="O451" s="3" t="n"/>
-      <c r="P451" s="3" t="n"/>
+      <c r="M451" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N451" s="3" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="O451" s="3" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="P451" s="3" t="n">
+        <v>14.77</v>
+      </c>
       <c r="Q451" s="3" t="n">
         <v>292.5</v>
       </c>
-      <c r="R451" s="3" t="n"/>
+      <c r="R451" s="3" t="n">
+        <v>11.5</v>
+      </c>
       <c r="S451" s="3">
         <f>IF(OR(Q451="",R451="",Q451=0),"",R451/Q451*100)</f>
         <v/>
@@ -28050,12 +31060,24 @@
           <t>其他電子</t>
         </is>
       </c>
-      <c r="D452" s="3" t="n"/>
-      <c r="E452" s="3" t="n"/>
-      <c r="F452" s="3" t="n"/>
-      <c r="G452" s="3" t="n"/>
-      <c r="H452" s="3" t="n"/>
-      <c r="I452" s="3" t="n"/>
+      <c r="D452" s="3" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="E452" s="3" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="F452" s="3" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="G452" s="3" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="H452" s="3" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="I452" s="3" t="n">
+        <v>19.86</v>
+      </c>
       <c r="J452" s="4">
         <f>IF(OR(D452="",G452=""),"",G452-D452)</f>
         <v/>
@@ -28068,14 +31090,24 @@
         <f>IF(OR(F452="",I452=""),"",I452-F452)</f>
         <v/>
       </c>
-      <c r="M452" s="3" t="n"/>
-      <c r="N452" s="3" t="n"/>
-      <c r="O452" s="3" t="n"/>
-      <c r="P452" s="3" t="n"/>
+      <c r="M452" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N452" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O452" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P452" s="3" t="n">
+        <v>78.33</v>
+      </c>
       <c r="Q452" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="R452" s="3" t="n"/>
+      <c r="R452" s="3" t="n">
+        <v>1.97</v>
+      </c>
       <c r="S452" s="3">
         <f>IF(OR(Q452="",R452="",Q452=0),"",R452/Q452*100)</f>
         <v/>
@@ -28136,7 +31168,9 @@
       <c r="O453" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="P453" s="3" t="n"/>
+      <c r="P453" s="3" t="n">
+        <v>558.33</v>
+      </c>
       <c r="Q453" s="3" t="n">
         <v>169.5</v>
       </c>
@@ -28162,12 +31196,24 @@
           <t>半導體業</t>
         </is>
       </c>
-      <c r="D454" s="3" t="n"/>
-      <c r="E454" s="3" t="n"/>
-      <c r="F454" s="3" t="n"/>
-      <c r="G454" s="3" t="n"/>
-      <c r="H454" s="3" t="n"/>
-      <c r="I454" s="3" t="n"/>
+      <c r="D454" s="3" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="E454" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F454" s="3" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="G454" s="3" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="H454" s="3" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="I454" s="3" t="n">
+        <v>21.62</v>
+      </c>
       <c r="J454" s="4">
         <f>IF(OR(D454="",G454=""),"",G454-D454)</f>
         <v/>
@@ -28180,14 +31226,24 @@
         <f>IF(OR(F454="",I454=""),"",I454-F454)</f>
         <v/>
       </c>
-      <c r="M454" s="3" t="n"/>
-      <c r="N454" s="3" t="n"/>
-      <c r="O454" s="3" t="n"/>
-      <c r="P454" s="3" t="n"/>
+      <c r="M454" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N454" s="3" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O454" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P454" s="3" t="n">
+        <v>43.46</v>
+      </c>
       <c r="Q454" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="R454" s="3" t="n"/>
+      <c r="R454" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="S454" s="3">
         <f>IF(OR(Q454="",R454="",Q454=0),"",R454/Q454*100)</f>
         <v/>
@@ -28209,12 +31265,24 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="D455" s="3" t="n"/>
-      <c r="E455" s="3" t="n"/>
-      <c r="F455" s="3" t="n"/>
-      <c r="G455" s="3" t="n"/>
-      <c r="H455" s="3" t="n"/>
-      <c r="I455" s="3" t="n"/>
+      <c r="D455" s="3" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="E455" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F455" s="3" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="G455" s="3" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="H455" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I455" s="3" t="n">
+        <v>9.859999999999999</v>
+      </c>
       <c r="J455" s="4">
         <f>IF(OR(D455="",G455=""),"",G455-D455)</f>
         <v/>
@@ -28227,10 +31295,18 @@
         <f>IF(OR(F455="",I455=""),"",I455-F455)</f>
         <v/>
       </c>
-      <c r="M455" s="3" t="n"/>
-      <c r="N455" s="3" t="n"/>
-      <c r="O455" s="3" t="n"/>
-      <c r="P455" s="3" t="n"/>
+      <c r="M455" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N455" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O455" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P455" s="3" t="n">
+        <v>385.42</v>
+      </c>
       <c r="Q455" s="3" t="n">
         <v>179</v>
       </c>
@@ -28370,7 +31446,9 @@
       <c r="Q457" s="3" t="n">
         <v>1160</v>
       </c>
-      <c r="R457" s="3" t="n"/>
+      <c r="R457" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S457" s="3">
         <f>IF(OR(Q457="",R457="",Q457=0),"",R457/Q457*100)</f>
         <v/>
@@ -28530,12 +31608,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D460" s="3" t="n"/>
-      <c r="E460" s="3" t="n"/>
-      <c r="F460" s="3" t="n"/>
-      <c r="G460" s="3" t="n"/>
-      <c r="H460" s="3" t="n"/>
-      <c r="I460" s="3" t="n"/>
+      <c r="D460" s="3" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="E460" s="3" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F460" s="3" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="G460" s="3" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="H460" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I460" s="3" t="n">
+        <v>13.63</v>
+      </c>
       <c r="J460" s="4">
         <f>IF(OR(D460="",G460=""),"",G460-D460)</f>
         <v/>
@@ -28548,14 +31638,24 @@
         <f>IF(OR(F460="",I460=""),"",I460-F460)</f>
         <v/>
       </c>
-      <c r="M460" s="3" t="n"/>
-      <c r="N460" s="3" t="n"/>
-      <c r="O460" s="3" t="n"/>
-      <c r="P460" s="3" t="n"/>
+      <c r="M460" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N460" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O460" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P460" s="3" t="n">
+        <v>28.99</v>
+      </c>
       <c r="Q460" s="3" t="n">
         <v>49.3</v>
       </c>
-      <c r="R460" s="3" t="n"/>
+      <c r="R460" s="3" t="n">
+        <v>0.68</v>
+      </c>
       <c r="S460" s="3">
         <f>IF(OR(Q460="",R460="",Q460=0),"",R460/Q460*100)</f>
         <v/>
@@ -28920,12 +32020,24 @@
           <t>電子工業</t>
         </is>
       </c>
-      <c r="D466" s="3" t="n"/>
-      <c r="E466" s="3" t="n"/>
-      <c r="F466" s="3" t="n"/>
-      <c r="G466" s="3" t="n"/>
-      <c r="H466" s="3" t="n"/>
-      <c r="I466" s="3" t="n"/>
+      <c r="D466" s="3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E466" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F466" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G466" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H466" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I466" s="3" t="n">
+        <v>1.96</v>
+      </c>
       <c r="J466" s="4">
         <f>IF(OR(D466="",G466=""),"",G466-D466)</f>
         <v/>
@@ -28938,14 +32050,24 @@
         <f>IF(OR(F466="",I466=""),"",I466-F466)</f>
         <v/>
       </c>
-      <c r="M466" s="3" t="n"/>
-      <c r="N466" s="3" t="n"/>
-      <c r="O466" s="3" t="n"/>
-      <c r="P466" s="3" t="n"/>
+      <c r="M466" s="3" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="N466" s="3" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="O466" s="3" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="P466" s="3" t="n">
+        <v>7.22</v>
+      </c>
       <c r="Q466" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="R466" s="3" t="n"/>
+      <c r="R466" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="S466" s="3">
         <f>IF(OR(Q466="",R466="",Q466=0),"",R466/Q466*100)</f>
         <v/>
@@ -28967,12 +32089,24 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="D467" s="3" t="n"/>
-      <c r="E467" s="3" t="n"/>
-      <c r="F467" s="3" t="n"/>
-      <c r="G467" s="3" t="n"/>
-      <c r="H467" s="3" t="n"/>
-      <c r="I467" s="3" t="n"/>
+      <c r="D467" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E467" s="3" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="F467" s="3" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="G467" s="3" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="H467" s="3" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="I467" s="3" t="n">
+        <v>14.68</v>
+      </c>
       <c r="J467" s="4">
         <f>IF(OR(D467="",G467=""),"",G467-D467)</f>
         <v/>
@@ -28985,14 +32119,24 @@
         <f>IF(OR(F467="",I467=""),"",I467-F467)</f>
         <v/>
       </c>
-      <c r="M467" s="3" t="n"/>
-      <c r="N467" s="3" t="n"/>
-      <c r="O467" s="3" t="n"/>
-      <c r="P467" s="3" t="n"/>
+      <c r="M467" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N467" s="3" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="O467" s="3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="P467" s="3" t="n">
+        <v>13.93</v>
+      </c>
       <c r="Q467" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="R467" s="3" t="n"/>
+      <c r="R467" s="3" t="n">
+        <v>11.47</v>
+      </c>
       <c r="S467" s="3">
         <f>IF(OR(Q467="",R467="",Q467=0),"",R467/Q467*100)</f>
         <v/>
@@ -29299,9 +32443,15 @@
       <c r="F472" s="3" t="n">
         <v>6.65</v>
       </c>
-      <c r="G472" s="3" t="n"/>
-      <c r="H472" s="3" t="n"/>
-      <c r="I472" s="3" t="n"/>
+      <c r="G472" s="3" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="H472" s="3" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I472" s="3" t="n">
+        <v>6.24</v>
+      </c>
       <c r="J472" s="4">
         <f>IF(OR(D472="",G472=""),"",G472-D472)</f>
         <v/>
@@ -29317,8 +32467,12 @@
       <c r="M472" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="N472" s="3" t="n"/>
-      <c r="O472" s="3" t="n"/>
+      <c r="N472" s="3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O472" s="3" t="n">
+        <v>1.44</v>
+      </c>
       <c r="P472" s="3" t="n">
         <v>22.07</v>
       </c>
@@ -29349,12 +32503,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D473" s="3" t="n"/>
-      <c r="E473" s="3" t="n"/>
-      <c r="F473" s="3" t="n"/>
-      <c r="G473" s="3" t="n"/>
-      <c r="H473" s="3" t="n"/>
-      <c r="I473" s="3" t="n"/>
+      <c r="D473" s="3" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="E473" s="3" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="F473" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G473" s="3" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="H473" s="3" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="I473" s="3" t="n">
+        <v>20.41</v>
+      </c>
       <c r="J473" s="4">
         <f>IF(OR(D473="",G473=""),"",G473-D473)</f>
         <v/>
@@ -29367,10 +32533,18 @@
         <f>IF(OR(F473="",I473=""),"",I473-F473)</f>
         <v/>
       </c>
-      <c r="M473" s="3" t="n"/>
-      <c r="N473" s="3" t="n"/>
-      <c r="O473" s="3" t="n"/>
-      <c r="P473" s="3" t="n"/>
+      <c r="M473" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N473" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O473" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P473" s="3" t="n">
+        <v>26.61</v>
+      </c>
       <c r="Q473" s="3" t="n">
         <v>177.5</v>
       </c>
@@ -29396,12 +32570,24 @@
           <t>半導體</t>
         </is>
       </c>
-      <c r="D474" s="3" t="n"/>
-      <c r="E474" s="3" t="n"/>
-      <c r="F474" s="3" t="n"/>
-      <c r="G474" s="3" t="n"/>
-      <c r="H474" s="3" t="n"/>
-      <c r="I474" s="3" t="n"/>
+      <c r="D474" s="3" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="E474" s="3" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="F474" s="3" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="G474" s="3" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="H474" s="3" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="I474" s="3" t="n">
+        <v>28.71</v>
+      </c>
       <c r="J474" s="4">
         <f>IF(OR(D474="",G474=""),"",G474-D474)</f>
         <v/>
@@ -29414,14 +32600,24 @@
         <f>IF(OR(F474="",I474=""),"",I474-F474)</f>
         <v/>
       </c>
-      <c r="M474" s="3" t="n"/>
-      <c r="N474" s="3" t="n"/>
-      <c r="O474" s="3" t="n"/>
-      <c r="P474" s="3" t="n"/>
+      <c r="M474" s="3" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="N474" s="3" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="O474" s="3" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="P474" s="3" t="n">
+        <v>5.78</v>
+      </c>
       <c r="Q474" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="R474" s="3" t="n"/>
+      <c r="R474" s="3" t="n">
+        <v>4.448</v>
+      </c>
       <c r="S474" s="3">
         <f>IF(OR(Q474="",R474="",Q474=0),"",R474/Q474*100)</f>
         <v/>
@@ -29687,11 +32883,15 @@
       <c r="O478" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="P478" s="3" t="n"/>
+      <c r="P478" s="3" t="n">
+        <v>27.97</v>
+      </c>
       <c r="Q478" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="R478" s="3" t="n"/>
+      <c r="R478" s="3" t="n">
+        <v>1.198</v>
+      </c>
       <c r="S478" s="3">
         <f>IF(OR(Q478="",R478="",Q478=0),"",R478/Q478*100)</f>
         <v/>
@@ -29851,12 +33051,24 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D481" s="3" t="n"/>
-      <c r="E481" s="3" t="n"/>
-      <c r="F481" s="3" t="n"/>
-      <c r="G481" s="3" t="n"/>
-      <c r="H481" s="3" t="n"/>
-      <c r="I481" s="3" t="n"/>
+      <c r="D481" s="3" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="E481" s="3" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="F481" s="3" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="G481" s="3" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="H481" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I481" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="J481" s="4">
         <f>IF(OR(D481="",G481=""),"",G481-D481)</f>
         <v/>
@@ -29869,14 +33081,24 @@
         <f>IF(OR(F481="",I481=""),"",I481-F481)</f>
         <v/>
       </c>
-      <c r="M481" s="3" t="n"/>
-      <c r="N481" s="3" t="n"/>
-      <c r="O481" s="3" t="n"/>
-      <c r="P481" s="3" t="n"/>
+      <c r="M481" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N481" s="3" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="O481" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P481" s="3" t="n">
+        <v>9.94</v>
+      </c>
       <c r="Q481" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="R481" s="3" t="n"/>
+      <c r="R481" s="3" t="n">
+        <v>6.5</v>
+      </c>
       <c r="S481" s="3">
         <f>IF(OR(Q481="",R481="",Q481=0),"",R481/Q481*100)</f>
         <v/>
@@ -29898,12 +33120,24 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="D482" s="3" t="n"/>
-      <c r="E482" s="3" t="n"/>
-      <c r="F482" s="3" t="n"/>
-      <c r="G482" s="3" t="n"/>
-      <c r="H482" s="3" t="n"/>
-      <c r="I482" s="3" t="n"/>
+      <c r="D482" s="3" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="E482" s="3" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F482" s="3" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="G482" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H482" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I482" s="3" t="n">
+        <v>6.69</v>
+      </c>
       <c r="J482" s="4">
         <f>IF(OR(D482="",G482=""),"",G482-D482)</f>
         <v/>
@@ -29916,14 +33150,24 @@
         <f>IF(OR(F482="",I482=""),"",I482-F482)</f>
         <v/>
       </c>
-      <c r="M482" s="3" t="n"/>
-      <c r="N482" s="3" t="n"/>
-      <c r="O482" s="3" t="n"/>
-      <c r="P482" s="3" t="n"/>
+      <c r="M482" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N482" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O482" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P482" s="3" t="n">
+        <v>15.74</v>
+      </c>
       <c r="Q482" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="R482" s="3" t="n"/>
+      <c r="R482" s="3" t="n">
+        <v>2.12</v>
+      </c>
       <c r="S482" s="3">
         <f>IF(OR(Q482="",R482="",Q482=0),"",R482/Q482*100)</f>
         <v/>
@@ -30083,12 +33327,24 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D485" s="3" t="n"/>
-      <c r="E485" s="3" t="n"/>
-      <c r="F485" s="3" t="n"/>
-      <c r="G485" s="3" t="n"/>
-      <c r="H485" s="3" t="n"/>
-      <c r="I485" s="3" t="n"/>
+      <c r="D485" s="3" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="E485" s="3" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="F485" s="3" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G485" s="3" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I485" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="J485" s="4">
         <f>IF(OR(D485="",G485=""),"",G485-D485)</f>
         <v/>
@@ -30101,14 +33357,24 @@
         <f>IF(OR(F485="",I485=""),"",I485-F485)</f>
         <v/>
       </c>
-      <c r="M485" s="3" t="n"/>
-      <c r="N485" s="3" t="n"/>
-      <c r="O485" s="3" t="n"/>
-      <c r="P485" s="3" t="n"/>
+      <c r="M485" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N485" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O485" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P485" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Q485" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="R485" s="3" t="n"/>
+      <c r="R485" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S485" s="3">
         <f>IF(OR(Q485="",R485="",Q485=0),"",R485/Q485*100)</f>
         <v/>
@@ -30199,12 +33465,24 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="D487" s="3" t="n"/>
-      <c r="E487" s="3" t="n"/>
-      <c r="F487" s="3" t="n"/>
-      <c r="G487" s="3" t="n"/>
-      <c r="H487" s="3" t="n"/>
-      <c r="I487" s="3" t="n"/>
+      <c r="D487" s="3" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="E487" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F487" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G487" s="3" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="H487" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I487" s="3" t="n">
+        <v>2.52</v>
+      </c>
       <c r="J487" s="4">
         <f>IF(OR(D487="",G487=""),"",G487-D487)</f>
         <v/>
@@ -30217,14 +33495,24 @@
         <f>IF(OR(F487="",I487=""),"",I487-F487)</f>
         <v/>
       </c>
-      <c r="M487" s="3" t="n"/>
-      <c r="N487" s="3" t="n"/>
-      <c r="O487" s="3" t="n"/>
-      <c r="P487" s="3" t="n"/>
+      <c r="M487" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N487" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O487" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P487" s="3" t="n">
+        <v>16.11</v>
+      </c>
       <c r="Q487" s="3" t="n">
         <v>15.35</v>
       </c>
-      <c r="R487" s="3" t="n"/>
+      <c r="R487" s="3" t="n">
+        <v>1.18</v>
+      </c>
       <c r="S487" s="3">
         <f>IF(OR(Q487="",R487="",Q487=0),"",R487/Q487*100)</f>
         <v/>
@@ -30246,12 +33534,24 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="D488" s="3" t="n"/>
-      <c r="E488" s="3" t="n"/>
-      <c r="F488" s="3" t="n"/>
-      <c r="G488" s="3" t="n"/>
-      <c r="H488" s="3" t="n"/>
-      <c r="I488" s="3" t="n"/>
+      <c r="D488" s="3" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="E488" s="3" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="F488" s="3" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="G488" s="3" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="H488" s="3" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="I488" s="3" t="n">
+        <v>48.91</v>
+      </c>
       <c r="J488" s="4">
         <f>IF(OR(D488="",G488=""),"",G488-D488)</f>
         <v/>
@@ -30264,14 +33564,24 @@
         <f>IF(OR(F488="",I488=""),"",I488-F488)</f>
         <v/>
       </c>
-      <c r="M488" s="3" t="n"/>
-      <c r="N488" s="3" t="n"/>
-      <c r="O488" s="3" t="n"/>
-      <c r="P488" s="3" t="n"/>
+      <c r="M488" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N488" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O488" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P488" s="3" t="n">
+        <v>13.9</v>
+      </c>
       <c r="Q488" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R488" s="3" t="n"/>
+      <c r="R488" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="S488" s="3">
         <f>IF(OR(Q488="",R488="",Q488=0),"",R488/Q488*100)</f>
         <v/>
@@ -30338,7 +33648,9 @@
       <c r="Q489" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="R489" s="3" t="n"/>
+      <c r="R489" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="S489" s="3">
         <f>IF(OR(Q489="",R489="",Q489=0),"",R489/Q489*100)</f>
         <v/>
@@ -30360,12 +33672,24 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="D490" s="3" t="n"/>
-      <c r="E490" s="3" t="n"/>
-      <c r="F490" s="3" t="n"/>
-      <c r="G490" s="3" t="n"/>
-      <c r="H490" s="3" t="n"/>
-      <c r="I490" s="3" t="n"/>
+      <c r="D490" s="3" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="E490" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F490" s="3" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="G490" s="3" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="H490" s="3" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="I490" s="3" t="n">
+        <v>11.67</v>
+      </c>
       <c r="J490" s="4">
         <f>IF(OR(D490="",G490=""),"",G490-D490)</f>
         <v/>
@@ -30378,14 +33702,24 @@
         <f>IF(OR(F490="",I490=""),"",I490-F490)</f>
         <v/>
       </c>
-      <c r="M490" s="3" t="n"/>
-      <c r="N490" s="3" t="n"/>
-      <c r="O490" s="3" t="n"/>
-      <c r="P490" s="3" t="n"/>
+      <c r="M490" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N490" s="3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O490" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P490" s="3" t="n">
+        <v>12.87</v>
+      </c>
       <c r="Q490" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="R490" s="3" t="n"/>
+      <c r="R490" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="S490" s="3">
         <f>IF(OR(Q490="",R490="",Q490=0),"",R490/Q490*100)</f>
         <v/>
@@ -30407,12 +33741,24 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="D491" s="3" t="n"/>
-      <c r="E491" s="3" t="n"/>
-      <c r="F491" s="3" t="n"/>
-      <c r="G491" s="3" t="n"/>
-      <c r="H491" s="3" t="n"/>
-      <c r="I491" s="3" t="n"/>
+      <c r="D491" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E491" s="3" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F491" s="3" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G491" s="3" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="H491" s="3" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="I491" s="3" t="n">
+        <v>4.86</v>
+      </c>
       <c r="J491" s="4">
         <f>IF(OR(D491="",G491=""),"",G491-D491)</f>
         <v/>
@@ -30425,14 +33771,24 @@
         <f>IF(OR(F491="",I491=""),"",I491-F491)</f>
         <v/>
       </c>
-      <c r="M491" s="3" t="n"/>
-      <c r="N491" s="3" t="n"/>
-      <c r="O491" s="3" t="n"/>
-      <c r="P491" s="3" t="n"/>
+      <c r="M491" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N491" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O491" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P491" s="3" t="n">
+        <v>24.49</v>
+      </c>
       <c r="Q491" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="R491" s="3" t="n"/>
+      <c r="R491" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="S491" s="3">
         <f>IF(OR(Q491="",R491="",Q491=0),"",R491/Q491*100)</f>
         <v/>
@@ -30568,7 +33924,9 @@
       <c r="Q493" s="3" t="n">
         <v>104.5</v>
       </c>
-      <c r="R493" s="3" t="n"/>
+      <c r="R493" s="3" t="n">
+        <v>1.819</v>
+      </c>
       <c r="S493" s="3">
         <f>IF(OR(Q493="",R493="",Q493=0),"",R493/Q493*100)</f>
         <v/>
@@ -30629,11 +33987,15 @@
       <c r="O494" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="P494" s="3" t="n"/>
+      <c r="P494" s="3" t="n">
+        <v>13.15</v>
+      </c>
       <c r="Q494" s="3" t="n">
         <v>39.9</v>
       </c>
-      <c r="R494" s="3" t="n"/>
+      <c r="R494" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="S494" s="3">
         <f>IF(OR(Q494="",R494="",Q494=0),"",R494/Q494*100)</f>
         <v/>
@@ -30860,12 +34222,24 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="D498" s="3" t="n"/>
-      <c r="E498" s="3" t="n"/>
-      <c r="F498" s="3" t="n"/>
-      <c r="G498" s="3" t="n"/>
-      <c r="H498" s="3" t="n"/>
-      <c r="I498" s="3" t="n"/>
+      <c r="D498" s="3" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="E498" s="3" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F498" s="3" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G498" s="3" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="H498" s="3" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="I498" s="3" t="n">
+        <v>15.1</v>
+      </c>
       <c r="J498" s="4">
         <f>IF(OR(D498="",G498=""),"",G498-D498)</f>
         <v/>
@@ -30878,14 +34252,24 @@
         <f>IF(OR(F498="",I498=""),"",I498-F498)</f>
         <v/>
       </c>
-      <c r="M498" s="3" t="n"/>
-      <c r="N498" s="3" t="n"/>
-      <c r="O498" s="3" t="n"/>
-      <c r="P498" s="3" t="n"/>
+      <c r="M498" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N498" s="3" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O498" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P498" s="3" t="n">
+        <v>12.18</v>
+      </c>
       <c r="Q498" s="3" t="n">
         <v>132.5</v>
       </c>
-      <c r="R498" s="3" t="n"/>
+      <c r="R498" s="3" t="n">
+        <v>6.2</v>
+      </c>
       <c r="S498" s="3">
         <f>IF(OR(Q498="",R498="",Q498=0),"",R498/Q498*100)</f>
         <v/>
@@ -31021,7 +34405,9 @@
       <c r="Q500" s="3" t="n">
         <v>28.75</v>
       </c>
-      <c r="R500" s="3" t="n"/>
+      <c r="R500" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="S500" s="3">
         <f>IF(OR(Q500="",R500="",Q500=0),"",R500/Q500*100)</f>
         <v/>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>26.65</v>
+        <v>26.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.85</v>
+        <v>28.95</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.7</v>
+        <v>41.95</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.8</v>
+        <v>81.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>57.8</v>
+        <v>60.1</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>188.5</v>
+        <v>207</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>11.85</v>
+        <v>12.3</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.65</v>
+        <v>11.9</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>7.9</v>
+        <v>7.99</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>58</v>
+        <v>60.3</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>29</v>
+        <v>28.55</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.45</v>
+        <v>24.85</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>65.3</v>
+        <v>66.7</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>199.5</v>
+        <v>202</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>70.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>165.5</v>
+        <v>166</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>100.5</v>
+        <v>102</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2790,7 +2790,7 @@
         <v>59.91</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>2</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1460</v>
+        <v>1470</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.45</v>
+        <v>39.4</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.6</v>
+        <v>37.6</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.35</v>
+        <v>38</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>41.25</v>
+        <v>44.2</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.5</v>
+        <v>16.55</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.65</v>
+        <v>10.7</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>126.5</v>
+        <v>128.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>158</v>
+        <v>160.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>102.5</v>
+        <v>103</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>18.95</v>
+        <v>19.05</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>194</v>
+        <v>195.5</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>58</v>
+        <v>59.7</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>36.35</v>
+        <v>35.6</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>30.45</v>
+        <v>30.4</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.05</v>
+        <v>19.35</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.65</v>
+        <v>22.8</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.2</v>
+        <v>17.25</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>345.5</v>
+        <v>353</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14285</v>
+        <v>14510</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>33.15</v>
+        <v>33</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>31.35</v>
+        <v>31.4</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>48</v>
+        <v>48.35</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>225.5</v>
+        <v>226</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31</v>
+        <v>31.55</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>125</v>
+        <v>123.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1710</v>
+        <v>1750</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.4</v>
+        <v>31.9</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>217.5</v>
+        <v>222</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>243</v>
+        <v>246.5</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>40.8</v>
+        <v>40.95</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>44.7</v>
+        <v>45.35</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>43.35</v>
+        <v>44.15</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2400</v>
+        <v>2415</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>122</v>
+        <v>125.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>38.55</v>
+        <v>39.65</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>179</v>
+        <v>181.5</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2030</v>
+        <v>2055</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>86.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>199.5</v>
+        <v>219</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.15</v>
+        <v>28.1</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.05</v>
+        <v>31.4</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>41.65</v>
+        <v>42.65</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>925</v>
+        <v>971</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>145</v>
+        <v>146.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1965</v>
+        <v>1980</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>48.55</v>
+        <v>49.2</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>50.4</v>
+        <v>51.3</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>43.05</v>
+        <v>44.8</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>971</v>
+        <v>1040</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>27.7</v>
+        <v>27.65</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>122.5</v>
+        <v>124</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>347.5</v>
+        <v>351.5</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>328.5</v>
+        <v>332.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5595</v>
+        <v>5895</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45.1</v>
+        <v>45.15</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>65.2</v>
+        <v>66.8</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.15</v>
+        <v>25.65</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>55.8</v>
+        <v>56.1</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>25.65</v>
+        <v>25.5</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>136.5</v>
+        <v>136</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>144</v>
+        <v>151.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>90.8</v>
+        <v>99.8</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>249.5</v>
+        <v>252</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>239.5</v>
+        <v>244</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>3735</v>
+        <v>3945</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>419.5</v>
+        <v>428</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>137.5</v>
+        <v>139.5</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>535</v>
+        <v>570</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>218</v>
+        <v>218.5</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>204.5</v>
+        <v>206.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>120.5</v>
+        <v>125.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>120.5</v>
+        <v>122</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>137</v>
+        <v>150.5</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>258</v>
+        <v>262.5</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>40.55</v>
+        <v>41.5</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>268</v>
+        <v>269.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>171</v>
+        <v>181.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.85</v>
+        <v>32.1</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.35</v>
+        <v>19.6</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>96.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>168</v>
+        <v>171.5</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>36.7</v>
+        <v>34.85</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>63.6</v>
+        <v>57.6</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>126.5</v>
+        <v>115</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.2</v>
+        <v>43</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.3</v>
+        <v>26.35</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>95.5</v>
+        <v>91.2</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>170.5</v>
+        <v>179</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.55</v>
+        <v>46.35</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>180.5</v>
+        <v>181</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.45</v>
+        <v>17.55</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>24.65</v>
+        <v>27.1</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>270</v>
+        <v>273.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>5720</v>
+        <v>6290</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>130</v>
+        <v>129.5</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>130.5</v>
+        <v>132.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>96.8</v>
+        <v>102</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>2950</v>
+        <v>3155</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>93</v>
+        <v>92.5</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>320.5</v>
+        <v>314.5</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>66</v>
+        <v>66.3</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>110.5</v>
+        <v>110</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>282.5</v>
+        <v>288.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>45.95</v>
+        <v>45.4</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>172</v>
+        <v>180.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>1095</v>
+        <v>1160</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>2960</v>
+        <v>3255</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>166</v>
+        <v>165.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2260</v>
+        <v>2485</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>180</v>
+        <v>185.5</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>674</v>
+        <v>716</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>835</v>
+        <v>881</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>135.5</v>
+        <v>136.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>194</v>
+        <v>197.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>178.5</v>
+        <v>182</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>418.5</v>
+        <v>416</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>213</v>
+        <v>217.5</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>168</v>
+        <v>173.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>135</v>
+        <v>140.5</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>311</v>
+        <v>333.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>27.25</v>
+        <v>27.75</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>690</v>
+        <v>759</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>285.5</v>
+        <v>287.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>175</v>
+        <v>180.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5570</v>
+        <v>6125</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>533</v>
+        <v>574</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>46.8</v>
+        <v>46.4</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1270</v>
+        <v>1345</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2195</v>
+        <v>2410</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1605</v>
+        <v>1625</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>656</v>
+        <v>685</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.1</v>
+        <v>17.05</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>693</v>
+        <v>741</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>251.5</v>
+        <v>255.5</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>225.5</v>
+        <v>227</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>247.5</v>
+        <v>251.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5205</v>
+        <v>5725</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>3865</v>
+        <v>3960</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2075</v>
+        <v>2005</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>66</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>461.5</v>
+        <v>488</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>62</v>
+        <v>63.6</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>59.6</v>
+        <v>62.7</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>109.5</v>
+        <v>114</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.8</v>
+        <v>78.2</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>32.45</v>
+        <v>32.1</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>63.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>35.15</v>
+        <v>34.65</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>46.95</v>
+        <v>47.8</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>44.95</v>
+        <v>46.6</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>343.5</v>
+        <v>344.5</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>307</v>
+        <v>324.5</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>206.5</v>
+        <v>209</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>260.5</v>
+        <v>261</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>102.5</v>
+        <v>101</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>34.55</v>
+        <v>37.3</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>59.8</v>
+        <v>60.2</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>245</v>
+        <v>255.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>88.8</v>
+        <v>89.3</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>164.5</v>
+        <v>165.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>445</v>
+        <v>489.5</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.75</v>
+        <v>33.55</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.4</v>
+        <v>21.45</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1415</v>
+        <v>1455</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>15400</v>
+        <v>15690</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>31.45</v>
+        <v>34.55</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>77</v>
+        <v>80.8</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>150.5</v>
+        <v>152</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>115.5</v>
+        <v>117</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>241.5</v>
+        <v>248</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>102.5</v>
+        <v>105.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>53.9</v>
+        <v>54.3</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>398</v>
+        <v>399.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>195</v>
+        <v>192.5</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>169</v>
+        <v>185.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>203.5</v>
+        <v>198</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>48.05</v>
+        <v>48.35</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>67.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>66.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>56.7</v>
+        <v>58.6</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>139.5</v>
+        <v>142.5</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>530</v>
+        <v>583</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>181.5</v>
+        <v>181</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>154</v>
+        <v>161.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5600</v>
+        <v>5040</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>273.5</v>
+        <v>286</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>198.5</v>
+        <v>204</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>61.9</v>
+        <v>66.3</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>199.5</v>
+        <v>208</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1485</v>
+        <v>1530</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>181.5</v>
+        <v>199.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>44</v>
+        <v>45.3</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>77</v>
+        <v>78.2</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>233.5</v>
+        <v>242</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>383.5</v>
+        <v>400</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>451.5</v>
+        <v>469</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>26.45</v>
+        <v>26.3</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1490</v>
+        <v>1585</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>423</v>
+        <v>454.5</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>372.5</v>
+        <v>379</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>71</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2680</v>
+        <v>2620</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6255</v>
+        <v>6025</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>136</v>
+        <v>141.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>876</v>
+        <v>916</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>77.5</v>
+        <v>82.5</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>70.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>61.6</v>
+        <v>62.1</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>138.5</v>
+        <v>139.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>247.5</v>
+        <v>260.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>980</v>
+        <v>1005</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>414.5</v>
+        <v>433</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>346</v>
+        <v>355.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>6440</v>
+        <v>6785</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>264</v>
+        <v>264.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>270.5</v>
+        <v>276.5</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>363.5</v>
+        <v>363</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>960</v>
+        <v>999</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>139.5</v>
+        <v>144</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.8</v>
+        <v>56.3</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1065</v>
+        <v>1040</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>420.5</v>
+        <v>458.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>269</v>
+        <v>268.5</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>1845</v>
+        <v>2025</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>491</v>
+        <v>526</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>159.5</v>
+        <v>175</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>16.35</v>
+        <v>16.7</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>306</v>
+        <v>313.5</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>1355</v>
+        <v>1490</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.25</v>
+        <v>31.7</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1635</v>
+        <v>1610</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2890</v>
+        <v>3100</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>382</v>
+        <v>376.5</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2350</v>
+        <v>2370</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>283</v>
+        <v>291.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6210</v>
+        <v>6335</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.85</v>
+        <v>16.9</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>258.5</v>
+        <v>273.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>356.5</v>
+        <v>366</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1520</v>
+        <v>1580</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>292.5</v>
+        <v>296</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>404</v>
+        <v>418.5</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>169.5</v>
+        <v>178</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>242</v>
+        <v>246.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>179</v>
+        <v>192.5</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>291.5</v>
+        <v>320.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>103.5</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>49.3</v>
+        <v>51.3</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>115.5</v>
+        <v>117</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>215</v>
+        <v>216.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>45.65</v>
+        <v>45.8</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>94</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>61.5</v>
+        <v>62.8</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>87.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>324</v>
+        <v>350.5</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>177.5</v>
+        <v>186</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2085</v>
+        <v>2125</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>429</v>
+        <v>449.5</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>38.15</v>
+        <v>37.7</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>27.2</v>
+        <v>27.25</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>251.5</v>
+        <v>255</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>367.5</v>
+        <v>373.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1215</v>
+        <v>1195</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>73</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>25.1</v>
+        <v>25.05</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29</v>
+        <v>29.15</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>70</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>86.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33853,7 +33853,7 @@
         <v>15.67</v>
       </c>
       <c r="Q492" s="3" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="R492" s="3" t="n">
         <v>5.7</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.9</v>
+        <v>39.95</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63.2</v>
+        <v>63.7</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55</v>
+        <v>55.3</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>132.5</v>
+        <v>133</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>86.8</v>
+        <v>85.8</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.75</v>
+        <v>28.9</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>94.8</v>
+        <v>95.3</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>109</v>
+        <v>108.5</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>77.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.95</v>
+        <v>28.85</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.95</v>
+        <v>42.15</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>60.1</v>
+        <v>63.1</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>207</v>
+        <v>227.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.9</v>
+        <v>12.15</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>7.99</v>
+        <v>8.16</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>82.3</v>
+        <v>81.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>60.3</v>
+        <v>63.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.55</v>
+        <v>28.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.85</v>
+        <v>25</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>66.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>17.9</v>
+        <v>18.05</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.75</v>
+        <v>13.85</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>197</v>
+        <v>198.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>166</v>
+        <v>170.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>717</v>
+        <v>770</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>50.1</v>
+        <v>51.1</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1470</v>
+        <v>1480</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>39.4</v>
+        <v>38.9</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>37.6</v>
+        <v>38.2</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>38</v>
+        <v>37.75</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>44.2</v>
+        <v>43.5</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>39.9</v>
+        <v>39.85</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>88</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>160.5</v>
+        <v>160</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>195.5</v>
+        <v>194</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>59.7</v>
+        <v>59.2</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>35.6</v>
+        <v>35.95</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>118</v>
+        <v>116.5</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.35</v>
+        <v>25.45</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.55</v>
+        <v>13.5</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.35</v>
+        <v>19.15</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>82.2</v>
+        <v>80.8</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.25</v>
+        <v>17.15</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>50</v>
+        <v>48.65</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>353</v>
+        <v>359.5</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14510</v>
+        <v>14340</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>149</v>
+        <v>149.5</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.2</v>
+        <v>27.75</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.25</v>
+        <v>17.1</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>28.8</v>
+        <v>28.65</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>48.35</v>
+        <v>47.85</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.55</v>
+        <v>31.6</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>123.5</v>
+        <v>118.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1750</v>
+        <v>1770</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>161</v>
+        <v>160.5</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>246.5</v>
+        <v>252</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>40.95</v>
+        <v>39.75</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>45.35</v>
+        <v>46.7</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>44.15</v>
+        <v>43.8</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2415</v>
+        <v>2410</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>125.5</v>
+        <v>127.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>39.65</v>
+        <v>39.2</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>181.5</v>
+        <v>186</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2055</v>
+        <v>2090</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>61.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>42.65</v>
+        <v>44.4</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>66.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>146.5</v>
+        <v>147.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>49.2</v>
+        <v>48.55</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>44.8</v>
+        <v>45.55</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>27.65</v>
+        <v>29.2</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>124</v>
+        <v>130.5</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>351.5</v>
+        <v>345</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>332.5</v>
+        <v>333.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5895</v>
+        <v>5500</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45.15</v>
+        <v>46.65</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>66.8</v>
+        <v>66.5</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.65</v>
+        <v>25.75</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>25.5</v>
+        <v>25.25</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>136</v>
+        <v>135.5</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>151.5</v>
+        <v>159.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>99.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>244</v>
+        <v>247.5</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>3945</v>
+        <v>3865</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>218.5</v>
+        <v>229</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>206.5</v>
+        <v>207.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>125.5</v>
+        <v>126.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>150.5</v>
+        <v>146.5</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>262.5</v>
+        <v>259</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>41.5</v>
+        <v>40.05</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>269.5</v>
+        <v>285</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>181.5</v>
+        <v>185</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>32.1</v>
+        <v>31.95</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>35.8</v>
+        <v>35.65</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.6</v>
+        <v>19.35</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>48</v>
+        <v>47.75</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.9</v>
+        <v>35.25</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>231</v>
+        <v>232.5</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>34.85</v>
+        <v>34.4</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>72</v>
+        <v>74.3</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>57.6</v>
+        <v>57.9</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>115</v>
+        <v>113.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>43</v>
+        <v>42.75</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>69</v>
+        <v>70.3</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>91.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>179</v>
+        <v>178.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>46.35</v>
+        <v>45.85</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>235</v>
+        <v>233.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.6</v>
+        <v>22.35</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.55</v>
+        <v>17.4</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>223</v>
+        <v>220.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>59.3</v>
+        <v>58.6</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>273.5</v>
+        <v>274</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>6290</v>
+        <v>6915</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>129.5</v>
+        <v>129</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>87.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>132.5</v>
+        <v>132</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>102</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3155</v>
+        <v>3340</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>92.5</v>
+        <v>91.5</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>314.5</v>
+        <v>320</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>614</v>
+        <v>675</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>66.3</v>
+        <v>65.5</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>288.5</v>
+        <v>296.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>180.5</v>
+        <v>176.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>196.5</v>
+        <v>193</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>185.5</v>
+        <v>192</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3255</v>
+        <v>3370</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>125</v>
+        <v>123.5</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>165.5</v>
+        <v>168.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>405</v>
+        <v>445.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2485</v>
+        <v>2490</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>185.5</v>
+        <v>182.5</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>716</v>
+        <v>742</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>881</v>
+        <v>914</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>364</v>
+        <v>397.5</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>136.5</v>
+        <v>138</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>197.5</v>
+        <v>198</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>182</v>
+        <v>179.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>180.5</v>
+        <v>180</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>416</v>
+        <v>415.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>217.5</v>
+        <v>219.5</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>173.5</v>
+        <v>176.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>140.5</v>
+        <v>142</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>108</v>
+        <v>111.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>209.5</v>
+        <v>217</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>202</v>
+        <v>204.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>650</v>
+        <v>704</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>333.5</v>
+        <v>351</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>27.75</v>
+        <v>27.85</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>759</v>
+        <v>834</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>180.5</v>
+        <v>182.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>6125</v>
+        <v>5920</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>46.4</v>
+        <v>46.25</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1345</v>
+        <v>1425</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>280</v>
+        <v>281.5</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2410</v>
+        <v>2650</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>255.5</v>
+        <v>254</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>159.5</v>
+        <v>160</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>251.5</v>
+        <v>248.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5725</v>
+        <v>5645</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>3960</v>
+        <v>3870</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2005</v>
+        <v>2055</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>283</v>
+        <v>278.5</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>488</v>
+        <v>490.5</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>108</v>
+        <v>101.5</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>42</v>
+        <v>42.45</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>62.7</v>
+        <v>63.5</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>114</v>
+        <v>116.5</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>78.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.9</v>
+        <v>29.85</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>32.1</v>
+        <v>31.85</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>169.5</v>
+        <v>168</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>203</v>
+        <v>215.5</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>463</v>
+        <v>468.5</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>301</v>
+        <v>302.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>34.65</v>
+        <v>32.2</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>47.8</v>
+        <v>47.15</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>755</v>
+        <v>789</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>46.6</v>
+        <v>45.8</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>344.5</v>
+        <v>345</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>324.5</v>
+        <v>329</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>261</v>
+        <v>265.5</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>255.5</v>
+        <v>265.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>165.5</v>
+        <v>165</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>272.5</v>
+        <v>275.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>489.5</v>
+        <v>538</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.5</v>
+        <v>55.9</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.55</v>
+        <v>33.6</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.45</v>
+        <v>21.35</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>91.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>15690</v>
+        <v>15305</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>34.55</v>
+        <v>38</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>80.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>117</v>
+        <v>116.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>64</v>
+        <v>63.8</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>54.3</v>
+        <v>52.3</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>117</v>
+        <v>114.5</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>185.5</v>
+        <v>186</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>74.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.4</v>
+        <v>14.85</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>399.5</v>
+        <v>409</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>290</v>
+        <v>295.5</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>192.5</v>
+        <v>193</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>185.5</v>
+        <v>187.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>198</v>
+        <v>217.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>98.2</v>
+        <v>95.5</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>48.35</v>
+        <v>47.9</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1300</v>
+        <v>1430</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>500</v>
+        <v>497.5</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>58.6</v>
+        <v>59.2</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>142.5</v>
+        <v>140.5</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>161.5</v>
+        <v>177.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5040</v>
+        <v>5090</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>66.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1530</v>
+        <v>1445</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>199.5</v>
+        <v>206</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>45.3</v>
+        <v>45.15</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>241</v>
+        <v>250.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1030</v>
+        <v>1045</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>398</v>
+        <v>393.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>469</v>
+        <v>470.5</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1610</v>
+        <v>1595</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1585</v>
+        <v>1560</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>454.5</v>
+        <v>452</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>457</v>
+        <v>439.5</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2620</v>
+        <v>2740</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6025</v>
+        <v>6105</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>82.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>61.9</v>
+        <v>63.1</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>146.5</v>
+        <v>148</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>139.5</v>
+        <v>142</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>260.5</v>
+        <v>266</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1005</v>
+        <v>1075</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>433</v>
+        <v>442.5</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>355.5</v>
+        <v>355</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>6785</v>
+        <v>6815</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>264.5</v>
+        <v>277.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>276.5</v>
+        <v>281.5</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1135</v>
+        <v>1245</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>363</v>
+        <v>351.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>195</v>
+        <v>194.5</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>999</v>
+        <v>1095</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>144</v>
+        <v>144.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>70.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>458.5</v>
+        <v>462.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>268.5</v>
+        <v>270.5</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2025</v>
+        <v>2225</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>175</v>
+        <v>173.5</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>16.7</v>
+        <v>16.55</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>313.5</v>
+        <v>314</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.7</v>
+        <v>31.35</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1610</v>
+        <v>1595</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>3100</v>
+        <v>2870</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>376.5</v>
+        <v>373</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2370</v>
+        <v>2450</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1805</v>
+        <v>1985</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>291.5</v>
+        <v>290</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6335</v>
+        <v>6345</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.9</v>
+        <v>17.05</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>273.5</v>
+        <v>298</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>366</v>
+        <v>383.5</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>928</v>
+        <v>957</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1580</v>
+        <v>1650</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>418.5</v>
+        <v>422.5</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>246.5</v>
+        <v>248.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>192.5</v>
+        <v>199</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>320.5</v>
+        <v>352.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1180</v>
+        <v>1295</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>103.5</v>
+        <v>104.5</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>262</v>
+        <v>261.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>216.5</v>
+        <v>218</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>45.8</v>
+        <v>46.15</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>350.5</v>
+        <v>364.5</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2125</v>
+        <v>2155</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>449.5</v>
+        <v>494</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.7</v>
+        <v>37.25</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>255</v>
+        <v>255.5</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>373.5</v>
+        <v>368.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>144</v>
+        <v>144.5</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>57.1</v>
+        <v>57.4</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1195</v>
+        <v>1310</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.35</v>
+        <v>15.45</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29.15</v>
+        <v>29</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>104.5</v>
+        <v>105</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.95</v>
+        <v>39.8</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63.7</v>
+        <v>63.1</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>85.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>95.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.1</v>
+        <v>34.55</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>26.6</v>
+        <v>26.45</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.85</v>
+        <v>28.65</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>81</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>227.5</v>
+        <v>220.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.4</v>
+        <v>12.05</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>12.15</v>
+        <v>11.85</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>63.2</v>
+        <v>62.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.05</v>
+        <v>17.85</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.85</v>
+        <v>13.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>314</v>
+        <v>311.5</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>198.5</v>
+        <v>195.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>212.5</v>
+        <v>205.5</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>170.5</v>
+        <v>168</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1480</v>
+        <v>1415</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>38.2</v>
+        <v>37.85</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.75</v>
+        <v>38.1</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>39.85</v>
+        <v>39.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.55</v>
+        <v>16.7</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>75.8</v>
+        <v>77.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>128</v>
+        <v>125.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>19.05</v>
+        <v>19.1</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>59.2</v>
+        <v>60.8</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>35.95</v>
+        <v>34.8</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>116.5</v>
+        <v>125.5</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.45</v>
+        <v>25.15</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>30.6</v>
+        <v>29.9</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.15</v>
+        <v>19.05</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.15</v>
+        <v>17.05</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>65.2</v>
+        <v>64.5</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.85</v>
+        <v>13.65</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>48.65</v>
+        <v>48.4</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>359.5</v>
+        <v>354</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14340</v>
+        <v>14300</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>149.5</v>
+        <v>144</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>32.9</v>
+        <v>31.75</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>27.75</v>
+        <v>28.2</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>31.1</v>
+        <v>30.55</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.1</v>
+        <v>16.85</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>28.65</v>
+        <v>28.4</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54</v>
+        <v>53.4</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.5</v>
+        <v>63.1</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.85</v>
+        <v>48</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>301</v>
+        <v>317.5</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>118.5</v>
+        <v>130</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>160.5</v>
+        <v>164</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>39.75</v>
+        <v>39.7</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>43.8</v>
+        <v>44.1</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>127.5</v>
+        <v>126.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>39.2</v>
+        <v>40</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>186</v>
+        <v>181.5</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2090</v>
+        <v>2125</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>240</v>
+        <v>239.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.2</v>
+        <v>30.85</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>147.5</v>
+        <v>145.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>48.55</v>
+        <v>47.75</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>50.7</v>
+        <v>51.8</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>45.55</v>
+        <v>44.8</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1030</v>
+        <v>1130</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>130.5</v>
+        <v>133</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>333.5</v>
+        <v>332.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5500</v>
+        <v>5490</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>72.5</v>
+        <v>73.3</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>46.65</v>
+        <v>44.5</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.75</v>
+        <v>25.9</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>25.25</v>
+        <v>25.85</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>159.5</v>
+        <v>163.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>114</v>
+        <v>118.5</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>247.5</v>
+        <v>270</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>3865</v>
+        <v>3985</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>139.5</v>
+        <v>138.5</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>229</v>
+        <v>232.5</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>207.5</v>
+        <v>206.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>126.5</v>
+        <v>125.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>125</v>
+        <v>129.5</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>146.5</v>
+        <v>154</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>40.05</v>
+        <v>40.2</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>285</v>
+        <v>313.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>185</v>
+        <v>181.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.5</v>
+        <v>40.55</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.95</v>
+        <v>31.7</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>12.05</v>
+        <v>11.95</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>35.65</v>
+        <v>35.3</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.35</v>
+        <v>19.25</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>91.5</v>
+        <v>91</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>34.5</v>
+        <v>34.35</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>47.75</v>
+        <v>47</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>35.25</v>
+        <v>34.95</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>171.5</v>
+        <v>172</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>232.5</v>
+        <v>231.5</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>34.4</v>
+        <v>35.05</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>74.3</v>
+        <v>72.2</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>52.3</v>
+        <v>51.7</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>57.9</v>
+        <v>56.2</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.8</v>
+        <v>20.35</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>113.5</v>
+        <v>111.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.75</v>
+        <v>41.8</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.35</v>
+        <v>26.25</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>70.3</v>
+        <v>67.8</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>178.5</v>
+        <v>174</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>21.1</v>
+        <v>20.85</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.85</v>
+        <v>45.35</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>181</v>
+        <v>179.5</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>233.5</v>
+        <v>234</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.35</v>
+        <v>22.1</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.4</v>
+        <v>17.45</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>220.5</v>
+        <v>218.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>27.2</v>
+        <v>25.85</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>274</v>
+        <v>269.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>6915</v>
+        <v>7065</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>132</v>
+        <v>131.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>138</v>
+        <v>138.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>91.5</v>
+        <v>90.3</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>65.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>112</v>
+        <v>111.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>296.5</v>
+        <v>293.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>45.2</v>
+        <v>45.05</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>176.5</v>
+        <v>180.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>1180</v>
+        <v>1110</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>192</v>
+        <v>188.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3370</v>
+        <v>3305</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>123.5</v>
+        <v>124</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>168.5</v>
+        <v>174</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>445.5</v>
+        <v>439</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2490</v>
+        <v>2485</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>182.5</v>
+        <v>181</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>67.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>776</v>
+        <v>754</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>742</v>
+        <v>783</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>397.5</v>
+        <v>400</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>138</v>
+        <v>137.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>179.5</v>
+        <v>178</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>180</v>
+        <v>181.5</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>415.5</v>
+        <v>412</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>219.5</v>
+        <v>235</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>176.5</v>
+        <v>186.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>142</v>
+        <v>140.5</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>111.5</v>
+        <v>116.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1060</v>
+        <v>1140</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>204.5</v>
+        <v>199.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>27.85</v>
+        <v>28.15</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>834</v>
+        <v>917</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5920</v>
+        <v>6015</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>578</v>
+        <v>635</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>46.25</v>
+        <v>48.6</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1425</v>
+        <v>1510</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>281.5</v>
+        <v>286</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2650</v>
+        <v>2540</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1625</v>
+        <v>1735</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.05</v>
+        <v>17.5</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>254</v>
+        <v>252.5</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>248.5</v>
+        <v>243.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5645</v>
+        <v>5785</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>3870</v>
+        <v>4065</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2055</v>
+        <v>2260</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>278.5</v>
+        <v>277.5</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>490.5</v>
+        <v>500</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>101.5</v>
+        <v>100</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.65</v>
+        <v>19.4</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>42.45</v>
+        <v>42</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>63.5</v>
+        <v>62.6</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>116.5</v>
+        <v>125</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.85</v>
+        <v>29.9</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>31.85</v>
+        <v>31.7</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>168</v>
+        <v>167.5</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>215.5</v>
+        <v>216</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>468.5</v>
+        <v>467</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>302.5</v>
+        <v>300.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>32.2</v>
+        <v>32.55</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>213</v>
+        <v>213.5</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>47.15</v>
+        <v>46.95</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>45.8</v>
+        <v>45.65</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>228</v>
+        <v>249.5</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>265.5</v>
+        <v>265</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>265.5</v>
+        <v>272.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>477</v>
+        <v>480.5</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>275.5</v>
+        <v>273.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>55.9</v>
+        <v>56.4</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.35</v>
+        <v>21.3</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>302</v>
+        <v>303.5</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1465</v>
+        <v>1450</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>15305</v>
+        <v>15630</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>323</v>
+        <v>321.5</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1490</v>
+        <v>1470</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>38</v>
+        <v>34.2</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>116.5</v>
+        <v>116</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>262</v>
+        <v>264.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>106.5</v>
+        <v>112</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>73</v>
+        <v>74.8</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>182</v>
+        <v>183.5</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.8</v>
+        <v>62.8</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.7</v>
+        <v>75.3</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>52.3</v>
+        <v>51.5</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>114.5</v>
+        <v>113</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.85</v>
+        <v>14.5</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>409</v>
+        <v>405.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51.3</v>
+        <v>51</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>295.5</v>
+        <v>297</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>193</v>
+        <v>192.5</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>187.5</v>
+        <v>182.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>117</v>
+        <v>116.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>217.5</v>
+        <v>239</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>95.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.9</v>
+        <v>47.55</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1430</v>
+        <v>1365</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>69.5</v>
+        <v>68.8</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>68.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>497.5</v>
+        <v>492.5</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>308</v>
+        <v>309.5</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>140.5</v>
+        <v>138.5</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>182.5</v>
+        <v>181</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>177.5</v>
+        <v>175</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>206</v>
+        <v>201.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>45.15</v>
+        <v>45.3</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>77.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>250.5</v>
+        <v>248</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>417</v>
+        <v>400.5</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>78.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>393.5</v>
+        <v>390</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>470.5</v>
+        <v>458</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1595</v>
+        <v>1615</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>26.7</v>
+        <v>26.65</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1560</v>
+        <v>1545</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>452</v>
+        <v>453.5</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>71.8</v>
+        <v>74.3</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>439.5</v>
+        <v>435</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>72.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2740</v>
+        <v>2680</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6105</v>
+        <v>6250</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>141.5</v>
+        <v>144.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>917</v>
+        <v>895</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>63.1</v>
+        <v>65</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>322</v>
+        <v>322.5</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>620</v>
+        <v>682</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>61.6</v>
+        <v>60.5</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>266</v>
+        <v>275.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>442.5</v>
+        <v>437</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>355</v>
+        <v>359.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>277.5</v>
+        <v>272.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>281.5</v>
+        <v>289.5</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1245</v>
+        <v>1200</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>351.5</v>
+        <v>353.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>144.5</v>
+        <v>138.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>56.2</v>
+        <v>55.1</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>64.8</v>
+        <v>64.2</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>462.5</v>
+        <v>461</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>270.5</v>
+        <v>271</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2225</v>
+        <v>2345</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>173.5</v>
+        <v>169</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>16.55</v>
+        <v>16.15</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>103</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>281</v>
+        <v>292.5</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.35</v>
+        <v>31.15</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1595</v>
+        <v>1495</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2870</v>
+        <v>2995</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2450</v>
+        <v>2300</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1985</v>
+        <v>1790</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>290</v>
+        <v>290.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6345</v>
+        <v>6490</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>17.05</v>
+        <v>16.95</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>298</v>
+        <v>327.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>383.5</v>
+        <v>379</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>162</v>
+        <v>159.5</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>422.5</v>
+        <v>454</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>248.5</v>
+        <v>249</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>199</v>
+        <v>189.5</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>352.5</v>
+        <v>343.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>104.5</v>
+        <v>103</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>159</v>
+        <v>160.5</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>261.5</v>
+        <v>260</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>218</v>
+        <v>220.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>110</v>
+        <v>109.5</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>46.15</v>
+        <v>46</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>92.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>197.5</v>
+        <v>195</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>63.3</v>
+        <v>62.7</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>90.3</v>
+        <v>90.5</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>364.5</v>
+        <v>372</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>185</v>
+        <v>187.5</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>234</v>
+        <v>232.5</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>494</v>
+        <v>543</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.25</v>
+        <v>36.75</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>255.5</v>
+        <v>250</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>368.5</v>
+        <v>366.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>144.5</v>
+        <v>141.5</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>105</v>
+        <v>94.3</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.8</v>
+        <v>24.35</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.45</v>
+        <v>15.35</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29</v>
+        <v>29.05</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.8</v>
+        <v>39.85</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>41.6</v>
+        <v>40.6</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>26.45</v>
+        <v>26.65</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>108.5</v>
+        <v>107.5</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>75.7</v>
+        <v>76.2</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.65</v>
+        <v>28.85</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>42.15</v>
+        <v>41.8</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>62.7</v>
+        <v>66.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>220.5</v>
+        <v>242.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.05</v>
+        <v>12.65</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.85</v>
+        <v>12.15</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.050000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>62.1</v>
+        <v>68.3</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.1</v>
+        <v>28.35</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>17.85</v>
+        <v>18.15</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>311.5</v>
+        <v>309</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>195.5</v>
+        <v>194.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>205.5</v>
+        <v>200</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>50.3</v>
+        <v>49.6</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>37.85</v>
+        <v>37.7</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>38.1</v>
+        <v>37.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>43.9</v>
+        <v>43.35</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>39.8</v>
+        <v>39.95</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>77.7</v>
+        <v>82.5</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.75</v>
+        <v>10.9</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.6</v>
+        <v>44.55</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>86.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>125.5</v>
+        <v>126</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>159.5</v>
+        <v>164</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>125.5</v>
+        <v>126.5</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.15</v>
+        <v>25.2</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.9</v>
+        <v>29.85</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.05</v>
+        <v>18.95</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.5</v>
+        <v>63.8</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.65</v>
+        <v>14.15</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14300</v>
+        <v>14180</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>144</v>
+        <v>141.5</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.75</v>
+        <v>31.25</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.55</v>
+        <v>30.9</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>16.85</v>
+        <v>17.1</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>28.4</v>
+        <v>29.75</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>48</v>
+        <v>47.4</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>230</v>
+        <v>230.5</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>317.5</v>
+        <v>305</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.8</v>
+        <v>32.35</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>241</v>
+        <v>248.5</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>164</v>
+        <v>159.5</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>39.7</v>
+        <v>40.35</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>597</v>
+        <v>545</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>20.4</v>
+        <v>19.9</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>126.5</v>
+        <v>126</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>40</v>
+        <v>39.05</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>181.5</v>
+        <v>182.5</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2125</v>
+        <v>2035</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>86.5</v>
+        <v>87</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>239.5</v>
+        <v>232.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.2</v>
+        <v>28.35</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>30.85</v>
+        <v>31.5</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>63.9</v>
+        <v>64.7</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>44.5</v>
+        <v>43.9</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>965</v>
+        <v>999</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>145.5</v>
+        <v>144.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2010</v>
+        <v>1960</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51.8</v>
+        <v>51.1</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>44.8</v>
+        <v>44.45</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1130</v>
+        <v>1165</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>28.5</v>
+        <v>28.05</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>69</v>
+        <v>68.7</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>332.5</v>
+        <v>338.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5490</v>
+        <v>5485</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>108</v>
+        <v>106.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>73.3</v>
+        <v>72.7</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.9</v>
+        <v>25.25</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>56.6</v>
+        <v>59.7</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>25.85</v>
+        <v>26.65</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>163.5</v>
+        <v>179.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>118.5</v>
+        <v>115.5</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>294</v>
+        <v>294.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>3985</v>
+        <v>3925</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>138.5</v>
+        <v>135.5</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>104.5</v>
+        <v>99</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>232.5</v>
+        <v>224</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>206.5</v>
+        <v>208.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>129.5</v>
+        <v>123.5</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>40.2</v>
+        <v>42.2</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>313.5</v>
+        <v>295</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>181.5</v>
+        <v>179.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.55</v>
+        <v>40.2</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.5</v>
+        <v>22.35</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.7</v>
+        <v>31.2</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>11.95</v>
+        <v>12.05</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>35.3</v>
+        <v>36.45</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.25</v>
+        <v>18.8</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>91</v>
+        <v>90.3</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>34.35</v>
+        <v>36.15</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>48.2</v>
+        <v>49.9</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>47</v>
+        <v>46.65</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.95</v>
+        <v>34.25</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>93.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>231.5</v>
+        <v>233.5</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>35.05</v>
+        <v>35.35</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>72.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>51.7</v>
+        <v>52.7</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>56.2</v>
+        <v>59.5</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.35</v>
+        <v>20.25</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>111.5</v>
+        <v>114</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.25</v>
+        <v>26</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>67.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.85</v>
+        <v>20.9</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.35</v>
+        <v>44.4</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>234</v>
+        <v>235.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.1</v>
+        <v>22.35</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.45</v>
+        <v>17.5</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>218.5</v>
+        <v>216.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>57.3</v>
+        <v>56</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>25.85</v>
+        <v>24.2</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>269.5</v>
+        <v>292.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>7065</v>
+        <v>7650</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>89.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>131.5</v>
+        <v>128.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>103</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3360</v>
+        <v>3425</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>138.5</v>
+        <v>143</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>317</v>
+        <v>312.5</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>111.5</v>
+        <v>113</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>293.5</v>
+        <v>290.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>45.05</v>
+        <v>44.55</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>180.5</v>
+        <v>175</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>1110</v>
+        <v>999</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>188.5</v>
+        <v>185.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>490</v>
+        <v>496.5</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>115.5</v>
+        <v>116</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3305</v>
+        <v>3530</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>439</v>
+        <v>447.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2485</v>
+        <v>2410</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>899</v>
+        <v>819</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>400</v>
+        <v>386.5</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>137.5</v>
+        <v>136.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>181.5</v>
+        <v>185</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>412</v>
+        <v>413.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>186.5</v>
+        <v>178</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>140.5</v>
+        <v>138</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>707</v>
+        <v>730</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>116.5</v>
+        <v>112</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1140</v>
+        <v>1250</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>223</v>
+        <v>215.5</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>199.5</v>
+        <v>202</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>701</v>
+        <v>747</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>386</v>
+        <v>422.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>28.15</v>
+        <v>28.5</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>917</v>
+        <v>1005</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>287.5</v>
+        <v>279</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>6015</v>
+        <v>6100</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>48.6</v>
+        <v>49.85</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1510</v>
+        <v>1380</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>220</v>
+        <v>222.5</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2540</v>
+        <v>2400</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1735</v>
+        <v>1690</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>749</v>
+        <v>724</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>252.5</v>
+        <v>247</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>161.5</v>
+        <v>158</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>243.5</v>
+        <v>254</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5785</v>
+        <v>5990</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4065</v>
+        <v>4075</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2260</v>
+        <v>2170</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>277.5</v>
+        <v>272.5</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.4</v>
+        <v>19.55</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>42</v>
+        <v>41.65</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>63.8</v>
+        <v>62.5</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>62.6</v>
+        <v>61.6</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>125</v>
+        <v>120.5</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>31.7</v>
+        <v>31.25</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>167.5</v>
+        <v>162</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>162</v>
+        <v>159.5</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>216</v>
+        <v>216.5</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>300.5</v>
+        <v>293.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>32.55</v>
+        <v>33.4</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>213.5</v>
+        <v>208</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>46.95</v>
+        <v>46.5</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>45.65</v>
+        <v>46.3</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>249.5</v>
+        <v>241</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>313</v>
+        <v>310.5</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>215</v>
+        <v>212.5</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>100.5</v>
+        <v>101</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>59.6</v>
+        <v>59.4</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>122.5</v>
+        <v>120</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>272.5</v>
+        <v>259</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>88.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>480.5</v>
+        <v>500</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>161</v>
+        <v>162.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>273.5</v>
+        <v>276</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>568</v>
+        <v>600</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.3</v>
+        <v>33.15</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>303.5</v>
+        <v>295.5</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>91.3</v>
+        <v>90.3</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>15630</v>
+        <v>16065</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>321.5</v>
+        <v>323</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1470</v>
+        <v>1450</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>34.2</v>
+        <v>36</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>84.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>153</v>
+        <v>151.5</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>96.3</v>
+        <v>94.8</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>264.5</v>
+        <v>267.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>74.8</v>
+        <v>74</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>201</v>
+        <v>204.5</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>183.5</v>
+        <v>178</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>62.8</v>
+        <v>61.7</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>405.5</v>
+        <v>404</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>182.5</v>
+        <v>175.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>116.5</v>
+        <v>115.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.55</v>
+        <v>47.1</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>110</v>
+        <v>105.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1365</v>
+        <v>1345</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>68.8</v>
+        <v>67.2</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>84.7</v>
+        <v>83.7</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>492.5</v>
+        <v>485</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>309.5</v>
+        <v>302.5</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>59.4</v>
+        <v>57.9</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>138.5</v>
+        <v>138</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>582</v>
+        <v>548</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>181</v>
+        <v>183.5</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>219</v>
+        <v>208.5</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>201.5</v>
+        <v>199.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>248</v>
+        <v>253.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>400.5</v>
+        <v>405</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>390</v>
+        <v>389.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>458</v>
+        <v>412.5</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1615</v>
+        <v>1630</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>26.65</v>
+        <v>26</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1545</v>
+        <v>1395</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>453.5</v>
+        <v>456</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>74.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>972</v>
+        <v>912</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>377</v>
+        <v>399.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2680</v>
+        <v>2845</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6250</v>
+        <v>6285</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>144.5</v>
+        <v>139.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>895</v>
+        <v>927</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>65</v>
+        <v>63.9</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>73.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>322.5</v>
+        <v>321</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>147</v>
+        <v>146.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>682</v>
+        <v>629</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>139</v>
+        <v>138.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>275.5</v>
+        <v>278.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1060</v>
+        <v>1140</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>437</v>
+        <v>411.5</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>359.5</v>
+        <v>347.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>7200</v>
+        <v>7095</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>272.5</v>
+        <v>287.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>289.5</v>
+        <v>275</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>353.5</v>
+        <v>318.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>194.5</v>
+        <v>188</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1140</v>
+        <v>1180</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>138.5</v>
+        <v>140.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.1</v>
+        <v>56.1</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>64.2</v>
+        <v>65</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>461</v>
+        <v>467.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>271</v>
+        <v>270.5</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2345</v>
+        <v>2305</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>16.15</v>
+        <v>15.85</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>292.5</v>
+        <v>282</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.15</v>
+        <v>31.55</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>487</v>
+        <v>535</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2995</v>
+        <v>2825</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2300</v>
+        <v>2270</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1790</v>
+        <v>1615</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>290.5</v>
+        <v>291.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6490</v>
+        <v>5860</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.95</v>
+        <v>16.75</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>327.5</v>
+        <v>316</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>379</v>
+        <v>367.5</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>953</v>
+        <v>914</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>159.5</v>
+        <v>154.5</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1800</v>
+        <v>1765</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>185</v>
+        <v>179.5</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>189.5</v>
+        <v>187</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>343.5</v>
+        <v>327</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>160.5</v>
+        <v>156.5</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>260</v>
+        <v>255.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>220.5</v>
+        <v>217.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>46</v>
+        <v>45.65</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>62.7</v>
+        <v>63.7</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>990</v>
+        <v>969</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>152</v>
+        <v>147.5</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>187.5</v>
+        <v>178.5</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>232.5</v>
+        <v>227.5</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2150</v>
+        <v>2165</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>366.5</v>
+        <v>374</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>56.8</v>
+        <v>55.9</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>94.3</v>
+        <v>96</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1265</v>
+        <v>1175</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.35</v>
+        <v>24.85</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.35</v>
+        <v>15.25</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29.05</v>
+        <v>29</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68.2</v>
+        <v>67.7</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33853,7 +33853,7 @@
         <v>15.67</v>
       </c>
       <c r="Q492" s="3" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="R492" s="3" t="n">
         <v>5.7</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.85</v>
+        <v>39.3</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>132</v>
+        <v>131.5</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>92.2</v>
+        <v>90.3</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.4</v>
+        <v>25.3</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34.55</v>
+        <v>35.15</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>26.65</v>
+        <v>27.1</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.85</v>
+        <v>28.45</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>242.5</v>
+        <v>234.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.18</v>
+        <v>8.26</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>68.3</v>
+        <v>74.3</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.35</v>
+        <v>29.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.6</v>
+        <v>25.65</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>65.7</v>
+        <v>67.2</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.15</v>
+        <v>18.35</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.9</v>
+        <v>13.85</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>309</v>
+        <v>314.5</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>194.5</v>
+        <v>195.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>200</v>
+        <v>208.5</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.6</v>
+        <v>49.35</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>683</v>
+        <v>744</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1425</v>
+        <v>1445</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>39.2</v>
+        <v>38.75</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>37.7</v>
+        <v>37.35</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.6</v>
+        <v>37.25</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>43.35</v>
+        <v>44</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>39.95</v>
+        <v>40.15</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.9</v>
+        <v>18.55</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>82.5</v>
+        <v>84.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.9</v>
+        <v>11.15</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.55</v>
+        <v>44.65</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>164</v>
+        <v>171.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>186</v>
+        <v>186.5</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.1</v>
+        <v>34.85</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>126.5</v>
+        <v>129</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.2</v>
+        <v>24.85</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>18.95</v>
+        <v>19.05</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>80.8</v>
+        <v>81.2</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.7</v>
+        <v>22.45</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>63.8</v>
+        <v>64.2</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>14.15</v>
+        <v>13.7</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.25</v>
+        <v>31.4</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.9</v>
+        <v>31.15</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.1</v>
+        <v>17.45</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>29.75</v>
+        <v>31.5</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54</v>
+        <v>54.8</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.3</v>
+        <v>19.15</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.4</v>
+        <v>48.05</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>230.5</v>
+        <v>231</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.1</v>
+        <v>31.5</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>305</v>
+        <v>300.5</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>129</v>
+        <v>132.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>32.35</v>
+        <v>33.05</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>248.5</v>
+        <v>252</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>159.5</v>
+        <v>166.5</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>40.35</v>
+        <v>39.9</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>19.9</v>
+        <v>19.85</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>126</v>
+        <v>122.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>39.05</v>
+        <v>39.25</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>182.5</v>
+        <v>176</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>232.5</v>
+        <v>226</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.35</v>
+        <v>28.4</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.5</v>
+        <v>31.75</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>64.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>66.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>144.5</v>
+        <v>144</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1960</v>
+        <v>2030</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>47.75</v>
+        <v>47.7</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>44.45</v>
+        <v>44.65</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>28.05</v>
+        <v>28.65</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>338.5</v>
+        <v>342</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>72.7</v>
+        <v>73.3</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.25</v>
+        <v>25.45</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>59.7</v>
+        <v>62.2</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>26.65</v>
+        <v>26.4</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>97.8</v>
+        <v>107.5</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>115.5</v>
+        <v>119.5</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>294.5</v>
+        <v>295</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>135.5</v>
+        <v>138</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>180</v>
+        <v>184.5</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>208.5</v>
+        <v>213.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>125.5</v>
+        <v>127.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>157</v>
+        <v>155.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>42.2</v>
+        <v>42.8</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>295</v>
+        <v>302.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>179.5</v>
+        <v>187</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.2</v>
+        <v>40.9</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.2</v>
+        <v>31.45</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.45</v>
+        <v>36.1</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>18.8</v>
+        <v>19.75</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>90.3</v>
+        <v>89.2</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>36.15</v>
+        <v>35.55</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>49.9</v>
+        <v>48.1</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>46.65</v>
+        <v>47.9</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>39.8</v>
+        <v>38.65</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.25</v>
+        <v>34.55</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>171</v>
+        <v>170.5</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>233.5</v>
+        <v>238</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>35.35</v>
+        <v>34.75</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>52.7</v>
+        <v>53.6</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>59.5</v>
+        <v>57.6</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.25</v>
+        <v>20.35</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>114</v>
+        <v>114.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26</v>
+        <v>26.25</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.9</v>
+        <v>20.65</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>235.5</v>
+        <v>232.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.35</v>
+        <v>22.2</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>216.5</v>
+        <v>216</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>24.2</v>
+        <v>24.75</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>117</v>
+        <v>118.5</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>292.5</v>
+        <v>278.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>7650</v>
+        <v>7580</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>128.5</v>
+        <v>131.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>143</v>
+        <v>143.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>90.3</v>
+        <v>92.5</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>312.5</v>
+        <v>320</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>113</v>
+        <v>112.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>290.5</v>
+        <v>297.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>44.55</v>
+        <v>44.25</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>175</v>
+        <v>183.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>185.5</v>
+        <v>182</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>496.5</v>
+        <v>503</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>116</v>
+        <v>115.5</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3530</v>
+        <v>3425</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>123</v>
+        <v>125.5</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>447.5</v>
+        <v>492</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2410</v>
+        <v>2480</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>182.5</v>
+        <v>173</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>819</v>
+        <v>874</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>386.5</v>
+        <v>406</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>136.5</v>
+        <v>138</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>192</v>
+        <v>196.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>413.5</v>
+        <v>412</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>228</v>
+        <v>237.5</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>178</v>
+        <v>182.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>112</v>
+        <v>114.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1250</v>
+        <v>1375</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>747</v>
+        <v>786</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>422.5</v>
+        <v>421.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>28.5</v>
+        <v>28.35</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>6100</v>
+        <v>5995</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>49.85</v>
+        <v>49.3</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1380</v>
+        <v>1480</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>222.5</v>
+        <v>224.5</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2400</v>
+        <v>2640</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1690</v>
+        <v>1745</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>724</v>
+        <v>773</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>247</v>
+        <v>253.5</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>219</v>
+        <v>224.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>158</v>
+        <v>159.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>254</v>
+        <v>251.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5990</v>
+        <v>5885</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4075</v>
+        <v>4275</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2170</v>
+        <v>2315</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>68.2</v>
+        <v>67.8</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>272.5</v>
+        <v>278.5</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>493</v>
+        <v>542</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>41.65</v>
+        <v>41.7</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>92.5</v>
+        <v>95.7</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>62.5</v>
+        <v>63.2</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>61.6</v>
+        <v>62.5</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>120.5</v>
+        <v>132.5</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>31.25</v>
+        <v>31.05</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>121.5</v>
+        <v>122</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>162</v>
+        <v>164.5</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>159.5</v>
+        <v>167.5</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>216.5</v>
+        <v>230.5</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>460</v>
+        <v>467.5</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>293.5</v>
+        <v>294.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>33.4</v>
+        <v>32.25</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>46.5</v>
+        <v>46.45</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>46.3</v>
+        <v>50</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>310.5</v>
+        <v>307.5</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>212.5</v>
+        <v>221.5</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>258</v>
+        <v>261.5</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.2</v>
+        <v>38.2</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>259</v>
+        <v>260.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>500</v>
+        <v>535</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>162.5</v>
+        <v>167.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.15</v>
+        <v>34.15</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>295.5</v>
+        <v>301</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>90.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1425</v>
+        <v>1470</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>16065</v>
+        <v>17120</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>118</v>
+        <v>119.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>267.5</v>
+        <v>275</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>113</v>
+        <v>111.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>204.5</v>
+        <v>200.5</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>178</v>
+        <v>183.5</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>864</v>
+        <v>883</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>404</v>
+        <v>408.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>292</v>
+        <v>293.5</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>192.5</v>
+        <v>194</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>175.5</v>
+        <v>183.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>115.5</v>
+        <v>117.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>246</v>
+        <v>261.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>91.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.1</v>
+        <v>47.55</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>105.5</v>
+        <v>116</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1345</v>
+        <v>1375</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>67.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>83.7</v>
+        <v>84.3</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>302.5</v>
+        <v>317</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>57.9</v>
+        <v>59</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>183.5</v>
+        <v>182.5</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>172.5</v>
+        <v>189.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5130</v>
+        <v>5410</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>208.5</v>
+        <v>221.5</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>199.5</v>
+        <v>200</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>253.5</v>
+        <v>259.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>389.5</v>
+        <v>396</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>412.5</v>
+        <v>418.5</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>26</v>
+        <v>25.75</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1395</v>
+        <v>1310</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>399.5</v>
+        <v>396.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>73.5</v>
+        <v>76.7</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>2845</v>
+        <v>3125</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6285</v>
+        <v>6910</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>139.5</v>
+        <v>143</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>607</v>
+        <v>667</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>63.9</v>
+        <v>61.3</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>321</v>
+        <v>322.5</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>146.5</v>
+        <v>150</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>629</v>
+        <v>667</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>138.5</v>
+        <v>138</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>278.5</v>
+        <v>274</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>411.5</v>
+        <v>422</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>347.5</v>
+        <v>365</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>287.5</v>
+        <v>277.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>275</v>
+        <v>278.5</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1210</v>
+        <v>1330</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>157</v>
+        <v>157.5</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>318.5</v>
+        <v>335.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1180</v>
+        <v>1150</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>140.5</v>
+        <v>142.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>73</v>
+        <v>70.8</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1125</v>
+        <v>1155</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>467.5</v>
+        <v>490</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>270.5</v>
+        <v>270</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2305</v>
+        <v>2285</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>15.85</v>
+        <v>15.45</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>94.8</v>
+        <v>91.2</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.55</v>
+        <v>32.45</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1505</v>
+        <v>1605</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>285</v>
+        <v>280.5</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2825</v>
+        <v>2880</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2270</v>
+        <v>2345</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1615</v>
+        <v>1660</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>291.5</v>
+        <v>292.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>5860</v>
+        <v>5870</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.75</v>
+        <v>16.85</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>117</v>
+        <v>117.5</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>316</v>
+        <v>320.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>367.5</v>
+        <v>370</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>914</v>
+        <v>940</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1765</v>
+        <v>1810</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>289</v>
+        <v>297.5</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>179.5</v>
+        <v>185</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>187</v>
+        <v>185.5</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>156.5</v>
+        <v>158</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>255.5</v>
+        <v>259.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>217.5</v>
+        <v>221</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>109</v>
+        <v>111.5</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>45.65</v>
+        <v>45.15</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>90.8</v>
+        <v>91.3</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>63.7</v>
+        <v>63.5</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>365</v>
+        <v>369.5</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>969</v>
+        <v>990</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>147.5</v>
+        <v>150</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>178.5</v>
+        <v>182</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>227.5</v>
+        <v>226</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2165</v>
+        <v>2125</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>36.75</v>
+        <v>37.15</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.8</v>
+        <v>26.75</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>374</v>
+        <v>372.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>55.9</v>
+        <v>56.7</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>96</v>
+        <v>93.7</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>71.5</v>
+        <v>71.7</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.85</v>
+        <v>24.9</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.25</v>
+        <v>15.45</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>83</v>
+        <v>82.8</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.3</v>
+        <v>40.05</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>131.5</v>
+        <v>132.5</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>27.8</v>
+        <v>28.05</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>90.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>25.3</v>
+        <v>24.8</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.15</v>
+        <v>35</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.1</v>
+        <v>27.05</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.45</v>
+        <v>28.6</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.6</v>
+        <v>41.95</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>67.8</v>
+        <v>66.8</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>234.5</v>
+        <v>237.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.65</v>
+        <v>12.6</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>12.15</v>
+        <v>12.05</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.26</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>74.3</v>
+        <v>72.8</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>25.65</v>
+        <v>25.35</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.35</v>
+        <v>18.25</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.85</v>
+        <v>14.2</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>314.5</v>
+        <v>314</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>195.5</v>
+        <v>196</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>208.5</v>
+        <v>206</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>73.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>761</v>
+        <v>741</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.35</v>
+        <v>49.55</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>744</v>
+        <v>704</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.75</v>
+        <v>38.2</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>37.35</v>
+        <v>36.8</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.25</v>
+        <v>37.5</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>44</v>
+        <v>43.4</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40.15</v>
+        <v>41.05</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>18.55</v>
+        <v>17.35</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>84.7</v>
+        <v>80.8</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>11.15</v>
+        <v>10.8</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.65</v>
+        <v>44.6</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>171.5</v>
+        <v>163.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>186.5</v>
+        <v>184</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.85</v>
+        <v>35.45</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>24.85</v>
+        <v>24.55</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.7</v>
+        <v>13.85</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.85</v>
+        <v>30.1</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>81.2</v>
+        <v>82.7</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.05</v>
+        <v>16.95</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.7</v>
+        <v>13.85</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>49.8</v>
+        <v>49.55</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>14150</v>
+        <v>13865</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>141.5</v>
+        <v>139</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.4</v>
+        <v>31.65</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>31.15</v>
+        <v>30.95</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.45</v>
+        <v>17.4</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>31.5</v>
+        <v>31.95</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.15</v>
+        <v>19.05</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>48.05</v>
+        <v>47.9</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>231</v>
+        <v>231.5</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.5</v>
+        <v>31</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>300.5</v>
+        <v>315</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>33.05</v>
+        <v>33.15</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>166.5</v>
+        <v>161.5</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>43.7</v>
+        <v>43.35</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>19.85</v>
+        <v>19.3</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>39.25</v>
+        <v>39.15</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2205</v>
+        <v>2140</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>86</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.75</v>
+        <v>32.15</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>144</v>
+        <v>144.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2030</v>
+        <v>1975</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>47.7</v>
+        <v>48.7</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>44.65</v>
+        <v>44.05</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1225</v>
+        <v>1175</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>28.65</v>
+        <v>28.2</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>359</v>
+        <v>361.5</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5640</v>
+        <v>5445</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>107</v>
+        <v>109.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>73.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45.9</v>
+        <v>45.5</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.45</v>
+        <v>25.5</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>62.2</v>
+        <v>59.3</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1100</v>
+        <v>1025</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>136</v>
+        <v>137.5</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>107.5</v>
+        <v>104.5</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>256</v>
+        <v>250.5</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>119.5</v>
+        <v>116</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>279</v>
+        <v>270.5</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>295</v>
+        <v>296.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>184.5</v>
+        <v>202</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>99.5</v>
+        <v>104</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>213.5</v>
+        <v>211</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>127.5</v>
+        <v>125.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>123.5</v>
+        <v>121</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>155.5</v>
+        <v>156.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>42.8</v>
+        <v>42.25</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>302.5</v>
+        <v>293</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.9</v>
+        <v>41.65</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.45</v>
+        <v>31.4</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>12.05</v>
+        <v>12.1</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.1</v>
+        <v>35.85</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.75</v>
+        <v>19.25</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.55</v>
+        <v>34.95</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>48.1</v>
+        <v>46.9</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>47.9</v>
+        <v>47.95</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.65</v>
+        <v>38.3</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.55</v>
+        <v>34.25</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>93.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>170.5</v>
+        <v>170</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>238</v>
+        <v>234.5</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>34.75</v>
+        <v>35.05</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.35</v>
+        <v>20.45</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>114.5</v>
+        <v>112</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.4</v>
+        <v>42.15</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.25</v>
+        <v>26.2</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>67</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45</v>
+        <v>45.15</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>232.5</v>
+        <v>234.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.2</v>
+        <v>22.35</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>24.75</v>
+        <v>24.05</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>118.5</v>
+        <v>116</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>278.5</v>
+        <v>281.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>128</v>
+        <v>129.5</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>131.5</v>
+        <v>131</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3410</v>
+        <v>3310</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>143.5</v>
+        <v>157.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>92.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>731</v>
+        <v>686</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>297.5</v>
+        <v>288.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>44.25</v>
+        <v>44.65</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>183.5</v>
+        <v>184.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>115.5</v>
+        <v>116</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3425</v>
+        <v>3395</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>125.5</v>
+        <v>123</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>173</v>
+        <v>168.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>492</v>
+        <v>469.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2480</v>
+        <v>2405</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>64.2</v>
+        <v>63.4</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>874</v>
+        <v>847</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>138</v>
+        <v>135.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>196.5</v>
+        <v>195.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>182</v>
+        <v>185.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>412</v>
+        <v>412.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>237.5</v>
+        <v>233.5</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>182.5</v>
+        <v>178.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>143</v>
+        <v>141.5</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>114.5</v>
+        <v>112</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1375</v>
+        <v>1435</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>215.5</v>
+        <v>209</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>421.5</v>
+        <v>419.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>28.35</v>
+        <v>30.05</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>1005</v>
+        <v>1050</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>284</v>
+        <v>285.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>177</v>
+        <v>172.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5995</v>
+        <v>5895</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>49.3</v>
+        <v>49.05</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1480</v>
+        <v>1445</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>224.5</v>
+        <v>228.5</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>285</v>
+        <v>284.5</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2640</v>
+        <v>2395</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1745</v>
+        <v>1705</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>253.5</v>
+        <v>265</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>224.5</v>
+        <v>226.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>159.5</v>
+        <v>161</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>251.5</v>
+        <v>249</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5885</v>
+        <v>5770</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4275</v>
+        <v>4200</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2315</v>
+        <v>2170</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>67.8</v>
+        <v>67</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>278.5</v>
+        <v>274</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>100.5</v>
+        <v>102</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.55</v>
+        <v>19.4</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>95.7</v>
+        <v>94.7</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>63.2</v>
+        <v>62.2</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>132.5</v>
+        <v>124.5</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>31.05</v>
+        <v>30.85</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>62.4</v>
+        <v>63.4</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>167.5</v>
+        <v>166</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>230.5</v>
+        <v>242</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>467.5</v>
+        <v>478.5</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>32.25</v>
+        <v>31.45</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>208</v>
+        <v>201.5</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>46.45</v>
+        <v>46.65</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>350</v>
+        <v>346.5</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>307.5</v>
+        <v>298</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>221.5</v>
+        <v>216</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>261.5</v>
+        <v>256</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>101</v>
+        <v>102.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>38.2</v>
+        <v>36.95</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>59.8</v>
+        <v>60.3</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>124</v>
+        <v>120.5</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>260.5</v>
+        <v>250</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>91</v>
+        <v>91.7</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>167.5</v>
+        <v>169.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>34.15</v>
+        <v>33.55</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>17120</v>
+        <v>17725</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>35.3</v>
+        <v>34.2</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>84.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>153.5</v>
+        <v>149.5</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>119.5</v>
+        <v>117</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>95.2</v>
+        <v>92.5</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>275</v>
+        <v>269.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>74</v>
+        <v>73.7</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>200.5</v>
+        <v>190</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>183.5</v>
+        <v>179</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>62.4</v>
+        <v>63.2</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>883</v>
+        <v>823</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>51.7</v>
+        <v>55.6</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>185.5</v>
+        <v>185</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.3</v>
+        <v>14.15</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>408.5</v>
+        <v>404</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>293.5</v>
+        <v>288</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>770</v>
+        <v>721</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>194</v>
+        <v>192.5</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>183.5</v>
+        <v>182.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>117.5</v>
+        <v>117</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>261.5</v>
+        <v>260.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.55</v>
+        <v>47.2</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>116</v>
+        <v>110.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1375</v>
+        <v>1340</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>84.3</v>
+        <v>83.5</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>317</v>
+        <v>313.5</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>59</v>
+        <v>58.5</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>189.5</v>
+        <v>195.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>221.5</v>
+        <v>216</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>75.2</v>
+        <v>71.7</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>200</v>
+        <v>199.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>249</v>
+        <v>245.5</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>259.5</v>
+        <v>256.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1030</v>
+        <v>1005</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>396</v>
+        <v>391.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>418.5</v>
+        <v>426</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1635</v>
+        <v>1795</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>25.75</v>
+        <v>25.1</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>455</v>
+        <v>500</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>420</v>
+        <v>422.5</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>994</v>
+        <v>967</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>396.5</v>
+        <v>394</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>76.7</v>
+        <v>78.7</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3125</v>
+        <v>3435</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>6910</v>
+        <v>7050</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>74.8</v>
+        <v>82.2</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>72.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>322.5</v>
+        <v>325</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>150</v>
+        <v>148.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.2</v>
+        <v>61.2</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>138</v>
+        <v>137.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>274</v>
+        <v>264.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1120</v>
+        <v>1210</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>365</v>
+        <v>362.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>7800</v>
+        <v>2610</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>277.5</v>
+        <v>278.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>278.5</v>
+        <v>272</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1330</v>
+        <v>1460</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>631</v>
+        <v>607</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>335.5</v>
+        <v>341.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1150</v>
+        <v>1120</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>142.5</v>
+        <v>139</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.5</v>
+        <v>55.3</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>70.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1155</v>
+        <v>1115</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>490</v>
+        <v>483.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>270</v>
+        <v>269.5</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2285</v>
+        <v>2110</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>168</v>
+        <v>166.5</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>15.45</v>
+        <v>15.25</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>91.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>289</v>
+        <v>293.5</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>32.45</v>
+        <v>32.3</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1605</v>
+        <v>1520</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>575</v>
+        <v>610</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>280.5</v>
+        <v>277</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2880</v>
+        <v>2795</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2345</v>
+        <v>2300</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1660</v>
+        <v>1555</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>292.5</v>
+        <v>286</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>5870</v>
+        <v>5710</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.85</v>
+        <v>17.05</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>117.5</v>
+        <v>116.5</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>320.5</v>
+        <v>316</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1810</v>
+        <v>1760</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>297.5</v>
+        <v>295</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>255</v>
+        <v>245.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>185.5</v>
+        <v>181</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>319</v>
+        <v>313.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>105</v>
+        <v>104.5</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>158</v>
+        <v>154.5</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>259.5</v>
+        <v>257.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>221</v>
+        <v>220.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>111.5</v>
+        <v>109.5</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>45.15</v>
+        <v>44.7</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>91.3</v>
+        <v>91.2</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>196</v>
+        <v>198.5</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>63.5</v>
+        <v>62.6</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>93.2</v>
+        <v>90.2</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>369.5</v>
+        <v>369</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>150</v>
+        <v>146.5</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>226</v>
+        <v>225.5</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2125</v>
+        <v>2065</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.15</v>
+        <v>37.25</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.75</v>
+        <v>26.65</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>142</v>
+        <v>144.5</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>56.7</v>
+        <v>56.3</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>93.7</v>
+        <v>90.8</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1175</v>
+        <v>1265</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>71.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.9</v>
+        <v>24.75</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.45</v>
+        <v>15.5</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68.3</v>
+        <v>68</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>82.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>40.05</v>
+        <v>40</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63.2</v>
+        <v>63</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>41</v>
+        <v>40.75</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>132.5</v>
+        <v>131.5</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>80</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.05</v>
+        <v>28.3</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.8</v>
+        <v>24.45</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.05</v>
+        <v>27.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>109.5</v>
+        <v>110</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.6</v>
+        <v>28.55</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.95</v>
+        <v>42.1</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>156.5</v>
+        <v>155.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>66.8</v>
+        <v>65.7</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>237.5</v>
+        <v>221</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.6</v>
+        <v>12.45</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>12.05</v>
+        <v>11.9</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>83</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>72.8</v>
+        <v>69.7</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>25.35</v>
+        <v>24.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>67</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.25</v>
+        <v>18.1</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>314</v>
+        <v>313.5</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>165</v>
+        <v>162.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>103</v>
+        <v>100.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.2</v>
+        <v>37.6</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.8</v>
+        <v>36.35</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>43.4</v>
+        <v>41.55</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>41.05</v>
+        <v>40.6</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>17.35</v>
+        <v>16.55</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>80.8</v>
+        <v>76.8</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.6</v>
+        <v>44.65</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>163.5</v>
+        <v>161</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>184</v>
+        <v>181.5</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>60.8</v>
+        <v>58.6</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>35.45</v>
+        <v>35.8</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>24.55</v>
+        <v>25.1</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.85</v>
+        <v>13.65</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.05</v>
+        <v>19</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.45</v>
+        <v>22.55</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>16.95</v>
+        <v>16.9</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.85</v>
+        <v>13.8</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>49.55</v>
+        <v>50.2</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>352</v>
+        <v>344.5</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>13865</v>
+        <v>13450</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.65</v>
+        <v>31.4</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.3</v>
+        <v>27.95</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.95</v>
+        <v>30.7</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>31.95</v>
+        <v>31.4</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>19.05</v>
+        <v>18.85</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>231.5</v>
+        <v>229.5</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31</v>
+        <v>30.1</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>33.15</v>
+        <v>31.8</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>161.5</v>
+        <v>153</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>39.7</v>
+        <v>38.75</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>47.8</v>
+        <v>45.8</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>43.35</v>
+        <v>42.25</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>19.3</v>
+        <v>18.65</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>39.15</v>
+        <v>38.05</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>32.15</v>
+        <v>31.25</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>66.3</v>
+        <v>63.7</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>44</v>
+        <v>41.85</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>1010</v>
+        <v>971</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>144.5</v>
+        <v>140.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>48.7</v>
+        <v>47.25</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>44.05</v>
+        <v>42.3</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1175</v>
+        <v>1100</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>361.5</v>
+        <v>350.5</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>155</v>
+        <v>150.5</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>744</v>
+        <v>707</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>109.5</v>
+        <v>107.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45.5</v>
+        <v>45.35</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>66</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.5</v>
+        <v>24.85</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>59.3</v>
+        <v>57.3</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>26.4</v>
+        <v>26.55</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>137.5</v>
+        <v>138</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>168</v>
+        <v>164.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>104.5</v>
+        <v>95</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>250.5</v>
+        <v>244.5</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>78.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>116</v>
+        <v>113.5</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>270.5</v>
+        <v>261</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>296.5</v>
+        <v>286</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>104</v>
+        <v>94.7</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>211</v>
+        <v>206.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>125.5</v>
+        <v>122.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>121</v>
+        <v>114.5</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>156.5</v>
+        <v>155.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>288</v>
+        <v>259.5</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>42.25</v>
+        <v>40.9</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>293</v>
+        <v>271.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>41.65</v>
+        <v>41.6</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>12.1</v>
+        <v>11.95</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>35.85</v>
+        <v>36.9</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.25</v>
+        <v>19.55</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>34.95</v>
+        <v>35.1</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>46.9</v>
+        <v>47.15</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>47.95</v>
+        <v>48.65</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.3</v>
+        <v>38.35</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.25</v>
+        <v>34.65</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>234.5</v>
+        <v>239</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>35.05</v>
+        <v>35.5</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>57.5</v>
+        <v>57.8</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.45</v>
+        <v>20.55</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>112</v>
+        <v>115.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.15</v>
+        <v>42.8</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>96.3</v>
+        <v>99.8</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>176</v>
+        <v>171.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.65</v>
+        <v>20.7</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.15</v>
+        <v>45.25</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>179</v>
+        <v>178.5</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>234.5</v>
+        <v>231.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.35</v>
+        <v>22.3</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>217</v>
+        <v>216.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>57.2</v>
+        <v>56.8</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>24.05</v>
+        <v>23.65</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>281.5</v>
+        <v>277</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>129.5</v>
+        <v>127.5</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>89.5</v>
+        <v>86</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>131</v>
+        <v>130.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>157.5</v>
+        <v>143</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>686</v>
+        <v>638</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>112.5</v>
+        <v>109</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>288.5</v>
+        <v>293.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>44.65</v>
+        <v>44.15</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>184.5</v>
+        <v>180</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>187</v>
+        <v>190.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>502</v>
+        <v>487.5</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3395</v>
+        <v>3120</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>168.5</v>
+        <v>162.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>469.5</v>
+        <v>446.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2405</v>
+        <v>2365</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>176</v>
+        <v>172.5</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>63.4</v>
+        <v>59.5</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>766</v>
+        <v>720</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>774</v>
+        <v>730</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>847</v>
+        <v>775</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>135.5</v>
+        <v>134</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>195.5</v>
+        <v>191.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>185.5</v>
+        <v>188.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>211</v>
+        <v>194.5</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>412.5</v>
+        <v>395</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>233.5</v>
+        <v>226</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>178.5</v>
+        <v>173</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>141.5</v>
+        <v>138</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>112</v>
+        <v>108.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1435</v>
+        <v>1350</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>419.5</v>
+        <v>400</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>30.05</v>
+        <v>29</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>1050</v>
+        <v>991</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>285.5</v>
+        <v>280</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>172.5</v>
+        <v>165</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>602</v>
+        <v>554</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>49.05</v>
+        <v>48.1</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>228.5</v>
+        <v>220</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>284.5</v>
+        <v>280</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2395</v>
+        <v>2330</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1705</v>
+        <v>1670</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>710</v>
+        <v>676</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.3</v>
+        <v>17.05</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>265</v>
+        <v>249.5</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>226.5</v>
+        <v>221</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>249</v>
+        <v>241.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>67</v>
+        <v>64.7</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.4</v>
+        <v>19.95</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>42.1</v>
+        <v>40</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>94.7</v>
+        <v>91.5</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>62.2</v>
+        <v>60.5</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>124.5</v>
+        <v>118</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.7</v>
+        <v>77.3</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>30.85</v>
+        <v>30.55</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>63.4</v>
+        <v>63.2</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>164.5</v>
+        <v>163.5</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>478.5</v>
+        <v>462</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>294.5</v>
+        <v>288</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>31.45</v>
+        <v>30.4</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>201.5</v>
+        <v>195.5</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>46.65</v>
+        <v>44.75</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>787</v>
+        <v>759</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>51.5</v>
+        <v>49.1</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>240</v>
+        <v>217.5</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>346.5</v>
+        <v>342</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>298</v>
+        <v>290.5</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.95</v>
+        <v>35.5</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>60.3</v>
+        <v>59.6</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>120.5</v>
+        <v>115</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>250</v>
+        <v>239.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>91.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>169.5</v>
+        <v>166</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>278</v>
+        <v>272.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>669</v>
+        <v>611</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>624</v>
+        <v>572</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>530</v>
+        <v>484.5</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.55</v>
+        <v>33.35</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>297</v>
+        <v>289.5</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>91.8</v>
+        <v>88.3</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1460</v>
+        <v>1440</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>17725</v>
+        <v>17850</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1420</v>
+        <v>1345</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>34.2</v>
+        <v>31</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>149.5</v>
+        <v>147</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>76.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>92.5</v>
+        <v>91.2</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>269.5</v>
+        <v>261</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>73.7</v>
+        <v>71.2</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>190</v>
+        <v>182.5</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>76.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>113</v>
+        <v>111.5</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>185</v>
+        <v>184.5</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.15</v>
+        <v>13.9</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>404</v>
+        <v>394.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>192.5</v>
+        <v>185</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>182.5</v>
+        <v>189</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>260.5</v>
+        <v>241</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>92.3</v>
+        <v>90.3</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.2</v>
+        <v>48.75</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>110.5</v>
+        <v>104.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1340</v>
+        <v>1300</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>83.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>313.5</v>
+        <v>299</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>58.5</v>
+        <v>57</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>138</v>
+        <v>134.5</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5290</v>
+        <v>5045</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>71.7</v>
+        <v>65</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>223</v>
+        <v>215.5</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1410</v>
+        <v>1345</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>199.5</v>
+        <v>191.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>44.5</v>
+        <v>43.2</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>78</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>245.5</v>
+        <v>233.5</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>256.5</v>
+        <v>245.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>1005</v>
+        <v>972</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>79.2</v>
+        <v>77.3</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>391.5</v>
+        <v>381</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1795</v>
+        <v>1770</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>25.1</v>
+        <v>24.55</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1305</v>
+        <v>1350</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>225</v>
+        <v>216.5</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>422.5</v>
+        <v>411.5</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>394</v>
+        <v>380.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>78.7</v>
+        <v>76.5</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3435</v>
+        <v>3350</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7050</v>
+        <v>7000</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>137</v>
+        <v>135.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>957</v>
+        <v>912</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>61.5</v>
+        <v>61.8</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>325</v>
+        <v>322.5</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>148.5</v>
+        <v>142.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>658</v>
+        <v>629</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>61.2</v>
+        <v>60.9</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>137.5</v>
+        <v>137</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>264.5</v>
+        <v>257</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1210</v>
+        <v>1185</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>362.5</v>
+        <v>363</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>278.5</v>
+        <v>275</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1460</v>
+        <v>1385</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>157.5</v>
+        <v>156.5</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>341.5</v>
+        <v>307.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1120</v>
+        <v>1075</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.3</v>
+        <v>55.9</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1115</v>
+        <v>1060</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>483.5</v>
+        <v>465.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>269.5</v>
+        <v>271</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2110</v>
+        <v>2095</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>609</v>
+        <v>585</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>166.5</v>
+        <v>169</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>15.25</v>
+        <v>14.9</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>310</v>
+        <v>305.5</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>293.5</v>
+        <v>278</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1520</v>
+        <v>1655</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>610</v>
+        <v>575</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>277</v>
+        <v>274.5</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2795</v>
+        <v>2710</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>540</v>
+        <v>521</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>370</v>
+        <v>363.5</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1555</v>
+        <v>1465</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>5710</v>
+        <v>5870</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>17.05</v>
+        <v>16.65</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>930</v>
+        <v>898</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>152</v>
+        <v>151.5</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>459</v>
+        <v>413.5</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>245.5</v>
+        <v>236.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>313.5</v>
+        <v>293</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>104.5</v>
+        <v>102</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>154.5</v>
+        <v>147</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>50.6</v>
+        <v>49.2</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>257.5</v>
+        <v>251.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>220.5</v>
+        <v>214.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>109.5</v>
+        <v>104</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>44.7</v>
+        <v>43.25</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>91.2</v>
+        <v>89.3</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>198.5</v>
+        <v>189</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>90.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>146.5</v>
+        <v>145</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>225.5</v>
+        <v>217</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2065</v>
+        <v>2000</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.25</v>
+        <v>37.35</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.65</v>
+        <v>26.15</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>372.5</v>
+        <v>367.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>144.5</v>
+        <v>141</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>56.3</v>
+        <v>56.6</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>90.8</v>
+        <v>89.7</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.75</v>
+        <v>24.55</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.5</v>
+        <v>15.35</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29</v>
+        <v>29.05</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68</v>
+        <v>67.7</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>81</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63</v>
+        <v>62.4</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.3</v>
+        <v>28.25</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>90.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.45</v>
+        <v>24.6</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>42.1</v>
+        <v>41.85</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>155.5</v>
+        <v>157</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>65.7</v>
+        <v>66</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>221</v>
+        <v>225.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.45</v>
+        <v>12.35</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>29.1</v>
+        <v>29.15</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.6</v>
+        <v>24.55</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>313.5</v>
+        <v>313</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>194</v>
+        <v>196.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>201</v>
+        <v>207.5</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>71</v>
+        <v>72.2</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>162.5</v>
+        <v>165.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>100.5</v>
+        <v>102</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>722</v>
+        <v>746</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1375</v>
+        <v>1395</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>37.6</v>
+        <v>38.4</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.35</v>
+        <v>36.5</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37</v>
+        <v>37.35</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>41.55</v>
+        <v>42.3</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40.6</v>
+        <v>40.65</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.55</v>
+        <v>16.65</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>76.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.65</v>
+        <v>44.8</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>122</v>
+        <v>125.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>161</v>
+        <v>162.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>181.5</v>
+        <v>182</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>58.6</v>
+        <v>59.1</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>35.8</v>
+        <v>34.7</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>120</v>
+        <v>118.5</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>30.3</v>
+        <v>29.85</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.8</v>
+        <v>13.85</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>344.5</v>
+        <v>363</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>13450</v>
+        <v>13860</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.4</v>
+        <v>31.35</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>27.95</v>
+        <v>28.25</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.7</v>
+        <v>30.95</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54.4</v>
+        <v>54.1</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.1</v>
+        <v>63.4</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>18.85</v>
+        <v>18.8</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.6</v>
+        <v>47.65</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>229.5</v>
+        <v>231.5</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1760</v>
+        <v>1825</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.8</v>
+        <v>32.85</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>236</v>
+        <v>249.5</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>247.5</v>
+        <v>256</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>38.75</v>
+        <v>41.6</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>511</v>
+        <v>562</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>45.8</v>
+        <v>46.6</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>42.25</v>
+        <v>42.9</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2390</v>
+        <v>2410</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>18.65</v>
+        <v>19.55</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>117</v>
+        <v>121.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>38.05</v>
+        <v>38.6</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>223</v>
+        <v>239.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.5</v>
+        <v>29.25</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.25</v>
+        <v>32.7</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>63.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>41.85</v>
+        <v>42.8</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>971</v>
+        <v>1025</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>140.5</v>
+        <v>142</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2015</v>
+        <v>2030</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>47.25</v>
+        <v>49.3</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>50.1</v>
+        <v>51.1</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>42.3</v>
+        <v>43.1</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1100</v>
+        <v>1045</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>27.6</v>
+        <v>28.15</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>350.5</v>
+        <v>361</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>150.5</v>
+        <v>161.5</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5290</v>
+        <v>5415</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>107.5</v>
+        <v>110.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>75</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45.35</v>
+        <v>45.6</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>24.85</v>
+        <v>25.7</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1035</v>
+        <v>1070</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>477.5</v>
+        <v>496</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>26.55</v>
+        <v>26.8</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>138</v>
+        <v>137.5</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>164.5</v>
+        <v>178</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>95</v>
+        <v>104.5</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>244.5</v>
+        <v>260</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>113.5</v>
+        <v>116</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>286</v>
+        <v>284.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4340</v>
+        <v>4415</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>206.5</v>
+        <v>209.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>114.5</v>
+        <v>125.5</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>155.5</v>
+        <v>156</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>259.5</v>
+        <v>256</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>271.5</v>
+        <v>298.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>179</v>
+        <v>181.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.5</v>
+        <v>22.55</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>11.95</v>
+        <v>12.15</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.55</v>
+        <v>20.15</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>48.65</v>
+        <v>48.55</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.35</v>
+        <v>38.45</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.65</v>
+        <v>34.85</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>93.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>35.5</v>
+        <v>35.85</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.55</v>
+        <v>20.45</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>115.5</v>
+        <v>115</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>171.5</v>
+        <v>173.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.7</v>
+        <v>20.65</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.25</v>
+        <v>45.5</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>231.5</v>
+        <v>232</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>216.5</v>
+        <v>216</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>56.8</v>
+        <v>57.6</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>23.65</v>
+        <v>25.6</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>277</v>
+        <v>278.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>7150</v>
+        <v>7400</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>127.5</v>
+        <v>129</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>130.5</v>
+        <v>131.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>98.3</v>
+        <v>101</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3300</v>
+        <v>3570</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>143</v>
+        <v>144.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>87.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>638</v>
+        <v>701</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>109</v>
+        <v>111.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>293.5</v>
+        <v>284</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>44.15</v>
+        <v>43.95</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>190.5</v>
+        <v>192.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>923</v>
+        <v>902</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>174</v>
+        <v>173.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>487.5</v>
+        <v>488.5</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3120</v>
+        <v>3170</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>162.5</v>
+        <v>176.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>446.5</v>
+        <v>449.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2365</v>
+        <v>2385</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>172.5</v>
+        <v>173</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>59.5</v>
+        <v>60.6</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>720</v>
+        <v>775</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>730</v>
+        <v>803</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>775</v>
+        <v>819</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>191.5</v>
+        <v>192</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>188.5</v>
+        <v>198</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>194.5</v>
+        <v>206</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>395</v>
+        <v>400.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>173</v>
+        <v>176.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>108.5</v>
+        <v>111</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1350</v>
+        <v>1485</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>774</v>
+        <v>735</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>991</v>
+        <v>1055</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>280</v>
+        <v>282.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>165</v>
+        <v>172.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5800</v>
+        <v>5810</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1405</v>
+        <v>1505</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2330</v>
+        <v>2385</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1670</v>
+        <v>1685</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.05</v>
+        <v>17.15</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>742</v>
+        <v>711</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>249.5</v>
+        <v>255</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>157</v>
+        <v>159.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>241.5</v>
+        <v>248</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5615</v>
+        <v>5875</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4050</v>
+        <v>4220</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2100</v>
+        <v>2145</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>64.7</v>
+        <v>65.5</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.95</v>
+        <v>20</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>91.5</v>
+        <v>92.5</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>60.5</v>
+        <v>62</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>61.5</v>
+        <v>66.8</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.3</v>
+        <v>77</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>30.55</v>
+        <v>30.15</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>63.2</v>
+        <v>63.6</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>163.5</v>
+        <v>164.5</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>161</v>
+        <v>171.5</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>462</v>
+        <v>473.5</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>288</v>
+        <v>294.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>195.5</v>
+        <v>200.5</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>44.75</v>
+        <v>44.65</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>759</v>
+        <v>776</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>49.1</v>
+        <v>50.3</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>217.5</v>
+        <v>231.5</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>290.5</v>
+        <v>306</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>217</v>
+        <v>226.5</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>103.5</v>
+        <v>104</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>35.5</v>
+        <v>36.9</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>59.6</v>
+        <v>60.8</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>239.5</v>
+        <v>251</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>166</v>
+        <v>165.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>272.5</v>
+        <v>276</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>572</v>
+        <v>629</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>484.5</v>
+        <v>497</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.35</v>
+        <v>33.2</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>289.5</v>
+        <v>293</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>88.3</v>
+        <v>90</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>17850</v>
+        <v>17470</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1345</v>
+        <v>1360</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>110</v>
+        <v>112.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>91.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>261</v>
+        <v>261.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>110</v>
+        <v>112.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>71.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>182.5</v>
+        <v>190</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>176</v>
+        <v>183.5</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.8</v>
+        <v>64</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>817</v>
+        <v>853</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>57.2</v>
+        <v>56.8</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>184.5</v>
+        <v>185</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>13.9</v>
+        <v>14.05</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>394.5</v>
+        <v>397</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>280</v>
+        <v>286.5</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>185</v>
+        <v>182.5</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>189</v>
+        <v>182.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>114</v>
+        <v>121.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>241</v>
+        <v>260.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>90.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>48.75</v>
+        <v>49.2</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>104.5</v>
+        <v>111</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>67.3</v>
+        <v>68</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>57</v>
+        <v>58.8</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>134.5</v>
+        <v>138.5</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>183</v>
+        <v>185.5</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>195.5</v>
+        <v>188.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5045</v>
+        <v>5155</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>275</v>
+        <v>276.5</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>65</v>
+        <v>67.7</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>215.5</v>
+        <v>237</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1345</v>
+        <v>1365</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>191.5</v>
+        <v>200</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>233.5</v>
+        <v>243.5</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>245.5</v>
+        <v>270</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>458</v>
+        <v>456.5</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>411</v>
+        <v>428.5</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1770</v>
+        <v>1755</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>24.55</v>
+        <v>24.95</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1350</v>
+        <v>1310</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>216.5</v>
+        <v>237.5</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>411.5</v>
+        <v>416</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>927</v>
+        <v>981</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>380.5</v>
+        <v>385</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>76.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7000</v>
+        <v>7075</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>135.5</v>
+        <v>138</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>75.5</v>
+        <v>79.7</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>71.3</v>
+        <v>75.2</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>322.5</v>
+        <v>322</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>142.5</v>
+        <v>150.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>137</v>
+        <v>138.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>257</v>
+        <v>258.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1185</v>
+        <v>1250</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>403</v>
+        <v>407.5</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>363</v>
+        <v>355.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2475</v>
+        <v>2565</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>275</v>
+        <v>275.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>307.5</v>
+        <v>320</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1075</v>
+        <v>1135</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>137</v>
+        <v>137.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>67.8</v>
+        <v>68.5</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1060</v>
+        <v>1115</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>465.5</v>
+        <v>468</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>271</v>
+        <v>270.5</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2095</v>
+        <v>2200</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>169</v>
+        <v>169.5</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>14.9</v>
+        <v>14.95</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>305.5</v>
+        <v>312.5</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>84.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.8</v>
+        <v>31.95</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1655</v>
+        <v>1820</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>575</v>
+        <v>632</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>274.5</v>
+        <v>280</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2710</v>
+        <v>2890</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>363.5</v>
+        <v>368.5</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2200</v>
+        <v>2415</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1465</v>
+        <v>1610</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>278</v>
+        <v>282.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>5870</v>
+        <v>5980</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.65</v>
+        <v>16.7</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>898</v>
+        <v>922</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>151.5</v>
+        <v>151</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1755</v>
+        <v>1930</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>290</v>
+        <v>293.5</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>413.5</v>
+        <v>420</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>177</v>
+        <v>181.5</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>236.5</v>
+        <v>239</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>293</v>
+        <v>297.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1080</v>
+        <v>1055</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>147</v>
+        <v>148.5</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>49.2</v>
+        <v>50.5</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>251.5</v>
+        <v>254.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>214.5</v>
+        <v>215</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>43.25</v>
+        <v>43.55</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>89.3</v>
+        <v>90.5</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>189</v>
+        <v>194.5</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>60.5</v>
+        <v>61.4</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>348</v>
+        <v>348.5</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>948</v>
+        <v>986</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>173</v>
+        <v>180.5</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2000</v>
+        <v>2015</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.35</v>
+        <v>37.55</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.15</v>
+        <v>26.1</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>367.5</v>
+        <v>373.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>56.6</v>
+        <v>57.5</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>89.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1185</v>
+        <v>1300</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.35</v>
+        <v>15.25</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>67.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33853,7 +33853,7 @@
         <v>15.67</v>
       </c>
       <c r="Q492" s="3" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="R492" s="3" t="n">
         <v>5.7</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>100.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.7</v>
+        <v>39.55</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>62.4</v>
+        <v>63.1</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.8</v>
+        <v>40.4</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.25</v>
+        <v>28.45</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.1</v>
+        <v>35.05</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.55</v>
+        <v>28.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.85</v>
+        <v>41.65</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>157</v>
+        <v>157.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>225.5</v>
+        <v>230.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.35</v>
+        <v>12.2</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>69.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>29.15</v>
+        <v>28.7</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.55</v>
+        <v>24.35</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>196.5</v>
+        <v>195</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>165.5</v>
+        <v>167</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>49.8</v>
+        <v>48.95</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>695</v>
+        <v>730</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2790,7 +2790,7 @@
         <v>59.91</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>66</v>
+        <v>79.5</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>2</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1395</v>
+        <v>1370</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.4</v>
+        <v>37.9</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.5</v>
+        <v>36.05</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.35</v>
+        <v>37.2</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>51.2</v>
+        <v>50</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40.65</v>
+        <v>40.3</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.65</v>
+        <v>16.45</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>125.5</v>
+        <v>126</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>162.5</v>
+        <v>160.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>182</v>
+        <v>180.5</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>59.1</v>
+        <v>60.7</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.7</v>
+        <v>34.25</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>118.5</v>
+        <v>130</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>24.8</v>
+        <v>24.45</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.85</v>
+        <v>29.1</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.85</v>
+        <v>13.95</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>50.2</v>
+        <v>49.1</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>363</v>
+        <v>364.5</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>13860</v>
+        <v>13905</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.35</v>
+        <v>31.1</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>28.25</v>
+        <v>27.4</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.95</v>
+        <v>30.7</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.3</v>
+        <v>16.95</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>54.1</v>
+        <v>53.6</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.65</v>
+        <v>48.3</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>231.5</v>
+        <v>234</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>32.85</v>
+        <v>32.3</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>249.5</v>
+        <v>240</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>41.6</v>
+        <v>40.05</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.6</v>
+        <v>46</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2410</v>
+        <v>2460</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>19.55</v>
+        <v>19.45</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>121.5</v>
+        <v>124.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>38.6</v>
+        <v>38.55</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>88</v>
+        <v>89.3</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>239.5</v>
+        <v>233.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>29.25</v>
+        <v>29</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>32.7</v>
+        <v>32.3</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>67.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>1025</v>
+        <v>999</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2030</v>
+        <v>2230</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>49.3</v>
+        <v>47.95</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51.1</v>
+        <v>52.5</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>43.1</v>
+        <v>42.4</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1045</v>
+        <v>1120</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>361</v>
+        <v>364.5</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>345</v>
+        <v>347.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5415</v>
+        <v>5495</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>45.6</v>
+        <v>44.35</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>64.8</v>
+        <v>63.5</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>711</v>
+        <v>680</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.7</v>
+        <v>25.55</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>57.1</v>
+        <v>56.1</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>26.8</v>
+        <v>28.7</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>137.5</v>
+        <v>138</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>178</v>
+        <v>171.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>104.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>260</v>
+        <v>259.5</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>284.5</v>
+        <v>289.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4415</v>
+        <v>4760</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>97.2</v>
+        <v>100.5</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>209.5</v>
+        <v>208.5</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>125.5</v>
+        <v>127</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>156</v>
+        <v>157.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>256</v>
+        <v>254.5</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>298.5</v>
+        <v>323</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>181.5</v>
+        <v>184</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.25</v>
+        <v>31.3</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>12.15</v>
+        <v>11.9</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>20.15</v>
+        <v>19.75</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35</v>
+        <v>35.15</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>47.15</v>
+        <v>46.9</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>48.55</v>
+        <v>48</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.45</v>
+        <v>38.65</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.85</v>
+        <v>34.5</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>35.85</v>
+        <v>36.35</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>78.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>115</v>
+        <v>114.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.5</v>
+        <v>42.1</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>65</v>
+        <v>66.3</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>99.8</v>
+        <v>99.2</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>173.5</v>
+        <v>174</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.65</v>
+        <v>20.5</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.3</v>
+        <v>22.25</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>18.15</v>
+        <v>17.9</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>25.6</v>
+        <v>27.1</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>278.5</v>
+        <v>297</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>7400</v>
+        <v>6660</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>129</v>
+        <v>129.5</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>88</v>
+        <v>86.3</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>131.5</v>
+        <v>132</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3570</v>
+        <v>3420</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>144.5</v>
+        <v>142</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>340</v>
+        <v>339.5</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>701</v>
+        <v>771</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>111.5</v>
+        <v>109.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>43.95</v>
+        <v>43.25</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>179.5</v>
+        <v>179</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>902</v>
+        <v>949</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>173.5</v>
+        <v>176.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>488.5</v>
+        <v>493</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3170</v>
+        <v>3070</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>176.5</v>
+        <v>171.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>449.5</v>
+        <v>450.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2385</v>
+        <v>2555</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>803</v>
+        <v>883</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>192</v>
+        <v>190.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>206</v>
+        <v>199.5</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>400.5</v>
+        <v>412</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>176.5</v>
+        <v>176</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>140</v>
+        <v>140.5</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>111</v>
+        <v>109.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>214</v>
+        <v>213.5</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>430</v>
+        <v>469.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>211</v>
+        <v>206.5</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>30</v>
+        <v>29.85</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>1055</v>
+        <v>987</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>282.5</v>
+        <v>284</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>172.5</v>
+        <v>169.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5810</v>
+        <v>5935</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>48.5</v>
+        <v>49.95</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1505</v>
+        <v>1510</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2385</v>
+        <v>2570</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1685</v>
+        <v>1695</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.15</v>
+        <v>17.05</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>255</v>
+        <v>252.5</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>224</v>
+        <v>221.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>248</v>
+        <v>248.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5875</v>
+        <v>5655</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4220</v>
+        <v>4040</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2145</v>
+        <v>2070</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>65.5</v>
+        <v>65.8</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>20</v>
+        <v>19.75</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>40.1</v>
+        <v>39.7</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56.1</v>
+        <v>56.4</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>92.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>62</v>
+        <v>61.2</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>66.8</v>
+        <v>67.2</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>118</v>
+        <v>119.5</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77</v>
+        <v>76.5</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.8</v>
+        <v>29.65</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>30.15</v>
+        <v>29.55</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>63.6</v>
+        <v>62.7</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>164.5</v>
+        <v>163</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>171.5</v>
+        <v>167.5</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>473.5</v>
+        <v>462</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>294.5</v>
+        <v>297.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>30.1</v>
+        <v>28.3</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>200.5</v>
+        <v>200</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>44.65</v>
+        <v>45.6</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>231.5</v>
+        <v>228</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>346</v>
+        <v>344.5</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>226.5</v>
+        <v>239</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>120</v>
+        <v>122.5</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>276</v>
+        <v>277.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>629</v>
+        <v>590</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>33.2</v>
+        <v>32.75</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>20.9</v>
+        <v>20.85</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>90</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>17470</v>
+        <v>19215</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>330</v>
+        <v>318.5</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>32</v>
+        <v>35.2</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>79.2</v>
+        <v>81.2</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>112.5</v>
+        <v>118.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>261.5</v>
+        <v>262.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>112.5</v>
+        <v>120</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>64</v>
+        <v>63.3</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>50</v>
+        <v>49.45</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>56.8</v>
+        <v>55.2</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>111.5</v>
+        <v>112.5</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.05</v>
+        <v>14.2</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>397</v>
+        <v>386.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>286.5</v>
+        <v>288</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>182.5</v>
+        <v>181</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>182.5</v>
+        <v>191</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>121.5</v>
+        <v>116</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>260.5</v>
+        <v>286.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>49.2</v>
+        <v>47.4</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>111</v>
+        <v>111.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1305</v>
+        <v>1370</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>68</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>138.5</v>
+        <v>136</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>185.5</v>
+        <v>185</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>188.5</v>
+        <v>181.5</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5155</v>
+        <v>5490</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>276.5</v>
+        <v>280</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>237</v>
+        <v>232.5</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>44</v>
+        <v>44.35</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>243.5</v>
+        <v>239.5</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>270</v>
+        <v>269.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>456.5</v>
+        <v>442.5</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>395</v>
+        <v>389.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>428.5</v>
+        <v>418</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1755</v>
+        <v>1700</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>24.95</v>
+        <v>24.6</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1310</v>
+        <v>1325</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>237.5</v>
+        <v>231.5</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>449</v>
+        <v>448.5</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>385</v>
+        <v>379.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3350</v>
+        <v>3470</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7075</v>
+        <v>7000</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>138</v>
+        <v>133.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>911</v>
+        <v>960</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>79.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>61.5</v>
+        <v>63.4</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>75.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>150.5</v>
+        <v>152</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>61</v>
+        <v>60.6</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>258.5</v>
+        <v>265</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>407.5</v>
+        <v>411</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>355.5</v>
+        <v>356.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2565</v>
+        <v>2490</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>275.5</v>
+        <v>276</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>289</v>
+        <v>299.5</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1360</v>
+        <v>1410</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1135</v>
+        <v>1110</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>68.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1115</v>
+        <v>1080</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>270.5</v>
+        <v>271.5</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2200</v>
+        <v>2265</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>169.5</v>
+        <v>166</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>312.5</v>
+        <v>315</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>283</v>
+        <v>286.5</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>696</v>
+        <v>719</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>1490</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.95</v>
+        <v>31.8</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>1820</v>
+        <v>2000</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2890</v>
+        <v>2915</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>368.5</v>
+        <v>354</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2415</v>
+        <v>2375</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1610</v>
+        <v>1590</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>282.5</v>
+        <v>283</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>5980</v>
+        <v>6565</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.7</v>
+        <v>16.65</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>116.5</v>
+        <v>115.5</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>335</v>
+        <v>316.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1930</v>
+        <v>1870</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>293.5</v>
+        <v>291.5</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>181.5</v>
+        <v>185.5</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>239</v>
+        <v>249.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>297.5</v>
+        <v>327</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>112</v>
+        <v>122.5</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>148.5</v>
+        <v>150.5</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>254.5</v>
+        <v>253</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>215</v>
+        <v>216.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>104.5</v>
+        <v>105</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>43.55</v>
+        <v>43.85</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>194.5</v>
+        <v>189.5</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>61.4</v>
+        <v>61.9</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>348.5</v>
+        <v>347</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>986</v>
+        <v>937</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>180.5</v>
+        <v>181</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2015</v>
+        <v>2095</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.55</v>
+        <v>37.2</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.1</v>
+        <v>26.05</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>373.5</v>
+        <v>361</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>142</v>
+        <v>142.5</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1300</v>
+        <v>1240</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>72.3</v>
+        <v>72</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.25</v>
+        <v>15.3</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29.05</v>
+        <v>29.2</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>81.2</v>
+        <v>81.7</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>79.3</v>
+        <v>77.8</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.2</v>
+        <v>55.7</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>131.5</v>
+        <v>129</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.45</v>
+        <v>27.9</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.05</v>
+        <v>35.2</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.5</v>
+        <v>27.45</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.4</v>
+        <v>28.55</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.65</v>
+        <v>41.7</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>230.5</v>
+        <v>235</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.2</v>
+        <v>12.35</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>81.7</v>
+        <v>79</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.7</v>
+        <v>28.65</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.35</v>
+        <v>24.45</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>207.5</v>
+        <v>204.5</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>71.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>48.95</v>
+        <v>47.9</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2790,7 +2790,7 @@
         <v>59.91</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>79.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>2</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1370</v>
+        <v>1335</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.05</v>
+        <v>36.65</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>40.9</v>
+        <v>39.5</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40.3</v>
+        <v>40.85</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.45</v>
+        <v>16.25</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>73.5</v>
+        <v>72.3</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.45</v>
+        <v>10.4</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.6</v>
+        <v>44.55</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>126</v>
+        <v>126.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>160.5</v>
+        <v>164</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>19.4</v>
+        <v>19.15</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>60.7</v>
+        <v>59.9</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.25</v>
+        <v>34.85</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.1</v>
+        <v>29.15</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>80.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>49.1</v>
+        <v>49.35</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>364.5</v>
+        <v>350</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>13905</v>
+        <v>12520</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>31.1</v>
+        <v>30.65</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>27.4</v>
+        <v>25.75</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>30.8</v>
+        <v>30.45</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.4</v>
+        <v>63.7</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.5</v>
+        <v>31.85</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1850</v>
+        <v>1805</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>256</v>
+        <v>251.5</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>40.05</v>
+        <v>39.05</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>43.3</v>
+        <v>42.7</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2460</v>
+        <v>2470</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>19.45</v>
+        <v>18.75</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>124.5</v>
+        <v>126</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>38.55</v>
+        <v>37.75</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2100</v>
+        <v>1955</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>233.5</v>
+        <v>227.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>29</v>
+        <v>28.65</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>32.3</v>
+        <v>31.05</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>65.7</v>
+        <v>64.5</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>42.2</v>
+        <v>41.9</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>142</v>
+        <v>135.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2230</v>
+        <v>2265</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>47.95</v>
+        <v>47.55</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>42.4</v>
+        <v>41.5</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1120</v>
+        <v>1075</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>28.15</v>
+        <v>27.8</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>364.5</v>
+        <v>357</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>158.5</v>
+        <v>152.5</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>729</v>
+        <v>692</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>347.5</v>
+        <v>328</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5495</v>
+        <v>5340</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>110.5</v>
+        <v>105.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>77.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>44.35</v>
+        <v>42.8</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>63.5</v>
+        <v>62.6</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>680</v>
+        <v>657</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.55</v>
+        <v>24.85</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>56.1</v>
+        <v>54.6</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1080</v>
+        <v>1055</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>171.5</v>
+        <v>168</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>259.5</v>
+        <v>253.5</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>118</v>
+        <v>114.5</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>273</v>
+        <v>268.5</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>289.5</v>
+        <v>286</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4760</v>
+        <v>4710</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>131</v>
+        <v>130.5</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>203</v>
+        <v>194.5</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>100.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>226</v>
+        <v>215.5</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>208.5</v>
+        <v>205</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>122</v>
+        <v>119.5</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>157.5</v>
+        <v>155.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>158</v>
+        <v>152.5</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>254.5</v>
+        <v>245.5</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>40.9</v>
+        <v>39.15</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>323</v>
+        <v>318.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>184</v>
+        <v>179.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.75</v>
+        <v>19.85</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.15</v>
+        <v>35.25</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>38.65</v>
+        <v>39.05</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>94.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>36.35</v>
+        <v>36.5</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>58.1</v>
+        <v>57.3</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.45</v>
+        <v>20.6</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>114.5</v>
+        <v>112</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.1</v>
+        <v>42.45</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>66.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>99.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>174</v>
+        <v>172.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.6</v>
+        <v>45.55</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.25</v>
+        <v>22.45</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>17.9</v>
+        <v>18.25</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>56.7</v>
+        <v>57.4</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>113</v>
+        <v>112.5</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>297</v>
+        <v>298.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>6660</v>
+        <v>6500</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>129.5</v>
+        <v>127</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>86.3</v>
+        <v>83.8</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3420</v>
+        <v>3285</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>142</v>
+        <v>138.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>91.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>339.5</v>
+        <v>323</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>63.4</v>
+        <v>62.3</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>109.5</v>
+        <v>111.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>43.25</v>
+        <v>43.3</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>192.5</v>
+        <v>189.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>176.5</v>
+        <v>172</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>3070</v>
+        <v>2865</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>171.5</v>
+        <v>167.5</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>450.5</v>
+        <v>441.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2555</v>
+        <v>2635</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>752</v>
+        <v>726</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>883</v>
+        <v>938</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>384</v>
+        <v>375.5</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>136</v>
+        <v>133.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>197</v>
+        <v>186.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>176</v>
+        <v>166.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>140.5</v>
+        <v>138</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>109.5</v>
+        <v>103.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1440</v>
+        <v>1340</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>213.5</v>
+        <v>206.5</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>190</v>
+        <v>187.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>469.5</v>
+        <v>475</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>29.85</v>
+        <v>29.9</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>987</v>
+        <v>1010</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>284</v>
+        <v>281.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>169.5</v>
+        <v>160.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5935</v>
+        <v>5960</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>585</v>
+        <v>527</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>49.95</v>
+        <v>48.8</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1510</v>
+        <v>1490</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>231</v>
+        <v>221.5</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2570</v>
+        <v>2825</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1695</v>
+        <v>1620</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>17.05</v>
+        <v>16.9</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>722</v>
+        <v>740</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>252.5</v>
+        <v>246</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>221.5</v>
+        <v>218.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>159.5</v>
+        <v>155.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>248.5</v>
+        <v>245</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5655</v>
+        <v>5550</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>2070</v>
+        <v>1935</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>65.8</v>
+        <v>63.9</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>105</v>
+        <v>104.5</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.75</v>
+        <v>19.85</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>39.7</v>
+        <v>38.9</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56.4</v>
+        <v>56.1</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>61.2</v>
+        <v>60</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>119.5</v>
+        <v>126.5</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.65</v>
+        <v>29.6</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>29.55</v>
+        <v>30.4</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>62.7</v>
+        <v>65.3</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>163</v>
+        <v>162.5</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>167.5</v>
+        <v>163</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>247</v>
+        <v>235.5</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>297.5</v>
+        <v>297</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>394</v>
+        <v>392.5</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>45.6</v>
+        <v>46.95</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>50.6</v>
+        <v>49.15</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>228</v>
+        <v>218.5</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>344.5</v>
+        <v>346</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>250.5</v>
+        <v>249.5</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.8</v>
+        <v>36.1</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>60.2</v>
+        <v>60.5</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>122.5</v>
+        <v>118</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>247.5</v>
+        <v>241.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>165.5</v>
+        <v>177.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>277.5</v>
+        <v>280.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>32.75</v>
+        <v>32.8</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>20.85</v>
+        <v>21.15</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1440</v>
+        <v>1400</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>19215</v>
+        <v>19220</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>318.5</v>
+        <v>309.5</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1405</v>
+        <v>1370</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>35.2</v>
+        <v>38.7</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>81.2</v>
+        <v>82.5</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>118.5</v>
+        <v>117</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>75.3</v>
+        <v>73.5</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>262.5</v>
+        <v>257.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>120</v>
+        <v>114.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>72.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>183.5</v>
+        <v>180</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>49.45</v>
+        <v>49.4</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>55.2</v>
+        <v>54.9</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>112.5</v>
+        <v>115</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>386.5</v>
+        <v>378.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>191</v>
+        <v>186.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>116</v>
+        <v>114.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>286.5</v>
+        <v>273.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.4</v>
+        <v>47.75</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>111.5</v>
+        <v>109</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1370</v>
+        <v>1385</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>65.5</v>
+        <v>65</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>308</v>
+        <v>300.5</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>59</v>
+        <v>56.9</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>181.5</v>
+        <v>178</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5490</v>
+        <v>5795</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>280</v>
+        <v>275.5</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>67.8</v>
+        <v>65.8</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>232.5</v>
+        <v>223</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1370</v>
+        <v>1345</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>195</v>
+        <v>188.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>44.35</v>
+        <v>43.25</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>239.5</v>
+        <v>236</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>269.5</v>
+        <v>264.5</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>442.5</v>
+        <v>463.5</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>77</v>
+        <v>74.7</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>389.5</v>
+        <v>376</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1325</v>
+        <v>1405</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>231.5</v>
+        <v>225</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>448.5</v>
+        <v>435</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>68.8</v>
+        <v>66.8</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>416</v>
+        <v>412.5</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>379.5</v>
+        <v>376</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3470</v>
+        <v>3620</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7000</v>
+        <v>7700</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>133.5</v>
+        <v>130.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>960</v>
+        <v>931</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>152</v>
+        <v>147.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.6</v>
+        <v>60.3</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>137.5</v>
+        <v>135.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>265</v>
+        <v>258.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1300</v>
+        <v>1215</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2490</v>
+        <v>2340</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>299.5</v>
+        <v>294</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>190</v>
+        <v>183.5</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>137.5</v>
+        <v>134.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>271.5</v>
+        <v>271</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2265</v>
+        <v>2155</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>14.95</v>
+        <v>15.25</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>85.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>286.5</v>
+        <v>287.5</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.8</v>
+        <v>31.25</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>2000</v>
+        <v>2065</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>660</v>
+        <v>594</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>279</v>
+        <v>272.5</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2915</v>
+        <v>2910</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>561</v>
+        <v>523</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2375</v>
+        <v>2315</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1590</v>
+        <v>1545</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>283</v>
+        <v>275.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6565</v>
+        <v>6970</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.65</v>
+        <v>16.55</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>115.5</v>
+        <v>115</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>316.5</v>
+        <v>291.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>395</v>
+        <v>382.5</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>930</v>
+        <v>899</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>1870</v>
+        <v>2035</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>291.5</v>
+        <v>278</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>185.5</v>
+        <v>177</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>249.5</v>
+        <v>236.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>177</v>
+        <v>174.5</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>327</v>
+        <v>294.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>122.5</v>
+        <v>134.5</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>150.5</v>
+        <v>147</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>253</v>
+        <v>248.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>112.5</v>
+        <v>110</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>216.5</v>
+        <v>213.5</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>43.85</v>
+        <v>43.75</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>189.5</v>
+        <v>180</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>91.3</v>
+        <v>90.3</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>347</v>
+        <v>341.5</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>937</v>
+        <v>907</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>143</v>
+        <v>139.5</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>181</v>
+        <v>170.5</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>222</v>
+        <v>219.5</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2095</v>
+        <v>2085</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.2</v>
+        <v>37.05</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.05</v>
+        <v>26.6</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>242</v>
+        <v>239.5</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>361</v>
+        <v>371.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>142.5</v>
+        <v>141.5</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>57.9</v>
+        <v>57.2</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>94.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1240</v>
+        <v>1225</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>72</v>
+        <v>71.2</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.3</v>
+        <v>15.25</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>69.8</v>
+        <v>71.8</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>77.8</v>
+        <v>77</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>97.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.55</v>
+        <v>39.6</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.3</v>
+        <v>39.1</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.7</v>
+        <v>55.2</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>129</v>
+        <v>128.5</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>27.9</v>
+        <v>28.05</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.3</v>
+        <v>24.75</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>76.7</v>
+        <v>76</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.7</v>
+        <v>41.95</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>235</v>
+        <v>236.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.35</v>
+        <v>12.8</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.8</v>
+        <v>12.15</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.109999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.65</v>
+        <v>28.7</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>24.45</v>
+        <v>26.85</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>67.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>17.8</v>
+        <v>18.15</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.6</v>
+        <v>13.75</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>300</v>
+        <v>295.5</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>204.5</v>
+        <v>206</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2790,7 +2790,7 @@
         <v>59.91</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>2</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.1</v>
+        <v>38.35</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.65</v>
+        <v>37</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.6</v>
+        <v>38.1</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>39.5</v>
+        <v>39.85</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.25</v>
+        <v>16.8</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.4</v>
+        <v>10.85</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.55</v>
+        <v>44.2</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>126.5</v>
+        <v>126</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>164</v>
+        <v>164.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>100</v>
+        <v>101.5</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>180.5</v>
+        <v>179</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>59.9</v>
+        <v>60.2</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.85</v>
+        <v>35.1</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>24.45</v>
+        <v>24.55</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.2</v>
+        <v>13.45</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.15</v>
+        <v>29.2</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.1</v>
+        <v>19.25</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.4</v>
+        <v>22.55</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17</v>
+        <v>17.05</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>49.35</v>
+        <v>48.6</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>350</v>
+        <v>370.5</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>30.65</v>
+        <v>30.85</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>16.95</v>
+        <v>17.05</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>30.45</v>
+        <v>30.5</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.2</v>
+        <v>84</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>48</v>
+        <v>47.85</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>233</v>
+        <v>232.5</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.85</v>
+        <v>31.8</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>291</v>
+        <v>292.5</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>251.5</v>
+        <v>252</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>39.05</v>
+        <v>38.9</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>42.7</v>
+        <v>42.65</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>18.75</v>
+        <v>19.15</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>126</v>
+        <v>126.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>37.75</v>
+        <v>41.5</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>1955</v>
+        <v>2015</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>227.5</v>
+        <v>237.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.65</v>
+        <v>28.8</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.05</v>
+        <v>31.8</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>41.9</v>
+        <v>42.65</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>64</v>
+        <v>64.3</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>135.5</v>
+        <v>133.5</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2265</v>
+        <v>2335</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>47.55</v>
+        <v>48.3</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>41.5</v>
+        <v>42.2</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>27.8</v>
+        <v>28.05</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>357</v>
+        <v>349.5</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>152.5</v>
+        <v>156.5</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>24.85</v>
+        <v>25.15</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>29.6</v>
+        <v>30.5</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>139</v>
+        <v>139.5</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>168</v>
+        <v>167.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>97.5</v>
+        <v>99.5</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>253.5</v>
+        <v>248.5</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>268.5</v>
+        <v>270</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>286</v>
+        <v>287.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>130.5</v>
+        <v>130</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>194.5</v>
+        <v>197.5</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>103.5</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>215.5</v>
+        <v>215</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>119.5</v>
+        <v>120</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>121</v>
+        <v>122.5</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>152.5</v>
+        <v>152</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>245.5</v>
+        <v>249.5</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>39.15</v>
+        <v>39.45</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>318.5</v>
+        <v>319.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>179.5</v>
+        <v>180</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.6</v>
+        <v>31.55</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>11.9</v>
+        <v>12.05</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.85</v>
+        <v>19.8</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.25</v>
+        <v>35.75</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>48.2</v>
+        <v>49.1</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>39.05</v>
+        <v>39.4</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>36.5</v>
+        <v>36.95</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>77.8</v>
+        <v>79.7</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>57.3</v>
+        <v>58.5</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.6</v>
+        <v>20.45</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.45</v>
+        <v>42.55</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>172.5</v>
+        <v>174.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.6</v>
+        <v>20.55</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>45.55</v>
+        <v>46.3</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.45</v>
+        <v>22.4</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>18.25</v>
+        <v>18.05</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>217</v>
+        <v>217.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>112.5</v>
+        <v>115</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>298.5</v>
+        <v>306.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>83.8</v>
+        <v>87</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>101.5</v>
+        <v>100</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>138.5</v>
+        <v>142.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>111.5</v>
+        <v>111</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>43.3</v>
+        <v>41.85</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>175</v>
+        <v>176.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>189.5</v>
+        <v>191.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>172</v>
+        <v>184.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>118</v>
+        <v>119.5</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>121</v>
+        <v>126.5</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>167.5</v>
+        <v>166</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>441.5</v>
+        <v>464</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2635</v>
+        <v>2555</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>60.2</v>
+        <v>62.5</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>938</v>
+        <v>900</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>375.5</v>
+        <v>367</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>133.5</v>
+        <v>128.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>186.5</v>
+        <v>185.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>186.5</v>
+        <v>189</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>414</v>
+        <v>414.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>166.5</v>
+        <v>167.5</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>103.5</v>
+        <v>104.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1340</v>
+        <v>1385</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>206.5</v>
+        <v>208</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>187.5</v>
+        <v>189.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>475</v>
+        <v>478.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>203.5</v>
+        <v>206</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>29.9</v>
+        <v>30.4</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>1010</v>
+        <v>1110</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>281.5</v>
+        <v>282</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>48.8</v>
+        <v>50.1</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1490</v>
+        <v>1455</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>221.5</v>
+        <v>225.5</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2825</v>
+        <v>2780</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>16.9</v>
+        <v>16.95</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>218.5</v>
+        <v>222</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>155.5</v>
+        <v>157.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5550</v>
+        <v>5760</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4030</v>
+        <v>3905</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>1935</v>
+        <v>1975</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>63.9</v>
+        <v>64.2</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>274</v>
+        <v>271.5</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>521</v>
+        <v>566</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>669</v>
+        <v>700</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>104.5</v>
+        <v>105</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.85</v>
+        <v>19.95</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>91.3</v>
+        <v>81.8</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>126.5</v>
+        <v>135</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.6</v>
+        <v>29.95</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>30.4</v>
+        <v>30.55</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>65.3</v>
+        <v>62.8</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>162.5</v>
+        <v>166</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>235.5</v>
+        <v>244</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>28.3</v>
+        <v>27.2</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>392.5</v>
+        <v>0</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>46.95</v>
+        <v>45.8</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>49.15</v>
+        <v>48.3</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>218.5</v>
+        <v>226.5</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>346</v>
+        <v>340.5</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>234</v>
+        <v>249.5</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>249.5</v>
+        <v>246</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.1</v>
+        <v>36.6</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>60.5</v>
+        <v>61.4</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>241.5</v>
+        <v>252.5</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>91.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>177.5</v>
+        <v>177</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>280.5</v>
+        <v>281.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>32.8</v>
+        <v>32.55</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.15</v>
+        <v>21.05</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>296</v>
+        <v>296.5</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>19220</v>
+        <v>18605</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>309.5</v>
+        <v>314</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1370</v>
+        <v>1355</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>38.7</v>
+        <v>42.55</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>82.5</v>
+        <v>84.8</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>257.5</v>
+        <v>264.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>114.5</v>
+        <v>111.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>54.9</v>
+        <v>55.8</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>185</v>
+        <v>184.5</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.3</v>
+        <v>14.65</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>378.5</v>
+        <v>383</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>276</v>
+        <v>272.5</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>186.5</v>
+        <v>198</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>273.5</v>
+        <v>268.5</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>47.75</v>
+        <v>48.45</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1385</v>
+        <v>1330</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>65</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>81.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>300.5</v>
+        <v>302.5</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>134</v>
+        <v>137.5</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>185</v>
+        <v>187.5</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>275.5</v>
+        <v>281</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>65.8</v>
+        <v>69.3</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>223</v>
+        <v>226.5</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>188.5</v>
+        <v>193.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>43.25</v>
+        <v>43.7</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>236</v>
+        <v>233.5</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>264.5</v>
+        <v>275</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>463.5</v>
+        <v>480</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>958</v>
+        <v>926</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>376</v>
+        <v>378.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>24</v>
+        <v>23.95</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1405</v>
+        <v>1345</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>225</v>
+        <v>225.5</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>66.8</v>
+        <v>67.5</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>412.5</v>
+        <v>407.5</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3620</v>
+        <v>3610</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7700</v>
+        <v>7280</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>931</v>
+        <v>999</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>77.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>64</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>320</v>
+        <v>317.5</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>147.5</v>
+        <v>149</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>258.5</v>
+        <v>264.5</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1215</v>
+        <v>1200</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>356.5</v>
+        <v>353.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>279</v>
+        <v>279.5</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>294</v>
+        <v>299.5</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1405</v>
+        <v>1370</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>325</v>
+        <v>354.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>183.5</v>
+        <v>182.5</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1145</v>
+        <v>1200</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>134.5</v>
+        <v>135</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>55.4</v>
+        <v>54.9</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>63.7</v>
+        <v>63.4</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>463</v>
+        <v>475.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2155</v>
+        <v>2295</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>15.25</v>
+        <v>15.1</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>287.5</v>
+        <v>291</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>60.4</v>
+        <v>54.9</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.25</v>
+        <v>31.1</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>2065</v>
+        <v>2030</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>272.5</v>
+        <v>272</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2910</v>
+        <v>2980</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>355</v>
+        <v>355.5</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2315</v>
+        <v>2270</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1545</v>
+        <v>1610</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>275.5</v>
+        <v>276.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6970</v>
+        <v>6720</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.55</v>
+        <v>16.65</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>291.5</v>
+        <v>320.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>382.5</v>
+        <v>386.5</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>151</v>
+        <v>151.5</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>2035</v>
+        <v>2080</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>450</v>
+        <v>442.5</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>236.5</v>
+        <v>236</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>294.5</v>
+        <v>289.5</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1025</v>
+        <v>1110</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>134.5</v>
+        <v>134</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>147</v>
+        <v>149.5</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>50</v>
+        <v>49.85</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>248.5</v>
+        <v>251</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>110</v>
+        <v>113.5</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>213.5</v>
+        <v>212</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>101</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>43.75</v>
+        <v>43.3</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>89.5</v>
+        <v>86.5</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>61.9</v>
+        <v>63.5</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>90.3</v>
+        <v>91.5</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>341.5</v>
+        <v>348</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>139.5</v>
+        <v>138.5</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>219.5</v>
+        <v>217.5</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>37.05</v>
+        <v>36.7</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.6</v>
+        <v>26.25</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>239.5</v>
+        <v>238.5</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>371.5</v>
+        <v>375</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>141.5</v>
+        <v>141</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>57.2</v>
+        <v>59.3</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1225</v>
+        <v>1345</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.7</v>
+        <v>24.55</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.25</v>
+        <v>15.35</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29.1</v>
+        <v>29.05</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>71.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>77</v>
+        <v>79.2</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33853,7 +33853,7 @@
         <v>15.67</v>
       </c>
       <c r="Q492" s="3" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="R492" s="3" t="n">
         <v>5.7</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.6</v>
+        <v>39.75</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>39.1</v>
+        <v>40.15</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.2</v>
+        <v>55.7</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>128.5</v>
+        <v>127.5</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34334,7 +34334,7 @@
         <v>12.04</v>
       </c>
       <c r="Q499" s="3" t="n">
-        <v>81</v>
+        <v>80.3</v>
       </c>
       <c r="R499" s="3" t="n">
         <v>4.38</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.05</v>
+        <v>28.2</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.75</v>
+        <v>24.8</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.4</v>
+        <v>35.45</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.45</v>
+        <v>27.25</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>76</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.55</v>
+        <v>28.35</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.95</v>
+        <v>41.75</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.5</v>
+        <v>80.2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>66.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>236.5</v>
+        <v>244</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.8</v>
+        <v>12.45</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>12.15</v>
+        <v>11.85</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.210000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>28.7</v>
+        <v>28.65</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>1.25</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>26.85</v>
+        <v>25.15</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18.15</v>
+        <v>18</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>295.5</v>
+        <v>290</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>167</v>
+        <v>165.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1330</v>
+        <v>1305</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>38.35</v>
+        <v>37.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>37</v>
+        <v>36.45</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>38.1</v>
+        <v>37.75</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>50.2</v>
+        <v>49.4</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>39.85</v>
+        <v>39.05</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40.85</v>
+        <v>40.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>72.3</v>
+        <v>71.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.85</v>
+        <v>10.6</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>44.2</v>
+        <v>43.75</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>164.5</v>
+        <v>161.5</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>101.5</v>
+        <v>98.3</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>19.15</v>
+        <v>18.6</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>60.2</v>
+        <v>59.6</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>35.1</v>
+        <v>34.4</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>24.55</v>
+        <v>25.55</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.45</v>
+        <v>13.3</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.2</v>
+        <v>29.15</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.25</v>
+        <v>19.1</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>82</v>
+        <v>81.2</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.55</v>
+        <v>22.4</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>17.05</v>
+        <v>16.9</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>370.5</v>
+        <v>363</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>12400</v>
+        <v>12600</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>133</v>
+        <v>130.5</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>30.85</v>
+        <v>30.4</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>26.5</v>
+        <v>25.85</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>17.05</v>
+        <v>16.85</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>64.2</v>
+        <v>64</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>84</v>
+        <v>83.5</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.85</v>
+        <v>47.05</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5871,7 +5871,7 @@
         <v>16.2</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>232.5</v>
+        <v>230</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>14.5</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.8</v>
+        <v>31.1</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>292.5</v>
+        <v>291</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>141.5</v>
+        <v>142.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1795</v>
+        <v>1675</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.8</v>
+        <v>31.15</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>228</v>
+        <v>225.5</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>38.9</v>
+        <v>38.65</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>42.65</v>
+        <v>42.2</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2465</v>
+        <v>2450</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>19.15</v>
+        <v>18.85</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>126.5</v>
+        <v>122.5</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>41.5</v>
+        <v>45.65</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>183</v>
+        <v>179.5</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>2015</v>
+        <v>1965</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>237.5</v>
+        <v>235.5</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>42.65</v>
+        <v>41.85</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>64.3</v>
+        <v>62.6</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>133.5</v>
+        <v>130</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2335</v>
+        <v>2180</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>42.2</v>
+        <v>41.15</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1100</v>
+        <v>1045</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>28.05</v>
+        <v>27.85</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8185,7 +8185,7 @@
         <v>20.71</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>67.7</v>
+        <v>67.3</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>1.99</v>
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>349.5</v>
+        <v>351.5</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>12.14</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>156.5</v>
+        <v>149</v>
       </c>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3">
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>106.5</v>
+        <v>103.5</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>62.7</v>
+        <v>61.8</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>54.6</v>
+        <v>54.2</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>167.5</v>
+        <v>165</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>99.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>248.5</v>
+        <v>250.5</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>114.5</v>
+        <v>115</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>270</v>
+        <v>271.5</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>287.5</v>
+        <v>282.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4625</v>
+        <v>4720</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>197.5</v>
+        <v>193.5</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>103.5</v>
+        <v>101.5</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10375,7 +10375,7 @@
         <v>13.61</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R144" s="3" t="n">
         <v>7.11</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>122.5</v>
+        <v>124</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>155.5</v>
+        <v>156.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>152</v>
+        <v>154.5</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>249.5</v>
+        <v>242</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>39.45</v>
+        <v>38.6</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>319.5</v>
+        <v>334</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>180</v>
+        <v>174.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.5</v>
+        <v>40.15</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.4</v>
+        <v>22.25</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.55</v>
+        <v>31.45</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11163,7 +11163,7 @@
         <v>25</v>
       </c>
       <c r="Q156" s="3" t="n">
-        <v>12.05</v>
+        <v>12</v>
       </c>
       <c r="R156" s="3" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.9</v>
+        <v>36.75</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.8</v>
+        <v>19.55</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>88.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.75</v>
+        <v>35.35</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>49.1</v>
+        <v>49.45</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11553,7 +11553,7 @@
         <v>10.69</v>
       </c>
       <c r="Q162" s="3" t="n">
-        <v>48.2</v>
+        <v>46.5</v>
       </c>
       <c r="R162" s="3" t="n">
         <v>4</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>36.95</v>
+        <v>36.25</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>79.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53.5</v>
+        <v>53</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>58.5</v>
+        <v>58</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.45</v>
+        <v>20.2</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>116</v>
+        <v>110.5</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>42.55</v>
+        <v>41.8</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12485,7 +12485,7 @@
         <v>33.48</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>65.3</v>
+        <v>63.8</v>
       </c>
       <c r="R176" s="3" t="n">
         <v>0.78</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>174.5</v>
+        <v>172.5</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.55</v>
+        <v>20.3</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12826,7 +12826,7 @@
         <v>12.67</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>178</v>
+        <v>177.5</v>
       </c>
       <c r="R181" s="3" t="n">
         <v>10.75</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>229</v>
+        <v>229.5</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>18.05</v>
+        <v>18.35</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>217.5</v>
+        <v>218.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>57.4</v>
+        <v>56.9</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>306.5</v>
+        <v>312</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>6870</v>
+        <v>6720</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="P191" s="3" t="n"/>
       <c r="Q191" s="3" t="n">
-        <v>125</v>
+        <v>124.5</v>
       </c>
       <c r="R191" s="3" t="n">
         <v>5.3</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>131</v>
+        <v>131.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3380</v>
+        <v>3460</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>142.5</v>
+        <v>139</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>85.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>758</v>
+        <v>803</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>271</v>
+        <v>266.5</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>41.85</v>
+        <v>42.05</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>176.5</v>
+        <v>179</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>191.5</v>
+        <v>192.5</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>184.5</v>
+        <v>180.5</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>119.5</v>
+        <v>120</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>2850</v>
+        <v>2830</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>126.5</v>
+        <v>126</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>464</v>
+        <v>461.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2555</v>
+        <v>2460</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>62.5</v>
+        <v>61.4</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>900</v>
+        <v>848</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>128.5</v>
+        <v>127.5</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>185.5</v>
+        <v>183.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>414.5</v>
+        <v>407</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>167.5</v>
+        <v>171</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>104.5</v>
+        <v>101.5</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1385</v>
+        <v>1440</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>189.5</v>
+        <v>182.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>478.5</v>
+        <v>488</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>206</v>
+        <v>189.5</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>30.4</v>
+        <v>30.65</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>1110</v>
+        <v>1070</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>282</v>
+        <v>283.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>160.5</v>
+        <v>161</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>5925</v>
+        <v>6225</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>50.1</v>
+        <v>49.35</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1455</v>
+        <v>1355</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>225.5</v>
+        <v>221.5</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2780</v>
+        <v>2730</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1625</v>
+        <v>1575</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>688</v>
+        <v>668</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>16.95</v>
+        <v>16.65</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>222</v>
+        <v>221.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>157.5</v>
+        <v>154.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5760</v>
+        <v>5790</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>3905</v>
+        <v>4055</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>1975</v>
+        <v>1930</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>64.2</v>
+        <v>62.6</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>271.5</v>
+        <v>269</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>566</v>
+        <v>535</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.95</v>
+        <v>19.9</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56.3</v>
+        <v>56</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>60.1</v>
+        <v>61.8</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>63.7</v>
+        <v>62</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.95</v>
+        <v>29.75</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>30.55</v>
+        <v>30.35</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>62.8</v>
+        <v>61.6</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>121.5</v>
+        <v>121</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>166</v>
+        <v>164.5</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>292</v>
+        <v>290.5</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>27.2</v>
+        <v>26.75</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>45.8</v>
+        <v>45.55</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>48.3</v>
+        <v>48.35</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>226.5</v>
+        <v>220.5</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>340.5</v>
+        <v>339</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>249.5</v>
+        <v>239</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.6</v>
+        <v>36.35</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>61.4</v>
+        <v>62.1</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>119</v>
+        <v>116.5</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>252.5</v>
+        <v>244</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -20939,7 +20939,7 @@
         <v>15.99</v>
       </c>
       <c r="Q300" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="R300" s="3" t="n">
         <v>4.01</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>502</v>
+        <v>494.5</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>177</v>
+        <v>172.5</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>281.5</v>
+        <v>276.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>610</v>
+        <v>571</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>21.05</v>
+        <v>20.85</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>296.5</v>
+        <v>290</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>92.2</v>
+        <v>90.2</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1395</v>
+        <v>1360</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>18605</v>
+        <v>18700</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1355</v>
+        <v>1290</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>42.55</v>
+        <v>46.8</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>84.8</v>
+        <v>85.7</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>157</v>
+        <v>161.5</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>118</v>
+        <v>115.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>73</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>90</v>
+        <v>89.3</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22549,7 +22549,7 @@
         <v>19.69</v>
       </c>
       <c r="Q324" s="3" t="n">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="R324" s="3" t="n">
         <v>13.42</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>264.5</v>
+        <v>258</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>111.5</v>
+        <v>108</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>193</v>
+        <v>184.5</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>75.8</v>
+        <v>74.5</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>55.8</v>
+        <v>52.3</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>184.5</v>
+        <v>185</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.65</v>
+        <v>14.7</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>383</v>
+        <v>378.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>272.5</v>
+        <v>271.5</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>198</v>
+        <v>190.5</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24053,7 +24053,7 @@
         <v>22.62</v>
       </c>
       <c r="Q346" s="3" t="n">
-        <v>115.5</v>
+        <v>112.5</v>
       </c>
       <c r="R346" s="3" t="n">
         <v>1.2</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>268.5</v>
+        <v>295</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>90.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24260,7 +24260,7 @@
         <v>5.24</v>
       </c>
       <c r="Q349" s="3" t="n">
-        <v>48.45</v>
+        <v>47.5</v>
       </c>
       <c r="R349" s="3" t="n">
         <v>3</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>110.5</v>
+        <v>108.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1330</v>
+        <v>1280</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>69</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>302.5</v>
+        <v>301</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>57.2</v>
+        <v>56.6</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>137.5</v>
+        <v>135</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25145,7 +25145,7 @@
         <v>120.99</v>
       </c>
       <c r="Q362" s="3" t="n">
-        <v>5615</v>
+        <v>5620</v>
       </c>
       <c r="R362" s="3" t="n">
         <v>22</v>
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>281</v>
+        <v>283.5</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>69.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>226.5</v>
+        <v>227</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1345</v>
+        <v>1395</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>193.5</v>
+        <v>191.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>233.5</v>
+        <v>227</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>926</v>
+        <v>876</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26012,7 +26012,7 @@
         <v>12.85</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>74.7</v>
+        <v>73.7</v>
       </c>
       <c r="R375" s="3" t="n">
         <v>3.7</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>378.5</v>
+        <v>372.5</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1345</v>
+        <v>1320</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>225.5</v>
+        <v>226.5</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>67.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>407.5</v>
+        <v>405.5</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>373</v>
+        <v>366.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>87.5</v>
+        <v>86.2</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3610</v>
+        <v>3670</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7280</v>
+        <v>7195</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>130.5</v>
+        <v>129.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>999</v>
+        <v>1030</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>71.7</v>
+        <v>70.8</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>149</v>
+        <v>148.5</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>586</v>
+        <v>554</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>136</v>
+        <v>135.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>264.5</v>
+        <v>265</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>433</v>
+        <v>423.5</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>353.5</v>
+        <v>346.5</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2325</v>
+        <v>2345</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>279.5</v>
+        <v>276</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>299.5</v>
+        <v>299</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28199,7 +28199,7 @@
         <v>61.16</v>
       </c>
       <c r="Q408" s="3" t="n">
-        <v>1370</v>
+        <v>1290</v>
       </c>
       <c r="R408" s="3" t="n">
         <v>9</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>158</v>
+        <v>156.5</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>354.5</v>
+        <v>336.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>182.5</v>
+        <v>184.5</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>135</v>
+        <v>135.5</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="P415" s="3" t="n"/>
       <c r="Q415" s="3" t="n">
-        <v>54.9</v>
+        <v>54.2</v>
       </c>
       <c r="R415" s="3" t="n"/>
       <c r="S415" s="3">
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>63.4</v>
+        <v>62.4</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1065</v>
+        <v>1030</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>475.5</v>
+        <v>469.5</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2295</v>
+        <v>2190</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>316</v>
+        <v>300.5</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>54.9</v>
+        <v>58.8</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>272</v>
+        <v>267.5</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2980</v>
+        <v>2810</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2270</v>
+        <v>2215</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>276.5</v>
+        <v>271.5</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6720</v>
+        <v>6475</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.65</v>
+        <v>16.55</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>115.5</v>
+        <v>114.5</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>320.5</v>
+        <v>308</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>386.5</v>
+        <v>425</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>902</v>
+        <v>866</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>151.5</v>
+        <v>153</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>2080</v>
+        <v>2055</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>442.5</v>
+        <v>438</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>236</v>
+        <v>229.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>174.5</v>
+        <v>171.5</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>289.5</v>
+        <v>275</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1110</v>
+        <v>1070</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>134</v>
+        <v>126.5</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>149.5</v>
+        <v>147</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>49.85</v>
+        <v>49.45</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>113.5</v>
+        <v>109.5</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>43.3</v>
+        <v>42.75</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>86.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>180</v>
+        <v>178.5</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>63.5</v>
+        <v>62</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>91.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>138.5</v>
+        <v>137</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>170.5</v>
+        <v>168</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>217.5</v>
+        <v>211</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2085</v>
+        <v>2065</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>36.7</v>
+        <v>36.35</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.25</v>
+        <v>26.3</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>238.5</v>
+        <v>234</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>375</v>
+        <v>368.5</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>59.3</v>
+        <v>58.7</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1345</v>
+        <v>1300</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>71.2</v>
+        <v>66</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.55</v>
+        <v>24.1</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.35</v>
+        <v>15.3</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33715,7 +33715,7 @@
         <v>12.87</v>
       </c>
       <c r="Q490" s="3" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="R490" s="3" t="n">
         <v>5</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>79.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33853,7 +33853,7 @@
         <v>15.67</v>
       </c>
       <c r="Q492" s="3" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="R492" s="3" t="n">
         <v>5.7</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>98.5</v>
+        <v>97.3</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.75</v>
+        <v>39.7</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.15</v>
+        <v>40.35</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>127.5</v>
+        <v>128</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>28.2</v>
+        <v>27.75</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>91.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>

--- a/taiwan_stocks_top500.xlsx
+++ b/taiwan_stocks_top500.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>9.24</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>35.45</v>
+        <v>35.3</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>2.3</v>
@@ -811,7 +811,7 @@
         <v>9.94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>27.25</v>
+        <v>27.2</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>1.85</v>
@@ -880,7 +880,7 @@
         <v>12.75</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>3</v>
@@ -949,7 +949,7 @@
         <v>12.9</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>111</v>
+        <v>110.5</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>18.31</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>3</v>
@@ -1087,7 +1087,7 @@
         <v>18.26</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28.35</v>
+        <v>28.45</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>1.34</v>
@@ -1156,7 +1156,7 @@
         <v>16.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.75</v>
+        <v>40.7</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>1.8</v>
@@ -1225,7 +1225,7 @@
         <v>18.27</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.5</v>
@@ -1294,7 +1294,7 @@
         <v>17.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>156.5</v>
+        <v>156</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>7.2</v>
@@ -1363,7 +1363,7 @@
         <v>35.24</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.5</v>
@@ -1432,7 +1432,7 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>244</v>
+        <v>234.5</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0.8</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>12.45</v>
+        <v>12.35</v>
       </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>11.85</v>
+        <v>11.95</v>
       </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3">
@@ -1696,7 +1696,7 @@
         <v>13.47</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
         <v>24.75</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>71.3</v>
+        <v>70.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0.6</v>
@@ -1901,7 +1901,7 @@
         <v>11.48</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>25.15</v>
+        <v>24.45</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0.9</v>
@@ -1970,7 +1970,7 @@
         <v>4.81</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>66.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>1.8</v>
@@ -2039,7 +2039,7 @@
         <v>19.02</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0.5</v>
@@ -2108,7 +2108,7 @@
         <v>466.67</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0.3</v>
@@ -2177,7 +2177,7 @@
         <v>13.34</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>290</v>
+        <v>288.5</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>15</v>
@@ -2246,7 +2246,7 @@
         <v>14.88</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>197.5</v>
+        <v>196.5</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>15</v>
@@ -2315,7 +2315,7 @@
         <v>27.34</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P27" s="3" t="n"/>
       <c r="Q27" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>2</v>
@@ -2451,7 +2451,7 @@
         <v>18.67</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>165.5</v>
+        <v>165</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>6</v>
@@ -2520,7 +2520,7 @@
         <v>28.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>102</v>
+        <v>100.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>2</v>
@@ -2589,7 +2589,7 @@
         <v>46.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>11</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>47.8</v>
+        <v>47.35</v>
       </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="n">
-        <v>733</v>
+        <v>790</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>3.66</v>
@@ -2790,7 +2790,7 @@
         <v>59.91</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>78.2</v>
+        <v>76</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>2</v>
@@ -2859,7 +2859,7 @@
         <v>31.09</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1305</v>
+        <v>1285</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>29.11</v>
@@ -2928,7 +2928,7 @@
         <v>11.3</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0.5</v>
@@ -2997,7 +2997,7 @@
         <v>3.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>36.45</v>
+        <v>36.2</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>2</v>
@@ -3066,7 +3066,7 @@
         <v>13.67</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>37.75</v>
+        <v>37.85</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0.7</v>
@@ -3135,7 +3135,7 @@
         <v>12.45</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>1.6</v>
@@ -3204,7 +3204,7 @@
         <v>308.46</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>39.05</v>
+        <v>38.45</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>14.68</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>40.8</v>
+        <v>40.25</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.5</v>
@@ -3342,7 +3342,7 @@
         <v>14.41</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.5</v>
+        <v>15.35</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0.18</v>
@@ -3411,7 +3411,7 @@
         <v>36.95</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>71.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>18.14</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3">
@@ -3547,7 +3547,7 @@
         <v>55.06</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>43.75</v>
+        <v>43.25</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>2</v>
@@ -3616,7 +3616,7 @@
         <v>28.39</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>82.3</v>
+        <v>81.7</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>1.85</v>
@@ -3685,7 +3685,7 @@
         <v>11.48</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>125</v>
+        <v>128.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>4.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.89</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>161.5</v>
+        <v>159</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>15.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>98.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>389</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0.29</v>
@@ -3961,7 +3961,7 @@
         <v>13.89</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>177</v>
+        <v>173.5</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>2.57</v>
@@ -4030,7 +4030,7 @@
         <v>66.98</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>59.6</v>
+        <v>58.2</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>8.75</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>34.4</v>
+        <v>34.45</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>1.5</v>
@@ -4168,7 +4168,7 @@
         <v>31.01</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>126</v>
+        <v>127.5</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0.5</v>
@@ -4237,7 +4237,7 @@
         <v>11.84</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>25.55</v>
+        <v>24.8</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0.45</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P55" s="3" t="n"/>
       <c r="Q55" s="3" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3">
@@ -4371,7 +4371,7 @@
         <v>17.91</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>29.15</v>
+        <v>29.05</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P57" s="3" t="n"/>
       <c r="Q57" s="3" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0.15</v>
@@ -4503,7 +4503,7 @@
         <v>10.74</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>81.2</v>
+        <v>82.5</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>4.3</v>
@@ -4572,7 +4572,7 @@
         <v>9.08</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>22.4</v>
+        <v>22.05</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P60" s="3" t="n"/>
       <c r="Q60" s="3" t="n">
-        <v>16.9</v>
+        <v>16.65</v>
       </c>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3">
@@ -4706,7 +4706,7 @@
         <v>14.86</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>64.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>3.3</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P62" s="3" t="n"/>
       <c r="Q62" s="3" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3">
@@ -4840,7 +4840,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>48.2</v>
+        <v>46.5</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>1.5</v>
@@ -4909,7 +4909,7 @@
         <v>52.88</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>2</v>
@@ -4978,7 +4978,7 @@
         <v>68.91</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>12600</v>
+        <v>12080</v>
       </c>
       <c r="R65" s="3" t="n">
         <v>51</v>
@@ -5047,7 +5047,7 @@
         <v>10.49</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>130.5</v>
+        <v>127</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>13.08</v>
@@ -5116,7 +5116,7 @@
         <v>5.72</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>30.4</v>
+        <v>30.25</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>1.3</v>
@@ -5183,7 +5183,7 @@
         <v>10.78</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>25.85</v>
+        <v>25.75</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.27</v>
@@ -5252,7 +5252,7 @@
         <v>16.7</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>37.55</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>16.85</v>
+        <v>16.7</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.65</v>
@@ -5390,7 +5390,7 @@
         <v>32.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -5459,7 +5459,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>3.6</v>
@@ -5528,7 +5528,7 @@
         <v>10.2</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>64</v>
+        <v>63.1</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>3.06</v>
@@ -5597,7 +5597,7 @@
         <v>12.64</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>20</v>
@@ -5666,7 +5666,7 @@
         <v>39.9</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
         <v>11.44</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>83.5</v>
+        <v>82.7</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>6.5</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="n">
-        <v>47.05</v>
+        <v>47.1</v>
       </c>
       <c r="R77" s="3" t="n">
         <v>0.84</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="n">
-        <v>31.1</v>
+        <v>30.55</v>
       </c>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3">
@@ -6005,7 +6005,7 @@
         <v>31.23</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>5.5</v>
@@ -6074,7 +6074,7 @@
         <v>18.2</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>142.5</v>
+        <v>140.5</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>59.99</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>1675</v>
+        <v>1620</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>11.6</v>
@@ -6212,7 +6212,7 @@
         <v>28.36</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>31.15</v>
+        <v>30.45</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0.6</v>
@@ -6281,7 +6281,7 @@
         <v>34.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>225.5</v>
+        <v>221.5</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>2.8</v>
@@ -6350,7 +6350,7 @@
         <v>11.08</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>17.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>7.17</v>
@@ -6488,7 +6488,7 @@
         <v>21.71</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>38.65</v>
+        <v>37.8</v>
       </c>
       <c r="R87" s="3" t="n">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>41.89</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>6</v>
@@ -6626,7 +6626,7 @@
         <v>104.42</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="R89" s="3" t="n">
         <v>0.9</v>
@@ -6695,7 +6695,7 @@
         <v>19.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>42.2</v>
+        <v>41.6</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>32.47</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2450</v>
+        <v>2410</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>12</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="n">
-        <v>18.85</v>
+        <v>19</v>
       </c>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3">
@@ -6898,7 +6898,7 @@
         <v>32.46</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>122.5</v>
+        <v>119</v>
       </c>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P94" s="3" t="n"/>
       <c r="Q94" s="3" t="n">
-        <v>45.65</v>
+        <v>47.75</v>
       </c>
       <c r="R94" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>20.23</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>179.5</v>
+        <v>171.5</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>0.5</v>
@@ -7101,7 +7101,7 @@
         <v>36.14</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>1965</v>
+        <v>1885</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>15</v>
@@ -7170,7 +7170,7 @@
         <v>12.44</v>
       </c>
       <c r="Q97" s="3" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="R97" s="3" t="n">
         <v>4.2</v>
@@ -7239,7 +7239,7 @@
         <v>46.8</v>
       </c>
       <c r="Q98" s="3" t="n">
-        <v>235.5</v>
+        <v>234</v>
       </c>
       <c r="R98" s="3" t="n">
         <v>1.03</v>
@@ -7308,7 +7308,7 @@
         <v>38.31</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="P100" s="3" t="n"/>
       <c r="Q100" s="3" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>1.3</v>
@@ -7444,7 +7444,7 @@
         <v>25.51</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>65</v>
+        <v>65.7</v>
       </c>
       <c r="R101" s="3" t="n">
         <v>1.5</v>
@@ -7513,7 +7513,7 @@
         <v>21.95</v>
       </c>
       <c r="Q102" s="3" t="n">
-        <v>41.85</v>
+        <v>41.5</v>
       </c>
       <c r="R102" s="3" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>20.81</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>62.6</v>
+        <v>62</v>
       </c>
       <c r="R103" s="3" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>13.35</v>
       </c>
       <c r="Q104" s="3" t="n">
-        <v>989</v>
+        <v>924</v>
       </c>
       <c r="R104" s="3" t="n">
         <v>42</v>
@@ -7716,7 +7716,7 @@
         <v>23.99</v>
       </c>
       <c r="Q105" s="3" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3">
@@ -7779,7 +7779,7 @@
         <v>54.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>2180</v>
+        <v>2160</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>19.5</v>
@@ -7848,7 +7848,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>47.6</v>
+        <v>47.15</v>
       </c>
       <c r="R107" s="3" t="n">
         <v>2</v>
@@ -7917,7 +7917,7 @@
         <v>93.89</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0.61</v>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P109" s="3" t="n"/>
       <c r="Q109" s="3" t="n">
-        <v>41.15</v>
+        <v>40.7</v>
       </c>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3">
@@ -8051,7 +8051,7 @@
         <v>36.79</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>9.800000000000001</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P111" s="3" t="n"/>
       <c r="Q111" s="3" t="n">
-        <v>27.85</v>
+        <v>27.45</v>
       </c>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3">
@@ -8254,7 +8254,7 @@
         <v>29.45</v>
       </c>
       <c r="Q113" s="3" t="n">
-        <v>122</v>
+        <v>118.5</v>
       </c>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3">
@@ -8317,7 +8317,7 @@
         <v>12.87</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>351.5</v>
+        <v>349</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>12</v>
@@ -8453,7 +8453,7 @@
         <v>25.49</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3">
@@ -8520,7 +8520,7 @@
         <v>14.25</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>336</v>
+        <v>336.5</v>
       </c>
       <c r="R117" s="3" t="n">
         <v>15.6</v>
@@ -8589,7 +8589,7 @@
         <v>93.59</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5375</v>
+        <v>5365</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>25</v>
@@ -8658,7 +8658,7 @@
         <v>12.01</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="R119" s="3" t="n">
         <v>7.2</v>
@@ -8727,7 +8727,7 @@
         <v>46.19</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>77.7</v>
+        <v>75.2</v>
       </c>
       <c r="R120" s="3" t="n">
         <v>0.05</v>
@@ -8796,7 +8796,7 @@
         <v>5.36</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>43.4</v>
+        <v>42.3</v>
       </c>
       <c r="R121" s="3" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>13.8</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>61.8</v>
+        <v>62.1</v>
       </c>
       <c r="R122" s="3" t="n">
         <v>4.14</v>
@@ -8934,7 +8934,7 @@
         <v>43.26</v>
       </c>
       <c r="Q123" s="3" t="n">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="R123" s="3" t="n">
         <v>9.17</v>
@@ -9003,7 +9003,7 @@
         <v>255</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>24.9</v>
+        <v>24.1</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>32.81</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>2</v>
@@ -9141,7 +9141,7 @@
         <v>16.97</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>1060</v>
+        <v>1005</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>40</v>
@@ -9210,7 +9210,7 @@
         <v>19.87</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="R127" s="3" t="n">
         <v>1.35</v>
@@ -9279,7 +9279,7 @@
         <v>106.67</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>31.2</v>
+        <v>30.2</v>
       </c>
       <c r="R128" s="3" t="n">
         <v>0.4</v>
@@ -9348,7 +9348,7 @@
         <v>26.52</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>139.5</v>
+        <v>140.5</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>5.2</v>
@@ -9417,7 +9417,7 @@
         <v>15.32</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="R130" s="3" t="n">
         <v>5.24</v>
@@ -9486,7 +9486,7 @@
         <v>822</v>
       </c>
       <c r="Q131" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R131" s="3" t="n">
         <v>0.1</v>
@@ -9555,7 +9555,7 @@
         <v>18.02</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>250.5</v>
+        <v>255</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>5.9</v>
@@ -9624,7 +9624,7 @@
         <v>15.05</v>
       </c>
       <c r="Q133" s="3" t="n">
-        <v>77.2</v>
+        <v>76.5</v>
       </c>
       <c r="R133" s="3" t="n">
         <v>4.084</v>
@@ -9693,7 +9693,7 @@
         <v>20.83</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>115</v>
+        <v>111.5</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>3.01</v>
@@ -9762,7 +9762,7 @@
         <v>32.37</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>271.5</v>
+        <v>263</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>5.09</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>282.5</v>
+        <v>276.5</v>
       </c>
       <c r="R136" s="3" t="n">
         <v>11.78</v>
@@ -9900,7 +9900,7 @@
         <v>69.53</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>4720</v>
+        <v>4585</v>
       </c>
       <c r="R137" s="3" t="n">
         <v>53.5</v>
@@ -9969,7 +9969,7 @@
         <v>99.51000000000001</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="R138" s="3" t="n">
         <v>2.62</v>
@@ -10038,7 +10038,7 @@
         <v>13.06</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>128</v>
+        <v>126.5</v>
       </c>
       <c r="R139" s="3" t="n">
         <v>8.851000000000001</v>
@@ -10101,7 +10101,7 @@
         <v>505.26</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>193.5</v>
+        <v>188.5</v>
       </c>
       <c r="R140" s="3" t="n">
         <v>0.5</v>
@@ -10170,7 +10170,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>101.5</v>
+        <v>106</v>
       </c>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3">
@@ -10237,7 +10237,7 @@
         <v>53.39</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="R142" s="3" t="n">
         <v>5.5</v>
@@ -10306,7 +10306,7 @@
         <v>22.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>217</v>
+        <v>213.5</v>
       </c>
       <c r="R143" s="3" t="n">
         <v>3.5</v>
@@ -10444,7 +10444,7 @@
         <v>18.78</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R145" s="3" t="n">
         <v>2.97</v>
@@ -10507,7 +10507,7 @@
         <v>24.79</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>124</v>
+        <v>118.5</v>
       </c>
       <c r="R146" s="3" t="n">
         <v>2</v>
@@ -10576,7 +10576,7 @@
         <v>18.09</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="R147" s="3" t="n">
         <v>7.8</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>154.5</v>
+        <v>150</v>
       </c>
       <c r="R148" s="3" t="n">
         <v>1.8</v>
@@ -10702,7 +10702,7 @@
         <v>214.66</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>242</v>
+        <v>237.5</v>
       </c>
       <c r="R149" s="3" t="n">
         <v>0.25</v>
@@ -10771,7 +10771,7 @@
         <v>25.65</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>38.6</v>
+        <v>36.9</v>
       </c>
       <c r="R150" s="3" t="n">
         <v>1.2</v>
@@ -10840,7 +10840,7 @@
         <v>33.99</v>
       </c>
       <c r="Q151" s="3" t="n">
-        <v>334</v>
+        <v>311.5</v>
       </c>
       <c r="R151" s="3" t="n">
         <v>2.5</v>
@@ -10903,7 +10903,7 @@
         <v>33.27</v>
       </c>
       <c r="Q152" s="3" t="n">
-        <v>174.5</v>
+        <v>173.5</v>
       </c>
       <c r="R152" s="3" t="n">
         <v>4</v>
@@ -10966,7 +10966,7 @@
         <v>15.64</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>40.15</v>
+        <v>39.95</v>
       </c>
       <c r="R153" s="3" t="n">
         <v>0.5</v>
@@ -11035,7 +11035,7 @@
         <v>8.07</v>
       </c>
       <c r="Q154" s="3" t="n">
-        <v>22.25</v>
+        <v>22.15</v>
       </c>
       <c r="R154" s="3" t="n">
         <v>1.2</v>
@@ -11104,7 +11104,7 @@
         <v>9.81</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>31.45</v>
+        <v>31.3</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>2.6</v>
@@ -11228,7 +11228,7 @@
         <v>10.85</v>
       </c>
       <c r="Q157" s="3" t="n">
-        <v>36.75</v>
+        <v>36.45</v>
       </c>
       <c r="R157" s="3" t="n">
         <v>1.62</v>
@@ -11287,7 +11287,7 @@
         <v>29.47</v>
       </c>
       <c r="Q158" s="3" t="n">
-        <v>19.55</v>
+        <v>20.1</v>
       </c>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3">
@@ -11348,7 +11348,7 @@
         <v>8.91</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>4.6</v>
@@ -11417,7 +11417,7 @@
         <v>9.81</v>
       </c>
       <c r="Q160" s="3" t="n">
-        <v>35.35</v>
+        <v>35.15</v>
       </c>
       <c r="R160" s="3" t="n">
         <v>0.6</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P161" s="3" t="n"/>
       <c r="Q161" s="3" t="n">
-        <v>49.45</v>
+        <v>49.1</v>
       </c>
       <c r="R161" s="3" t="n">
         <v>0.62</v>
@@ -11616,7 +11616,7 @@
         <v>13.37</v>
       </c>
       <c r="Q163" s="3" t="n">
-        <v>39.1</v>
+        <v>37.9</v>
       </c>
       <c r="R163" s="3" t="n">
         <v>1.03</v>
@@ -11679,7 +11679,7 @@
         <v>36.53</v>
       </c>
       <c r="Q164" s="3" t="n">
-        <v>34.4</v>
+        <v>33.75</v>
       </c>
       <c r="R164" s="3" t="n">
         <v>2.8</v>
@@ -11738,7 +11738,7 @@
         <v>7.81</v>
       </c>
       <c r="Q165" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R165" s="3" t="n">
         <v>8</v>
@@ -11801,7 +11801,7 @@
         <v>14.45</v>
       </c>
       <c r="Q166" s="3" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R166" s="3" t="n">
         <v>9.67</v>
@@ -11870,7 +11870,7 @@
         <v>8.68</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>231</v>
+        <v>234.5</v>
       </c>
       <c r="R167" s="3" t="n">
         <v>16</v>
@@ -11933,7 +11933,7 @@
         <v>7.47</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>36.25</v>
+        <v>36.5</v>
       </c>
       <c r="R168" s="3" t="n">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>10.71</v>
       </c>
       <c r="Q169" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="R169" s="3" t="n">
         <v>2.8</v>
@@ -12071,7 +12071,7 @@
         <v>10.46</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="R170" s="3" t="n">
         <v>2.7</v>
@@ -12140,7 +12140,7 @@
         <v>11.62</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>58</v>
+        <v>59.4</v>
       </c>
       <c r="R171" s="3" t="n">
         <v>2</v>
@@ -12209,7 +12209,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="R172" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -12278,7 +12278,7 @@
         <v>6.22</v>
       </c>
       <c r="Q173" s="3" t="n">
-        <v>110.5</v>
+        <v>112</v>
       </c>
       <c r="R173" s="3" t="n">
         <v>3</v>
@@ -12347,7 +12347,7 @@
         <v>8.4</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>41.8</v>
+        <v>42.35</v>
       </c>
       <c r="R174" s="3" t="n">
         <v>2</v>
@@ -12416,7 +12416,7 @@
         <v>21.23</v>
       </c>
       <c r="Q175" s="3" t="n">
-        <v>26</v>
+        <v>26.05</v>
       </c>
       <c r="R175" s="3" t="n">
         <v>1.15</v>
@@ -12554,7 +12554,7 @@
         <v>11.35</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>100.5</v>
+        <v>101</v>
       </c>
       <c r="R177" s="3" t="n">
         <v>3.5</v>
@@ -12623,7 +12623,7 @@
         <v>25.51</v>
       </c>
       <c r="Q178" s="3" t="n">
-        <v>172.5</v>
+        <v>173</v>
       </c>
       <c r="R178" s="3" t="n">
         <v>5</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P179" s="3" t="n"/>
       <c r="Q179" s="3" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3">
@@ -12757,7 +12757,7 @@
         <v>17.48</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>46</v>
+        <v>45.75</v>
       </c>
       <c r="R180" s="3" t="n">
         <v>0.5</v>
@@ -12895,7 +12895,7 @@
         <v>13.19</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>229.5</v>
+        <v>229</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>16.12</v>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P183" s="3" t="n"/>
       <c r="Q183" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>1.25</v>
@@ -13031,7 +13031,7 @@
         <v>6.51</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>18.35</v>
+        <v>18.5</v>
       </c>
       <c r="R184" s="3" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>19.32</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>218.5</v>
+        <v>216.5</v>
       </c>
       <c r="R185" s="3" t="n">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.28</v>
       </c>
       <c r="Q186" s="3" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="R186" s="3" t="n">
         <v>1.9</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="P187" s="3" t="n"/>
       <c r="Q187" s="3" t="n">
-        <v>27.3</v>
+        <v>25.4</v>
       </c>
       <c r="R187" s="3" t="n">
         <v>0.12</v>
@@ -13305,7 +13305,7 @@
         <v>13.84</v>
       </c>
       <c r="Q188" s="3" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="R188" s="3" t="n">
         <v>6.79</v>
@@ -13374,7 +13374,7 @@
         <v>8.09</v>
       </c>
       <c r="Q189" s="3" t="n">
-        <v>312</v>
+        <v>290.5</v>
       </c>
       <c r="R189" s="3" t="n">
         <v>1</v>
@@ -13443,7 +13443,7 @@
         <v>24.52</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>6720</v>
+        <v>6660</v>
       </c>
       <c r="R190" s="3" t="n">
         <v>93.5</v>
@@ -13579,7 +13579,7 @@
         <v>15.88</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="R192" s="3" t="n">
         <v>0.4</v>
@@ -13648,7 +13648,7 @@
         <v>13.13</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>131.5</v>
+        <v>130.5</v>
       </c>
       <c r="R193" s="3" t="n">
         <v>7.5</v>
@@ -13717,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>110</v>
+        <v>109.5</v>
       </c>
       <c r="R194" s="3" t="n">
         <v>0.5</v>
@@ -13786,7 +13786,7 @@
         <v>43.12</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>3460</v>
+        <v>3370</v>
       </c>
       <c r="R195" s="3" t="n">
         <v>17.9</v>
@@ -13855,7 +13855,7 @@
         <v>22.85</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>139</v>
+        <v>137.5</v>
       </c>
       <c r="R196" s="3" t="n">
         <v>4.6</v>
@@ -13924,7 +13924,7 @@
         <v>11.98</v>
       </c>
       <c r="Q197" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="R197" s="3" t="n">
         <v>3.5</v>
@@ -13993,7 +13993,7 @@
         <v>23.34</v>
       </c>
       <c r="Q198" s="3" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="R198" s="3" t="n">
         <v>9.1</v>
@@ -14062,7 +14062,7 @@
         <v>63.12</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>803</v>
+        <v>744</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>5.8</v>
@@ -14131,7 +14131,7 @@
         <v>9.35</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>62.3</v>
+        <v>61.7</v>
       </c>
       <c r="R200" s="3" t="n">
         <v>3</v>
@@ -14200,7 +14200,7 @@
         <v>15.83</v>
       </c>
       <c r="Q201" s="3" t="n">
-        <v>113</v>
+        <v>116.5</v>
       </c>
       <c r="R201" s="3" t="n">
         <v>5.5</v>
@@ -14269,7 +14269,7 @@
         <v>22.35</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>266.5</v>
+        <v>263</v>
       </c>
       <c r="R202" s="3" t="n">
         <v>7</v>
@@ -14338,7 +14338,7 @@
         <v>9.99</v>
       </c>
       <c r="Q203" s="3" t="n">
-        <v>42.05</v>
+        <v>41.55</v>
       </c>
       <c r="R203" s="3" t="n">
         <v>1.92</v>
@@ -14407,7 +14407,7 @@
         <v>17.86</v>
       </c>
       <c r="Q204" s="3" t="n">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="R204" s="3" t="n">
         <v>23</v>
@@ -14476,7 +14476,7 @@
         <v>68.31</v>
       </c>
       <c r="Q205" s="3" t="n">
-        <v>179</v>
+        <v>169.5</v>
       </c>
       <c r="R205" s="3" t="n">
         <v>1.8</v>
@@ -14545,7 +14545,7 @@
         <v>10.57</v>
       </c>
       <c r="Q206" s="3" t="n">
-        <v>192.5</v>
+        <v>191</v>
       </c>
       <c r="R206" s="3" t="n">
         <v>7.8</v>
@@ -14614,7 +14614,7 @@
         <v>67.91</v>
       </c>
       <c r="Q207" s="3" t="n">
-        <v>994</v>
+        <v>977</v>
       </c>
       <c r="R207" s="3" t="n">
         <v>1.98</v>
@@ -14673,7 +14673,7 @@
         <v>32.82</v>
       </c>
       <c r="Q208" s="3" t="n">
-        <v>180.5</v>
+        <v>176</v>
       </c>
       <c r="R208" s="3" t="n">
         <v>4.8</v>
@@ -14742,7 +14742,7 @@
         <v>20.91</v>
       </c>
       <c r="Q209" s="3" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="R209" s="3" t="n">
         <v>12.7</v>
@@ -14811,7 +14811,7 @@
         <v>21.74</v>
       </c>
       <c r="Q210" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R210" s="3" t="n">
         <v>3.94</v>
@@ -14880,7 +14880,7 @@
         <v>218.59</v>
       </c>
       <c r="Q211" s="3" t="n">
-        <v>2830</v>
+        <v>2810</v>
       </c>
       <c r="R211" s="3" t="n">
         <v>3</v>
@@ -14949,7 +14949,7 @@
         <v>15.63</v>
       </c>
       <c r="Q212" s="3" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R212" s="3" t="n">
         <v>2.9304</v>
@@ -15018,7 +15018,7 @@
         <v>19.92</v>
       </c>
       <c r="Q213" s="3" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="R213" s="3" t="n">
         <v>4.8</v>
@@ -15087,7 +15087,7 @@
         <v>44.42</v>
       </c>
       <c r="Q214" s="3" t="n">
-        <v>461.5</v>
+        <v>437.5</v>
       </c>
       <c r="R214" s="3" t="n">
         <v>2</v>
@@ -15156,7 +15156,7 @@
         <v>41.08</v>
       </c>
       <c r="Q215" s="3" t="n">
-        <v>2460</v>
+        <v>2325</v>
       </c>
       <c r="R215" s="3" t="n">
         <v>46.08</v>
@@ -15225,7 +15225,7 @@
         <v>6.7</v>
       </c>
       <c r="Q216" s="3" t="n">
-        <v>167</v>
+        <v>162.5</v>
       </c>
       <c r="R216" s="3" t="n">
         <v>3.2586</v>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="P217" s="3" t="n"/>
       <c r="Q217" s="3" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="R217" s="3" t="n"/>
       <c r="S217" s="3">
@@ -15359,7 +15359,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q218" s="3" t="n">
-        <v>707</v>
+        <v>670</v>
       </c>
       <c r="R218" s="3" t="n">
         <v>1.75</v>
@@ -15428,7 +15428,7 @@
         <v>47.34</v>
       </c>
       <c r="Q219" s="3" t="n">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="R219" s="3" t="n">
         <v>3.91</v>
@@ -15497,7 +15497,7 @@
         <v>159.93</v>
       </c>
       <c r="Q220" s="3" t="n">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="R220" s="3" t="n">
         <v>1.52</v>
@@ -15566,7 +15566,7 @@
         <v>52.7</v>
       </c>
       <c r="Q221" s="3" t="n">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="R221" s="3" t="n">
         <v>11.47</v>
@@ -15635,7 +15635,7 @@
         <v>10.97</v>
       </c>
       <c r="Q222" s="3" t="n">
-        <v>127.5</v>
+        <v>127</v>
       </c>
       <c r="R222" s="3" t="n">
         <v>10</v>
@@ -15704,7 +15704,7 @@
         <v>15.77</v>
       </c>
       <c r="Q223" s="3" t="n">
-        <v>183.5</v>
+        <v>181.5</v>
       </c>
       <c r="R223" s="3" t="n">
         <v>10.007</v>
@@ -15773,7 +15773,7 @@
         <v>15.37</v>
       </c>
       <c r="Q224" s="3" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="R224" s="3" t="n">
         <v>5.5</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="P225" s="3" t="n"/>
       <c r="Q225" s="3" t="n">
-        <v>195</v>
+        <v>187.5</v>
       </c>
       <c r="R225" s="3" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>5.2</v>
       </c>
       <c r="Q226" s="3" t="n">
-        <v>407</v>
+        <v>402.5</v>
       </c>
       <c r="R226" s="3" t="n">
         <v>17</v>
@@ -15978,7 +15978,7 @@
         <v>29.44</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>240</v>
+        <v>230.5</v>
       </c>
       <c r="R227" s="3" t="n">
         <v>4.2</v>
@@ -16047,7 +16047,7 @@
         <v>24.26</v>
       </c>
       <c r="Q228" s="3" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="R228" s="3" t="n">
         <v>4.1</v>
@@ -16116,7 +16116,7 @@
         <v>30.04</v>
       </c>
       <c r="Q229" s="3" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="R229" s="3" t="n">
         <v>3.43</v>
@@ -16185,7 +16185,7 @@
         <v>17.33</v>
       </c>
       <c r="Q230" s="3" t="n">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="R230" s="3" t="n">
         <v>36</v>
@@ -16254,7 +16254,7 @@
         <v>19.18</v>
       </c>
       <c r="Q231" s="3" t="n">
-        <v>101.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R231" s="3" t="n">
         <v>2.2833</v>
@@ -16323,7 +16323,7 @@
         <v>23.29</v>
       </c>
       <c r="Q232" s="3" t="n">
-        <v>1440</v>
+        <v>1360</v>
       </c>
       <c r="R232" s="3" t="n">
         <v>11.9</v>
@@ -16392,7 +16392,7 @@
         <v>21.44</v>
       </c>
       <c r="Q233" s="3" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="R233" s="3" t="n">
         <v>5.08</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="P234" s="3" t="n"/>
       <c r="Q234" s="3" t="n">
-        <v>182.5</v>
+        <v>179.5</v>
       </c>
       <c r="R234" s="3" t="n">
         <v>0</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P235" s="3" t="n"/>
       <c r="Q235" s="3" t="n">
-        <v>714</v>
+        <v>681</v>
       </c>
       <c r="R235" s="3" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>51.02</v>
       </c>
       <c r="Q236" s="3" t="n">
-        <v>488</v>
+        <v>463.5</v>
       </c>
       <c r="R236" s="3" t="n">
         <v>2.5</v>
@@ -16664,7 +16664,7 @@
         <v>126.21</v>
       </c>
       <c r="Q237" s="3" t="n">
-        <v>189.5</v>
+        <v>183</v>
       </c>
       <c r="R237" s="3" t="n">
         <v>2</v>
@@ -16733,7 +16733,7 @@
         <v>188.94</v>
       </c>
       <c r="Q238" s="3" t="n">
-        <v>30.65</v>
+        <v>30.75</v>
       </c>
       <c r="R238" s="3" t="n"/>
       <c r="S238" s="3">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="P239" s="3" t="n"/>
       <c r="Q239" s="3" t="n">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="R239" s="3" t="n">
         <v>17</v>
@@ -16867,7 +16867,7 @@
         <v>14.17</v>
       </c>
       <c r="Q240" s="3" t="n">
-        <v>283.5</v>
+        <v>279.5</v>
       </c>
       <c r="R240" s="3" t="n">
         <v>10.98</v>
@@ -16936,7 +16936,7 @@
         <v>20.39</v>
       </c>
       <c r="Q241" s="3" t="n">
-        <v>161</v>
+        <v>160.5</v>
       </c>
       <c r="R241" s="3" t="n">
         <v>5.0959</v>
@@ -17005,7 +17005,7 @@
         <v>137.52</v>
       </c>
       <c r="Q242" s="3" t="n">
-        <v>6225</v>
+        <v>6120</v>
       </c>
       <c r="R242" s="3" t="n">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>111.76</v>
       </c>
       <c r="Q243" s="3" t="n">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="R243" s="3" t="n">
         <v>1</v>
@@ -17143,7 +17143,7 @@
         <v>64.23</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>49.35</v>
+        <v>47.7</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>0.5</v>
@@ -17212,7 +17212,7 @@
         <v>109.3</v>
       </c>
       <c r="Q245" s="3" t="n">
-        <v>1355</v>
+        <v>1415</v>
       </c>
       <c r="R245" s="3" t="n">
         <v>6</v>
@@ -17281,7 +17281,7 @@
         <v>14.28</v>
       </c>
       <c r="Q246" s="3" t="n">
-        <v>221.5</v>
+        <v>207</v>
       </c>
       <c r="R246" s="3" t="n">
         <v>11</v>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P247" s="3" t="n"/>
       <c r="Q247" s="3" t="n">
-        <v>273</v>
+        <v>268.5</v>
       </c>
       <c r="R247" s="3" t="n">
         <v>13.53</v>
@@ -17417,7 +17417,7 @@
         <v>74.14</v>
       </c>
       <c r="Q248" s="3" t="n">
-        <v>2730</v>
+        <v>2580</v>
       </c>
       <c r="R248" s="3" t="n">
         <v>20.5</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P249" s="3" t="n"/>
       <c r="Q249" s="3" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="R249" s="3" t="n">
         <v>1</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P250" s="3" t="n"/>
       <c r="Q250" s="3" t="n">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="R250" s="3" t="n">
         <v>34.93</v>
@@ -17620,7 +17620,7 @@
         <v>39.02</v>
       </c>
       <c r="Q251" s="3" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="R251" s="3" t="n">
         <v>12</v>
@@ -17689,7 +17689,7 @@
         <v>32.04</v>
       </c>
       <c r="Q252" s="3" t="n">
-        <v>16.65</v>
+        <v>16.4</v>
       </c>
       <c r="R252" s="3" t="n"/>
       <c r="S252" s="3">
@@ -17756,7 +17756,7 @@
         <v>40.66</v>
       </c>
       <c r="Q253" s="3" t="n">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="R253" s="3" t="n">
         <v>11.7476</v>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="P254" s="3" t="n"/>
       <c r="Q254" s="3" t="n">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="R254" s="3" t="n">
         <v>4.21</v>
@@ -17892,7 +17892,7 @@
         <v>13.12</v>
       </c>
       <c r="Q255" s="3" t="n">
-        <v>221.5</v>
+        <v>219.5</v>
       </c>
       <c r="R255" s="3" t="n">
         <v>14.6</v>
@@ -17961,7 +17961,7 @@
         <v>12.38</v>
       </c>
       <c r="Q256" s="3" t="n">
-        <v>154.5</v>
+        <v>152.5</v>
       </c>
       <c r="R256" s="3" t="n">
         <v>8</v>
@@ -18030,7 +18030,7 @@
         <v>12.24</v>
       </c>
       <c r="Q257" s="3" t="n">
-        <v>239</v>
+        <v>242.5</v>
       </c>
       <c r="R257" s="3" t="n">
         <v>9.937099999999999</v>
@@ -18099,7 +18099,7 @@
         <v>126.38</v>
       </c>
       <c r="Q258" s="3" t="n">
-        <v>5790</v>
+        <v>5765</v>
       </c>
       <c r="R258" s="3" t="n">
         <v>21.72</v>
@@ -18158,7 +18158,7 @@
         <v>61.7</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>4055</v>
+        <v>3650</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>32.55</v>
@@ -18227,7 +18227,7 @@
         <v>44.4</v>
       </c>
       <c r="Q260" s="3" t="n">
-        <v>1930</v>
+        <v>1875</v>
       </c>
       <c r="R260" s="3" t="n">
         <v>15.18</v>
@@ -18296,7 +18296,7 @@
         <v>16.35</v>
       </c>
       <c r="Q261" s="3" t="n">
-        <v>62.6</v>
+        <v>61.7</v>
       </c>
       <c r="R261" s="3" t="n">
         <v>1.8</v>
@@ -18365,7 +18365,7 @@
         <v>46.77</v>
       </c>
       <c r="Q262" s="3" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="R262" s="3" t="n">
         <v>4</v>
@@ -18434,7 +18434,7 @@
         <v>31.17</v>
       </c>
       <c r="Q263" s="3" t="n">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="R263" s="3" t="n">
         <v>5</v>
@@ -18503,7 +18503,7 @@
         <v>34.76</v>
       </c>
       <c r="Q264" s="3" t="n">
-        <v>691</v>
+        <v>663</v>
       </c>
       <c r="R264" s="3" t="n">
         <v>8</v>
@@ -18572,7 +18572,7 @@
         <v>9.85</v>
       </c>
       <c r="Q265" s="3" t="n">
-        <v>108</v>
+        <v>106.5</v>
       </c>
       <c r="R265" s="3" t="n">
         <v>3.64</v>
@@ -18641,7 +18641,7 @@
         <v>10.08</v>
       </c>
       <c r="Q266" s="3" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="R266" s="3" t="n">
         <v>1.05</v>
@@ -18710,7 +18710,7 @@
         <v>13.74</v>
       </c>
       <c r="Q267" s="3" t="n">
-        <v>39.4</v>
+        <v>40.5</v>
       </c>
       <c r="R267" s="3" t="n">
         <v>0.4</v>
@@ -18779,7 +18779,7 @@
         <v>15.93</v>
       </c>
       <c r="Q268" s="3" t="n">
-        <v>56</v>
+        <v>55.8</v>
       </c>
       <c r="R268" s="3" t="n">
         <v>3</v>
@@ -18848,7 +18848,7 @@
         <v>16.55</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>82</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="R269" s="3" t="n"/>
       <c r="S269" s="3">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P270" s="3" t="n"/>
       <c r="Q270" s="3" t="n">
-        <v>61.8</v>
+        <v>59.2</v>
       </c>
       <c r="R270" s="3" t="n"/>
       <c r="S270" s="3">
@@ -18980,7 +18980,7 @@
         <v>44.57</v>
       </c>
       <c r="Q271" s="3" t="n">
-        <v>650</v>
+        <v>618</v>
       </c>
       <c r="R271" s="3" t="n">
         <v>6.58</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P272" s="3" t="n"/>
       <c r="Q272" s="3" t="n">
-        <v>62</v>
+        <v>61.7</v>
       </c>
       <c r="R272" s="3" t="n">
         <v>0.9</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P273" s="3" t="n"/>
       <c r="Q273" s="3" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R273" s="3" t="n">
         <v>1.08</v>
@@ -19183,7 +19183,7 @@
         <v>10.92</v>
       </c>
       <c r="Q274" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="R274" s="3" t="n">
         <v>4.5</v>
@@ -19248,7 +19248,7 @@
         <v>18.4</v>
       </c>
       <c r="Q275" s="3" t="n">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="R275" s="3" t="n">
         <v>0.85</v>
@@ -19317,7 +19317,7 @@
         <v>25.79</v>
       </c>
       <c r="Q276" s="3" t="n">
-        <v>30.35</v>
+        <v>30.25</v>
       </c>
       <c r="R276" s="3" t="n">
         <v>1.747</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P277" s="3" t="n"/>
       <c r="Q277" s="3" t="n">
-        <v>61.6</v>
+        <v>59.8</v>
       </c>
       <c r="R277" s="3" t="n"/>
       <c r="S277" s="3">
@@ -19451,7 +19451,7 @@
         <v>15.89</v>
       </c>
       <c r="Q278" s="3" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R278" s="3" t="n">
         <v>5.3</v>
@@ -19520,7 +19520,7 @@
         <v>12.98</v>
       </c>
       <c r="Q279" s="3" t="n">
-        <v>164.5</v>
+        <v>162</v>
       </c>
       <c r="R279" s="3" t="n">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>18.1</v>
       </c>
       <c r="Q280" s="3" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R280" s="3" t="n">
         <v>4.2</v>
@@ -19658,7 +19658,7 @@
         <v>60.42</v>
       </c>
       <c r="Q281" s="3" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="R281" s="3" t="n">
         <v>0.8</v>
@@ -19723,7 +19723,7 @@
         <v>35.71</v>
       </c>
       <c r="Q282" s="3" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="R282" s="3" t="n">
         <v>8</v>
@@ -19792,7 +19792,7 @@
         <v>105.22</v>
       </c>
       <c r="Q283" s="3" t="n">
-        <v>290.5</v>
+        <v>298</v>
       </c>
       <c r="R283" s="3" t="n">
         <v>1</v>
@@ -19861,7 +19861,7 @@
         <v>25.23</v>
       </c>
       <c r="Q284" s="3" t="n">
-        <v>26.75</v>
+        <v>26.15</v>
       </c>
       <c r="R284" s="3" t="n">
         <v>0.5</v>
@@ -19930,7 +19930,7 @@
         <v>110.95</v>
       </c>
       <c r="Q285" s="3" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R285" s="3" t="n">
         <v>1.18</v>
@@ -19999,7 +19999,7 @@
         <v>25.87</v>
       </c>
       <c r="Q286" s="3" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="R286" s="3" t="n">
         <v>12.1</v>
@@ -20068,7 +20068,7 @@
         <v>357.69</v>
       </c>
       <c r="Q287" s="3" t="n">
-        <v>45.55</v>
+        <v>43.9</v>
       </c>
       <c r="R287" s="3" t="n"/>
       <c r="S287" s="3">
@@ -20135,7 +20135,7 @@
         <v>61.06</v>
       </c>
       <c r="Q288" s="3" t="n">
-        <v>757</v>
+        <v>721</v>
       </c>
       <c r="R288" s="3" t="n">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="Q289" s="3" t="n">
-        <v>48.35</v>
+        <v>48.85</v>
       </c>
       <c r="R289" s="3" t="n"/>
       <c r="S289" s="3">
@@ -20261,7 +20261,7 @@
         <v>66.61</v>
       </c>
       <c r="Q290" s="3" t="n">
-        <v>220.5</v>
+        <v>215</v>
       </c>
       <c r="R290" s="3" t="n">
         <v>1</v>
@@ -20330,7 +20330,7 @@
         <v>15.04</v>
       </c>
       <c r="Q291" s="3" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="R291" s="3" t="n">
         <v>18</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="P292" s="3" t="n"/>
       <c r="Q292" s="3" t="n">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>0.22</v>
@@ -20466,7 +20466,7 @@
         <v>20.23</v>
       </c>
       <c r="Q293" s="3" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="R293" s="3" t="n">
         <v>6</v>
@@ -20535,7 +20535,7 @@
         <v>45.85</v>
       </c>
       <c r="Q294" s="3" t="n">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="R294" s="3" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         <v>24.09</v>
       </c>
       <c r="Q295" s="3" t="n">
-        <v>104.5</v>
+        <v>105.5</v>
       </c>
       <c r="R295" s="3" t="n">
         <v>3.45</v>
@@ -20673,7 +20673,7 @@
         <v>283.33</v>
       </c>
       <c r="Q296" s="3" t="n">
-        <v>36.35</v>
+        <v>35.9</v>
       </c>
       <c r="R296" s="3" t="n">
         <v>0.47</v>
@@ -20742,7 +20742,7 @@
         <v>12.22</v>
       </c>
       <c r="Q297" s="3" t="n">
-        <v>62.1</v>
+        <v>62.8</v>
       </c>
       <c r="R297" s="3" t="n">
         <v>4.57</v>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n">
-        <v>116.5</v>
+        <v>112.5</v>
       </c>
       <c r="R298" s="3" t="n"/>
       <c r="S298" s="3">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="P299" s="3" t="n"/>
       <c r="Q299" s="3" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="R299" s="3" t="n">
         <v>2.5</v>
@@ -21008,7 +21008,7 @@
         <v>57.93</v>
       </c>
       <c r="Q301" s="3" t="n">
-        <v>494.5</v>
+        <v>495</v>
       </c>
       <c r="R301" s="3" t="n">
         <v>3.42</v>
@@ -21077,7 +21077,7 @@
         <v>18.65</v>
       </c>
       <c r="Q302" s="3" t="n">
-        <v>172.5</v>
+        <v>170</v>
       </c>
       <c r="R302" s="3" t="n">
         <v>7.72</v>
@@ -21146,7 +21146,7 @@
         <v>18.13</v>
       </c>
       <c r="Q303" s="3" t="n">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="R303" s="3" t="n">
         <v>17.79</v>
@@ -21215,7 +21215,7 @@
         <v>4.13</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>276.5</v>
+        <v>280.5</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3.45</v>
@@ -21274,7 +21274,7 @@
         <v>94.3</v>
       </c>
       <c r="Q305" s="3" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="R305" s="3" t="n">
         <v>0.85</v>
@@ -21343,7 +21343,7 @@
         <v>85.43000000000001</v>
       </c>
       <c r="Q306" s="3" t="n">
-        <v>571</v>
+        <v>531</v>
       </c>
       <c r="R306" s="3" t="n">
         <v>2.15</v>
@@ -21402,7 +21402,7 @@
         <v>190.08</v>
       </c>
       <c r="Q307" s="3" t="n">
-        <v>488</v>
+        <v>448.5</v>
       </c>
       <c r="R307" s="3" t="n"/>
       <c r="S307" s="3">
@@ -21469,7 +21469,7 @@
         <v>15.93</v>
       </c>
       <c r="Q308" s="3" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="R308" s="3" t="n">
         <v>2.73</v>
@@ -21538,7 +21538,7 @@
         <v>15.55</v>
       </c>
       <c r="Q309" s="3" t="n">
-        <v>32.55</v>
+        <v>32.35</v>
       </c>
       <c r="R309" s="3" t="n">
         <v>1.2</v>
@@ -21607,7 +21607,7 @@
         <v>13.01</v>
       </c>
       <c r="Q310" s="3" t="n">
-        <v>20.85</v>
+        <v>20.7</v>
       </c>
       <c r="R310" s="3" t="n">
         <v>2.8</v>
@@ -21676,7 +21676,7 @@
         <v>36.1</v>
       </c>
       <c r="Q311" s="3" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="R311" s="3" t="n">
         <v>6.5</v>
@@ -21735,7 +21735,7 @@
         <v>17.93</v>
       </c>
       <c r="Q312" s="3" t="n">
-        <v>90.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R312" s="3" t="n">
         <v>2.2</v>
@@ -21804,7 +21804,7 @@
         <v>14.72</v>
       </c>
       <c r="Q313" s="3" t="n">
-        <v>1360</v>
+        <v>1315</v>
       </c>
       <c r="R313" s="3" t="n">
         <v>45.38</v>
@@ -21873,7 +21873,7 @@
         <v>118</v>
       </c>
       <c r="Q314" s="3" t="n">
-        <v>18700</v>
+        <v>17885</v>
       </c>
       <c r="R314" s="3" t="n">
         <v>80</v>
@@ -21932,7 +21932,7 @@
         <v>23.77</v>
       </c>
       <c r="Q315" s="3" t="n">
-        <v>308</v>
+        <v>297.5</v>
       </c>
       <c r="R315" s="3" t="n">
         <v>5</v>
@@ -22001,7 +22001,7 @@
         <v>8.19</v>
       </c>
       <c r="Q316" s="3" t="n">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="R316" s="3" t="n">
         <v>16.83</v>
@@ -22070,7 +22070,7 @@
         <v>3.5</v>
       </c>
       <c r="Q317" s="3" t="n">
-        <v>46.8</v>
+        <v>42.15</v>
       </c>
       <c r="R317" s="3" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>42.25</v>
       </c>
       <c r="Q318" s="3" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R318" s="3" t="n">
         <v>0.6</v>
@@ -22208,7 +22208,7 @@
         <v>34.74</v>
       </c>
       <c r="Q319" s="3" t="n">
-        <v>161.5</v>
+        <v>157.5</v>
       </c>
       <c r="R319" s="3" t="n">
         <v>4.47</v>
@@ -22277,7 +22277,7 @@
         <v>20.59</v>
       </c>
       <c r="Q320" s="3" t="n">
-        <v>115.5</v>
+        <v>108.5</v>
       </c>
       <c r="R320" s="3" t="n"/>
       <c r="S320" s="3">
@@ -22413,7 +22413,7 @@
         <v>17.36</v>
       </c>
       <c r="Q322" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="R322" s="3" t="n">
         <v>2.5</v>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P323" s="3" t="n"/>
       <c r="Q323" s="3" t="n">
-        <v>89.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="R323" s="3" t="n">
         <v>2.02</v>
@@ -22618,7 +22618,7 @@
         <v>13.65</v>
       </c>
       <c r="Q325" s="3" t="n">
-        <v>258</v>
+        <v>249.5</v>
       </c>
       <c r="R325" s="3" t="n">
         <v>7.2</v>
@@ -22687,7 +22687,7 @@
         <v>46.7</v>
       </c>
       <c r="Q326" s="3" t="n">
-        <v>108</v>
+        <v>105.5</v>
       </c>
       <c r="R326" s="3" t="n">
         <v>2.2</v>
@@ -22756,7 +22756,7 @@
         <v>13.07</v>
       </c>
       <c r="Q327" s="3" t="n">
-        <v>71.7</v>
+        <v>72.3</v>
       </c>
       <c r="R327" s="3" t="n">
         <v>2.52</v>
@@ -22825,7 +22825,7 @@
         <v>132.17</v>
       </c>
       <c r="Q328" s="3" t="n">
-        <v>184.5</v>
+        <v>175</v>
       </c>
       <c r="R328" s="3" t="n"/>
       <c r="S328" s="3">
@@ -22892,7 +22892,7 @@
         <v>12.16</v>
       </c>
       <c r="Q329" s="3" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R329" s="3" t="n">
         <v>7.5</v>
@@ -22961,7 +22961,7 @@
         <v>20.96</v>
       </c>
       <c r="Q330" s="3" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R330" s="3" t="n">
         <v>2.5</v>
@@ -23030,7 +23030,7 @@
         <v>6.19</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
       <c r="R331" s="3" t="n">
         <v>5.5</v>
@@ -23099,7 +23099,7 @@
         <v>15.16</v>
       </c>
       <c r="Q332" s="3" t="n">
-        <v>49.4</v>
+        <v>49.45</v>
       </c>
       <c r="R332" s="3" t="n"/>
       <c r="S332" s="3">
@@ -23166,7 +23166,7 @@
         <v>13.42</v>
       </c>
       <c r="Q333" s="3" t="n">
-        <v>74.5</v>
+        <v>74</v>
       </c>
       <c r="R333" s="3" t="n">
         <v>5.06</v>
@@ -23235,7 +23235,7 @@
         <v>21.94</v>
       </c>
       <c r="Q334" s="3" t="n">
-        <v>864</v>
+        <v>836</v>
       </c>
       <c r="R334" s="3" t="n">
         <v>20</v>
@@ -23304,7 +23304,7 @@
         <v>15.21</v>
       </c>
       <c r="Q335" s="3" t="n">
-        <v>52.3</v>
+        <v>53</v>
       </c>
       <c r="R335" s="3" t="n">
         <v>1.8</v>
@@ -23367,7 +23367,7 @@
         <v>10.44</v>
       </c>
       <c r="Q336" s="3" t="n">
-        <v>112.5</v>
+        <v>111.5</v>
       </c>
       <c r="R336" s="3" t="n">
         <v>5.8</v>
@@ -23436,7 +23436,7 @@
         <v>23.69</v>
       </c>
       <c r="Q337" s="3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R337" s="3" t="n">
         <v>6.5</v>
@@ -23505,7 +23505,7 @@
         <v>23.24</v>
       </c>
       <c r="Q338" s="3" t="n">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="R338" s="3" t="n">
         <v>25.5</v>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="P339" s="3" t="n"/>
       <c r="Q339" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="R339" s="3" t="n"/>
       <c r="S339" s="3">
@@ -23639,7 +23639,7 @@
         <v>12.44</v>
       </c>
       <c r="Q340" s="3" t="n">
-        <v>378.5</v>
+        <v>380.5</v>
       </c>
       <c r="R340" s="3" t="n">
         <v>12.3</v>
@@ -23708,7 +23708,7 @@
         <v>177.93</v>
       </c>
       <c r="Q341" s="3" t="n">
-        <v>49.8</v>
+        <v>48.5</v>
       </c>
       <c r="R341" s="3" t="n">
         <v>0.1</v>
@@ -23777,7 +23777,7 @@
         <v>19.84</v>
       </c>
       <c r="Q342" s="3" t="n">
-        <v>271.5</v>
+        <v>265</v>
       </c>
       <c r="R342" s="3" t="n">
         <v>10.15</v>
@@ -23846,7 +23846,7 @@
         <v>16.08</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>753</v>
+        <v>709</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>23</v>
@@ -23915,7 +23915,7 @@
         <v>17</v>
       </c>
       <c r="Q344" s="3" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R344" s="3" t="n">
         <v>12</v>
@@ -23984,7 +23984,7 @@
         <v>38.04</v>
       </c>
       <c r="Q345" s="3" t="n">
-        <v>190.5</v>
+        <v>181</v>
       </c>
       <c r="R345" s="3" t="n">
         <v>2.8</v>
@@ -24122,7 +24122,7 @@
         <v>38.27</v>
       </c>
       <c r="Q347" s="3" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="R347" s="3" t="n">
         <v>1.8</v>
@@ -24191,7 +24191,7 @@
         <v>10.05</v>
       </c>
       <c r="Q348" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R348" s="3" t="n">
         <v>3.5</v>
@@ -24329,7 +24329,7 @@
         <v>2787.5</v>
       </c>
       <c r="Q350" s="3" t="n">
-        <v>108.5</v>
+        <v>104.5</v>
       </c>
       <c r="R350" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q351" s="3" t="n">
-        <v>1280</v>
+        <v>1250</v>
       </c>
       <c r="R351" s="3" t="n">
         <v>11.66</v>
@@ -24467,7 +24467,7 @@
         <v>24.45</v>
       </c>
       <c r="Q352" s="3" t="n">
-        <v>63.5</v>
+        <v>62.6</v>
       </c>
       <c r="R352" s="3" t="n">
         <v>2.5</v>
@@ -24536,7 +24536,7 @@
         <v>26.68</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>1.93</v>
@@ -24605,7 +24605,7 @@
         <v>14.29</v>
       </c>
       <c r="Q354" s="3" t="n">
-        <v>82</v>
+        <v>82.3</v>
       </c>
       <c r="R354" s="3" t="n">
         <v>2.6</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="P355" s="3" t="n"/>
       <c r="Q355" s="3" t="n">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="R355" s="3" t="n">
         <v>6.45</v>
@@ -24741,7 +24741,7 @@
         <v>25.23</v>
       </c>
       <c r="Q356" s="3" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R356" s="3" t="n">
         <v>6.92</v>
@@ -24810,7 +24810,7 @@
         <v>46.75</v>
       </c>
       <c r="Q357" s="3" t="n">
-        <v>56.6</v>
+        <v>55.2</v>
       </c>
       <c r="R357" s="3" t="n">
         <v>0.68</v>
@@ -24879,7 +24879,7 @@
         <v>16.24</v>
       </c>
       <c r="Q358" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R358" s="3" t="n">
         <v>5.5</v>
@@ -24948,7 +24948,7 @@
         <v>74.42</v>
       </c>
       <c r="Q359" s="3" t="n">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="R359" s="3" t="n">
         <v>3</v>
@@ -25011,7 +25011,7 @@
         <v>16.75</v>
       </c>
       <c r="Q360" s="3" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="R360" s="3" t="n">
         <v>6</v>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="P361" s="3" t="n"/>
       <c r="Q361" s="3" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="R361" s="3" t="n"/>
       <c r="S361" s="3">
@@ -25214,7 +25214,7 @@
         <v>26.53</v>
       </c>
       <c r="Q363" s="3" t="n">
-        <v>283.5</v>
+        <v>273</v>
       </c>
       <c r="R363" s="3" t="n"/>
       <c r="S363" s="3">
@@ -25281,7 +25281,7 @@
         <v>24.33</v>
       </c>
       <c r="Q364" s="3" t="n">
-        <v>217</v>
+        <v>211.5</v>
       </c>
       <c r="R364" s="3" t="n">
         <v>2.73</v>
@@ -25338,7 +25338,7 @@
       <c r="O365" s="3" t="n"/>
       <c r="P365" s="3" t="n"/>
       <c r="Q365" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R365" s="3" t="n"/>
       <c r="S365" s="3">
@@ -25405,7 +25405,7 @@
         <v>21.7</v>
       </c>
       <c r="Q366" s="3" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="R366" s="3" t="n">
         <v>3</v>
@@ -25470,7 +25470,7 @@
         <v>85.06999999999999</v>
       </c>
       <c r="Q367" s="3" t="n">
-        <v>1395</v>
+        <v>1365</v>
       </c>
       <c r="R367" s="3" t="n">
         <v>7.5066</v>
@@ -25539,7 +25539,7 @@
         <v>19.07</v>
       </c>
       <c r="Q368" s="3" t="n">
-        <v>191.5</v>
+        <v>186.5</v>
       </c>
       <c r="R368" s="3" t="n">
         <v>5.565</v>
@@ -25598,7 +25598,7 @@
         <v>36.58</v>
       </c>
       <c r="Q369" s="3" t="n">
-        <v>43.2</v>
+        <v>42.75</v>
       </c>
       <c r="R369" s="3" t="n">
         <v>0.8</v>
@@ -25667,7 +25667,7 @@
         <v>20.21</v>
       </c>
       <c r="Q370" s="3" t="n">
-        <v>78.8</v>
+        <v>75.5</v>
       </c>
       <c r="R370" s="3" t="n">
         <v>1.8896</v>
@@ -25736,7 +25736,7 @@
         <v>26.83</v>
       </c>
       <c r="Q371" s="3" t="n">
-        <v>227</v>
+        <v>222.5</v>
       </c>
       <c r="R371" s="3" t="n">
         <v>4.3</v>
@@ -25805,7 +25805,7 @@
         <v>23.27</v>
       </c>
       <c r="Q372" s="3" t="n">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="R372" s="3" t="n">
         <v>6.19</v>
@@ -25874,7 +25874,7 @@
         <v>33.25</v>
       </c>
       <c r="Q373" s="3" t="n">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="R373" s="3" t="n">
         <v>6</v>
@@ -25943,7 +25943,7 @@
         <v>39.33</v>
       </c>
       <c r="Q374" s="3" t="n">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="R374" s="3" t="n">
         <v>36.7702</v>
@@ -26081,7 +26081,7 @@
         <v>16.4</v>
       </c>
       <c r="Q376" s="3" t="n">
-        <v>372.5</v>
+        <v>370</v>
       </c>
       <c r="R376" s="3" t="n">
         <v>13.78</v>
@@ -26140,7 +26140,7 @@
         <v>64.52</v>
       </c>
       <c r="Q377" s="3" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="R377" s="3" t="n">
         <v>2.55</v>
@@ -26209,7 +26209,7 @@
         <v>46.15</v>
       </c>
       <c r="Q378" s="3" t="n">
-        <v>1800</v>
+        <v>1670</v>
       </c>
       <c r="R378" s="3" t="n">
         <v>11.2587</v>
@@ -26276,7 +26276,7 @@
       </c>
       <c r="P379" s="3" t="n"/>
       <c r="Q379" s="3" t="n">
-        <v>23.65</v>
+        <v>23.2</v>
       </c>
       <c r="R379" s="3" t="n"/>
       <c r="S379" s="3">
@@ -26343,7 +26343,7 @@
         <v>73.45999999999999</v>
       </c>
       <c r="Q380" s="3" t="n">
-        <v>1320</v>
+        <v>1280</v>
       </c>
       <c r="R380" s="3" t="n">
         <v>1.49</v>
@@ -26412,7 +26412,7 @@
         <v>23.83</v>
       </c>
       <c r="Q381" s="3" t="n">
-        <v>226.5</v>
+        <v>217</v>
       </c>
       <c r="R381" s="3" t="n">
         <v>4.2</v>
@@ -26469,7 +26469,7 @@
       <c r="O382" s="3" t="n"/>
       <c r="P382" s="3" t="n"/>
       <c r="Q382" s="3" t="n">
-        <v>425</v>
+        <v>409.5</v>
       </c>
       <c r="R382" s="3" t="n">
         <v>0.2177</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="P383" s="3" t="n"/>
       <c r="Q383" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="R383" s="3" t="n"/>
       <c r="S383" s="3">
@@ -26603,7 +26603,7 @@
         <v>37.51</v>
       </c>
       <c r="Q384" s="3" t="n">
-        <v>405.5</v>
+        <v>399</v>
       </c>
       <c r="R384" s="3" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
         <v>49.03</v>
       </c>
       <c r="Q385" s="3" t="n">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="R385" s="3" t="n">
         <v>5.7</v>
@@ -26737,7 +26737,7 @@
         <v>15.51</v>
       </c>
       <c r="Q386" s="3" t="n">
-        <v>366.5</v>
+        <v>367.5</v>
       </c>
       <c r="R386" s="3" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
         <v>12.31</v>
       </c>
       <c r="Q387" s="3" t="n">
-        <v>86.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="R387" s="3" t="n">
         <v>1.2</v>
@@ -26875,7 +26875,7 @@
         <v>70.52</v>
       </c>
       <c r="Q388" s="3" t="n">
-        <v>3670</v>
+        <v>3480</v>
       </c>
       <c r="R388" s="3" t="n">
         <v>15.23</v>
@@ -26944,7 +26944,7 @@
         <v>110.51</v>
       </c>
       <c r="Q389" s="3" t="n">
-        <v>7195</v>
+        <v>6890</v>
       </c>
       <c r="R389" s="3" t="n">
         <v>24.72</v>
@@ -27003,7 +27003,7 @@
         <v>19.19</v>
       </c>
       <c r="Q390" s="3" t="n">
-        <v>129.5</v>
+        <v>124.5</v>
       </c>
       <c r="R390" s="3" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>33.83</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="R391" s="3" t="n">
         <v>7.5</v>
@@ -27141,7 +27141,7 @@
         <v>53.75</v>
       </c>
       <c r="Q392" s="3" t="n">
-        <v>1030</v>
+        <v>988</v>
       </c>
       <c r="R392" s="3" t="n">
         <v>6.99</v>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P393" s="3" t="n"/>
       <c r="Q393" s="3" t="n">
-        <v>78.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="R393" s="3" t="n"/>
       <c r="S393" s="3">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="P394" s="3" t="n"/>
       <c r="Q394" s="3" t="n">
-        <v>61.4</v>
+        <v>58.8</v>
       </c>
       <c r="R394" s="3" t="n"/>
       <c r="S394" s="3">
@@ -27340,7 +27340,7 @@
         <v>32.7</v>
       </c>
       <c r="Q395" s="3" t="n">
-        <v>70.8</v>
+        <v>70</v>
       </c>
       <c r="R395" s="3" t="n">
         <v>0.9</v>
@@ -27405,7 +27405,7 @@
         <v>21.5</v>
       </c>
       <c r="Q396" s="3" t="n">
-        <v>317.5</v>
+        <v>315</v>
       </c>
       <c r="R396" s="3" t="n">
         <v>7.6988</v>
@@ -27468,7 +27468,7 @@
         <v>20.22</v>
       </c>
       <c r="Q397" s="3" t="n">
-        <v>148.5</v>
+        <v>148</v>
       </c>
       <c r="R397" s="3" t="n">
         <v>3.75</v>
@@ -27537,7 +27537,7 @@
         <v>53.79</v>
       </c>
       <c r="Q398" s="3" t="n">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="R398" s="3" t="n"/>
       <c r="S398" s="3">
@@ -27604,7 +27604,7 @@
         <v>12.33</v>
       </c>
       <c r="Q399" s="3" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="R399" s="3" t="n">
         <v>3</v>
@@ -27663,7 +27663,7 @@
         <v>8.73</v>
       </c>
       <c r="Q400" s="3" t="n">
-        <v>135.5</v>
+        <v>137.5</v>
       </c>
       <c r="R400" s="3" t="n"/>
       <c r="S400" s="3">
@@ -27730,7 +27730,7 @@
         <v>16.06</v>
       </c>
       <c r="Q401" s="3" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="R401" s="3" t="n">
         <v>10</v>
@@ -27799,7 +27799,7 @@
         <v>64.78</v>
       </c>
       <c r="Q402" s="3" t="n">
-        <v>1210</v>
+        <v>1170</v>
       </c>
       <c r="R402" s="3" t="n">
         <v>12</v>
@@ -27868,7 +27868,7 @@
         <v>463.16</v>
       </c>
       <c r="Q403" s="3" t="n">
-        <v>423.5</v>
+        <v>406</v>
       </c>
       <c r="R403" s="3" t="n">
         <v>1.19</v>
@@ -27937,7 +27937,7 @@
         <v>20.96</v>
       </c>
       <c r="Q404" s="3" t="n">
-        <v>346.5</v>
+        <v>336</v>
       </c>
       <c r="R404" s="3" t="n">
         <v>10.14</v>
@@ -28002,7 +28002,7 @@
         <v>20.63</v>
       </c>
       <c r="Q405" s="3" t="n">
-        <v>2345</v>
+        <v>2310</v>
       </c>
       <c r="R405" s="3" t="n">
         <v>144.39</v>
@@ -28061,7 +28061,7 @@
         <v>10.85</v>
       </c>
       <c r="Q406" s="3" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R406" s="3" t="n">
         <v>16</v>
@@ -28130,7 +28130,7 @@
         <v>40.41</v>
       </c>
       <c r="Q407" s="3" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R407" s="3" t="n">
         <v>3.35</v>
@@ -28268,7 +28268,7 @@
         <v>21.78</v>
       </c>
       <c r="Q409" s="3" t="n">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="R409" s="3" t="n">
         <v>21</v>
@@ -28337,7 +28337,7 @@
         <v>31.61</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>156.5</v>
+        <v>154</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>3.5</v>
@@ -28406,7 +28406,7 @@
         <v>294.74</v>
       </c>
       <c r="Q411" s="3" t="n">
-        <v>336.5</v>
+        <v>321.5</v>
       </c>
       <c r="R411" s="3" t="n">
         <v>1.9431</v>
@@ -28475,7 +28475,7 @@
         <v>21.79</v>
       </c>
       <c r="Q412" s="3" t="n">
-        <v>184.5</v>
+        <v>180</v>
       </c>
       <c r="R412" s="3" t="n">
         <v>4.6</v>
@@ -28544,7 +28544,7 @@
         <v>42.78</v>
       </c>
       <c r="Q413" s="3" t="n">
-        <v>1320</v>
+        <v>1270</v>
       </c>
       <c r="R413" s="3" t="n">
         <v>13</v>
@@ -28613,7 +28613,7 @@
         <v>13.5</v>
       </c>
       <c r="Q414" s="3" t="n">
-        <v>135.5</v>
+        <v>134</v>
       </c>
       <c r="R414" s="3" t="n">
         <v>1.25</v>
@@ -28743,7 +28743,7 @@
         <v>13.07</v>
       </c>
       <c r="Q416" s="3" t="n">
-        <v>62.4</v>
+        <v>61.5</v>
       </c>
       <c r="R416" s="3" t="n">
         <v>5.16</v>
@@ -28812,7 +28812,7 @@
         <v>26.13</v>
       </c>
       <c r="Q417" s="3" t="n">
-        <v>73.5</v>
+        <v>70.7</v>
       </c>
       <c r="R417" s="3" t="n">
         <v>0.23</v>
@@ -28871,7 +28871,7 @@
         <v>28.62</v>
       </c>
       <c r="Q418" s="3" t="n">
-        <v>1030</v>
+        <v>1005</v>
       </c>
       <c r="R418" s="3" t="n">
         <v>19.1</v>
@@ -28940,7 +28940,7 @@
         <v>84.45</v>
       </c>
       <c r="Q419" s="3" t="n">
-        <v>469.5</v>
+        <v>446</v>
       </c>
       <c r="R419" s="3" t="n">
         <v>3</v>
@@ -29009,7 +29009,7 @@
         <v>14.56</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>15.78</v>
@@ -29078,7 +29078,7 @@
         <v>38.61</v>
       </c>
       <c r="Q421" s="3" t="n">
-        <v>2190</v>
+        <v>2150</v>
       </c>
       <c r="R421" s="3" t="n">
         <v>10.5</v>
@@ -29137,7 +29137,7 @@
         <v>1</v>
       </c>
       <c r="Q422" s="3" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="R422" s="3" t="n">
         <v>1</v>
@@ -29206,7 +29206,7 @@
         <v>115.9</v>
       </c>
       <c r="Q423" s="3" t="n">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="R423" s="3" t="n">
         <v>3</v>
@@ -29265,7 +29265,7 @@
         <v>16.67</v>
       </c>
       <c r="Q424" s="3" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="R424" s="3" t="n">
         <v>6.97</v>
@@ -29320,7 +29320,7 @@
       </c>
       <c r="P425" s="3" t="n"/>
       <c r="Q425" s="3" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="R425" s="3" t="n"/>
       <c r="S425" s="3">
@@ -29387,7 +29387,7 @@
         <v>14.41</v>
       </c>
       <c r="Q426" s="3" t="n">
-        <v>300.5</v>
+        <v>296.5</v>
       </c>
       <c r="R426" s="3" t="n">
         <v>8.5</v>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="P427" s="3" t="n"/>
       <c r="Q427" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="R427" s="3" t="n"/>
       <c r="S427" s="3">
@@ -29511,7 +29511,7 @@
         <v>57.36</v>
       </c>
       <c r="Q428" s="3" t="n">
-        <v>296</v>
+        <v>288.5</v>
       </c>
       <c r="R428" s="3" t="n">
         <v>1.4</v>
@@ -29580,7 +29580,7 @@
         <v>17.59</v>
       </c>
       <c r="Q429" s="3" t="n">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="R429" s="3" t="n">
         <v>17</v>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="P430" s="3" t="n"/>
       <c r="Q430" s="3" t="n">
-        <v>58.8</v>
+        <v>53</v>
       </c>
       <c r="R430" s="3" t="n"/>
       <c r="S430" s="3">
@@ -29702,7 +29702,7 @@
         <v>20.63</v>
       </c>
       <c r="Q431" s="3" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="R431" s="3" t="n">
         <v>1</v>
@@ -29771,7 +29771,7 @@
         <v>48.36</v>
       </c>
       <c r="Q432" s="3" t="n">
-        <v>2035</v>
+        <v>1975</v>
       </c>
       <c r="R432" s="3" t="n">
         <v>0.5</v>
@@ -29840,7 +29840,7 @@
         <v>19.38</v>
       </c>
       <c r="Q433" s="3" t="n">
-        <v>590</v>
+        <v>531</v>
       </c>
       <c r="R433" s="3" t="n">
         <v>8.9871</v>
@@ -29909,7 +29909,7 @@
         <v>34.98</v>
       </c>
       <c r="Q434" s="3" t="n">
-        <v>267.5</v>
+        <v>261.5</v>
       </c>
       <c r="R434" s="3" t="n">
         <v>1.5</v>
@@ -29978,7 +29978,7 @@
         <v>65.13</v>
       </c>
       <c r="Q435" s="3" t="n">
-        <v>2810</v>
+        <v>2580</v>
       </c>
       <c r="R435" s="3" t="n">
         <v>19.85</v>
@@ -30047,7 +30047,7 @@
         <v>21.64</v>
       </c>
       <c r="Q436" s="3" t="n">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="R436" s="3" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
         <v>30.21</v>
       </c>
       <c r="Q437" s="3" t="n">
-        <v>355.5</v>
+        <v>349.5</v>
       </c>
       <c r="R437" s="3" t="n">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>40.48</v>
       </c>
       <c r="Q438" s="3" t="n">
-        <v>2215</v>
+        <v>1995</v>
       </c>
       <c r="R438" s="3" t="n">
         <v>16</v>
@@ -30244,7 +30244,7 @@
         <v>56.01</v>
       </c>
       <c r="Q439" s="3" t="n">
-        <v>1500</v>
+        <v>1425</v>
       </c>
       <c r="R439" s="3" t="n">
         <v>10</v>
@@ -30313,7 +30313,7 @@
         <v>66.52</v>
       </c>
       <c r="Q440" s="3" t="n">
-        <v>271.5</v>
+        <v>263</v>
       </c>
       <c r="R440" s="3" t="n">
         <v>2.46</v>
@@ -30382,7 +30382,7 @@
         <v>68.04000000000001</v>
       </c>
       <c r="Q441" s="3" t="n">
-        <v>6475</v>
+        <v>6310</v>
       </c>
       <c r="R441" s="3" t="n">
         <v>54.99</v>
@@ -30445,7 +30445,7 @@
         <v>31.03</v>
       </c>
       <c r="Q442" s="3" t="n">
-        <v>16.55</v>
+        <v>16.4</v>
       </c>
       <c r="R442" s="3" t="n">
         <v>0.8934</v>
@@ -30514,7 +30514,7 @@
         <v>11.44</v>
       </c>
       <c r="Q443" s="3" t="n">
-        <v>114.5</v>
+        <v>115</v>
       </c>
       <c r="R443" s="3" t="n">
         <v>5.6</v>
@@ -30577,7 +30577,7 @@
         <v>29.91</v>
       </c>
       <c r="Q444" s="3" t="n">
-        <v>308</v>
+        <v>286.5</v>
       </c>
       <c r="R444" s="3" t="n">
         <v>2</v>
@@ -30646,7 +30646,7 @@
         <v>251.33</v>
       </c>
       <c r="Q445" s="3" t="n">
-        <v>534</v>
+        <v>507</v>
       </c>
       <c r="R445" s="3" t="n">
         <v>2.15</v>
@@ -30713,7 +30713,7 @@
       </c>
       <c r="P446" s="3" t="n"/>
       <c r="Q446" s="3" t="n">
-        <v>425</v>
+        <v>414.5</v>
       </c>
       <c r="R446" s="3" t="n"/>
       <c r="S446" s="3">
@@ -30780,7 +30780,7 @@
         <v>14.24</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>38</v>
@@ -30849,7 +30849,7 @@
         <v>51.64</v>
       </c>
       <c r="Q448" s="3" t="n">
-        <v>866</v>
+        <v>834</v>
       </c>
       <c r="R448" s="3" t="n">
         <v>6.39</v>
@@ -30898,7 +30898,7 @@
       <c r="O449" s="3" t="n"/>
       <c r="P449" s="3" t="n"/>
       <c r="Q449" s="3" t="n">
-        <v>153</v>
+        <v>152.5</v>
       </c>
       <c r="R449" s="3" t="n"/>
       <c r="S449" s="3">
@@ -30965,7 +30965,7 @@
         <v>174.44</v>
       </c>
       <c r="Q450" s="3" t="n">
-        <v>2055</v>
+        <v>1975</v>
       </c>
       <c r="R450" s="3" t="n">
         <v>4.53</v>
@@ -31034,7 +31034,7 @@
         <v>14.77</v>
       </c>
       <c r="Q451" s="3" t="n">
-        <v>279</v>
+        <v>277.5</v>
       </c>
       <c r="R451" s="3" t="n">
         <v>11.5</v>
@@ -31103,7 +31103,7 @@
         <v>78.33</v>
       </c>
       <c r="Q452" s="3" t="n">
-        <v>438</v>
+        <v>418.5</v>
       </c>
       <c r="R452" s="3" t="n">
         <v>1.97</v>
@@ -31172,7 +31172,7 @@
         <v>558.33</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>174</v>
+        <v>167.5</v>
       </c>
       <c r="R453" s="3" t="n"/>
       <c r="S453" s="3">
@@ -31239,7 +31239,7 @@
         <v>43.46</v>
       </c>
       <c r="Q454" s="3" t="n">
-        <v>229.5</v>
+        <v>225.5</v>
       </c>
       <c r="R454" s="3" t="n">
         <v>2.7</v>
@@ -31308,7 +31308,7 @@
         <v>385.42</v>
       </c>
       <c r="Q455" s="3" t="n">
-        <v>171.5</v>
+        <v>172.5</v>
       </c>
       <c r="R455" s="3" t="n"/>
       <c r="S455" s="3">
@@ -31375,7 +31375,7 @@
         <v>89.52</v>
       </c>
       <c r="Q456" s="3" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="R456" s="3" t="n">
         <v>1.99</v>
@@ -31444,7 +31444,7 @@
         <v>153.35</v>
       </c>
       <c r="Q457" s="3" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="R457" s="3" t="n">
         <v>2</v>
@@ -31513,7 +31513,7 @@
         <v>42.18</v>
       </c>
       <c r="Q458" s="3" t="n">
-        <v>126.5</v>
+        <v>115</v>
       </c>
       <c r="R458" s="3" t="n">
         <v>0.98</v>
@@ -31582,7 +31582,7 @@
         <v>16.1</v>
       </c>
       <c r="Q459" s="3" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R459" s="3" t="n">
         <v>5.89</v>
@@ -31651,7 +31651,7 @@
         <v>28.99</v>
       </c>
       <c r="Q460" s="3" t="n">
-        <v>49.45</v>
+        <v>49</v>
       </c>
       <c r="R460" s="3" t="n">
         <v>0.68</v>
@@ -31720,7 +31720,7 @@
         <v>13.97</v>
       </c>
       <c r="Q461" s="3" t="n">
-        <v>247.5</v>
+        <v>247</v>
       </c>
       <c r="R461" s="3" t="n">
         <v>16</v>
@@ -31789,7 +31789,7 @@
         <v>21.27</v>
       </c>
       <c r="Q462" s="3" t="n">
-        <v>109.5</v>
+        <v>106</v>
       </c>
       <c r="R462" s="3" t="n">
         <v>1.68</v>
@@ -31858,7 +31858,7 @@
         <v>24.06</v>
       </c>
       <c r="Q463" s="3" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R463" s="3" t="n">
         <v>4.22</v>
@@ -31927,7 +31927,7 @@
         <v>32.18</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>91.8</v>
+        <v>90.7</v>
       </c>
       <c r="R464" s="3" t="n"/>
       <c r="S464" s="3">
@@ -31994,7 +31994,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="Q465" s="3" t="n">
-        <v>42.75</v>
+        <v>42.15</v>
       </c>
       <c r="R465" s="3" t="n">
         <v>1.49</v>
@@ -32063,7 +32063,7 @@
         <v>7.22</v>
       </c>
       <c r="Q466" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R466" s="3" t="n">
         <v>3.8</v>
@@ -32132,7 +32132,7 @@
         <v>13.93</v>
       </c>
       <c r="Q467" s="3" t="n">
-        <v>178.5</v>
+        <v>177.5</v>
       </c>
       <c r="R467" s="3" t="n">
         <v>11.47</v>
@@ -32201,7 +32201,7 @@
         <v>18.09</v>
       </c>
       <c r="Q468" s="3" t="n">
-        <v>62</v>
+        <v>60.3</v>
       </c>
       <c r="R468" s="3" t="n">
         <v>1</v>
@@ -32270,7 +32270,7 @@
         <v>27.01</v>
       </c>
       <c r="Q469" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="R469" s="3" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>27.63</v>
       </c>
       <c r="Q470" s="3" t="n">
-        <v>339</v>
+        <v>325.5</v>
       </c>
       <c r="R470" s="3" t="n">
         <v>3.89</v>
@@ -32408,7 +32408,7 @@
         <v>25.27</v>
       </c>
       <c r="Q471" s="3" t="n">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="R471" s="3" t="n">
         <v>14</v>
@@ -32477,7 +32477,7 @@
         <v>22.07</v>
       </c>
       <c r="Q472" s="3" t="n">
-        <v>137</v>
+        <v>133.5</v>
       </c>
       <c r="R472" s="3" t="n">
         <v>3.5</v>
@@ -32546,7 +32546,7 @@
         <v>26.61</v>
       </c>
       <c r="Q473" s="3" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="R473" s="3" t="n"/>
       <c r="S473" s="3">
@@ -32613,7 +32613,7 @@
         <v>5.78</v>
       </c>
       <c r="Q474" s="3" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="R474" s="3" t="n">
         <v>4.448</v>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="P475" s="3" t="n"/>
       <c r="Q475" s="3" t="n">
-        <v>2065</v>
+        <v>1990</v>
       </c>
       <c r="R475" s="3" t="n">
         <v>16.96</v>
@@ -32749,7 +32749,7 @@
         <v>63.86</v>
       </c>
       <c r="Q476" s="3" t="n">
-        <v>521</v>
+        <v>485</v>
       </c>
       <c r="R476" s="3" t="n">
         <v>2</v>
@@ -32818,7 +32818,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q477" s="3" t="n">
-        <v>36.35</v>
+        <v>35.55</v>
       </c>
       <c r="R477" s="3" t="n">
         <v>1.5</v>
@@ -32887,7 +32887,7 @@
         <v>27.97</v>
       </c>
       <c r="Q478" s="3" t="n">
-        <v>26.3</v>
+        <v>26.05</v>
       </c>
       <c r="R478" s="3" t="n">
         <v>1.198</v>
@@ -32956,7 +32956,7 @@
         <v>25.26</v>
       </c>
       <c r="Q479" s="3" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="R479" s="3" t="n">
         <v>10</v>
@@ -33025,7 +33025,7 @@
         <v>16.47</v>
       </c>
       <c r="Q480" s="3" t="n">
-        <v>368.5</v>
+        <v>371</v>
       </c>
       <c r="R480" s="3" t="n">
         <v>16</v>
@@ -33094,7 +33094,7 @@
         <v>9.94</v>
       </c>
       <c r="Q481" s="3" t="n">
-        <v>141</v>
+        <v>141.5</v>
       </c>
       <c r="R481" s="3" t="n">
         <v>6.5</v>
@@ -33163,7 +33163,7 @@
         <v>15.74</v>
       </c>
       <c r="Q482" s="3" t="n">
-        <v>58.7</v>
+        <v>58</v>
       </c>
       <c r="R482" s="3" t="n">
         <v>2.12</v>
@@ -33232,7 +33232,7 @@
         <v>51.18</v>
       </c>
       <c r="Q483" s="3" t="n">
-        <v>92.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R483" s="3" t="n">
         <v>0.72</v>
@@ -33301,7 +33301,7 @@
         <v>86.2</v>
       </c>
       <c r="Q484" s="3" t="n">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="R484" s="3" t="n">
         <v>4.56</v>
@@ -33370,7 +33370,7 @@
         <v>14.1</v>
       </c>
       <c r="Q485" s="3" t="n">
-        <v>66</v>
+        <v>64.7</v>
       </c>
       <c r="R485" s="3" t="n">
         <v>2</v>
@@ -33439,7 +33439,7 @@
         <v>5.35</v>
       </c>
       <c r="Q486" s="3" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="R486" s="3" t="n">
         <v>1.3</v>
@@ -33508,7 +33508,7 @@
         <v>16.11</v>
       </c>
       <c r="Q487" s="3" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="R487" s="3" t="n">
         <v>1.18</v>
@@ -33577,7 +33577,7 @@
         <v>13.9</v>
       </c>
       <c r="Q488" s="3" t="n">
-        <v>29.05</v>
+        <v>28.95</v>
       </c>
       <c r="R488" s="3" t="n">
         <v>1.2</v>
@@ -33646,7 +33646,7 @@
         <v>14.11</v>
       </c>
       <c r="Q489" s="3" t="n">
-        <v>68.5</v>
+        <v>67.8</v>
       </c>
       <c r="R489" s="3" t="n">
         <v>4.1</v>
@@ -33784,7 +33784,7 @@
         <v>24.49</v>
       </c>
       <c r="Q491" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="R491" s="3" t="n">
         <v>2.8</v>
@@ -33922,7 +33922,7 @@
         <v>68.39</v>
       </c>
       <c r="Q493" s="3" t="n">
-        <v>97.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="R493" s="3" t="n">
         <v>1.819</v>
@@ -33991,7 +33991,7 @@
         <v>13.15</v>
       </c>
       <c r="Q494" s="3" t="n">
-        <v>39.7</v>
+        <v>39.55</v>
       </c>
       <c r="R494" s="3" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         <v>14.5</v>
       </c>
       <c r="Q495" s="3" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="R495" s="3" t="n">
         <v>4</v>
@@ -34129,7 +34129,7 @@
         <v>7.78</v>
       </c>
       <c r="Q496" s="3" t="n">
-        <v>40.35</v>
+        <v>41.7</v>
       </c>
       <c r="R496" s="3" t="n"/>
       <c r="S496" s="3">
@@ -34196,7 +34196,7 @@
         <v>21.44</v>
       </c>
       <c r="Q497" s="3" t="n">
-        <v>55.6</v>
+        <v>55</v>
       </c>
       <c r="R497" s="3" t="n">
         <v>2.2</v>
@@ -34265,7 +34265,7 @@
         <v>12.18</v>
       </c>
       <c r="Q498" s="3" t="n">
-        <v>128</v>
+        <v>129.5</v>
       </c>
       <c r="R498" s="3" t="n">
         <v>6.2</v>
@@ -34403,7 +34403,7 @@
         <v>5.21</v>
       </c>
       <c r="Q500" s="3" t="n">
-        <v>27.75</v>
+        <v>28.1</v>
       </c>
       <c r="R500" s="3" t="n">
         <v>1.1</v>
@@ -34472,7 +34472,7 @@
         <v>14.49</v>
       </c>
       <c r="Q501" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="R501" s="3" t="n">
         <v>4.5</v>
